--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -835,24 +835,24 @@
         <v>1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -861,24 +861,24 @@
         <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -887,17 +887,17 @@
         <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
@@ -913,17 +913,17 @@
         <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -939,24 +939,24 @@
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -965,24 +965,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -994,14 +994,14 @@
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>46.7</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
@@ -1017,284 +1017,284 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>Sliding Window</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
           <t>String, Simulation</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="5" t="n">
+      <c r="C18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H18" s="7" t="n">
         <v>47.2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr"/>
-      <c r="C18" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" s="9" t="n">
+      <c r="B19" s="8" t="inlineStr"/>
+      <c r="C19" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="E19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5" t="n">
+      <c r="C20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr"/>
-      <c r="C20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5" t="n">
+      <c r="C22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H22" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr"/>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="n">
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="G24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="9" t="n">
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9" t="n">
+      <c r="D25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="9" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>0</v>
@@ -1303,17 +1303,17 @@
         <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
@@ -1332,234 +1332,260 @@
         <v>2</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H30" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="9" t="n">
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9" t="n">
+      <c r="D31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5" t="n">
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr"/>
-      <c r="C34" s="9" t="n">
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="9" t="n">
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="C36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H36" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr"/>
-      <c r="C37" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="D37" s="11" t="n">
+      <c r="B38" s="10" t="inlineStr"/>
+      <c r="C38" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="G37" s="11" t="inlineStr"/>
-      <c r="H37" s="11" t="inlineStr"/>
+      <c r="E38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G38" s="11" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1575,7 +1601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3186,11 +3212,61 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Contains Duplicate II</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Hash Table, Sliding Window</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>46258.98878472222</v>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F34">
+  <conditionalFormatting sqref="F5:F35">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3232,6 +3308,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3243,7 +3320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3286,7 +3363,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   15 solved   (Low: 10 · Medium: 5 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   16 solved   (Low: 11 · Medium: 5 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -3646,7 +3723,7 @@
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B20" s="18" t="n"/>
@@ -3677,11 +3754,11 @@
       <c r="A22" s="5" t="inlineStr"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1353</v>
+        <v>219</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
@@ -3689,10 +3766,10 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
@@ -3700,7 +3777,7 @@
         </is>
       </c>
       <c r="H22" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -3711,7 +3788,7 @@
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B23" s="18" t="n"/>
@@ -3724,40 +3801,40 @@
       <c r="I23" s="18" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n"/>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="n"/>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="19" t="n"/>
-      <c r="F24" s="19" t="n"/>
-      <c r="G24" s="19" t="n"/>
-      <c r="H24" s="19" t="n"/>
-      <c r="I24" s="19" t="n"/>
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="21" t="n"/>
+      <c r="H24" s="21" t="n"/>
+      <c r="I24" s="21" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -3765,7 +3842,7 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -3776,7 +3853,7 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B26" s="18" t="n"/>
@@ -3789,40 +3866,40 @@
       <c r="I26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n"/>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="21" t="n"/>
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -3830,7 +3907,7 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -3841,7 +3918,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B29" s="18" t="n"/>
@@ -3872,11 +3949,11 @@
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
@@ -3884,10 +3961,10 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -3895,7 +3972,7 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -3906,7 +3983,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -3937,11 +4014,11 @@
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
@@ -3949,10 +4026,10 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -3960,7 +4037,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -3971,7 +4048,7 @@
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B35" s="18" t="n"/>
@@ -3984,40 +4061,40 @@
       <c r="I35" s="18" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n"/>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="19" t="n"/>
+      <c r="A36" s="21" t="n"/>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -4025,7 +4102,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4036,7 +4113,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
@@ -4049,40 +4126,40 @@
       <c r="I38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>3347</v>
+        <v>3373</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>46.7</v>
+        <v>117.3</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -4090,7 +4167,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -4101,7 +4178,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -4132,11 +4209,11 @@
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
@@ -4144,10 +4221,10 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4155,7 +4232,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -4166,7 +4243,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4197,201 +4274,201 @@
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
+          <t>Maximum Average Subarray I</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>643</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>46256.65385416667</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="n"/>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="18" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="21" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr"/>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C49" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E49" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F49" s="5" t="n">
         <v>47.2</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>46247.02123842593</v>
       </c>
-      <c r="I46" s="13" t="inlineStr">
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B48" s="18" t="n"/>
-      <c r="C48" s="18" t="n"/>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-      <c r="G48" s="18" t="n"/>
-      <c r="H48" s="18" t="n"/>
-      <c r="I48" s="18" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="n"/>
-      <c r="B49" s="22" t="inlineStr">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="n"/>
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n"/>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="21" t="n"/>
-      <c r="F49" s="21" t="n"/>
-      <c r="G49" s="21" t="n"/>
-      <c r="H49" s="21" t="n"/>
-      <c r="I49" s="21" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr"/>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="21" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C53" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="5" t="n">
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I50" s="13" t="inlineStr">
+      <c r="I53" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="n"/>
-      <c r="G51" s="2" t="n"/>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="n"/>
-      <c r="C52" s="18" t="n"/>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
-      <c r="G52" s="18" t="n"/>
-      <c r="H52" s="18" t="n"/>
-      <c r="I52" s="18" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="21" t="n"/>
-      <c r="B53" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C53" s="21" t="n"/>
-      <c r="D53" s="21" t="n"/>
-      <c r="E53" s="21" t="n"/>
-      <c r="F53" s="21" t="n"/>
-      <c r="G53" s="21" t="n"/>
-      <c r="H53" s="21" t="n"/>
-      <c r="I53" s="21" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr"/>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B55" s="18" t="n"/>
@@ -4422,11 +4499,11 @@
       <c r="A57" s="5" t="inlineStr"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C57" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
@@ -4434,18 +4511,18 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H57" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -4456,7 +4533,7 @@
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B58" s="18" t="n"/>
@@ -4487,171 +4564,171 @@
       <c r="A60" s="5" t="inlineStr"/>
       <c r="B60" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="n"/>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="21" t="n"/>
+      <c r="E62" s="21" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="21" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C63" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" s="5" t="n">
+      <c r="E63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I60" s="13" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="19" t="n"/>
-      <c r="B61" s="20" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr"/>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="19" t="n"/>
+      <c r="I64" s="19" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C65" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="5" t="n">
+      <c r="E65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H62" s="12" t="n">
+      <c r="H65" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I62" s="13" t="inlineStr">
+      <c r="I65" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="18" t="n"/>
-      <c r="I64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
-      <c r="G65" s="21" t="n"/>
-      <c r="H65" s="21" t="n"/>
-      <c r="I65" s="21" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr"/>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B67" s="18" t="n"/>
@@ -4664,40 +4741,40 @@
       <c r="I67" s="18" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="19" t="n"/>
-      <c r="B68" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C68" s="19" t="n"/>
-      <c r="D68" s="19" t="n"/>
-      <c r="E68" s="19" t="n"/>
-      <c r="F68" s="19" t="n"/>
-      <c r="G68" s="19" t="n"/>
-      <c r="H68" s="19" t="n"/>
-      <c r="I68" s="19" t="n"/>
+      <c r="A68" s="21" t="n"/>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="21" t="n"/>
+      <c r="E68" s="21" t="n"/>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="21" t="n"/>
+      <c r="H68" s="21" t="n"/>
+      <c r="I68" s="21" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr"/>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
@@ -4705,7 +4782,7 @@
         </is>
       </c>
       <c r="H69" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -4716,7 +4793,7 @@
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B70" s="18" t="n"/>
@@ -4729,40 +4806,40 @@
       <c r="I70" s="18" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="21" t="n"/>
-      <c r="B71" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C71" s="21" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="n"/>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
+      <c r="A71" s="19" t="n"/>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C71" s="19" t="n"/>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="19" t="n"/>
+      <c r="G71" s="19" t="n"/>
+      <c r="H71" s="19" t="n"/>
+      <c r="I71" s="19" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr"/>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
@@ -4770,7 +4847,7 @@
         </is>
       </c>
       <c r="H72" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -4781,7 +4858,7 @@
     <row r="73">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B73" s="18" t="n"/>
@@ -4812,11 +4889,11 @@
       <c r="A75" s="5" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
@@ -4827,15 +4904,15 @@
         <v>2</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H75" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -4846,7 +4923,7 @@
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B76" s="18" t="n"/>
@@ -4877,121 +4954,121 @@
       <c r="A78" s="5" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="n"/>
+      <c r="C79" s="18" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
+      <c r="G79" s="18" t="n"/>
+      <c r="H79" s="18" t="n"/>
+      <c r="I79" s="18" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="n"/>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C80" s="21" t="n"/>
+      <c r="D80" s="21" t="n"/>
+      <c r="E80" s="21" t="n"/>
+      <c r="F80" s="21" t="n"/>
+      <c r="G80" s="21" t="n"/>
+      <c r="H80" s="21" t="n"/>
+      <c r="I80" s="21" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr"/>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C81" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E81" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F81" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I78" s="13" t="inlineStr">
+      <c r="I81" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B80" s="18" t="n"/>
-      <c r="C80" s="18" t="n"/>
-      <c r="D80" s="18" t="n"/>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
-      <c r="G80" s="18" t="n"/>
-      <c r="H80" s="18" t="n"/>
-      <c r="I80" s="18" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="21" t="n"/>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C81" s="21" t="n"/>
-      <c r="D81" s="21" t="n"/>
-      <c r="E81" s="21" t="n"/>
-      <c r="F81" s="21" t="n"/>
-      <c r="G81" s="21" t="n"/>
-      <c r="H81" s="21" t="n"/>
-      <c r="I81" s="21" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr"/>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B83" s="18" t="n"/>
@@ -5007,7 +5084,7 @@
       <c r="A84" s="21" t="n"/>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C84" s="21" t="n"/>
@@ -5022,230 +5099,301 @@
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="n"/>
+      <c r="C86" s="18" t="n"/>
+      <c r="D86" s="18" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="18" t="n"/>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="18" t="n"/>
+      <c r="I86" s="18" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="n"/>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="n"/>
+      <c r="D87" s="21" t="n"/>
+      <c r="E87" s="21" t="n"/>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="21" t="n"/>
+      <c r="I87" s="21" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr"/>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C88" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E88" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F88" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H85" s="12" t="n">
+      <c r="H88" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="I88" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="7" t="inlineStr"/>
-      <c r="B86" s="6" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C86" s="7" t="n">
+      <c r="C89" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E86" s="7" t="n">
+      <c r="E89" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F86" s="7" t="n">
+      <c r="F89" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G86" s="7" t="inlineStr">
+      <c r="G89" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H86" s="14" t="n">
+      <c r="H89" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I86" s="15" t="inlineStr">
+      <c r="I89" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="17" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B87" s="18" t="n"/>
-      <c r="C87" s="18" t="n"/>
-      <c r="D87" s="18" t="n"/>
-      <c r="E87" s="18" t="n"/>
-      <c r="F87" s="18" t="n"/>
-      <c r="G87" s="18" t="n"/>
-      <c r="H87" s="18" t="n"/>
-      <c r="I87" s="18" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="21" t="n"/>
-      <c r="B88" s="22" t="inlineStr">
+      <c r="B90" s="18" t="n"/>
+      <c r="C90" s="18" t="n"/>
+      <c r="D90" s="18" t="n"/>
+      <c r="E90" s="18" t="n"/>
+      <c r="F90" s="18" t="n"/>
+      <c r="G90" s="18" t="n"/>
+      <c r="H90" s="18" t="n"/>
+      <c r="I90" s="18" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="n"/>
+      <c r="B91" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C88" s="21" t="n"/>
-      <c r="D88" s="21" t="n"/>
-      <c r="E88" s="21" t="n"/>
-      <c r="F88" s="21" t="n"/>
-      <c r="G88" s="21" t="n"/>
-      <c r="H88" s="21" t="n"/>
-      <c r="I88" s="21" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="C91" s="21" t="n"/>
+      <c r="D91" s="21" t="n"/>
+      <c r="E91" s="21" t="n"/>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="21" t="n"/>
+      <c r="I91" s="21" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr"/>
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C92" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="n">
+      <c r="E92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H89" s="12" t="n">
+      <c r="H92" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I89" s="13" t="inlineStr">
+      <c r="I92" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="16" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n"/>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
-      <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="17" t="inlineStr">
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="n"/>
+      <c r="I93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B91" s="18" t="n"/>
-      <c r="C91" s="18" t="n"/>
-      <c r="D91" s="18" t="n"/>
-      <c r="E91" s="18" t="n"/>
-      <c r="F91" s="18" t="n"/>
-      <c r="G91" s="18" t="n"/>
-      <c r="H91" s="18" t="n"/>
-      <c r="I91" s="18" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="21" t="n"/>
-      <c r="B92" s="22" t="inlineStr">
+      <c r="B94" s="18" t="n"/>
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+      <c r="G94" s="18" t="n"/>
+      <c r="H94" s="18" t="n"/>
+      <c r="I94" s="18" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="n"/>
+      <c r="B95" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="n"/>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr"/>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="C95" s="21" t="n"/>
+      <c r="D95" s="21" t="n"/>
+      <c r="E95" s="21" t="n"/>
+      <c r="F95" s="21" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr"/>
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C96" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E96" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F96" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H93" s="12" t="n">
+      <c r="H96" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I96" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="61">
+  <mergeCells count="63">
     <mergeCell ref="A41:I41"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="A54:I54"/>
     <mergeCell ref="A90:I90"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="B91:I91"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="B59:I59"/>
     <mergeCell ref="A55:I55"/>
     <mergeCell ref="B27:I27"/>
+    <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A86:I86"/>
     <mergeCell ref="B56:I56"/>
+    <mergeCell ref="B52:I52"/>
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B48:I48"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
@@ -5258,43 +5406,39 @@
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="A91:I91"/>
-    <mergeCell ref="B61:I61"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="B88:I88"/>
-    <mergeCell ref="B53:I53"/>
-    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="B87:I87"/>
+    <mergeCell ref="A93:I93"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="B49:I49"/>
-    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="A64:I64"/>
     <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B92:I92"/>
+    <mergeCell ref="A82:I82"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="B68:I68"/>
     <mergeCell ref="A51:I51"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="B33:I33"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="A94:I94"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="B80:I80"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A87:I87"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
@@ -5313,21 +5457,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5339,7 +5484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5855,24 +6000,63 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="392" customHeight="1">
+    <row r="16" ht="238" customHeight="1">
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
+          <t>Contains Duplicate II</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>219</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public boolean containsNearbyDuplicate(int[] nums, int k) {
+    int left = 0;
+    HashSet&lt;Integer&gt; hs = new HashSet&lt;&gt;();
+    for(int right = 0;right&lt;nums.length;right++){
+       if(right - left &gt; k){
+        hs.remove(nums[left]);
+        left++;
+       } 
+       if(hs.contains(nums[right])){
+        return true;
+       }
+       hs.add(nums[right]);
+    }
+    return false; 
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="392" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -5905,24 +6089,24 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="420" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="420" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
@@ -5950,24 +6134,24 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="546" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="546" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -6011,24 +6195,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="196" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="196" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -6047,24 +6231,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="406" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="406" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -6097,24 +6281,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="378" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="378" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -6146,24 +6330,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="560" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="560" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -6199,24 +6383,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="294" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="294" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -6242,24 +6426,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="378" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="378" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -6291,24 +6475,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="238" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="238" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -6330,24 +6514,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="308" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="308" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -6374,24 +6558,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="280" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="280" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -6414,24 +6598,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="448" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="448" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -6466,24 +6650,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="378" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="378" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -6515,24 +6699,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="490" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="490" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -6560,24 +6744,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="308" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="308" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -6603,24 +6787,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="238" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="238" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -6640,24 +6824,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="560" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="560" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -6698,24 +6882,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="294" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="294" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -203,13 +203,13 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1076,251 +1076,247 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr"/>
-      <c r="C19" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="D19" s="9" t="n">
+      <c r="B20" s="8" t="inlineStr"/>
+      <c r="C20" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="E20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n">
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr"/>
+      <c r="C22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7" t="n">
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H23" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7" t="n">
+      <c r="G25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="9" t="n">
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9" t="n">
+      <c r="D26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="7" t="n">
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -1329,17 +1325,17 @@
         <v>1</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -1358,234 +1354,260 @@
         <v>2</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H31" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="9" t="n">
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9" t="n">
+      <c r="D32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="7" t="n">
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7" t="n">
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="9" t="n">
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="9" t="n">
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
+      <c r="C37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H37" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr"/>
-      <c r="C38" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="D38" s="11" t="n">
+      <c r="B39" s="10" t="inlineStr"/>
+      <c r="C39" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="E38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="G38" s="11" t="inlineStr"/>
-      <c r="H38" s="11" t="inlineStr"/>
+      <c r="E39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1601,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1717,21 +1739,21 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3626</v>
+        <v>283</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Move Zeroes</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Enumeration</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -1741,21 +1763,15 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>42.5</v>
-      </c>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="12" t="n">
-        <v>46240.74578703703</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K5" s="12" t="n"/>
       <c r="L5" s="13" t="inlineStr">
         <is>
           <t>Open</t>
@@ -1767,21 +1783,21 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>58</v>
+        <v>3626</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Length of Last Word</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Enumeration</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1791,20 +1807,20 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>43.2</v>
+        <v>42.5</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>2</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>46241.78204861111</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -1817,16 +1833,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Reverse Integer</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1836,25 +1852,25 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>42.4</v>
+        <v>43.2</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>2</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>46241.79645833333</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
@@ -1867,44 +1883,44 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Single Number</t>
+          <t>Reverse Integer</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Bit Manipulation</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>47.1</v>
+        <v>42.4</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>46242.88846064815</v>
+        <v>46241.79645833333</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1917,21 +1933,21 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Single Number</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Bit Manipulation</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1941,20 +1957,20 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="K9" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46242.88846064815</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1967,11 +1983,11 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Valid Palindrome</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1981,7 +1997,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1991,20 +2007,20 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>44.6</v>
+        <v>45.3</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>46243.94849537037</v>
+        <v>46243.9169675926</v>
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
@@ -2017,21 +2033,21 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1353</v>
+        <v>242</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2045,16 +2061,16 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>46.3</v>
+        <v>44.6</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
@@ -2067,11 +2083,11 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1115</v>
+        <v>1353</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2081,7 +2097,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2095,16 +2111,16 @@
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>42.9</v>
+        <v>46.3</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>46244.79871527778</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
@@ -2117,21 +2133,21 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>680</v>
+        <v>1115</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome II</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers, Greedy</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2145,16 +2161,16 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>47.9</v>
+        <v>42.9</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46245.98399305555</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
@@ -2167,21 +2183,21 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>94</v>
+        <v>680</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Binary Tree Inorder Traversal</t>
+          <t>Valid Palindrome II</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Stack, Depth-First Search, Binary Tree</t>
+          <t>Two Pointers, Greedy</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2191,20 +2207,20 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>43.2</v>
+        <v>47.9</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>46246.86910879629</v>
+        <v>46245.98399305555</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -2217,11 +2233,11 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Minimum Depth of Binary Tree</t>
+          <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2231,7 +2247,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+          <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2245,16 +2261,16 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>82.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>46246.95925925926</v>
+        <v>46246.86910879629</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
@@ -2267,11 +2283,11 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>637</v>
+        <v>111</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Average of Levels in Binary Tree</t>
+          <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2291,20 +2307,20 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>48.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>46246.98880787037</v>
+        <v>46246.95925925926</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
@@ -2317,21 +2333,21 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>4281</v>
+        <v>637</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2345,16 +2361,16 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>47.2</v>
+        <v>48.8</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46246.98880787037</v>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
@@ -2367,21 +2383,21 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>1013</v>
+        <v>4281</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Fibonacci Number</t>
+          <t>Score Validator</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Math, Recursion, Memoization</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -2391,20 +2407,20 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>42.1</v>
+        <v>47.2</v>
       </c>
       <c r="J18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>46247.78516203703</v>
+        <v>46247.02123842593</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
@@ -2417,21 +2433,21 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>2775</v>
+        <v>1013</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Generate Fibonacci Sequence</t>
+          <t>Fibonacci Number</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Math, Recursion, Memoization</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2441,20 +2457,20 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>53.9</v>
+        <v>42.1</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>46247.79274305556</v>
+        <v>46247.78516203703</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
@@ -2467,16 +2483,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>4003</v>
+        <v>2775</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -2486,25 +2502,25 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>98</v>
+        <v>53.9</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>46247.80789351852</v>
+        <v>46247.79274305556</v>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
@@ -2517,26 +2533,26 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>543</v>
+        <v>4003</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Diameter of Binary Tree</t>
+          <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Depth-First Search, Binary Tree, DP on Trees</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2545,16 +2561,16 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="J21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>46248.99621527778</v>
+        <v>46247.80789351852</v>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
@@ -2567,21 +2583,21 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>1</v>
+        <v>543</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Two Sum</t>
+          <t>Diameter of Binary Tree</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2591,11 +2607,11 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>47</v>
@@ -2604,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>46251.8174537037</v>
+        <v>46248.99621527778</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
@@ -2617,11 +2633,11 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>3705</v>
+        <v>1</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Find the Largest Almost Missing Integer</t>
+          <t>Two Sum</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2645,16 +2661,16 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>45.1</v>
+        <v>47</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>46252.95966435185</v>
+        <v>46251.8174537037</v>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
@@ -2667,26 +2683,26 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>3</v>
+        <v>3705</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -2695,16 +2711,16 @@
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>47.9</v>
+        <v>45.1</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>46253.82314814815</v>
+        <v>46252.95966435185</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
@@ -2717,26 +2733,26 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>3347</v>
+        <v>3</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2745,16 +2761,16 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>46.7</v>
+        <v>47.9</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
@@ -2767,11 +2783,11 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>2106</v>
+        <v>3347</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -2781,7 +2797,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2795,16 +2811,16 @@
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>45.2</v>
+        <v>46.7</v>
       </c>
       <c r="J26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
@@ -2817,11 +2833,11 @@
         <v>23</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2831,12 +2847,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2845,16 +2861,16 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
@@ -2867,11 +2883,11 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>2722</v>
+        <v>3373</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -2881,12 +2897,12 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -2895,16 +2911,16 @@
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>82.5</v>
+        <v>117.3</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>46255.61045138889</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
@@ -2917,11 +2933,11 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>204</v>
+        <v>2722</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2931,12 +2947,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2945,16 +2961,16 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>709</v>
+        <v>7</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>79.8</v>
+        <v>82.5</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
@@ -2967,26 +2983,26 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>767</v>
+        <v>204</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Bit Manipulation, Primality Test</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -2995,16 +3011,16 @@
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>5</v>
+        <v>709</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>42.3</v>
+        <v>79.8</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>46255.88138888889</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
@@ -3017,26 +3033,26 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>137</v>
+        <v>767</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Single Number II</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bit Manipulation</t>
+          <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3045,16 +3061,16 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>45.1</v>
+        <v>42.3</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>46256.48149305556</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
@@ -3067,11 +3083,11 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>643</v>
+        <v>137</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Single Number II</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -3081,12 +3097,12 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Bit Manipulation</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -3098,13 +3114,13 @@
         <v>4</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>45.1</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>46256.65385416667</v>
+        <v>46256.48149305556</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
@@ -3117,11 +3133,11 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>209</v>
+        <v>643</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Minimum Size Subarray Sum</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -3131,12 +3147,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Binary Search, Sliding Window, Prefix Sum</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3145,16 +3161,16 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>69.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>46256.69032407407</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
@@ -3167,26 +3183,26 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>3918</v>
+        <v>209</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Binary Search, Sliding Window, Prefix Sum</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -3198,13 +3214,13 @@
         <v>1</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>42.3</v>
+        <v>69.2</v>
       </c>
       <c r="J34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>46256.95832175926</v>
+        <v>46256.69032407407</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
@@ -3217,46 +3233,96 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="7" t="n">
         <v>219</v>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Array</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Hash Table, Sliding Window</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G36" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H36" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="I35" s="5" t="n">
+      <c r="I36" s="7" t="n">
         <v>104.8</v>
       </c>
-      <c r="J35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" s="12" t="n">
+      <c r="J36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="14" t="n">
         <v>46258.98878472222</v>
       </c>
-      <c r="L35" s="13" t="inlineStr">
+      <c r="L36" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -3266,7 +3332,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F35">
+  <conditionalFormatting sqref="F5:F36">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3309,6 +3375,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3320,7 +3387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3363,7 +3430,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   16 solved   (Low: 11 · Medium: 5 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   17 solved   (Low: 12 · Medium: 5 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4371,169 +4438,163 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="18" t="n"/>
+      <c r="H50" s="18" t="n"/>
+      <c r="I50" s="18" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr"/>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Move Zeroes</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="n"/>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B51" s="18" t="n"/>
-      <c r="C51" s="18" t="n"/>
-      <c r="D51" s="18" t="n"/>
-      <c r="E51" s="18" t="n"/>
-      <c r="F51" s="18" t="n"/>
-      <c r="G51" s="18" t="n"/>
-      <c r="H51" s="18" t="n"/>
-      <c r="I51" s="18" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="n"/>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="18" t="n"/>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="21" t="n"/>
-      <c r="G52" s="21" t="n"/>
-      <c r="H52" s="21" t="n"/>
-      <c r="I52" s="21" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr"/>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="21" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C56" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
+      <c r="E56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H53" s="12" t="n">
+      <c r="H56" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I53" s="13" t="inlineStr">
+      <c r="I56" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="18" t="n"/>
-      <c r="E55" s="18" t="n"/>
-      <c r="F55" s="18" t="n"/>
-      <c r="G55" s="18" t="n"/>
-      <c r="H55" s="18" t="n"/>
-      <c r="I55" s="18" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="n"/>
-      <c r="B56" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="21" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="21" t="n"/>
-      <c r="I56" s="21" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr"/>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H57" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B58" s="18" t="n"/>
@@ -4564,11 +4625,11 @@
       <c r="A60" s="5" t="inlineStr"/>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
@@ -4576,18 +4637,18 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H60" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -4598,7 +4659,7 @@
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B61" s="18" t="n"/>
@@ -4629,171 +4690,171 @@
       <c r="A63" s="5" t="inlineStr"/>
       <c r="B63" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="18" t="n"/>
+      <c r="I64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="n"/>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="21" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C66" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="5" t="n">
+      <c r="E66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="H66" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I63" s="13" t="inlineStr">
+      <c r="I66" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="19" t="n"/>
-      <c r="B64" s="20" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="19" t="n"/>
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C64" s="19" t="n"/>
-      <c r="D64" s="19" t="n"/>
-      <c r="E64" s="19" t="n"/>
-      <c r="F64" s="19" t="n"/>
-      <c r="G64" s="19" t="n"/>
-      <c r="H64" s="19" t="n"/>
-      <c r="I64" s="19" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr"/>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="C67" s="19" t="n"/>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="19" t="n"/>
+      <c r="G67" s="19" t="n"/>
+      <c r="H67" s="19" t="n"/>
+      <c r="I67" s="19" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr"/>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C68" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="n">
+      <c r="E68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H65" s="12" t="n">
+      <c r="H68" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I65" s="13" t="inlineStr">
+      <c r="I68" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B67" s="18" t="n"/>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-      <c r="G67" s="18" t="n"/>
-      <c r="H67" s="18" t="n"/>
-      <c r="I67" s="18" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="21" t="n"/>
-      <c r="B68" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C68" s="21" t="n"/>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n"/>
-      <c r="H68" s="21" t="n"/>
-      <c r="I68" s="21" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr"/>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H69" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B70" s="18" t="n"/>
@@ -4806,40 +4867,40 @@
       <c r="I70" s="18" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="19" t="n"/>
-      <c r="B71" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C71" s="19" t="n"/>
-      <c r="D71" s="19" t="n"/>
-      <c r="E71" s="19" t="n"/>
-      <c r="F71" s="19" t="n"/>
-      <c r="G71" s="19" t="n"/>
-      <c r="H71" s="19" t="n"/>
-      <c r="I71" s="19" t="n"/>
+      <c r="A71" s="21" t="n"/>
+      <c r="B71" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="21" t="n"/>
+      <c r="E71" s="21" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="21" t="n"/>
+      <c r="I71" s="21" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr"/>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
@@ -4847,7 +4908,7 @@
         </is>
       </c>
       <c r="H72" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -4858,7 +4919,7 @@
     <row r="73">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B73" s="18" t="n"/>
@@ -4871,40 +4932,40 @@
       <c r="I73" s="18" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="21" t="n"/>
-      <c r="B74" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C74" s="21" t="n"/>
-      <c r="D74" s="21" t="n"/>
-      <c r="E74" s="21" t="n"/>
-      <c r="F74" s="21" t="n"/>
-      <c r="G74" s="21" t="n"/>
-      <c r="H74" s="21" t="n"/>
-      <c r="I74" s="21" t="n"/>
+      <c r="A74" s="19" t="n"/>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="19" t="n"/>
+      <c r="G74" s="19" t="n"/>
+      <c r="H74" s="19" t="n"/>
+      <c r="I74" s="19" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C75" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
@@ -4912,7 +4973,7 @@
         </is>
       </c>
       <c r="H75" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -4923,7 +4984,7 @@
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B76" s="18" t="n"/>
@@ -4954,11 +5015,11 @@
       <c r="A78" s="5" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C78" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
@@ -4969,15 +5030,15 @@
         <v>2</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H78" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -4988,7 +5049,7 @@
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B79" s="18" t="n"/>
@@ -5019,121 +5080,121 @@
       <c r="A81" s="5" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="n"/>
+      <c r="C82" s="18" t="n"/>
+      <c r="D82" s="18" t="n"/>
+      <c r="E82" s="18" t="n"/>
+      <c r="F82" s="18" t="n"/>
+      <c r="G82" s="18" t="n"/>
+      <c r="H82" s="18" t="n"/>
+      <c r="I82" s="18" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="n"/>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="n"/>
+      <c r="D83" s="21" t="n"/>
+      <c r="E83" s="21" t="n"/>
+      <c r="F83" s="21" t="n"/>
+      <c r="G83" s="21" t="n"/>
+      <c r="H83" s="21" t="n"/>
+      <c r="I83" s="21" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr"/>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C84" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E84" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F84" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H81" s="12" t="n">
+      <c r="H84" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I81" s="13" t="inlineStr">
+      <c r="I84" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="16" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n"/>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B83" s="18" t="n"/>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="18" t="n"/>
-      <c r="I83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="21" t="n"/>
-      <c r="B84" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="n"/>
-      <c r="D84" s="21" t="n"/>
-      <c r="E84" s="21" t="n"/>
-      <c r="F84" s="21" t="n"/>
-      <c r="G84" s="21" t="n"/>
-      <c r="H84" s="21" t="n"/>
-      <c r="I84" s="21" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr"/>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B86" s="18" t="n"/>
@@ -5149,7 +5210,7 @@
       <c r="A87" s="21" t="n"/>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C87" s="21" t="n"/>
@@ -5164,234 +5225,296 @@
       <c r="A88" s="5" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="n"/>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+      <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="n"/>
+      <c r="I89" s="18" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="n"/>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C90" s="21" t="n"/>
+      <c r="D90" s="21" t="n"/>
+      <c r="E90" s="21" t="n"/>
+      <c r="F90" s="21" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="21" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr"/>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C91" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E91" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F91" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H88" s="12" t="n">
+      <c r="H91" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I88" s="13" t="inlineStr">
+      <c r="I91" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="7" t="inlineStr"/>
-      <c r="B89" s="6" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C89" s="7" t="n">
+      <c r="C92" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E89" s="7" t="n">
+      <c r="E92" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F89" s="7" t="n">
+      <c r="F92" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G89" s="7" t="inlineStr">
+      <c r="G92" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H89" s="14" t="n">
+      <c r="H92" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I89" s="15" t="inlineStr">
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="17" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B90" s="18" t="n"/>
-      <c r="C90" s="18" t="n"/>
-      <c r="D90" s="18" t="n"/>
-      <c r="E90" s="18" t="n"/>
-      <c r="F90" s="18" t="n"/>
-      <c r="G90" s="18" t="n"/>
-      <c r="H90" s="18" t="n"/>
-      <c r="I90" s="18" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="21" t="n"/>
-      <c r="B91" s="22" t="inlineStr">
+      <c r="B93" s="18" t="n"/>
+      <c r="C93" s="18" t="n"/>
+      <c r="D93" s="18" t="n"/>
+      <c r="E93" s="18" t="n"/>
+      <c r="F93" s="18" t="n"/>
+      <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="n"/>
+      <c r="I93" s="18" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="n"/>
+      <c r="B94" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C91" s="21" t="n"/>
-      <c r="D91" s="21" t="n"/>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="21" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr"/>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="C94" s="21" t="n"/>
+      <c r="D94" s="21" t="n"/>
+      <c r="E94" s="21" t="n"/>
+      <c r="F94" s="21" t="n"/>
+      <c r="G94" s="21" t="n"/>
+      <c r="H94" s="21" t="n"/>
+      <c r="I94" s="21" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="5" t="n">
+      <c r="E95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H92" s="12" t="n">
+      <c r="H95" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I92" s="13" t="inlineStr">
+      <c r="I95" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="16" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B93" s="2" t="n"/>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
-      <c r="F93" s="2" t="n"/>
-      <c r="G93" s="2" t="n"/>
-      <c r="H93" s="2" t="n"/>
-      <c r="I93" s="2" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B94" s="18" t="n"/>
-      <c r="C94" s="18" t="n"/>
-      <c r="D94" s="18" t="n"/>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="18" t="n"/>
-      <c r="G94" s="18" t="n"/>
-      <c r="H94" s="18" t="n"/>
-      <c r="I94" s="18" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="21" t="n"/>
-      <c r="B95" s="22" t="inlineStr">
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="18" t="n"/>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="n"/>
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="n"/>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr"/>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="21" t="n"/>
+      <c r="E98" s="21" t="n"/>
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C99" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n">
+      <c r="E99" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F96" s="5" t="n">
+      <c r="F99" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H96" s="12" t="n">
+      <c r="H99" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I96" s="13" t="inlineStr">
+      <c r="I99" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="63">
+  <mergeCells count="65">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B62:I62"/>
     <mergeCell ref="A54:I54"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="B91:I91"/>
-    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="A89:I89"/>
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="B59:I59"/>
-    <mergeCell ref="A55:I55"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A86:I86"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="A57:I57"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="B39:I39"/>
@@ -5401,44 +5524,49 @@
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="A76:I76"/>
     <mergeCell ref="B77:I77"/>
+    <mergeCell ref="A85:I85"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B67:I67"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A97:I97"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A96:I96"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="B87:I87"/>
     <mergeCell ref="A93:I93"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A67:I67"/>
     <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="B84:I84"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="A64:I64"/>
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="A82:I82"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="A51:I51"/>
-    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="B83:I83"/>
     <mergeCell ref="B33:I33"/>
-    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="B55:I55"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="A94:I94"/>
+    <mergeCell ref="B51:I51"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
     <mergeCell ref="A61:I61"/>
     <mergeCell ref="B80:I80"/>
     <mergeCell ref="B45:I45"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="B94:I94"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
@@ -5458,21 +5586,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5484,7 +5613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6089,24 +6218,62 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="420" customHeight="1">
+    <row r="18" ht="238" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>Move Zeroes</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>283</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public void moveZeroes(int[] nums) {
+        if(nums.length&lt;1){ 
+            return;
+        }
+        int n=0;
+      for(int i=0;i&lt;nums.length;i++){ 
+        if(nums[i]!=0){ 
+            int temp=nums[i];
+           nums[i]=nums[n];
+           nums[n]=temp;
+           n++;
+         }
+      } 
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="420" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
@@ -6134,24 +6301,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="546" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="546" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -6195,24 +6362,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="196" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="196" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -6231,24 +6398,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="406" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="406" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -6281,24 +6448,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="378" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="378" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -6330,24 +6497,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="560" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="560" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -6383,24 +6550,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="294" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="294" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -6426,24 +6593,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="378" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="378" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -6475,24 +6642,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="238" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="238" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -6514,24 +6681,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="308" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="308" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -6558,24 +6725,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="280" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="280" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -6598,24 +6765,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="448" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="448" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -6650,24 +6817,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="378" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="378" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -6699,24 +6866,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="490" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="490" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -6744,24 +6911,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="308" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="308" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -6787,24 +6954,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="238" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="238" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -6824,24 +6991,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="560" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="560" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -6882,24 +7049,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="294" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="294" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -20,8 +20,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -203,13 +203,13 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1094,8 +1094,12 @@
       <c r="F19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+      <c r="G19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>47.8</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1739,21 +1743,21 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>283</v>
+        <v>3626</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Move Zeroes</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Enumeration</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -1763,15 +1767,21 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>42.5</v>
+      </c>
       <c r="J5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="12" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
           <t>Open</t>
@@ -1783,21 +1793,21 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3626</v>
+        <v>58</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Enumeration</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1807,20 +1817,20 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>2</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>46240.74578703703</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -1833,16 +1843,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Length of Last Word</t>
+          <t>Reverse Integer</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1852,25 +1862,25 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>43.2</v>
+        <v>42.4</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>2</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>46241.78204861111</v>
+        <v>46241.79645833333</v>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
@@ -1883,44 +1893,44 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Reverse Integer</t>
+          <t>Single Number</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Bit Manipulation</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>42.4</v>
+        <v>47.1</v>
       </c>
       <c r="J8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>46241.79645833333</v>
+        <v>46242.88846064815</v>
       </c>
       <c r="L8" s="15" t="inlineStr">
         <is>
@@ -1933,21 +1943,21 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Single Number</t>
+          <t>Valid Palindrome</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Bit Manipulation</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1957,20 +1967,20 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>47.1</v>
+        <v>45.3</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>46242.88846064815</v>
+        <v>46243.9169675926</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1983,11 +1993,11 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1997,7 +2007,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2007,20 +2017,20 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
@@ -2033,21 +2043,21 @@
         <v>7</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>242</v>
+        <v>1353</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -2061,16 +2071,16 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>44.6</v>
+        <v>46.3</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
@@ -2083,11 +2093,11 @@
         <v>8</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1353</v>
+        <v>1115</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2097,7 +2107,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2111,16 +2121,16 @@
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>46.3</v>
+        <v>42.9</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>46243.98008101852</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
@@ -2133,21 +2143,21 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1115</v>
+        <v>680</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Valid Palindrome II</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Two Pointers, Greedy</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2161,16 +2171,16 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>42.9</v>
+        <v>47.9</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46245.98399305555</v>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
@@ -2183,21 +2193,21 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>680</v>
+        <v>94</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Valid Palindrome II</t>
+          <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers, Greedy</t>
+          <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2207,20 +2217,20 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>46245.98399305555</v>
+        <v>46246.86910879629</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -2233,11 +2243,11 @@
         <v>11</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Binary Tree Inorder Traversal</t>
+          <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2247,7 +2257,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Stack, Depth-First Search, Binary Tree</t>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -2261,16 +2271,16 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>43.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>46246.86910879629</v>
+        <v>46246.95925925926</v>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
@@ -2283,11 +2293,11 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>111</v>
+        <v>637</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Minimum Depth of Binary Tree</t>
+          <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2307,20 +2317,20 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>82.09999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="J16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>46246.95925925926</v>
+        <v>46246.98880787037</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
@@ -2333,21 +2343,21 @@
         <v>13</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>637</v>
+        <v>4281</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Average of Levels in Binary Tree</t>
+          <t>Score Validator</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -2361,16 +2371,16 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>48.8</v>
+        <v>47.2</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>46246.98880787037</v>
+        <v>46247.02123842593</v>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
@@ -2383,21 +2393,21 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>4281</v>
+        <v>1013</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Fibonacci Number</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Dynamic Programming</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Math, Recursion, Memoization</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -2407,20 +2417,20 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>47.2</v>
+        <v>42.1</v>
       </c>
       <c r="J18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>46247.02123842593</v>
+        <v>46247.78516203703</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
@@ -2433,21 +2443,21 @@
         <v>15</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>1013</v>
+        <v>2775</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Fibonacci Number</t>
+          <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Dynamic Programming</t>
+          <t>Uncategorized</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Math, Recursion, Memoization</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2457,20 +2467,20 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>42.1</v>
+        <v>53.9</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>46247.78516203703</v>
+        <v>46247.79274305556</v>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
@@ -2483,16 +2493,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>2775</v>
+        <v>4003</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Generate Fibonacci Sequence</t>
+          <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Uncategorized</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -2502,25 +2512,25 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>53.9</v>
+        <v>98</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>46247.79274305556</v>
+        <v>46247.80789351852</v>
       </c>
       <c r="L20" s="15" t="inlineStr">
         <is>
@@ -2533,26 +2543,26 @@
         <v>17</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>4003</v>
+        <v>543</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Diameter of Binary Tree</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Tree</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -2561,16 +2571,16 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="J21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>46247.80789351852</v>
+        <v>46248.99621527778</v>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
@@ -2583,21 +2593,21 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>543</v>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Diameter of Binary Tree</t>
+          <t>Two Sum</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Tree</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Depth-First Search, Binary Tree, DP on Trees</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -2607,11 +2617,11 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>47</v>
@@ -2620,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>46248.99621527778</v>
+        <v>46251.8174537037</v>
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
@@ -2633,11 +2643,11 @@
         <v>19</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1</v>
+        <v>3705</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Two Sum</t>
+          <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2661,16 +2671,16 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>47</v>
+        <v>45.1</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>46251.8174537037</v>
+        <v>46252.95966435185</v>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
@@ -2683,26 +2693,26 @@
         <v>20</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>3705</v>
+        <v>3</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Find the Largest Almost Missing Integer</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>String</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -2711,16 +2721,16 @@
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>46252.95966435185</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
@@ -2733,26 +2743,26 @@
         <v>21</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>3</v>
+        <v>3347</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2761,16 +2771,16 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>47.9</v>
+        <v>46.7</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="L25" s="13" t="inlineStr">
         <is>
@@ -2783,11 +2793,11 @@
         <v>22</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>3347</v>
+        <v>2106</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -2797,7 +2807,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2811,16 +2821,16 @@
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>46.7</v>
+        <v>45.2</v>
       </c>
       <c r="J26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>46255.01133101852</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
@@ -2833,11 +2843,11 @@
         <v>23</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>2106</v>
+        <v>3373</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2847,12 +2857,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2861,16 +2871,16 @@
         </is>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>45.2</v>
+        <v>117.3</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="L27" s="13" t="inlineStr">
         <is>
@@ -2883,11 +2893,11 @@
         <v>24</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>3373</v>
+        <v>2722</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -2897,12 +2907,12 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
@@ -2911,16 +2921,16 @@
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>117.3</v>
+        <v>82.5</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
@@ -2933,11 +2943,11 @@
         <v>25</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>2722</v>
+        <v>204</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2947,12 +2957,12 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -2961,16 +2971,16 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>7</v>
+        <v>709</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>82.5</v>
+        <v>79.8</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
@@ -2983,26 +2993,26 @@
         <v>26</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>204</v>
+        <v>767</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -3011,16 +3021,16 @@
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>709</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>79.8</v>
+        <v>42.3</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>46255.64438657407</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
@@ -3033,26 +3043,26 @@
         <v>27</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>767</v>
+        <v>137</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
+          <t>Single Number II</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bit Manipulation, Primality Test</t>
+          <t>Bit Manipulation</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3061,16 +3071,16 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>42.3</v>
+        <v>45.1</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>46255.88138888889</v>
+        <v>46256.48149305556</v>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
@@ -3083,11 +3093,11 @@
         <v>28</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>137</v>
+        <v>643</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Single Number II</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -3097,12 +3107,12 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Bit Manipulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -3114,13 +3124,13 @@
         <v>4</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>45.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>46256.48149305556</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
@@ -3133,11 +3143,11 @@
         <v>29</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>643</v>
+        <v>209</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -3147,12 +3157,12 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Binary Search, Sliding Window, Prefix Sum</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3161,16 +3171,16 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="J33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46256.69032407407</v>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
@@ -3183,26 +3193,26 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>209</v>
+        <v>3918</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Minimum Size Subarray Sum</t>
+          <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Math</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Binary Search, Sliding Window, Prefix Sum</t>
+          <t>General</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -3214,13 +3224,13 @@
         <v>1</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>69.2</v>
+        <v>42.3</v>
       </c>
       <c r="J34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>46256.69032407407</v>
+        <v>46256.95832175926</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
@@ -3233,21 +3243,21 @@
         <v>31</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>3918</v>
+        <v>219</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Math</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -3261,16 +3271,16 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>42.3</v>
+        <v>104.8</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
@@ -3283,11 +3293,11 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Contains Duplicate II</t>
+          <t>Move Zeroes</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
@@ -3297,7 +3307,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -3311,16 +3321,16 @@
         </is>
       </c>
       <c r="H36" s="7" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>104.8</v>
+        <v>47.8</v>
       </c>
       <c r="J36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>46258.98878472222</v>
+        <v>46259.51340277777</v>
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
@@ -4482,14 +4492,20 @@
           <t>Easy</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
+      <c r="E52" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>47.8</v>
+      </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H52" s="12" t="n"/>
+      <c r="H52" s="12" t="n">
+        <v>46259.51340277777</v>
+      </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
           <t>Open</t>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -1092,13 +1092,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="20">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr"/>
       <c r="C20" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>5</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G20" s="9" t="inlineStr"/>
       <c r="H20" s="9" t="inlineStr"/>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="B39" s="10" t="inlineStr"/>
       <c r="C39" s="11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>7</v>
@@ -1608,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G39" s="11" t="inlineStr"/>
       <c r="H39" s="11" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3338,11 +3338,61 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Remove Duplicates from Sorted Array</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>46259.58225694444</v>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F36">
+  <conditionalFormatting sqref="F5:F37">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3386,6 +3436,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3397,7 +3448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3440,7 +3491,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   17 solved   (Low: 12 · Medium: 5 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   18 solved   (Low: 13 · Medium: 5 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4450,7 +4501,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -4466,7 +4517,7 @@
       <c r="A51" s="21" t="n"/>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 1 problem(s)</t>
+          <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
       <c r="C51" s="21" t="n"/>
@@ -4481,1037 +4532,1072 @@
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
+          <t>Remove Duplicates from Sorted Array</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>46259.58225694444</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr"/>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C53" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n">
+      <c r="E53" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F53" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H52" s="12" t="n">
+      <c r="H53" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I52" s="13" t="inlineStr">
+      <c r="I53" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-      <c r="G54" s="18" t="n"/>
-      <c r="H54" s="18" t="n"/>
-      <c r="I54" s="18" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="21" t="n"/>
-      <c r="B55" s="22" t="inlineStr">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="18" t="n"/>
+      <c r="H55" s="18" t="n"/>
+      <c r="I55" s="18" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C55" s="21" t="n"/>
-      <c r="D55" s="21" t="n"/>
-      <c r="E55" s="21" t="n"/>
-      <c r="F55" s="21" t="n"/>
-      <c r="G55" s="21" t="n"/>
-      <c r="H55" s="21" t="n"/>
-      <c r="I55" s="21" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr"/>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="n"/>
+      <c r="H56" s="21" t="n"/>
+      <c r="I56" s="21" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr"/>
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C57" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="n">
+      <c r="E57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H56" s="12" t="n">
+      <c r="H57" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I56" s="13" t="inlineStr">
+      <c r="I57" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B58" s="18" t="n"/>
-      <c r="C58" s="18" t="n"/>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="18" t="n"/>
-      <c r="I58" s="18" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="21" t="n"/>
-      <c r="B59" s="22" t="inlineStr">
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="n"/>
+      <c r="I59" s="18" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C59" s="21" t="n"/>
-      <c r="D59" s="21" t="n"/>
-      <c r="E59" s="21" t="n"/>
-      <c r="F59" s="21" t="n"/>
-      <c r="G59" s="21" t="n"/>
-      <c r="H59" s="21" t="n"/>
-      <c r="I59" s="21" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr"/>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C61" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n">
+      <c r="E61" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F61" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G61" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="H61" s="12" t="n">
         <v>46255.88138888889</v>
       </c>
-      <c r="I60" s="13" t="inlineStr">
+      <c r="I61" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B61" s="18" t="n"/>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="18" t="n"/>
-      <c r="I61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="21" t="n"/>
-      <c r="B62" s="22" t="inlineStr">
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="18" t="n"/>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="18" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="n"/>
+      <c r="B63" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C62" s="21" t="n"/>
-      <c r="D62" s="21" t="n"/>
-      <c r="E62" s="21" t="n"/>
-      <c r="F62" s="21" t="n"/>
-      <c r="G62" s="21" t="n"/>
-      <c r="H62" s="21" t="n"/>
-      <c r="I62" s="21" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="21" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr"/>
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C64" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="5" t="n">
+      <c r="E64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="H64" s="12" t="n">
         <v>46240.74578703703</v>
       </c>
-      <c r="I63" s="13" t="inlineStr">
+      <c r="I64" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="18" t="n"/>
-      <c r="I64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="22" t="inlineStr">
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="18" t="n"/>
+      <c r="H65" s="18" t="n"/>
+      <c r="I65" s="18" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="n"/>
+      <c r="B66" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
-      <c r="G65" s="21" t="n"/>
-      <c r="H65" s="21" t="n"/>
-      <c r="I65" s="21" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr"/>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="21" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C67" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" s="5" t="n">
+      <c r="E67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H66" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I66" s="13" t="inlineStr">
+      <c r="I67" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="19" t="n"/>
-      <c r="B67" s="20" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="19" t="n"/>
+      <c r="B68" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C67" s="19" t="n"/>
-      <c r="D67" s="19" t="n"/>
-      <c r="E67" s="19" t="n"/>
-      <c r="F67" s="19" t="n"/>
-      <c r="G67" s="19" t="n"/>
-      <c r="H67" s="19" t="n"/>
-      <c r="I67" s="19" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr"/>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="C68" s="19" t="n"/>
+      <c r="D68" s="19" t="n"/>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="19" t="n"/>
+      <c r="G68" s="19" t="n"/>
+      <c r="H68" s="19" t="n"/>
+      <c r="I68" s="19" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr"/>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C69" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" s="5" t="n">
+      <c r="E69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H68" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="I69" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B70" s="18" t="n"/>
-      <c r="C70" s="18" t="n"/>
-      <c r="D70" s="18" t="n"/>
-      <c r="E70" s="18" t="n"/>
-      <c r="F70" s="18" t="n"/>
-      <c r="G70" s="18" t="n"/>
-      <c r="H70" s="18" t="n"/>
-      <c r="I70" s="18" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="n"/>
-      <c r="B71" s="22" t="inlineStr">
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C71" s="21" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="n"/>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C73" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="n">
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H72" s="12" t="n">
+      <c r="H73" s="12" t="n">
         <v>46241.78204861111</v>
       </c>
-      <c r="I72" s="13" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="18" t="n"/>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="18" t="n"/>
-      <c r="I73" s="18" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="19" t="n"/>
-      <c r="B74" s="20" t="inlineStr">
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="19" t="n"/>
+      <c r="B75" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C74" s="19" t="n"/>
-      <c r="D74" s="19" t="n"/>
-      <c r="E74" s="19" t="n"/>
-      <c r="F74" s="19" t="n"/>
-      <c r="G74" s="19" t="n"/>
-      <c r="H74" s="19" t="n"/>
-      <c r="I74" s="19" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr"/>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="C75" s="19" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="19" t="n"/>
+      <c r="G75" s="19" t="n"/>
+      <c r="H75" s="19" t="n"/>
+      <c r="I75" s="19" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr"/>
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C76" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E76" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F76" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H75" s="12" t="n">
+      <c r="H76" s="12" t="n">
         <v>46253.82314814815</v>
       </c>
-      <c r="I75" s="13" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B76" s="18" t="n"/>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
-      <c r="H76" s="18" t="n"/>
-      <c r="I76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="n"/>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C77" s="21" t="n"/>
-      <c r="D77" s="21" t="n"/>
-      <c r="E77" s="21" t="n"/>
-      <c r="F77" s="21" t="n"/>
-      <c r="G77" s="21" t="n"/>
-      <c r="H77" s="21" t="n"/>
-      <c r="I77" s="21" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="21" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="21" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr"/>
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C79" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E79" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F79" s="5" t="n">
         <v>44.6</v>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="H79" s="12" t="n">
         <v>46243.94849537037</v>
       </c>
-      <c r="I78" s="13" t="inlineStr">
+      <c r="I79" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B79" s="18" t="n"/>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="18" t="n"/>
-      <c r="E79" s="18" t="n"/>
-      <c r="F79" s="18" t="n"/>
-      <c r="G79" s="18" t="n"/>
-      <c r="H79" s="18" t="n"/>
-      <c r="I79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="21" t="n"/>
-      <c r="B80" s="22" t="inlineStr">
+      <c r="B80" s="18" t="n"/>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="21" t="n"/>
+      <c r="B81" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C80" s="21" t="n"/>
-      <c r="D80" s="21" t="n"/>
-      <c r="E80" s="21" t="n"/>
-      <c r="F80" s="21" t="n"/>
-      <c r="G80" s="21" t="n"/>
-      <c r="H80" s="21" t="n"/>
-      <c r="I80" s="21" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr"/>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="21" t="n"/>
+      <c r="E81" s="21" t="n"/>
+      <c r="F81" s="21" t="n"/>
+      <c r="G81" s="21" t="n"/>
+      <c r="H81" s="21" t="n"/>
+      <c r="I81" s="21" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr"/>
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E82" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F82" s="5" t="n">
         <v>45.3</v>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H81" s="12" t="n">
+      <c r="H82" s="12" t="n">
         <v>46243.9169675926</v>
       </c>
-      <c r="I81" s="13" t="inlineStr">
+      <c r="I82" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="17" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B82" s="18" t="n"/>
-      <c r="C82" s="18" t="n"/>
-      <c r="D82" s="18" t="n"/>
-      <c r="E82" s="18" t="n"/>
-      <c r="F82" s="18" t="n"/>
-      <c r="G82" s="18" t="n"/>
-      <c r="H82" s="18" t="n"/>
-      <c r="I82" s="18" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="21" t="n"/>
-      <c r="B83" s="22" t="inlineStr">
+      <c r="B83" s="18" t="n"/>
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="n"/>
+      <c r="B84" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C83" s="21" t="n"/>
-      <c r="D83" s="21" t="n"/>
-      <c r="E83" s="21" t="n"/>
-      <c r="F83" s="21" t="n"/>
-      <c r="G83" s="21" t="n"/>
-      <c r="H83" s="21" t="n"/>
-      <c r="I83" s="21" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr"/>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="C84" s="21" t="n"/>
+      <c r="D84" s="21" t="n"/>
+      <c r="E84" s="21" t="n"/>
+      <c r="F84" s="21" t="n"/>
+      <c r="G84" s="21" t="n"/>
+      <c r="H84" s="21" t="n"/>
+      <c r="I84" s="21" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr"/>
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C85" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E85" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F85" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H84" s="12" t="n">
+      <c r="H85" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I84" s="13" t="inlineStr">
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n"/>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="17" t="inlineStr">
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B86" s="18" t="n"/>
-      <c r="C86" s="18" t="n"/>
-      <c r="D86" s="18" t="n"/>
-      <c r="E86" s="18" t="n"/>
-      <c r="F86" s="18" t="n"/>
-      <c r="G86" s="18" t="n"/>
-      <c r="H86" s="18" t="n"/>
-      <c r="I86" s="18" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="21" t="n"/>
-      <c r="B87" s="22" t="inlineStr">
+      <c r="B87" s="18" t="n"/>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="18" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+      <c r="G87" s="18" t="n"/>
+      <c r="H87" s="18" t="n"/>
+      <c r="I87" s="18" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="n"/>
+      <c r="B88" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C87" s="21" t="n"/>
-      <c r="D87" s="21" t="n"/>
-      <c r="E87" s="21" t="n"/>
-      <c r="F87" s="21" t="n"/>
-      <c r="G87" s="21" t="n"/>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="21" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr"/>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="C88" s="21" t="n"/>
+      <c r="D88" s="21" t="n"/>
+      <c r="E88" s="21" t="n"/>
+      <c r="F88" s="21" t="n"/>
+      <c r="G88" s="21" t="n"/>
+      <c r="H88" s="21" t="n"/>
+      <c r="I88" s="21" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr"/>
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C89" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="5" t="n">
+      <c r="E89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H88" s="12" t="n">
+      <c r="H89" s="12" t="n">
         <v>46248.99621527778</v>
       </c>
-      <c r="I88" s="13" t="inlineStr">
+      <c r="I89" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="17" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="18" t="n"/>
-      <c r="D89" s="18" t="n"/>
-      <c r="E89" s="18" t="n"/>
-      <c r="F89" s="18" t="n"/>
-      <c r="G89" s="18" t="n"/>
-      <c r="H89" s="18" t="n"/>
-      <c r="I89" s="18" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="21" t="n"/>
-      <c r="B90" s="22" t="inlineStr">
+      <c r="B90" s="18" t="n"/>
+      <c r="C90" s="18" t="n"/>
+      <c r="D90" s="18" t="n"/>
+      <c r="E90" s="18" t="n"/>
+      <c r="F90" s="18" t="n"/>
+      <c r="G90" s="18" t="n"/>
+      <c r="H90" s="18" t="n"/>
+      <c r="I90" s="18" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="n"/>
+      <c r="B91" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr"/>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="C91" s="21" t="n"/>
+      <c r="D91" s="21" t="n"/>
+      <c r="E91" s="21" t="n"/>
+      <c r="F91" s="21" t="n"/>
+      <c r="G91" s="21" t="n"/>
+      <c r="H91" s="21" t="n"/>
+      <c r="I91" s="21" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr"/>
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C92" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D92" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="E92" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F92" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H91" s="12" t="n">
+      <c r="H92" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I91" s="13" t="inlineStr">
+      <c r="I92" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="7" t="inlineStr"/>
-      <c r="B92" s="6" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr"/>
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C92" s="7" t="n">
+      <c r="C93" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D92" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E92" s="7" t="n">
+      <c r="E93" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F92" s="7" t="n">
+      <c r="F93" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G92" s="7" t="inlineStr">
+      <c r="G93" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H92" s="14" t="n">
+      <c r="H93" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I92" s="15" t="inlineStr">
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="17" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B93" s="18" t="n"/>
-      <c r="C93" s="18" t="n"/>
-      <c r="D93" s="18" t="n"/>
-      <c r="E93" s="18" t="n"/>
-      <c r="F93" s="18" t="n"/>
-      <c r="G93" s="18" t="n"/>
-      <c r="H93" s="18" t="n"/>
-      <c r="I93" s="18" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="21" t="n"/>
-      <c r="B94" s="22" t="inlineStr">
+      <c r="B94" s="18" t="n"/>
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+      <c r="G94" s="18" t="n"/>
+      <c r="H94" s="18" t="n"/>
+      <c r="I94" s="18" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="n"/>
+      <c r="B95" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C94" s="21" t="n"/>
-      <c r="D94" s="21" t="n"/>
-      <c r="E94" s="21" t="n"/>
-      <c r="F94" s="21" t="n"/>
-      <c r="G94" s="21" t="n"/>
-      <c r="H94" s="21" t="n"/>
-      <c r="I94" s="21" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="C95" s="21" t="n"/>
+      <c r="D95" s="21" t="n"/>
+      <c r="E95" s="21" t="n"/>
+      <c r="F95" s="21" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr"/>
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C96" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="5" t="n">
+      <c r="E96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H95" s="12" t="n">
+      <c r="H96" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I95" s="13" t="inlineStr">
+      <c r="I96" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="16" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n"/>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="n"/>
-      <c r="I96" s="2" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="17" t="inlineStr">
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="n"/>
-      <c r="B98" s="22" t="inlineStr">
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="18" t="n"/>
+      <c r="D98" s="18" t="n"/>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="n"/>
+      <c r="B99" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C98" s="21" t="n"/>
-      <c r="D98" s="21" t="n"/>
-      <c r="E98" s="21" t="n"/>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr"/>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="C99" s="21" t="n"/>
+      <c r="D99" s="21" t="n"/>
+      <c r="E99" s="21" t="n"/>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr"/>
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C100" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n">
+      <c r="E100" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="F100" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="H100" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I99" s="13" t="inlineStr">
+      <c r="I100" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -5519,70 +5605,70 @@
     </row>
   </sheetData>
   <mergeCells count="65">
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="A90:I90"/>
     <mergeCell ref="A54:I54"/>
-    <mergeCell ref="A89:I89"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B91:I91"/>
+    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B71:I71"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A86:I86"/>
-    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B48:I48"/>
+    <mergeCell ref="A71:I71"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="B77:I77"/>
-    <mergeCell ref="A85:I85"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="B60:I60"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="B98:I98"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A96:I96"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="B87:I87"/>
-    <mergeCell ref="A93:I93"/>
+    <mergeCell ref="B88:I88"/>
+    <mergeCell ref="B78:I78"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
+    <mergeCell ref="B99:I99"/>
     <mergeCell ref="A58:I58"/>
-    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="B84:I84"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="A64:I64"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="B83:I83"/>
+    <mergeCell ref="B68:I68"/>
     <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B55:I55"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B95:I95"/>
+    <mergeCell ref="A94:I94"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A61:I61"/>
-    <mergeCell ref="B80:I80"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="A87:I87"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
@@ -5603,21 +5689,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5629,7 +5716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5805,24 +5892,58 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="210" customHeight="1">
+    <row r="8" ht="168" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
+          <t>Remove Duplicates from Sorted Array</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int removeDuplicates(int[] nums) {
+    int j =1;
+    for(int i=1;i&lt;nums.length;i++){
+        if(nums[i] != nums[j-1]){
+            nums[j] =nums[i];
+            j++;
+        }
+    }
+    return j;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="210" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C9" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int lengthOfLastWord(String s) {
@@ -5842,24 +5963,24 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="560" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+    <row r="10" ht="560" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -5898,24 +6019,24 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="406" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+    <row r="11" ht="406" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;111 - Minimum Depth of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/minimum-depth-of-binary-tree/"&gt;minimum-depth-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a binary tree, find its minimum depth.&lt;/p&gt;
 &lt;p&gt;The minimum depth is the number of nodes along the shortest path from the root node down to the nearest leaf node.&lt;/p&gt;
@@ -5942,24 +6063,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="532" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="532" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -5993,24 +6114,24 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13" ht="126" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -6024,24 +6145,24 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="238" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14" ht="238" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -6063,24 +6184,24 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="294" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15" ht="294" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -6106,24 +6227,24 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="238" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="238" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -6145,24 +6266,24 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="238" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="17" ht="238" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -6184,24 +6305,24 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="392" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="392" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -6234,24 +6355,24 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="238" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="238" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -6272,24 +6393,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="420" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="420" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
@@ -6317,24 +6438,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="546" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="546" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -6378,24 +6499,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="196" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="196" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -6414,24 +6535,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="406" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="406" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -6464,24 +6585,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="378" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="378" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -6513,24 +6634,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="560" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="560" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -6566,24 +6687,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="294" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="294" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -6609,24 +6730,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="378" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="378" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -6658,24 +6779,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="238" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="238" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -6697,24 +6818,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="308" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="308" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -6741,24 +6862,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="280" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="280" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -6781,24 +6902,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="448" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="448" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -6833,24 +6954,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="378" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="378" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -6882,24 +7003,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="490" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="490" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -6927,24 +7048,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="308" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="308" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -6970,24 +7091,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="238" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="238" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -7007,24 +7128,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="560" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="560" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -7065,24 +7186,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="294" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="294" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1098,7 +1098,7 @@
         <v>1.5</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="20">
@@ -3374,10 +3374,10 @@
         <v>1</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>46259.58225694444</v>
@@ -4547,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="168" customHeight="1">
+    <row r="8" ht="154" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
@@ -5916,8 +5916,7 @@
     int j =1;
     for(int i=1;i&lt;nums.length;i++){
         if(nums[i] != nums[j-1]){
-            nums[j] =nums[i];
-            j++;
+            nums[j++] =nums[i];
         }
     }
     return j;

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1102,251 +1102,251 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Two Pointers, Greedy</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>77.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr"/>
-      <c r="C20" s="9" t="n">
+      <c r="B21" s="8" t="inlineStr"/>
+      <c r="C21" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Math, Recursion, Memoization</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Dynamic Programming — TOTAL</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Bit Manipulation, Primality Test</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Dynamic Programming</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Math, Recursion, Memoization</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>42.1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Dynamic Programming — TOTAL</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr"/>
-      <c r="C22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Math</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Bit Manipulation, Primality Test</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="H24" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="n">
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="G26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="9" t="n">
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9" t="n">
+      <c r="D27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="n">
+      <c r="C28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>0</v>
@@ -1355,17 +1355,17 @@
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
@@ -1384,234 +1384,260 @@
         <v>2</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H32" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr"/>
-      <c r="C32" s="9" t="n">
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="9" t="n">
+      <c r="D33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="9" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="5" t="n">
+      <c r="C36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="9" t="n">
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="9" t="n">
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H38" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr"/>
-      <c r="C38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr"/>
-      <c r="C39" s="11" t="n">
+      <c r="B40" s="10" t="inlineStr"/>
+      <c r="C40" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="D39" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="G39" s="11" t="inlineStr"/>
-      <c r="H39" s="11" t="inlineStr"/>
+      <c r="D40" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="G40" s="11" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1627,7 +1653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3388,11 +3414,61 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Container With Most Water</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Two Pointers, Greedy</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="14" t="n">
+        <v>46259.68393518519</v>
+      </c>
+      <c r="L38" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F37">
+  <conditionalFormatting sqref="F5:F38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3437,6 +3513,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3448,7 +3525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3491,7 +3568,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   18 solved   (Low: 13 · Medium: 5 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   19 solved   (Low: 13 · Medium: 6 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4599,169 +4676,169 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="18" t="n"/>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="n"/>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
+      <c r="G55" s="19" t="n"/>
+      <c r="H55" s="19" t="n"/>
+      <c r="I55" s="19" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Container With Most Water</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>46259.68393518519</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n"/>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B55" s="18" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="18" t="n"/>
-      <c r="E55" s="18" t="n"/>
-      <c r="F55" s="18" t="n"/>
-      <c r="G55" s="18" t="n"/>
-      <c r="H55" s="18" t="n"/>
-      <c r="I55" s="18" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="n"/>
-      <c r="B56" s="22" t="inlineStr">
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="18" t="n"/>
+      <c r="H58" s="18" t="n"/>
+      <c r="I58" s="18" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="n"/>
+      <c r="B59" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C56" s="21" t="n"/>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="21" t="n"/>
-      <c r="F56" s="21" t="n"/>
-      <c r="G56" s="21" t="n"/>
-      <c r="H56" s="21" t="n"/>
-      <c r="I56" s="21" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr"/>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="21" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="n"/>
+      <c r="H59" s="21" t="n"/>
+      <c r="I59" s="21" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C60" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H57" s="12" t="n">
+      <c r="H60" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I57" s="13" t="inlineStr">
+      <c r="I60" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B59" s="18" t="n"/>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="18" t="n"/>
-      <c r="I59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="21" t="n"/>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n"/>
-      <c r="D60" s="21" t="n"/>
-      <c r="E60" s="21" t="n"/>
-      <c r="F60" s="21" t="n"/>
-      <c r="G60" s="21" t="n"/>
-      <c r="H60" s="21" t="n"/>
-      <c r="I60" s="21" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr"/>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -4792,11 +4869,11 @@
       <c r="A64" s="5" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
@@ -4804,18 +4881,18 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -4826,7 +4903,7 @@
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -4857,171 +4934,171 @@
       <c r="A67" s="5" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="n"/>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="n"/>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="21" t="n"/>
+      <c r="E69" s="21" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="21" t="n"/>
+      <c r="I69" s="21" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr"/>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C70" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="n">
+      <c r="E70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H67" s="12" t="n">
+      <c r="H70" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I67" s="13" t="inlineStr">
+      <c r="I70" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="19" t="n"/>
-      <c r="B68" s="20" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="19" t="n"/>
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C68" s="19" t="n"/>
-      <c r="D68" s="19" t="n"/>
-      <c r="E68" s="19" t="n"/>
-      <c r="F68" s="19" t="n"/>
-      <c r="G68" s="19" t="n"/>
-      <c r="H68" s="19" t="n"/>
-      <c r="I68" s="19" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr"/>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="C71" s="19" t="n"/>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="19" t="n"/>
+      <c r="G71" s="19" t="n"/>
+      <c r="H71" s="19" t="n"/>
+      <c r="I71" s="19" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr"/>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C72" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="n">
+      <c r="E72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H69" s="12" t="n">
+      <c r="H72" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I69" s="13" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="18" t="n"/>
-      <c r="I71" s="18" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="21" t="n"/>
-      <c r="B72" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="21" t="n"/>
-      <c r="I72" s="21" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr"/>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B74" s="18" t="n"/>
@@ -5034,40 +5111,40 @@
       <c r="I74" s="18" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="19" t="n"/>
-      <c r="B75" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C75" s="19" t="n"/>
-      <c r="D75" s="19" t="n"/>
-      <c r="E75" s="19" t="n"/>
-      <c r="F75" s="19" t="n"/>
-      <c r="G75" s="19" t="n"/>
-      <c r="H75" s="19" t="n"/>
-      <c r="I75" s="19" t="n"/>
+      <c r="A75" s="21" t="n"/>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="n"/>
+      <c r="D75" s="21" t="n"/>
+      <c r="E75" s="21" t="n"/>
+      <c r="F75" s="21" t="n"/>
+      <c r="G75" s="21" t="n"/>
+      <c r="H75" s="21" t="n"/>
+      <c r="I75" s="21" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
@@ -5075,7 +5152,7 @@
         </is>
       </c>
       <c r="H76" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -5086,7 +5163,7 @@
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B77" s="18" t="n"/>
@@ -5099,40 +5176,40 @@
       <c r="I77" s="18" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="21" t="n"/>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="n"/>
-      <c r="D78" s="21" t="n"/>
-      <c r="E78" s="21" t="n"/>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="21" t="n"/>
-      <c r="H78" s="21" t="n"/>
-      <c r="I78" s="21" t="n"/>
+      <c r="A78" s="19" t="n"/>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="n"/>
+      <c r="D78" s="19" t="n"/>
+      <c r="E78" s="19" t="n"/>
+      <c r="F78" s="19" t="n"/>
+      <c r="G78" s="19" t="n"/>
+      <c r="H78" s="19" t="n"/>
+      <c r="I78" s="19" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
@@ -5140,7 +5217,7 @@
         </is>
       </c>
       <c r="H79" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -5151,7 +5228,7 @@
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B80" s="18" t="n"/>
@@ -5182,11 +5259,11 @@
       <c r="A82" s="5" t="inlineStr"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
@@ -5197,15 +5274,15 @@
         <v>2</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H82" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -5216,7 +5293,7 @@
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B83" s="18" t="n"/>
@@ -5247,121 +5324,121 @@
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="n"/>
+      <c r="C86" s="18" t="n"/>
+      <c r="D86" s="18" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="18" t="n"/>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="18" t="n"/>
+      <c r="I86" s="18" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="n"/>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="n"/>
+      <c r="D87" s="21" t="n"/>
+      <c r="E87" s="21" t="n"/>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="21" t="n"/>
+      <c r="I87" s="21" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr"/>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C88" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E88" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F88" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H85" s="12" t="n">
+      <c r="H88" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="I88" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n"/>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B87" s="18" t="n"/>
-      <c r="C87" s="18" t="n"/>
-      <c r="D87" s="18" t="n"/>
-      <c r="E87" s="18" t="n"/>
-      <c r="F87" s="18" t="n"/>
-      <c r="G87" s="18" t="n"/>
-      <c r="H87" s="18" t="n"/>
-      <c r="I87" s="18" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="21" t="n"/>
-      <c r="B88" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C88" s="21" t="n"/>
-      <c r="D88" s="21" t="n"/>
-      <c r="E88" s="21" t="n"/>
-      <c r="F88" s="21" t="n"/>
-      <c r="G88" s="21" t="n"/>
-      <c r="H88" s="21" t="n"/>
-      <c r="I88" s="21" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H89" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B90" s="18" t="n"/>
@@ -5377,7 +5454,7 @@
       <c r="A91" s="21" t="n"/>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C91" s="21" t="n"/>
@@ -5392,219 +5469,284 @@
       <c r="A92" s="5" t="inlineStr"/>
       <c r="B92" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="n"/>
+      <c r="C93" s="18" t="n"/>
+      <c r="D93" s="18" t="n"/>
+      <c r="E93" s="18" t="n"/>
+      <c r="F93" s="18" t="n"/>
+      <c r="G93" s="18" t="n"/>
+      <c r="H93" s="18" t="n"/>
+      <c r="I93" s="18" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="n"/>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C94" s="21" t="n"/>
+      <c r="D94" s="21" t="n"/>
+      <c r="E94" s="21" t="n"/>
+      <c r="F94" s="21" t="n"/>
+      <c r="G94" s="21" t="n"/>
+      <c r="H94" s="21" t="n"/>
+      <c r="I94" s="21" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C95" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D92" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="E95" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F95" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H92" s="12" t="n">
+      <c r="H95" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I92" s="13" t="inlineStr">
+      <c r="I95" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="7" t="inlineStr"/>
-      <c r="B93" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C93" s="7" t="n">
+      <c r="C96" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n">
+      <c r="E96" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F93" s="7" t="n">
+      <c r="F96" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G93" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H93" s="14" t="n">
+      <c r="H96" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I93" s="15" t="inlineStr">
+      <c r="I96" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B94" s="18" t="n"/>
-      <c r="C94" s="18" t="n"/>
-      <c r="D94" s="18" t="n"/>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="18" t="n"/>
-      <c r="G94" s="18" t="n"/>
-      <c r="H94" s="18" t="n"/>
-      <c r="I94" s="18" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="21" t="n"/>
-      <c r="B95" s="22" t="inlineStr">
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="18" t="n"/>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="n"/>
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="n"/>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr"/>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="21" t="n"/>
+      <c r="E98" s="21" t="n"/>
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C99" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="5" t="n">
+      <c r="E99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H96" s="12" t="n">
+      <c r="H99" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I96" s="13" t="inlineStr">
+      <c r="I99" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="16" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="17" t="inlineStr">
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
+      <c r="I100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B98" s="18" t="n"/>
-      <c r="C98" s="18" t="n"/>
-      <c r="D98" s="18" t="n"/>
-      <c r="E98" s="18" t="n"/>
-      <c r="F98" s="18" t="n"/>
-      <c r="G98" s="18" t="n"/>
-      <c r="H98" s="18" t="n"/>
-      <c r="I98" s="18" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="21" t="n"/>
-      <c r="B99" s="22" t="inlineStr">
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="18" t="n"/>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="n"/>
+      <c r="I101" s="18" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="21" t="n"/>
+      <c r="B102" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C99" s="21" t="n"/>
-      <c r="D99" s="21" t="n"/>
-      <c r="E99" s="21" t="n"/>
-      <c r="F99" s="21" t="n"/>
-      <c r="G99" s="21" t="n"/>
-      <c r="H99" s="21" t="n"/>
-      <c r="I99" s="21" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr"/>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="C102" s="21" t="n"/>
+      <c r="D102" s="21" t="n"/>
+      <c r="E102" s="21" t="n"/>
+      <c r="F102" s="21" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr"/>
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C103" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E103" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F103" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H100" s="12" t="n">
+      <c r="H103" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I100" s="13" t="inlineStr">
+      <c r="I103" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="65">
+  <mergeCells count="67">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A90:I90"/>
@@ -5613,19 +5755,21 @@
     <mergeCell ref="B91:I91"/>
     <mergeCell ref="B63:I63"/>
     <mergeCell ref="B81:I81"/>
-    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="A89:I89"/>
     <mergeCell ref="A80:I80"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A55:I55"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A50:I50"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B102:I102"/>
     <mergeCell ref="A86:I86"/>
-    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="A57:I57"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B48:I48"/>
-    <mergeCell ref="A71:I71"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
@@ -5636,39 +5780,39 @@
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A100:I100"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="B88:I88"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="B78:I78"/>
+    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B87:I87"/>
+    <mergeCell ref="A93:I93"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="B99:I99"/>
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="A77:I77"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="A59:I59"/>
-    <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="A73:I73"/>
     <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B55:I55"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="A94:I94"/>
-    <mergeCell ref="A70:I70"/>
     <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="B94:I94"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A87:I87"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
@@ -5690,21 +5834,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5716,7 +5861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5892,24 +6037,65 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="154" customHeight="1">
+    <row r="8" ht="266" customHeight="1">
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
+          <t>Container With Most Water</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int maxArea(int[] height) {
+       int max = Integer.MIN_VALUE;
+       int left = 0;
+       int right = height.length -1;
+       while(left&lt;=right){
+        int length = Math.min(height[left],height[right]);
+        int breadth = right - left;
+        int area = length*breadth;
+        max = Math.max(area,max);
+         if(height[left]&lt;height[right]) {
+			 left++;
+		 }else {
+			 right--;
+		 }
+       }
+       return max;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="154" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C9" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int removeDuplicates(int[] nums) {
@@ -5925,24 +6111,24 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="210" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+    <row r="10" ht="210" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int lengthOfLastWord(String s) {
@@ -5962,24 +6148,24 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="560" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
+    <row r="11" ht="560" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -6018,24 +6204,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="406" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="406" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;111 - Minimum Depth of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/minimum-depth-of-binary-tree/"&gt;minimum-depth-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a binary tree, find its minimum depth.&lt;/p&gt;
 &lt;p&gt;The minimum depth is the number of nodes along the shortest path from the root node down to the nearest leaf node.&lt;/p&gt;
@@ -6062,24 +6248,24 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="532" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13" ht="532" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -6113,24 +6299,24 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="126" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14" ht="126" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -6144,24 +6330,24 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="238" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15" ht="238" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -6183,24 +6369,24 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="294" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="294" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -6226,24 +6412,24 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="238" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="17" ht="238" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -6265,24 +6451,24 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="238" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="238" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="7" t="n">
         <v>219</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -6304,24 +6490,24 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="392" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="392" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -6354,24 +6540,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="238" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="238" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -6392,24 +6578,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="420" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="420" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
@@ -6437,24 +6623,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="546" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="546" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -6498,24 +6684,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="196" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="196" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -6534,24 +6720,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="406" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="406" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -6584,24 +6770,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="378" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="378" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -6633,24 +6819,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="560" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="560" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -6686,24 +6872,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="294" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="294" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -6729,24 +6915,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="378" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="378" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -6778,24 +6964,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="238" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="238" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -6817,24 +7003,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="308" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="308" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -6861,24 +7047,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="280" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="280" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -6901,24 +7087,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="448" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="448" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -6953,24 +7139,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="378" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="378" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -7002,24 +7188,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="490" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="490" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7047,24 +7233,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="308" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="308" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -7090,24 +7276,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="238" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="238" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -7127,24 +7313,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="560" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="560" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -7185,24 +7371,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="294" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="294" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1001,7 +1001,7 @@
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
@@ -1017,17 +1017,17 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>46.7</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1043,17 +1043,17 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -1069,21 +1069,21 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>47.2</v>
@@ -1105,274 +1105,274 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7" t="n">
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H21" s="5" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr"/>
-      <c r="C21" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D21" s="9" t="n">
+      <c r="B22" s="8" t="inlineStr"/>
+      <c r="C22" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D22" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="G21" s="9" t="inlineStr"/>
-      <c r="H21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="E22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="7" t="n">
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="9" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr"/>
+      <c r="C24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7" t="n">
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H25" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7" t="n">
+      <c r="G27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="9" t="n">
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9" t="n">
+      <c r="D28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="7" t="n">
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -1381,17 +1381,17 @@
         <v>1</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -1410,234 +1410,260 @@
         <v>2</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="n">
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H33" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr"/>
-      <c r="C33" s="9" t="n">
+      <c r="B34" s="8" t="inlineStr"/>
+      <c r="C34" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9" t="n">
+      <c r="D34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="9" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7" t="n">
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="7" t="n">
+      <c r="C37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="9" t="n">
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="9" t="n">
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H39" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr"/>
-      <c r="C39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr"/>
-      <c r="C40" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="D40" s="11" t="n">
+      <c r="B41" s="10" t="inlineStr"/>
+      <c r="C41" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="E40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="G40" s="11" t="inlineStr"/>
-      <c r="H40" s="11" t="inlineStr"/>
+      <c r="E41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1653,7 +1679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3464,11 +3490,61 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1693</v>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Sum of All Odd Length Subarrays</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Math, Prefix Sum</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>46261.883125</v>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F38">
+  <conditionalFormatting sqref="F5:F39">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3514,6 +3590,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3525,7 +3602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3568,7 +3645,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   19 solved   (Low: 13 · Medium: 6 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   20 solved   (Low: 14 · Medium: 6 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4383,7 +4460,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -4414,11 +4491,11 @@
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>3347</v>
+        <v>1693</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
@@ -4426,10 +4503,10 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>46.7</v>
+        <v>42.8</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4437,7 +4514,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46261.883125</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -4448,7 +4525,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4479,11 +4556,11 @@
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
@@ -4491,10 +4568,10 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4502,7 +4579,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -4513,7 +4590,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -4544,11 +4621,11 @@
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
@@ -4556,10 +4633,10 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -4567,7 +4644,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -4578,7 +4655,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -4594,7 +4671,7 @@
       <c r="A51" s="21" t="n"/>
       <c r="B51" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C51" s="21" t="n"/>
@@ -4609,301 +4686,301 @@
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="18" t="n"/>
+      <c r="H53" s="18" t="n"/>
+      <c r="I53" s="18" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="21" t="n"/>
+      <c r="I54" s="21" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr"/>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C55" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="5" t="n">
+      <c r="E55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="n">
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I52" s="13" t="inlineStr">
+      <c r="I55" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr"/>
-      <c r="B53" s="6" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C56" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E56" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F56" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H53" s="14" t="n">
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I53" s="15" t="inlineStr">
+      <c r="I56" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-      <c r="G54" s="18" t="n"/>
-      <c r="H54" s="18" t="n"/>
-      <c r="I54" s="18" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="19" t="n"/>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="19" t="n"/>
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="19" t="n"/>
-      <c r="G55" s="19" t="n"/>
-      <c r="H55" s="19" t="n"/>
-      <c r="I55" s="19" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr"/>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="19" t="n"/>
+      <c r="G58" s="19" t="n"/>
+      <c r="H58" s="19" t="n"/>
+      <c r="I58" s="19" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C59" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n">
+      <c r="E59" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F59" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H56" s="12" t="n">
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I56" s="13" t="inlineStr">
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="n"/>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n"/>
-      <c r="E57" s="2" t="n"/>
-      <c r="F57" s="2" t="n"/>
-      <c r="G57" s="2" t="n"/>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B58" s="18" t="n"/>
-      <c r="C58" s="18" t="n"/>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="18" t="n"/>
-      <c r="I58" s="18" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="21" t="n"/>
-      <c r="B59" s="22" t="inlineStr">
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="18" t="n"/>
+      <c r="I61" s="18" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="n"/>
+      <c r="B62" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C59" s="21" t="n"/>
-      <c r="D59" s="21" t="n"/>
-      <c r="E59" s="21" t="n"/>
-      <c r="F59" s="21" t="n"/>
-      <c r="G59" s="21" t="n"/>
-      <c r="H59" s="21" t="n"/>
-      <c r="I59" s="21" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr"/>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="21" t="n"/>
+      <c r="E62" s="21" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="21" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C63" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="5" t="n">
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I60" s="13" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="18" t="n"/>
-      <c r="D62" s="18" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="18" t="n"/>
-      <c r="G62" s="18" t="n"/>
-      <c r="H62" s="18" t="n"/>
-      <c r="I62" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="21" t="n"/>
-      <c r="B63" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="n"/>
-      <c r="D63" s="21" t="n"/>
-      <c r="E63" s="21" t="n"/>
-      <c r="F63" s="21" t="n"/>
-      <c r="G63" s="21" t="n"/>
-      <c r="H63" s="21" t="n"/>
-      <c r="I63" s="21" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr"/>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -4934,11 +5011,11 @@
       <c r="A67" s="5" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
@@ -4946,18 +5023,18 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H67" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -4968,7 +5045,7 @@
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B68" s="18" t="n"/>
@@ -4999,171 +5076,171 @@
       <c r="A70" s="5" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C73" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="5" t="n">
+      <c r="E73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="n">
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I70" s="13" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="19" t="n"/>
-      <c r="B71" s="20" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="19" t="n"/>
+      <c r="B74" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C71" s="19" t="n"/>
-      <c r="D71" s="19" t="n"/>
-      <c r="E71" s="19" t="n"/>
-      <c r="F71" s="19" t="n"/>
-      <c r="G71" s="19" t="n"/>
-      <c r="H71" s="19" t="n"/>
-      <c r="I71" s="19" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="C74" s="19" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="19" t="n"/>
+      <c r="G74" s="19" t="n"/>
+      <c r="H74" s="19" t="n"/>
+      <c r="I74" s="19" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr"/>
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C75" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="5" t="n">
+      <c r="E75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H72" s="12" t="n">
+      <c r="H75" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I72" s="13" t="inlineStr">
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B74" s="18" t="n"/>
-      <c r="C74" s="18" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
-      <c r="G74" s="18" t="n"/>
-      <c r="H74" s="18" t="n"/>
-      <c r="I74" s="18" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="21" t="n"/>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C75" s="21" t="n"/>
-      <c r="D75" s="21" t="n"/>
-      <c r="E75" s="21" t="n"/>
-      <c r="F75" s="21" t="n"/>
-      <c r="G75" s="21" t="n"/>
-      <c r="H75" s="21" t="n"/>
-      <c r="I75" s="21" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr"/>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B77" s="18" t="n"/>
@@ -5176,40 +5253,40 @@
       <c r="I77" s="18" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="19" t="n"/>
-      <c r="B78" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C78" s="19" t="n"/>
-      <c r="D78" s="19" t="n"/>
-      <c r="E78" s="19" t="n"/>
-      <c r="F78" s="19" t="n"/>
-      <c r="G78" s="19" t="n"/>
-      <c r="H78" s="19" t="n"/>
-      <c r="I78" s="19" t="n"/>
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="21" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="21" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
@@ -5217,7 +5294,7 @@
         </is>
       </c>
       <c r="H79" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -5228,7 +5305,7 @@
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B80" s="18" t="n"/>
@@ -5241,40 +5318,40 @@
       <c r="I80" s="18" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="21" t="n"/>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C81" s="21" t="n"/>
-      <c r="D81" s="21" t="n"/>
-      <c r="E81" s="21" t="n"/>
-      <c r="F81" s="21" t="n"/>
-      <c r="G81" s="21" t="n"/>
-      <c r="H81" s="21" t="n"/>
-      <c r="I81" s="21" t="n"/>
+      <c r="A81" s="19" t="n"/>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C81" s="19" t="n"/>
+      <c r="D81" s="19" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="19" t="n"/>
+      <c r="G81" s="19" t="n"/>
+      <c r="H81" s="19" t="n"/>
+      <c r="I81" s="19" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
@@ -5282,7 +5359,7 @@
         </is>
       </c>
       <c r="H82" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -5293,7 +5370,7 @@
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B83" s="18" t="n"/>
@@ -5324,11 +5401,11 @@
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
@@ -5339,15 +5416,15 @@
         <v>2</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H85" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -5358,7 +5435,7 @@
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B86" s="18" t="n"/>
@@ -5389,121 +5466,121 @@
       <c r="A88" s="5" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="n"/>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+      <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="n"/>
+      <c r="I89" s="18" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="n"/>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C90" s="21" t="n"/>
+      <c r="D90" s="21" t="n"/>
+      <c r="E90" s="21" t="n"/>
+      <c r="F90" s="21" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="21" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr"/>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C91" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E91" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F91" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="n">
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I88" s="13" t="inlineStr">
+      <c r="I91" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="16" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="2" t="n"/>
-      <c r="G89" s="2" t="n"/>
-      <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B90" s="18" t="n"/>
-      <c r="C90" s="18" t="n"/>
-      <c r="D90" s="18" t="n"/>
-      <c r="E90" s="18" t="n"/>
-      <c r="F90" s="18" t="n"/>
-      <c r="G90" s="18" t="n"/>
-      <c r="H90" s="18" t="n"/>
-      <c r="I90" s="18" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="21" t="n"/>
-      <c r="B91" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C91" s="21" t="n"/>
-      <c r="D91" s="21" t="n"/>
-      <c r="E91" s="21" t="n"/>
-      <c r="F91" s="21" t="n"/>
-      <c r="G91" s="21" t="n"/>
-      <c r="H91" s="21" t="n"/>
-      <c r="I91" s="21" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr"/>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
+      <c r="I92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B93" s="18" t="n"/>
@@ -5519,7 +5596,7 @@
       <c r="A94" s="21" t="n"/>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C94" s="21" t="n"/>
@@ -5534,262 +5611,327 @@
       <c r="A95" s="5" t="inlineStr"/>
       <c r="B95" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="n"/>
+      <c r="C96" s="18" t="n"/>
+      <c r="D96" s="18" t="n"/>
+      <c r="E96" s="18" t="n"/>
+      <c r="F96" s="18" t="n"/>
+      <c r="G96" s="18" t="n"/>
+      <c r="H96" s="18" t="n"/>
+      <c r="I96" s="18" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="n"/>
+      <c r="B97" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="n"/>
+      <c r="D97" s="21" t="n"/>
+      <c r="E97" s="21" t="n"/>
+      <c r="F97" s="21" t="n"/>
+      <c r="G97" s="21" t="n"/>
+      <c r="H97" s="21" t="n"/>
+      <c r="I97" s="21" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr"/>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C98" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E98" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F95" s="5" t="n">
+      <c r="F98" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H95" s="12" t="n">
+      <c r="H98" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I95" s="13" t="inlineStr">
+      <c r="I98" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr"/>
-      <c r="B96" s="6" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="7" t="inlineStr"/>
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C96" s="7" t="n">
+      <c r="C99" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D96" s="7" t="inlineStr">
+      <c r="D99" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E96" s="7" t="n">
+      <c r="E99" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="7" t="n">
+      <c r="F99" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H96" s="14" t="n">
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I96" s="15" t="inlineStr">
+      <c r="I99" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="17" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="n"/>
-      <c r="B98" s="22" t="inlineStr">
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="18" t="n"/>
+      <c r="D100" s="18" t="n"/>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+      <c r="G100" s="18" t="n"/>
+      <c r="H100" s="18" t="n"/>
+      <c r="I100" s="18" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="n"/>
+      <c r="B101" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C98" s="21" t="n"/>
-      <c r="D98" s="21" t="n"/>
-      <c r="E98" s="21" t="n"/>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr"/>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="C101" s="21" t="n"/>
+      <c r="D101" s="21" t="n"/>
+      <c r="E101" s="21" t="n"/>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr"/>
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C102" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="5" t="n">
+      <c r="E102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="H102" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I99" s="13" t="inlineStr">
+      <c r="I102" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="16" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B100" s="2" t="n"/>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="21" t="n"/>
-      <c r="B102" s="22" t="inlineStr">
+      <c r="B104" s="18" t="n"/>
+      <c r="C104" s="18" t="n"/>
+      <c r="D104" s="18" t="n"/>
+      <c r="E104" s="18" t="n"/>
+      <c r="F104" s="18" t="n"/>
+      <c r="G104" s="18" t="n"/>
+      <c r="H104" s="18" t="n"/>
+      <c r="I104" s="18" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C102" s="21" t="n"/>
-      <c r="D102" s="21" t="n"/>
-      <c r="E102" s="21" t="n"/>
-      <c r="F102" s="21" t="n"/>
-      <c r="G102" s="21" t="n"/>
-      <c r="H102" s="21" t="n"/>
-      <c r="I102" s="21" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr"/>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="C105" s="21" t="n"/>
+      <c r="D105" s="21" t="n"/>
+      <c r="E105" s="21" t="n"/>
+      <c r="F105" s="21" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr"/>
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C106" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E106" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F103" s="5" t="n">
+      <c r="F106" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H103" s="12" t="n">
+      <c r="H106" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="69">
+    <mergeCell ref="B97:I97"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="A54:I54"/>
-    <mergeCell ref="B75:I75"/>
-    <mergeCell ref="B91:I91"/>
-    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="B81:I81"/>
     <mergeCell ref="A89:I89"/>
+    <mergeCell ref="B72:I72"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="B66:I66"/>
-    <mergeCell ref="A74:I74"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B71:I71"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A101:I101"/>
-    <mergeCell ref="B102:I102"/>
     <mergeCell ref="A86:I86"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="A104:I104"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B48:I48"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="B105:I105"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A76:I76"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="B98:I98"/>
-    <mergeCell ref="A97:I97"/>
+    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A100:I100"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="A96:I96"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
+    <mergeCell ref="B101:I101"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="B78:I78"/>
     <mergeCell ref="B69:I69"/>
@@ -5797,18 +5939,20 @@
     <mergeCell ref="A93:I93"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A58:I58"/>
     <mergeCell ref="A77:I77"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="B84:I84"/>
+    <mergeCell ref="A92:I92"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="B74:I74"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A73:I73"/>
     <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="A103:I103"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B51:I51"/>
+    <mergeCell ref="A60:I60"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A61:I61"/>
     <mergeCell ref="B94:I94"/>
@@ -5833,23 +5977,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5861,7 +6006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6964,24 +7109,71 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="238" customHeight="1">
+    <row r="29" ht="350" customHeight="1">
       <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Sum of All Odd Length Subarrays</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1693</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static boolean isOdd(int num){
+        if((num &amp; 1) == 1){
+            return true;
+        }else{
+            return false;
+        }
+    }
+    public int sumOddLengthSubarrays(int[] arr) {
+        int sum = 0;
+    for(int i = 1;i&lt;arr.length;i++){
+        arr[i] += arr[i - 1];
+    } 
+    for(int start = 0;start&lt;arr.length;start++){
+        for(int end = start;end&lt;arr.length;end++){
+            int length = end - start +1;
+            if(isOdd(length)){
+               if(start == 0) sum+=arr[end];
+               else sum+=arr[end] - arr[start - 1];
+            }
+        }
+    } 
+    return sum;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="238" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -7003,24 +7195,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="308" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="308" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -7047,24 +7239,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="280" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="280" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -7087,24 +7279,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="448" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="448" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -7139,24 +7331,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="378" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="378" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -7188,24 +7380,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="490" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="490" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7233,24 +7425,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="308" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="308" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -7276,24 +7468,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="238" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="238" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -7313,24 +7505,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="560" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="560" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -7371,24 +7563,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="294" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="294" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1027,14 +1027,14 @@
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -1043,17 +1043,17 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -1069,17 +1069,17 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -1095,21 +1095,21 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="7" t="n">
         <v>0</v>
@@ -1118,10 +1118,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="7" t="n">
         <v>47.2</v>
@@ -1131,274 +1131,274 @@
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="5" t="n">
+      <c r="C22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H22" s="7" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr"/>
-      <c r="C22" s="9" t="n">
+      <c r="B23" s="8" t="inlineStr"/>
+      <c r="C23" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="D23" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5" t="n">
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="9" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5" t="n">
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H26" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
+      <c r="C28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="n">
+      <c r="G28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr"/>
-      <c r="C28" s="9" t="n">
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="9" t="n">
+      <c r="D29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="5" t="n">
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>0</v>
@@ -1407,17 +1407,17 @@
         <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
@@ -1436,234 +1436,260 @@
         <v>2</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="n">
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H34" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr"/>
-      <c r="C34" s="9" t="n">
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="9" t="n">
+      <c r="D35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="5" t="n">
+      <c r="C36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr"/>
-      <c r="C38" s="9" t="n">
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="9" t="n">
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
+      <c r="C40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H40" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr"/>
-      <c r="C41" s="11" t="n">
+      <c r="B42" s="10" t="inlineStr"/>
+      <c r="C42" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="D41" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="G41" s="11" t="inlineStr"/>
-      <c r="H41" s="11" t="inlineStr"/>
+      <c r="D42" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="G42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1679,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3540,11 +3566,61 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>1206</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Corporate Flight Bookings</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Prefix Sum</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>85</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="14" t="n">
+        <v>46262.6837962963</v>
+      </c>
+      <c r="L40" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F39">
+  <conditionalFormatting sqref="F5:F40">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3591,6 +3667,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3602,7 +3679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3645,7 +3722,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   20 solved   (Low: 14 · Medium: 6 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   21 solved   (Low: 14 · Medium: 7 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4525,7 +4602,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4538,40 +4615,40 @@
       <c r="I44" s="18" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="n"/>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
+      <c r="A45" s="19" t="n"/>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="19" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4579,7 +4656,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -4590,7 +4667,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -4621,11 +4698,11 @@
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
@@ -4633,10 +4710,10 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -4644,7 +4721,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -4655,7 +4732,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -4686,11 +4763,11 @@
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
@@ -4698,10 +4775,10 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -4709,7 +4786,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -4720,7 +4797,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -4736,7 +4813,7 @@
       <c r="A54" s="21" t="n"/>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C54" s="21" t="n"/>
@@ -4751,301 +4828,301 @@
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="18" t="n"/>
+      <c r="I56" s="18" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="21" t="n"/>
+      <c r="I57" s="21" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr"/>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C58" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="5" t="n">
+      <c r="E58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="n">
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I55" s="13" t="inlineStr">
+      <c r="I58" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr"/>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C59" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E56" s="7" t="n">
+      <c r="E59" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="7" t="n">
+      <c r="F59" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="n">
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I56" s="15" t="inlineStr">
+      <c r="I59" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B57" s="18" t="n"/>
-      <c r="C57" s="18" t="n"/>
-      <c r="D57" s="18" t="n"/>
-      <c r="E57" s="18" t="n"/>
-      <c r="F57" s="18" t="n"/>
-      <c r="G57" s="18" t="n"/>
-      <c r="H57" s="18" t="n"/>
-      <c r="I57" s="18" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="19" t="n"/>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
-      <c r="F58" s="19" t="n"/>
-      <c r="G58" s="19" t="n"/>
-      <c r="H58" s="19" t="n"/>
-      <c r="I58" s="19" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr"/>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+      <c r="G61" s="19" t="n"/>
+      <c r="H61" s="19" t="n"/>
+      <c r="I61" s="19" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr"/>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C62" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
+      <c r="E62" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F62" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H59" s="12" t="n">
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I59" s="13" t="inlineStr">
+      <c r="I62" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B61" s="18" t="n"/>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="18" t="n"/>
-      <c r="I61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="21" t="n"/>
-      <c r="B62" s="22" t="inlineStr">
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="18" t="n"/>
+      <c r="I64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="n"/>
+      <c r="B65" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C62" s="21" t="n"/>
-      <c r="D62" s="21" t="n"/>
-      <c r="E62" s="21" t="n"/>
-      <c r="F62" s="21" t="n"/>
-      <c r="G62" s="21" t="n"/>
-      <c r="H62" s="21" t="n"/>
-      <c r="I62" s="21" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="21" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C66" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="H66" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I63" s="13" t="inlineStr">
+      <c r="I66" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-      <c r="G65" s="18" t="n"/>
-      <c r="H65" s="18" t="n"/>
-      <c r="I65" s="18" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="21" t="n"/>
-      <c r="B66" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="21" t="n"/>
-      <c r="I66" s="21" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr"/>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n"/>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B68" s="18" t="n"/>
@@ -5076,11 +5153,11 @@
       <c r="A70" s="5" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
@@ -5088,18 +5165,18 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H70" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -5110,7 +5187,7 @@
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B71" s="18" t="n"/>
@@ -5141,171 +5218,171 @@
       <c r="A73" s="5" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="n"/>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="n"/>
+      <c r="D75" s="21" t="n"/>
+      <c r="E75" s="21" t="n"/>
+      <c r="F75" s="21" t="n"/>
+      <c r="G75" s="21" t="n"/>
+      <c r="H75" s="21" t="n"/>
+      <c r="I75" s="21" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr"/>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C76" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="5" t="n">
+      <c r="E76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="n">
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I73" s="13" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="19" t="n"/>
-      <c r="B74" s="20" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="19" t="n"/>
+      <c r="B77" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C74" s="19" t="n"/>
-      <c r="D74" s="19" t="n"/>
-      <c r="E74" s="19" t="n"/>
-      <c r="F74" s="19" t="n"/>
-      <c r="G74" s="19" t="n"/>
-      <c r="H74" s="19" t="n"/>
-      <c r="I74" s="19" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr"/>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="C77" s="19" t="n"/>
+      <c r="D77" s="19" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="19" t="n"/>
+      <c r="G77" s="19" t="n"/>
+      <c r="H77" s="19" t="n"/>
+      <c r="I77" s="19" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr"/>
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="5" t="n">
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H75" s="12" t="n">
+      <c r="H78" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I75" s="13" t="inlineStr">
+      <c r="I78" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="n"/>
-      <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B77" s="18" t="n"/>
-      <c r="C77" s="18" t="n"/>
-      <c r="D77" s="18" t="n"/>
-      <c r="E77" s="18" t="n"/>
-      <c r="F77" s="18" t="n"/>
-      <c r="G77" s="18" t="n"/>
-      <c r="H77" s="18" t="n"/>
-      <c r="I77" s="18" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="21" t="n"/>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="n"/>
-      <c r="D78" s="21" t="n"/>
-      <c r="E78" s="21" t="n"/>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="21" t="n"/>
-      <c r="H78" s="21" t="n"/>
-      <c r="I78" s="21" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr"/>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B80" s="18" t="n"/>
@@ -5318,40 +5395,40 @@
       <c r="I80" s="18" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="19" t="n"/>
-      <c r="B81" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C81" s="19" t="n"/>
-      <c r="D81" s="19" t="n"/>
-      <c r="E81" s="19" t="n"/>
-      <c r="F81" s="19" t="n"/>
-      <c r="G81" s="19" t="n"/>
-      <c r="H81" s="19" t="n"/>
-      <c r="I81" s="19" t="n"/>
+      <c r="A81" s="21" t="n"/>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="21" t="n"/>
+      <c r="E81" s="21" t="n"/>
+      <c r="F81" s="21" t="n"/>
+      <c r="G81" s="21" t="n"/>
+      <c r="H81" s="21" t="n"/>
+      <c r="I81" s="21" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
@@ -5359,7 +5436,7 @@
         </is>
       </c>
       <c r="H82" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -5370,7 +5447,7 @@
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B83" s="18" t="n"/>
@@ -5383,40 +5460,40 @@
       <c r="I83" s="18" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="21" t="n"/>
-      <c r="B84" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="n"/>
-      <c r="D84" s="21" t="n"/>
-      <c r="E84" s="21" t="n"/>
-      <c r="F84" s="21" t="n"/>
-      <c r="G84" s="21" t="n"/>
-      <c r="H84" s="21" t="n"/>
-      <c r="I84" s="21" t="n"/>
+      <c r="A84" s="19" t="n"/>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="n"/>
+      <c r="D84" s="19" t="n"/>
+      <c r="E84" s="19" t="n"/>
+      <c r="F84" s="19" t="n"/>
+      <c r="G84" s="19" t="n"/>
+      <c r="H84" s="19" t="n"/>
+      <c r="I84" s="19" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
@@ -5424,7 +5501,7 @@
         </is>
       </c>
       <c r="H85" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -5435,7 +5512,7 @@
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B86" s="18" t="n"/>
@@ -5466,11 +5543,11 @@
       <c r="A88" s="5" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
@@ -5481,15 +5558,15 @@
         <v>2</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H88" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -5500,7 +5577,7 @@
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B89" s="18" t="n"/>
@@ -5531,121 +5608,121 @@
       <c r="A91" s="5" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="n"/>
+      <c r="D92" s="18" t="n"/>
+      <c r="E92" s="18" t="n"/>
+      <c r="F92" s="18" t="n"/>
+      <c r="G92" s="18" t="n"/>
+      <c r="H92" s="18" t="n"/>
+      <c r="I92" s="18" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="n"/>
+      <c r="B93" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="n"/>
+      <c r="D93" s="21" t="n"/>
+      <c r="E93" s="21" t="n"/>
+      <c r="F93" s="21" t="n"/>
+      <c r="G93" s="21" t="n"/>
+      <c r="H93" s="21" t="n"/>
+      <c r="I93" s="21" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr"/>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C94" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="E94" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F94" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H91" s="12" t="n">
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I91" s="13" t="inlineStr">
+      <c r="I94" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="16" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B93" s="18" t="n"/>
-      <c r="C93" s="18" t="n"/>
-      <c r="D93" s="18" t="n"/>
-      <c r="E93" s="18" t="n"/>
-      <c r="F93" s="18" t="n"/>
-      <c r="G93" s="18" t="n"/>
-      <c r="H93" s="18" t="n"/>
-      <c r="I93" s="18" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="21" t="n"/>
-      <c r="B94" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C94" s="21" t="n"/>
-      <c r="D94" s="21" t="n"/>
-      <c r="E94" s="21" t="n"/>
-      <c r="F94" s="21" t="n"/>
-      <c r="G94" s="21" t="n"/>
-      <c r="H94" s="21" t="n"/>
-      <c r="I94" s="21" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H95" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="2" t="n"/>
+      <c r="G95" s="2" t="n"/>
+      <c r="H95" s="2" t="n"/>
+      <c r="I95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B96" s="18" t="n"/>
@@ -5661,7 +5738,7 @@
       <c r="A97" s="21" t="n"/>
       <c r="B97" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C97" s="21" t="n"/>
@@ -5676,286 +5753,353 @@
       <c r="A98" s="5" t="inlineStr"/>
       <c r="B98" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B99" s="18" t="n"/>
+      <c r="C99" s="18" t="n"/>
+      <c r="D99" s="18" t="n"/>
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="18" t="n"/>
+      <c r="G99" s="18" t="n"/>
+      <c r="H99" s="18" t="n"/>
+      <c r="I99" s="18" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="n"/>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C100" s="21" t="n"/>
+      <c r="D100" s="21" t="n"/>
+      <c r="E100" s="21" t="n"/>
+      <c r="F100" s="21" t="n"/>
+      <c r="G100" s="21" t="n"/>
+      <c r="H100" s="21" t="n"/>
+      <c r="I100" s="21" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr"/>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C101" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E98" s="5" t="n">
+      <c r="E101" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F98" s="5" t="n">
+      <c r="F101" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H98" s="12" t="n">
+      <c r="H101" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I98" s="13" t="inlineStr">
+      <c r="I101" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="7" t="inlineStr"/>
-      <c r="B99" s="6" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="7" t="inlineStr"/>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C99" s="7" t="n">
+      <c r="C102" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E99" s="7" t="n">
+      <c r="E102" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F99" s="7" t="n">
+      <c r="F102" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H99" s="14" t="n">
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H102" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I99" s="15" t="inlineStr">
+      <c r="I102" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="17" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B100" s="18" t="n"/>
-      <c r="C100" s="18" t="n"/>
-      <c r="D100" s="18" t="n"/>
-      <c r="E100" s="18" t="n"/>
-      <c r="F100" s="18" t="n"/>
-      <c r="G100" s="18" t="n"/>
-      <c r="H100" s="18" t="n"/>
-      <c r="I100" s="18" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="21" t="n"/>
-      <c r="B101" s="22" t="inlineStr">
+      <c r="B103" s="18" t="n"/>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="n"/>
+      <c r="B104" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C101" s="21" t="n"/>
-      <c r="D101" s="21" t="n"/>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr"/>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="C104" s="21" t="n"/>
+      <c r="D104" s="21" t="n"/>
+      <c r="E104" s="21" t="n"/>
+      <c r="F104" s="21" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="21" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr"/>
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C105" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D105" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="5" t="n">
+      <c r="E105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G105" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H102" s="12" t="n">
+      <c r="H105" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I102" s="13" t="inlineStr">
+      <c r="I105" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="16" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="17" t="inlineStr">
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B104" s="18" t="n"/>
-      <c r="C104" s="18" t="n"/>
-      <c r="D104" s="18" t="n"/>
-      <c r="E104" s="18" t="n"/>
-      <c r="F104" s="18" t="n"/>
-      <c r="G104" s="18" t="n"/>
-      <c r="H104" s="18" t="n"/>
-      <c r="I104" s="18" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="n"/>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="18" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="18" t="n"/>
+      <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="n"/>
+      <c r="I107" s="18" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="n"/>
+      <c r="B108" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C105" s="21" t="n"/>
-      <c r="D105" s="21" t="n"/>
-      <c r="E105" s="21" t="n"/>
-      <c r="F105" s="21" t="n"/>
-      <c r="G105" s="21" t="n"/>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="C108" s="21" t="n"/>
+      <c r="D108" s="21" t="n"/>
+      <c r="E108" s="21" t="n"/>
+      <c r="F108" s="21" t="n"/>
+      <c r="G108" s="21" t="n"/>
+      <c r="H108" s="21" t="n"/>
+      <c r="I108" s="21" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr"/>
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C109" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E106" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F106" s="5" t="n">
+      <c r="F109" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G106" s="5" t="inlineStr">
+      <c r="G109" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H106" s="12" t="n">
+      <c r="H109" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I106" s="13" t="inlineStr">
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="71">
     <mergeCell ref="B97:I97"/>
-    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="A99:I99"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="B81:I81"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="B90:I90"/>
-    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="A74:I74"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="B93:I93"/>
     <mergeCell ref="A86:I86"/>
-    <mergeCell ref="B58:I58"/>
-    <mergeCell ref="A104:I104"/>
-    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A95:I95"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="A71:I71"/>
-    <mergeCell ref="B105:I105"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
+    <mergeCell ref="A106:I106"/>
     <mergeCell ref="A53:I53"/>
+    <mergeCell ref="B61:I61"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="B57:I57"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A96:I96"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="B101:I101"/>
     <mergeCell ref="A68:I68"/>
-    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="A63:I63"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="B87:I87"/>
-    <mergeCell ref="A93:I93"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="B108:I108"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="B84:I84"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="A64:I64"/>
-    <mergeCell ref="B74:I74"/>
     <mergeCell ref="B30:I30"/>
+    <mergeCell ref="A107:I107"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="A103:I103"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="A60:I60"/>
+    <mergeCell ref="B104:I104"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="A61:I61"/>
-    <mergeCell ref="B94:I94"/>
+    <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
@@ -5978,23 +6122,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6006,7 +6151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7060,24 +7205,62 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="378" customHeight="1">
+    <row r="28" ht="224" customHeight="1">
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
+          <t>Corporate Flight Bookings</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] corpFlightBookings(int[][] bookings, int n) {
+        int[] arr = new int[n];
+    for(int[] booking:bookings){
+        int start = booking[0];
+        int end = booking[1];
+        int value= booking[2];
+        arr[--start] += value;
+        if(end&lt;n) arr[end]-=value;
+    }   
+    for(int i=1;i&lt;n;i++){
+        arr[i]+=arr[i-1];
+    }  
+    return arr;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="378" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -7109,24 +7292,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="350" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="350" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -7156,24 +7339,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="238" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="238" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -7195,24 +7378,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="308" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="308" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -7239,24 +7422,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="280" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="280" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -7279,24 +7462,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="448" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="448" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -7331,24 +7514,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="378" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="378" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -7380,24 +7563,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="490" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="490" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7425,24 +7608,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="308" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="308" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -7468,24 +7651,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="238" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="238" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -7505,24 +7688,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="560" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="560" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -7563,24 +7746,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="294" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="294" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1027,7 +1027,7 @@
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1043,24 +1043,24 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1069,17 +1069,17 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -1095,17 +1095,17 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
@@ -1121,21 +1121,21 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>47.2</v>
@@ -1157,274 +1157,274 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7" t="n">
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H23" s="5" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr"/>
-      <c r="C23" s="9" t="n">
+      <c r="B24" s="8" t="inlineStr"/>
+      <c r="C24" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="D23" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="9" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="D24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7" t="n">
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="n">
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H27" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="7" t="n">
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="9" t="n">
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9" t="n">
+      <c r="D30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="7" t="n">
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>0</v>
@@ -1433,17 +1433,17 @@
         <v>1</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -1462,234 +1462,260 @@
         <v>2</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="n">
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H35" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="9" t="n">
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="9" t="n">
+      <c r="D36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="7" t="n">
+      <c r="C37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr"/>
-      <c r="C39" s="9" t="n">
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="9" t="n">
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H41" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr"/>
-      <c r="C42" s="11" t="n">
+      <c r="B43" s="10" t="inlineStr"/>
+      <c r="C43" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="D42" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="G42" s="11" t="inlineStr"/>
-      <c r="H42" s="11" t="inlineStr"/>
+      <c r="D43" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1705,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3616,11 +3642,61 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Matrix Block Sum</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Matrix, Prefix Sum</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>46262.8983912037</v>
+      </c>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F40">
+  <conditionalFormatting sqref="F5:F41">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3668,6 +3744,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3679,7 +3756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I109"/>
+  <dimension ref="A1:I112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3722,7 +3799,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   21 solved   (Low: 14 · Medium: 7 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   22 solved   (Low: 14 · Medium: 8 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4602,7 +4679,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4633,11 +4710,11 @@
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Corporate Flight Bookings</t>
+          <t>Matrix Block Sum</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
@@ -4645,10 +4722,10 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4656,7 +4733,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46262.6837962963</v>
+        <v>46262.8983912037</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -4667,7 +4744,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -4680,40 +4757,40 @@
       <c r="I47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="n"/>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
+      <c r="A48" s="19" t="n"/>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="19" t="n"/>
+      <c r="H48" s="19" t="n"/>
+      <c r="I48" s="19" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -4721,7 +4798,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -4732,7 +4809,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -4763,11 +4840,11 @@
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
@@ -4775,10 +4852,10 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -4786,7 +4863,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -4797,7 +4874,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -4828,11 +4905,11 @@
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
@@ -4840,10 +4917,10 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -4851,7 +4928,7 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -4862,7 +4939,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -4878,7 +4955,7 @@
       <c r="A57" s="21" t="n"/>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C57" s="21" t="n"/>
@@ -4893,301 +4970,301 @@
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="18" t="n"/>
+      <c r="I59" s="18" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr"/>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C61" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="5" t="n">
+      <c r="E61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="n">
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I58" s="13" t="inlineStr">
+      <c r="I61" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr"/>
-      <c r="B59" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C62" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n">
+      <c r="E62" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F59" s="7" t="n">
+      <c r="F62" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H59" s="14" t="n">
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I59" s="15" t="inlineStr">
+      <c r="I62" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B60" s="18" t="n"/>
-      <c r="C60" s="18" t="n"/>
-      <c r="D60" s="18" t="n"/>
-      <c r="E60" s="18" t="n"/>
-      <c r="F60" s="18" t="n"/>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="18" t="n"/>
-      <c r="I60" s="18" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="19" t="n"/>
-      <c r="B61" s="20" t="inlineStr">
+      <c r="B63" s="18" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="n"/>
+      <c r="I63" s="18" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr"/>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="19" t="n"/>
+      <c r="I64" s="19" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C65" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
+      <c r="E65" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="F65" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H62" s="12" t="n">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I62" s="13" t="inlineStr">
+      <c r="I65" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="18" t="n"/>
-      <c r="I64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="22" t="inlineStr">
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="18" t="n"/>
+      <c r="I67" s="18" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="n"/>
+      <c r="B68" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
-      <c r="G65" s="21" t="n"/>
-      <c r="H65" s="21" t="n"/>
-      <c r="I65" s="21" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr"/>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="21" t="n"/>
+      <c r="E68" s="21" t="n"/>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="21" t="n"/>
+      <c r="H68" s="21" t="n"/>
+      <c r="I68" s="21" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr"/>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C69" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="5" t="n">
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H66" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I66" s="13" t="inlineStr">
+      <c r="I69" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B68" s="18" t="n"/>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="18" t="n"/>
-      <c r="I68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="21" t="n"/>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr"/>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="n"/>
+      <c r="I70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B71" s="18" t="n"/>
@@ -5218,11 +5295,11 @@
       <c r="A73" s="5" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
@@ -5230,18 +5307,18 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H73" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -5252,7 +5329,7 @@
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B74" s="18" t="n"/>
@@ -5283,171 +5360,171 @@
       <c r="A76" s="5" t="inlineStr"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="21" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="21" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr"/>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C79" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E76" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="5" t="n">
+      <c r="E79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="n">
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I76" s="13" t="inlineStr">
+      <c r="I79" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="19" t="n"/>
-      <c r="B77" s="20" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="19" t="n"/>
+      <c r="B80" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C77" s="19" t="n"/>
-      <c r="D77" s="19" t="n"/>
-      <c r="E77" s="19" t="n"/>
-      <c r="F77" s="19" t="n"/>
-      <c r="G77" s="19" t="n"/>
-      <c r="H77" s="19" t="n"/>
-      <c r="I77" s="19" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="C80" s="19" t="n"/>
+      <c r="D80" s="19" t="n"/>
+      <c r="E80" s="19" t="n"/>
+      <c r="F80" s="19" t="n"/>
+      <c r="G80" s="19" t="n"/>
+      <c r="H80" s="19" t="n"/>
+      <c r="I80" s="19" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr"/>
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C81" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5" t="n">
+      <c r="E81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I78" s="13" t="inlineStr">
+      <c r="I81" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B80" s="18" t="n"/>
-      <c r="C80" s="18" t="n"/>
-      <c r="D80" s="18" t="n"/>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
-      <c r="G80" s="18" t="n"/>
-      <c r="H80" s="18" t="n"/>
-      <c r="I80" s="18" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="21" t="n"/>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C81" s="21" t="n"/>
-      <c r="D81" s="21" t="n"/>
-      <c r="E81" s="21" t="n"/>
-      <c r="F81" s="21" t="n"/>
-      <c r="G81" s="21" t="n"/>
-      <c r="H81" s="21" t="n"/>
-      <c r="I81" s="21" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr"/>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B83" s="18" t="n"/>
@@ -5460,40 +5537,40 @@
       <c r="I83" s="18" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="19" t="n"/>
-      <c r="B84" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C84" s="19" t="n"/>
-      <c r="D84" s="19" t="n"/>
-      <c r="E84" s="19" t="n"/>
-      <c r="F84" s="19" t="n"/>
-      <c r="G84" s="19" t="n"/>
-      <c r="H84" s="19" t="n"/>
-      <c r="I84" s="19" t="n"/>
+      <c r="A84" s="21" t="n"/>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="n"/>
+      <c r="D84" s="21" t="n"/>
+      <c r="E84" s="21" t="n"/>
+      <c r="F84" s="21" t="n"/>
+      <c r="G84" s="21" t="n"/>
+      <c r="H84" s="21" t="n"/>
+      <c r="I84" s="21" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
@@ -5501,7 +5578,7 @@
         </is>
       </c>
       <c r="H85" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -5512,7 +5589,7 @@
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B86" s="18" t="n"/>
@@ -5525,40 +5602,40 @@
       <c r="I86" s="18" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="21" t="n"/>
-      <c r="B87" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C87" s="21" t="n"/>
-      <c r="D87" s="21" t="n"/>
-      <c r="E87" s="21" t="n"/>
-      <c r="F87" s="21" t="n"/>
-      <c r="G87" s="21" t="n"/>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="21" t="n"/>
+      <c r="A87" s="19" t="n"/>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C87" s="19" t="n"/>
+      <c r="D87" s="19" t="n"/>
+      <c r="E87" s="19" t="n"/>
+      <c r="F87" s="19" t="n"/>
+      <c r="G87" s="19" t="n"/>
+      <c r="H87" s="19" t="n"/>
+      <c r="I87" s="19" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
@@ -5566,7 +5643,7 @@
         </is>
       </c>
       <c r="H88" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -5577,7 +5654,7 @@
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B89" s="18" t="n"/>
@@ -5608,11 +5685,11 @@
       <c r="A91" s="5" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
@@ -5623,15 +5700,15 @@
         <v>2</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H91" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -5642,7 +5719,7 @@
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B92" s="18" t="n"/>
@@ -5673,121 +5750,121 @@
       <c r="A94" s="5" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="n"/>
+      <c r="C95" s="18" t="n"/>
+      <c r="D95" s="18" t="n"/>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="18" t="n"/>
+      <c r="G95" s="18" t="n"/>
+      <c r="H95" s="18" t="n"/>
+      <c r="I95" s="18" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="n"/>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="21" t="n"/>
+      <c r="E96" s="21" t="n"/>
+      <c r="F96" s="21" t="n"/>
+      <c r="G96" s="21" t="n"/>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="21" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr"/>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C97" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D94" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E94" s="5" t="n">
+      <c r="E97" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F94" s="5" t="n">
+      <c r="F97" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H94" s="12" t="n">
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I94" s="13" t="inlineStr">
+      <c r="I97" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="16" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n"/>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="n"/>
-      <c r="G95" s="2" t="n"/>
-      <c r="H95" s="2" t="n"/>
-      <c r="I95" s="2" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B96" s="18" t="n"/>
-      <c r="C96" s="18" t="n"/>
-      <c r="D96" s="18" t="n"/>
-      <c r="E96" s="18" t="n"/>
-      <c r="F96" s="18" t="n"/>
-      <c r="G96" s="18" t="n"/>
-      <c r="H96" s="18" t="n"/>
-      <c r="I96" s="18" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="21" t="n"/>
-      <c r="B97" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C97" s="21" t="n"/>
-      <c r="D97" s="21" t="n"/>
-      <c r="E97" s="21" t="n"/>
-      <c r="F97" s="21" t="n"/>
-      <c r="G97" s="21" t="n"/>
-      <c r="H97" s="21" t="n"/>
-      <c r="I97" s="21" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr"/>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B99" s="18" t="n"/>
@@ -5803,7 +5880,7 @@
       <c r="A100" s="21" t="n"/>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C100" s="21" t="n"/>
@@ -5818,237 +5895,301 @@
       <c r="A101" s="5" t="inlineStr"/>
       <c r="B101" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="n"/>
+      <c r="C102" s="18" t="n"/>
+      <c r="D102" s="18" t="n"/>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="n"/>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C103" s="21" t="n"/>
+      <c r="D103" s="21" t="n"/>
+      <c r="E103" s="21" t="n"/>
+      <c r="F103" s="21" t="n"/>
+      <c r="G103" s="21" t="n"/>
+      <c r="H103" s="21" t="n"/>
+      <c r="I103" s="21" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr"/>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C104" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D104" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n">
+      <c r="E104" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F101" s="5" t="n">
+      <c r="F104" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G104" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H101" s="12" t="n">
+      <c r="H104" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I101" s="13" t="inlineStr">
+      <c r="I104" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="7" t="inlineStr"/>
-      <c r="B102" s="6" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="7" t="inlineStr"/>
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C102" s="7" t="n">
+      <c r="C105" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E102" s="7" t="n">
+      <c r="E105" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F102" s="7" t="n">
+      <c r="F105" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H102" s="14" t="n">
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I102" s="15" t="inlineStr">
+      <c r="I105" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="17" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B103" s="18" t="n"/>
-      <c r="C103" s="18" t="n"/>
-      <c r="D103" s="18" t="n"/>
-      <c r="E103" s="18" t="n"/>
-      <c r="F103" s="18" t="n"/>
-      <c r="G103" s="18" t="n"/>
-      <c r="H103" s="18" t="n"/>
-      <c r="I103" s="18" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="n"/>
-      <c r="B104" s="22" t="inlineStr">
+      <c r="B106" s="18" t="n"/>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="n"/>
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C104" s="21" t="n"/>
-      <c r="D104" s="21" t="n"/>
-      <c r="E104" s="21" t="n"/>
-      <c r="F104" s="21" t="n"/>
-      <c r="G104" s="21" t="n"/>
-      <c r="H104" s="21" t="n"/>
-      <c r="I104" s="21" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr"/>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="C107" s="21" t="n"/>
+      <c r="D107" s="21" t="n"/>
+      <c r="E107" s="21" t="n"/>
+      <c r="F107" s="21" t="n"/>
+      <c r="G107" s="21" t="n"/>
+      <c r="H107" s="21" t="n"/>
+      <c r="I107" s="21" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr"/>
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C108" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E105" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="5" t="n">
+      <c r="E108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="G108" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H105" s="12" t="n">
+      <c r="H108" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I105" s="13" t="inlineStr">
+      <c r="I108" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="16" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n"/>
-      <c r="I106" s="2" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="17" t="inlineStr">
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="n"/>
+      <c r="G109" s="2" t="n"/>
+      <c r="H109" s="2" t="n"/>
+      <c r="I109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B107" s="18" t="n"/>
-      <c r="C107" s="18" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="21" t="n"/>
-      <c r="B108" s="22" t="inlineStr">
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="18" t="n"/>
+      <c r="E110" s="18" t="n"/>
+      <c r="F110" s="18" t="n"/>
+      <c r="G110" s="18" t="n"/>
+      <c r="H110" s="18" t="n"/>
+      <c r="I110" s="18" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="n"/>
+      <c r="B111" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C108" s="21" t="n"/>
-      <c r="D108" s="21" t="n"/>
-      <c r="E108" s="21" t="n"/>
-      <c r="F108" s="21" t="n"/>
-      <c r="G108" s="21" t="n"/>
-      <c r="H108" s="21" t="n"/>
-      <c r="I108" s="21" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr"/>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="C111" s="21" t="n"/>
+      <c r="D111" s="21" t="n"/>
+      <c r="E111" s="21" t="n"/>
+      <c r="F111" s="21" t="n"/>
+      <c r="G111" s="21" t="n"/>
+      <c r="H111" s="21" t="n"/>
+      <c r="I111" s="21" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr"/>
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C112" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E112" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F112" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="G112" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H109" s="12" t="n">
+      <c r="H112" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I109" s="13" t="inlineStr">
+      <c r="I112" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="71">
-    <mergeCell ref="B97:I97"/>
+  <mergeCells count="73">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B100:I100"/>
     <mergeCell ref="B75:I75"/>
     <mergeCell ref="A99:I99"/>
     <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="A66:I66"/>
     <mergeCell ref="A89:I89"/>
     <mergeCell ref="B72:I72"/>
-    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="B90:I90"/>
     <mergeCell ref="A74:I74"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="B93:I93"/>
     <mergeCell ref="A86:I86"/>
+    <mergeCell ref="B96:I96"/>
     <mergeCell ref="A95:I95"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B48:I48"/>
@@ -6058,48 +6199,51 @@
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="B111:I111"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
+    <mergeCell ref="B107:I107"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A106:I106"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="B61:I61"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A96:I96"/>
+    <mergeCell ref="A109:I109"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A63:I63"/>
-    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B78:I78"/>
     <mergeCell ref="B87:I87"/>
     <mergeCell ref="A13:I13"/>
+    <mergeCell ref="B103:I103"/>
     <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A102:I102"/>
     <mergeCell ref="A67:I67"/>
-    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="A77:I77"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="B84:I84"/>
-    <mergeCell ref="B65:I65"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A107:I107"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="B64:I64"/>
     <mergeCell ref="B33:I33"/>
-    <mergeCell ref="A103:I103"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B51:I51"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="B104:I104"/>
+    <mergeCell ref="A70:I70"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="A110:I110"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
@@ -6123,23 +6267,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6151,7 +6296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7243,24 +7388,76 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="378" customHeight="1">
+    <row r="29" ht="420" customHeight="1">
       <c r="A29" s="5" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Matrix Block Sum</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[][] matrixBlockSum(int[][] mat, int k) {
+     for(int i =0;i&lt;mat.length;i++){
+        for(int j=0;j&lt;mat[i].length;j++){
+            if(i==0 &amp;&amp; j&gt;0){
+                mat[i][j]+= mat[i][j-1];
+            }else if(i&gt;0 &amp;&amp; j==0){
+                mat[i][j]+=mat[i-1][j];
+            }else if(i&gt;0 &amp;&amp; j&gt;0){
+                mat[i][j]+=mat[i][j-1]+mat[i-1][j]-mat[i-1][j-1];
+            }
+        }
+     }
+     int[][] result = new int[mat.length][];
+     for(int i=0;i&lt;result.length;i++){
+        result[i] = new int[mat[i].length];
+          for(int j=0;j&lt;mat[i].length;j++){
+            int rowStart = Math.max(0, i-k);
+            int rowEnd = Math.min(mat.length-1,i+k);
+            int columnStart = Math.max(0,j-k);
+            int columnEnd = Math.min(mat[i].length-1,j+k);
+            result[i][j] = mat[rowEnd][columnEnd];
+            if(rowStart&gt;0) result[i][j]-=mat[rowStart-1][columnEnd];
+            if(columnStart &gt;0) result[i][j]-=mat[rowEnd][columnStart-1];
+            if(rowStart &gt;0 &amp;&amp; columnStart &gt;0) result[i][j]+=mat[rowStart-1][columnStart-1];
+          }
+     } 
+     return result; 
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="378" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -7292,24 +7489,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="350" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="350" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -7339,24 +7536,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="238" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="238" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -7378,24 +7575,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="308" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="308" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -7422,24 +7619,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="280" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="280" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -7462,24 +7659,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="448" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="448" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -7514,24 +7711,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="378" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="378" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -7563,24 +7760,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="490" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="490" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7608,24 +7805,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="308" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="308" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -7651,24 +7848,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="238" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="238" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -7688,24 +7885,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="560" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="560" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -7746,24 +7943,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="294" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="294" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -767,14 +767,14 @@
       <c r="A7" s="4" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Design, Prefix Sum</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -783,47 +783,47 @@
         <v>1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>98</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>26.5</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>0</v>
@@ -832,20 +832,20 @@
         <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>36</v>
+        <v>26.5</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>104.8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -861,24 +861,24 @@
         <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -887,24 +887,24 @@
         <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -913,17 +913,17 @@
         <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -939,17 +939,17 @@
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
@@ -965,24 +965,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -991,24 +991,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1017,24 +1017,24 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -1043,17 +1043,17 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -1069,24 +1069,24 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -1095,17 +1095,17 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
@@ -1121,17 +1121,17 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -1147,21 +1147,21 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>0</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="7" t="n">
         <v>47.2</v>
@@ -1183,274 +1183,274 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5" t="n">
+      <c r="C24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H24" s="7" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr"/>
-      <c r="C24" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="D24" s="9" t="n">
+      <c r="B25" s="8" t="inlineStr"/>
+      <c r="C25" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="9" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="E25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="5" t="n">
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="n">
+      <c r="C28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H28" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n">
+      <c r="G30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="9" t="n">
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9" t="n">
+      <c r="D31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5" t="n">
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>0</v>
@@ -1459,17 +1459,17 @@
         <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -1488,234 +1488,260 @@
         <v>2</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
+      <c r="C36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H36" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="9" t="n">
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="9" t="n">
+      <c r="D37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5" t="n">
+      <c r="C40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="9" t="n">
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H42" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr"/>
-      <c r="C42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr"/>
-      <c r="C43" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="D43" s="11" t="n">
+      <c r="B44" s="10" t="inlineStr"/>
+      <c r="C44" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D44" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="G43" s="11" t="inlineStr"/>
-      <c r="H43" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="G44" s="11" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1731,7 +1757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3692,11 +3718,61 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>303</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Range Sum Query - Immutable</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Design, Prefix Sum</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="14" t="n">
+        <v>46262.9494212963</v>
+      </c>
+      <c r="L42" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F41">
+  <conditionalFormatting sqref="F5:F42">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3745,6 +3821,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3756,7 +3833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3799,7 +3876,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   22 solved   (Low: 14 · Medium: 8 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   23 solved   (Low: 15 · Medium: 8 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -3994,7 +4071,7 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Design, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B13" s="18" t="n"/>
@@ -4007,48 +4084,48 @@
       <c r="I13" s="18" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n"/>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Range Sum Query - Immutable</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4003</v>
+        <v>303</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>98</v>
+        <v>47.7</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H15" s="12" t="n">
-        <v>46247.80789351852</v>
+        <v>46262.9494212963</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -4059,7 +4136,7 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
@@ -4072,150 +4149,150 @@
       <c r="I16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n"/>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>Longest Fibonacci Subarray</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4003</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>46247.80789351852</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="n"/>
+      <c r="I19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>Two Sum</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="C21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E21" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>46251.8174537037</v>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C22" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="7" t="n">
+      <c r="E22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="7" t="n">
         <v>45.1</v>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="n">
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="n">
         <v>46252.95966435185</v>
       </c>
-      <c r="I19" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="18" t="n"/>
-      <c r="I20" s="18" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="21" t="n"/>
-      <c r="H21" s="21" t="n"/>
-      <c r="I21" s="21" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Contains Duplicate II</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>46258.98878472222</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4224,7 +4301,7 @@
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B23" s="18" t="n"/>
@@ -4255,11 +4332,11 @@
       <c r="A25" s="5" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1353</v>
+        <v>219</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
@@ -4267,10 +4344,10 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -4278,7 +4355,7 @@
         </is>
       </c>
       <c r="H25" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -4289,7 +4366,7 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B26" s="18" t="n"/>
@@ -4302,40 +4379,40 @@
       <c r="I26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
+      <c r="A27" s="21" t="n"/>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="21" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="21" t="n"/>
+      <c r="H27" s="21" t="n"/>
+      <c r="I27" s="21" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -4343,7 +4420,7 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -4354,7 +4431,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B29" s="18" t="n"/>
@@ -4367,40 +4444,40 @@
       <c r="I29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="n"/>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -4408,7 +4485,7 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -4419,7 +4496,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -4450,11 +4527,11 @@
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
@@ -4462,10 +4539,10 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -4473,7 +4550,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -4484,7 +4561,7 @@
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B35" s="18" t="n"/>
@@ -4515,11 +4592,11 @@
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
@@ -4527,10 +4604,10 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -4538,7 +4615,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4549,7 +4626,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
@@ -4562,40 +4639,40 @@
       <c r="I38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="21" t="n"/>
+      <c r="I39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -4603,7 +4680,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -4614,7 +4691,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -4627,40 +4704,40 @@
       <c r="I41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="n"/>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4668,7 +4745,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -4679,7 +4756,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4692,40 +4769,40 @@
       <c r="I44" s="18" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="n"/>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="21" t="n"/>
+      <c r="I45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4733,7 +4810,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -4744,7 +4821,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -4775,11 +4852,11 @@
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Corporate Flight Bookings</t>
+          <t>Matrix Block Sum</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
@@ -4787,10 +4864,10 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -4798,7 +4875,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46262.6837962963</v>
+        <v>46262.8983912037</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -4809,7 +4886,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -4822,40 +4899,40 @@
       <c r="I50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="n"/>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
+      <c r="A51" s="19" t="n"/>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
+      <c r="G51" s="19" t="n"/>
+      <c r="H51" s="19" t="n"/>
+      <c r="I51" s="19" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -4863,7 +4940,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -4874,7 +4951,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -4905,11 +4982,11 @@
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
@@ -4917,10 +4994,10 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -4928,7 +5005,7 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -4939,7 +5016,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -4970,11 +5047,11 @@
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
@@ -4982,10 +5059,10 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -4993,7 +5070,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -5004,7 +5081,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -5020,7 +5097,7 @@
       <c r="A60" s="21" t="n"/>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C60" s="21" t="n"/>
@@ -5035,301 +5112,301 @@
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="18" t="n"/>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="18" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="n"/>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="21" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr"/>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C64" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="5" t="n">
+      <c r="E64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="n">
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I61" s="13" t="inlineStr">
+      <c r="I64" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr"/>
-      <c r="B62" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C65" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E62" s="7" t="n">
+      <c r="E65" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F62" s="7" t="n">
+      <c r="F65" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H62" s="14" t="n">
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I65" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B63" s="18" t="n"/>
-      <c r="C63" s="18" t="n"/>
-      <c r="D63" s="18" t="n"/>
-      <c r="E63" s="18" t="n"/>
-      <c r="F63" s="18" t="n"/>
-      <c r="G63" s="18" t="n"/>
-      <c r="H63" s="18" t="n"/>
-      <c r="I63" s="18" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="19" t="n"/>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="18" t="n"/>
+      <c r="I66" s="18" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="19" t="n"/>
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C64" s="19" t="n"/>
-      <c r="D64" s="19" t="n"/>
-      <c r="E64" s="19" t="n"/>
-      <c r="F64" s="19" t="n"/>
-      <c r="G64" s="19" t="n"/>
-      <c r="H64" s="19" t="n"/>
-      <c r="I64" s="19" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="5" t="inlineStr"/>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="C67" s="19" t="n"/>
+      <c r="D67" s="19" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="19" t="n"/>
+      <c r="G67" s="19" t="n"/>
+      <c r="H67" s="19" t="n"/>
+      <c r="I67" s="19" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr"/>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C68" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
+      <c r="E68" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F68" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="n">
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I65" s="13" t="inlineStr">
+      <c r="I68" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B67" s="18" t="n"/>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-      <c r="G67" s="18" t="n"/>
-      <c r="H67" s="18" t="n"/>
-      <c r="I67" s="18" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="21" t="n"/>
-      <c r="B68" s="22" t="inlineStr">
+      <c r="B70" s="18" t="n"/>
+      <c r="C70" s="18" t="n"/>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="18" t="n"/>
+      <c r="G70" s="18" t="n"/>
+      <c r="H70" s="18" t="n"/>
+      <c r="I70" s="18" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="n"/>
+      <c r="B71" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C68" s="21" t="n"/>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n"/>
-      <c r="H68" s="21" t="n"/>
-      <c r="I68" s="21" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr"/>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="21" t="n"/>
+      <c r="E71" s="21" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="21" t="n"/>
+      <c r="I71" s="21" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr"/>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C72" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5" t="n">
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H69" s="12" t="n">
+      <c r="H72" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I69" s="13" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="16" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="n"/>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="18" t="n"/>
-      <c r="I71" s="18" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="21" t="n"/>
-      <c r="B72" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="21" t="n"/>
-      <c r="I72" s="21" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr"/>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H73" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B74" s="18" t="n"/>
@@ -5360,11 +5437,11 @@
       <c r="A76" s="5" t="inlineStr"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
@@ -5372,18 +5449,18 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H76" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -5394,7 +5471,7 @@
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B77" s="18" t="n"/>
@@ -5425,171 +5502,171 @@
       <c r="A79" s="5" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="n"/>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="21" t="n"/>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="21" t="n"/>
+      <c r="E81" s="21" t="n"/>
+      <c r="F81" s="21" t="n"/>
+      <c r="G81" s="21" t="n"/>
+      <c r="H81" s="21" t="n"/>
+      <c r="I81" s="21" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr"/>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="5" t="n">
+      <c r="E82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="n">
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I79" s="13" t="inlineStr">
+      <c r="I82" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="19" t="n"/>
-      <c r="B80" s="20" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="19" t="n"/>
+      <c r="B83" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C80" s="19" t="n"/>
-      <c r="D80" s="19" t="n"/>
-      <c r="E80" s="19" t="n"/>
-      <c r="F80" s="19" t="n"/>
-      <c r="G80" s="19" t="n"/>
-      <c r="H80" s="19" t="n"/>
-      <c r="I80" s="19" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr"/>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="C83" s="19" t="n"/>
+      <c r="D83" s="19" t="n"/>
+      <c r="E83" s="19" t="n"/>
+      <c r="F83" s="19" t="n"/>
+      <c r="G83" s="19" t="n"/>
+      <c r="H83" s="19" t="n"/>
+      <c r="I83" s="19" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr"/>
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C84" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="5" t="n">
+      <c r="E84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G84" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H81" s="12" t="n">
+      <c r="H84" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I81" s="13" t="inlineStr">
+      <c r="I84" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="16" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n"/>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B83" s="18" t="n"/>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="18" t="n"/>
-      <c r="I83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="21" t="n"/>
-      <c r="B84" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C84" s="21" t="n"/>
-      <c r="D84" s="21" t="n"/>
-      <c r="E84" s="21" t="n"/>
-      <c r="F84" s="21" t="n"/>
-      <c r="G84" s="21" t="n"/>
-      <c r="H84" s="21" t="n"/>
-      <c r="I84" s="21" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr"/>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n"/>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B86" s="18" t="n"/>
@@ -5602,40 +5679,40 @@
       <c r="I86" s="18" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="19" t="n"/>
-      <c r="B87" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="n"/>
-      <c r="D87" s="19" t="n"/>
-      <c r="E87" s="19" t="n"/>
-      <c r="F87" s="19" t="n"/>
-      <c r="G87" s="19" t="n"/>
-      <c r="H87" s="19" t="n"/>
-      <c r="I87" s="19" t="n"/>
+      <c r="A87" s="21" t="n"/>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="n"/>
+      <c r="D87" s="21" t="n"/>
+      <c r="E87" s="21" t="n"/>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="21" t="n"/>
+      <c r="I87" s="21" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C88" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
@@ -5643,7 +5720,7 @@
         </is>
       </c>
       <c r="H88" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -5654,7 +5731,7 @@
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B89" s="18" t="n"/>
@@ -5667,40 +5744,40 @@
       <c r="I89" s="18" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="21" t="n"/>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
+      <c r="A90" s="19" t="n"/>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="n"/>
+      <c r="D90" s="19" t="n"/>
+      <c r="E90" s="19" t="n"/>
+      <c r="F90" s="19" t="n"/>
+      <c r="G90" s="19" t="n"/>
+      <c r="H90" s="19" t="n"/>
+      <c r="I90" s="19" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
@@ -5708,7 +5785,7 @@
         </is>
       </c>
       <c r="H91" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -5719,7 +5796,7 @@
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B92" s="18" t="n"/>
@@ -5750,11 +5827,11 @@
       <c r="A94" s="5" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
@@ -5765,15 +5842,15 @@
         <v>2</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H94" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -5784,7 +5861,7 @@
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B95" s="18" t="n"/>
@@ -5815,121 +5892,121 @@
       <c r="A97" s="5" t="inlineStr"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="18" t="n"/>
+      <c r="D98" s="18" t="n"/>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="n"/>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="n"/>
+      <c r="D99" s="21" t="n"/>
+      <c r="E99" s="21" t="n"/>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr"/>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C100" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E97" s="5" t="n">
+      <c r="E100" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F97" s="5" t="n">
+      <c r="F100" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H97" s="12" t="n">
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I97" s="13" t="inlineStr">
+      <c r="I100" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="16" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B98" s="2" t="n"/>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B99" s="18" t="n"/>
-      <c r="C99" s="18" t="n"/>
-      <c r="D99" s="18" t="n"/>
-      <c r="E99" s="18" t="n"/>
-      <c r="F99" s="18" t="n"/>
-      <c r="G99" s="18" t="n"/>
-      <c r="H99" s="18" t="n"/>
-      <c r="I99" s="18" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="21" t="n"/>
-      <c r="B100" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C100" s="21" t="n"/>
-      <c r="D100" s="21" t="n"/>
-      <c r="E100" s="21" t="n"/>
-      <c r="F100" s="21" t="n"/>
-      <c r="G100" s="21" t="n"/>
-      <c r="H100" s="21" t="n"/>
-      <c r="I100" s="21" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr"/>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="2" t="n"/>
+      <c r="H101" s="2" t="n"/>
+      <c r="I101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B102" s="18" t="n"/>
@@ -5945,7 +6022,7 @@
       <c r="A103" s="21" t="n"/>
       <c r="B103" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C103" s="21" t="n"/>
@@ -5960,291 +6037,358 @@
       <c r="A104" s="5" t="inlineStr"/>
       <c r="B104" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B105" s="18" t="n"/>
+      <c r="C105" s="18" t="n"/>
+      <c r="D105" s="18" t="n"/>
+      <c r="E105" s="18" t="n"/>
+      <c r="F105" s="18" t="n"/>
+      <c r="G105" s="18" t="n"/>
+      <c r="H105" s="18" t="n"/>
+      <c r="I105" s="18" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="n"/>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C106" s="21" t="n"/>
+      <c r="D106" s="21" t="n"/>
+      <c r="E106" s="21" t="n"/>
+      <c r="F106" s="21" t="n"/>
+      <c r="G106" s="21" t="n"/>
+      <c r="H106" s="21" t="n"/>
+      <c r="I106" s="21" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr"/>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C107" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E104" s="5" t="n">
+      <c r="E107" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F104" s="5" t="n">
+      <c r="F107" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G104" s="5" t="inlineStr">
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H104" s="12" t="n">
+      <c r="H107" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I104" s="13" t="inlineStr">
+      <c r="I107" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="7" t="inlineStr"/>
-      <c r="B105" s="6" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr"/>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C105" s="7" t="n">
+      <c r="C108" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D108" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n">
+      <c r="E108" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F105" s="7" t="n">
+      <c r="F108" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H105" s="14" t="n">
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H108" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I105" s="15" t="inlineStr">
+      <c r="I108" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="17" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B106" s="18" t="n"/>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="18" t="n"/>
-      <c r="G106" s="18" t="n"/>
-      <c r="H106" s="18" t="n"/>
-      <c r="I106" s="18" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="21" t="n"/>
-      <c r="B107" s="22" t="inlineStr">
+      <c r="B109" s="18" t="n"/>
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="18" t="n"/>
+      <c r="E109" s="18" t="n"/>
+      <c r="F109" s="18" t="n"/>
+      <c r="G109" s="18" t="n"/>
+      <c r="H109" s="18" t="n"/>
+      <c r="I109" s="18" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="n"/>
+      <c r="B110" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C107" s="21" t="n"/>
-      <c r="D107" s="21" t="n"/>
-      <c r="E107" s="21" t="n"/>
-      <c r="F107" s="21" t="n"/>
-      <c r="G107" s="21" t="n"/>
-      <c r="H107" s="21" t="n"/>
-      <c r="I107" s="21" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr"/>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="C110" s="21" t="n"/>
+      <c r="D110" s="21" t="n"/>
+      <c r="E110" s="21" t="n"/>
+      <c r="F110" s="21" t="n"/>
+      <c r="G110" s="21" t="n"/>
+      <c r="H110" s="21" t="n"/>
+      <c r="I110" s="21" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr"/>
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C108" s="5" t="n">
+      <c r="C111" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E108" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="5" t="n">
+      <c r="E111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G108" s="5" t="inlineStr">
+      <c r="G111" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H108" s="12" t="n">
+      <c r="H111" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I108" s="13" t="inlineStr">
+      <c r="I111" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="16" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="n"/>
-      <c r="G109" s="2" t="n"/>
-      <c r="H109" s="2" t="n"/>
-      <c r="I109" s="2" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="17" t="inlineStr">
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B110" s="18" t="n"/>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="18" t="n"/>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="18" t="n"/>
-      <c r="G110" s="18" t="n"/>
-      <c r="H110" s="18" t="n"/>
-      <c r="I110" s="18" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="21" t="n"/>
-      <c r="B111" s="22" t="inlineStr">
+      <c r="B113" s="18" t="n"/>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="n"/>
+      <c r="B114" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C111" s="21" t="n"/>
-      <c r="D111" s="21" t="n"/>
-      <c r="E111" s="21" t="n"/>
-      <c r="F111" s="21" t="n"/>
-      <c r="G111" s="21" t="n"/>
-      <c r="H111" s="21" t="n"/>
-      <c r="I111" s="21" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr"/>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="C114" s="21" t="n"/>
+      <c r="D114" s="21" t="n"/>
+      <c r="E114" s="21" t="n"/>
+      <c r="F114" s="21" t="n"/>
+      <c r="G114" s="21" t="n"/>
+      <c r="H114" s="21" t="n"/>
+      <c r="I114" s="21" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr"/>
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C115" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E112" s="5" t="n">
+      <c r="E115" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F112" s="5" t="n">
+      <c r="F115" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G112" s="5" t="inlineStr">
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H112" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I112" s="13" t="inlineStr">
+      <c r="I115" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="75">
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B100:I100"/>
+    <mergeCell ref="B106:I106"/>
     <mergeCell ref="B75:I75"/>
-    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="B63:I63"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="A66:I66"/>
+    <mergeCell ref="B81:I81"/>
     <mergeCell ref="A89:I89"/>
-    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="B90:I90"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="A74:I74"/>
+    <mergeCell ref="A105:I105"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="A50:I50"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="B93:I93"/>
+    <mergeCell ref="A101:I101"/>
     <mergeCell ref="A86:I86"/>
     <mergeCell ref="B96:I96"/>
     <mergeCell ref="A95:I95"/>
-    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="A113:I113"/>
     <mergeCell ref="B48:I48"/>
-    <mergeCell ref="A71:I71"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="B111:I111"/>
+    <mergeCell ref="A85:I85"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="B107:I107"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="B60:I60"/>
     <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A106:I106"/>
+    <mergeCell ref="B67:I67"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="A38:I38"/>
     <mergeCell ref="A109:I109"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="A112:I112"/>
+    <mergeCell ref="A19:I19"/>
     <mergeCell ref="B78:I78"/>
     <mergeCell ref="B87:I87"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="B103:I103"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A102:I102"/>
-    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="B99:I99"/>
     <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="B84:I84"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="A59:I59"/>
-    <mergeCell ref="A82:I82"/>
     <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="B83:I83"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B24:I24"/>
     <mergeCell ref="B51:I51"/>
+    <mergeCell ref="B20:I20"/>
     <mergeCell ref="A70:I70"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B80:I80"/>
-    <mergeCell ref="A110:I110"/>
+    <mergeCell ref="B114:I114"/>
     <mergeCell ref="B45:I45"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="B110:I110"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
@@ -6253,7 +6397,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId9"/>
@@ -6268,23 +6412,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6296,7 +6441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7013,24 +7158,65 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="420" customHeight="1">
+    <row r="21" ht="308" customHeight="1">
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>Range Sum Query - Immutable</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>303</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>class NumArray {
+    int[] prefix;
+    public NumArray(int[] nums) {
+        prefix = new int[nums.length];
+        prefix[0] = nums[0];
+    for(int i=1;i&lt;nums.length;i++){
+        prefix[i] =prefix[i-1]+nums[i];
+    } 
+    }
+    public int sumRange(int left, int right) {
+      if(left==0) return prefix[right];
+      return prefix[right] - prefix[left-1]; 
+    }
+}
+/**
+ * Your NumArray object will be instantiated and called as such:
+ * NumArray obj = new NumArray(nums);
+ * int param_1 = obj.sumRange(left,right);
+ */</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="420" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
@@ -7058,24 +7244,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="546" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="546" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -7119,24 +7305,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="196" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="196" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -7155,24 +7341,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="406" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="406" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -7205,24 +7391,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="378" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="378" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -7254,24 +7440,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="560" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="560" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -7307,24 +7493,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="294" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="294" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -7350,24 +7536,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="224" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="224" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -7388,24 +7574,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="420" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="420" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -7440,24 +7626,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="378" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="378" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -7489,24 +7675,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="350" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="350" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -7536,24 +7722,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="238" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="238" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -7575,24 +7761,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="308" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="308" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -7619,24 +7805,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="280" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="280" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -7659,24 +7845,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="448" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="448" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -7711,24 +7897,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="378" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="378" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -7760,24 +7946,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="490" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="490" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7805,24 +7991,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="308" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="308" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -7848,24 +8034,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="238" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="238" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -7885,24 +8071,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="560" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="560" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -7943,24 +8129,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="294" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="294" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -767,14 +767,14 @@
       <c r="A7" s="4" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Design, Prefix Sum</t>
+          <t>Design, Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>0</v>
@@ -783,24 +783,24 @@
         <v>1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>47.7</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Design, Prefix Sum</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -809,47 +809,47 @@
         <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>98</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>26.5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>0</v>
@@ -858,20 +858,20 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>36</v>
+        <v>26.5</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>104.8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
@@ -887,24 +887,24 @@
         <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -913,24 +913,24 @@
         <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -939,17 +939,17 @@
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
@@ -965,17 +965,17 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -991,24 +991,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1017,24 +1017,24 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -1043,24 +1043,24 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1069,17 +1069,17 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -1095,24 +1095,24 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1121,17 +1121,17 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -1147,17 +1147,17 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
@@ -1173,21 +1173,21 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
@@ -1196,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>47.2</v>
@@ -1209,274 +1209,274 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7" t="n">
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H25" s="5" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr"/>
-      <c r="C25" s="9" t="n">
+      <c r="B26" s="8" t="inlineStr"/>
+      <c r="C26" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D25" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="9" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="D26" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr"/>
+      <c r="H26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="7" t="n">
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H29" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="7" t="n">
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="9" t="n">
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9" t="n">
+      <c r="D32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="7" t="n">
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>0</v>
@@ -1485,17 +1485,17 @@
         <v>1</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -1514,234 +1514,260 @@
         <v>2</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
+      <c r="C37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="7" t="n">
+      <c r="H37" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr"/>
-      <c r="C37" s="9" t="n">
+      <c r="B38" s="8" t="inlineStr"/>
+      <c r="C38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="9" t="n">
+      <c r="D38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="G38" s="9" t="inlineStr"/>
+      <c r="H38" s="9" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="n">
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="9" t="n">
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9" t="n">
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H42" s="7" t="n">
+      <c r="H43" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr"/>
-      <c r="C43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr"/>
+      <c r="C44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="9" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr"/>
-      <c r="C44" s="11" t="n">
+      <c r="B45" s="10" t="inlineStr"/>
+      <c r="C45" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="D44" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="G44" s="11" t="inlineStr"/>
-      <c r="H44" s="11" t="inlineStr"/>
+      <c r="D45" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1757,7 +1783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3768,11 +3794,61 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>304</v>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Range Sum Query 2D - Immutable</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Design, Matrix, Prefix Sum</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" s="12" t="n">
+        <v>46263.00756944445</v>
+      </c>
+      <c r="L43" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F42">
+  <conditionalFormatting sqref="F5:F43">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3822,6 +3898,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3833,7 +3910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3876,7 +3953,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   23 solved   (Low: 15 · Medium: 8 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   24 solved   (Low: 15 · Medium: 9 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4071,7 +4148,7 @@
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Design, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Design, Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B13" s="18" t="n"/>
@@ -4084,40 +4161,40 @@
       <c r="I13" s="18" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n"/>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
+      <c r="A14" s="19" t="n"/>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Range Sum Query - Immutable</t>
+          <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>47.7</v>
+        <v>142</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -4125,7 +4202,7 @@
         </is>
       </c>
       <c r="H15" s="12" t="n">
-        <v>46262.9494212963</v>
+        <v>46263.00756944445</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -4136,7 +4213,7 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Design, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
@@ -4149,48 +4226,48 @@
       <c r="I16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n"/>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="19" t="n"/>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="19" t="n"/>
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="21" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Range Sum Query - Immutable</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>4003</v>
+        <v>303</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>98</v>
+        <v>47.7</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H18" s="12" t="n">
-        <v>46247.80789351852</v>
+        <v>46262.9494212963</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -4201,7 +4278,7 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B19" s="18" t="n"/>
@@ -4214,150 +4291,150 @@
       <c r="I19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="21" t="n"/>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
+      <c r="A20" s="19" t="n"/>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>Longest Fibonacci Subarray</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>4003</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>46247.80789351852</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n"/>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="21" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="21" t="n"/>
+      <c r="H23" s="21" t="n"/>
+      <c r="I23" s="21" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>Two Sum</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="C24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E24" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F24" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n">
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>46251.8174537037</v>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr"/>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C25" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="7" t="n">
+      <c r="E25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="7" t="n">
         <v>45.1</v>
       </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="n">
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="n">
         <v>46252.95966435185</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n"/>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-      <c r="G24" s="21" t="n"/>
-      <c r="H24" s="21" t="n"/>
-      <c r="I24" s="21" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Contains Duplicate II</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>46258.98878472222</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
+      <c r="I25" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4366,7 +4443,7 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B26" s="18" t="n"/>
@@ -4397,11 +4474,11 @@
       <c r="A28" s="5" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1353</v>
+        <v>219</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
@@ -4409,10 +4486,10 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -4420,7 +4497,7 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -4431,7 +4508,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B29" s="18" t="n"/>
@@ -4444,40 +4521,40 @@
       <c r="I29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -4485,7 +4562,7 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -4496,7 +4573,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -4509,40 +4586,40 @@
       <c r="I32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n"/>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -4550,7 +4627,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -4561,7 +4638,7 @@
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B35" s="18" t="n"/>
@@ -4592,11 +4669,11 @@
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
@@ -4604,10 +4681,10 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -4615,7 +4692,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4626,7 +4703,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
@@ -4657,11 +4734,11 @@
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
@@ -4669,10 +4746,10 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -4680,7 +4757,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -4691,7 +4768,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -4704,40 +4781,40 @@
       <c r="I41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="19" t="n"/>
-      <c r="B42" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="19" t="n"/>
-      <c r="I42" s="19" t="n"/>
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="n"/>
+      <c r="H42" s="21" t="n"/>
+      <c r="I42" s="21" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4745,7 +4822,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -4756,7 +4833,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4769,40 +4846,40 @@
       <c r="I44" s="18" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="21" t="n"/>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
+      <c r="A45" s="19" t="n"/>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="19" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4810,7 +4887,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -4821,7 +4898,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -4834,40 +4911,40 @@
       <c r="I47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n"/>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -4875,7 +4952,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -4886,7 +4963,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -4917,11 +4994,11 @@
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Corporate Flight Bookings</t>
+          <t>Matrix Block Sum</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
@@ -4929,10 +5006,10 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -4940,7 +5017,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46262.6837962963</v>
+        <v>46262.8983912037</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -4951,7 +5028,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -4964,40 +5041,40 @@
       <c r="I53" s="18" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="n"/>
-      <c r="B54" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
+      <c r="A54" s="19" t="n"/>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="19" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -5005,7 +5082,7 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -5016,7 +5093,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -5047,11 +5124,11 @@
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
@@ -5059,10 +5136,10 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -5070,7 +5147,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -5081,7 +5158,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -5112,11 +5189,11 @@
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
@@ -5124,10 +5201,10 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
@@ -5135,7 +5212,7 @@
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -5146,7 +5223,7 @@
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -5162,7 +5239,7 @@
       <c r="A63" s="21" t="n"/>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C63" s="21" t="n"/>
@@ -5177,301 +5254,301 @@
       <c r="A64" s="5" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="18" t="n"/>
+      <c r="H65" s="18" t="n"/>
+      <c r="I65" s="18" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="n"/>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="21" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="21" t="n"/>
+      <c r="H66" s="21" t="n"/>
+      <c r="I66" s="21" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C67" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="n">
+      <c r="E67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="n">
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I64" s="13" t="inlineStr">
+      <c r="I67" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr"/>
-      <c r="B65" s="6" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C68" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E68" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F68" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H65" s="14" t="n">
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I65" s="15" t="inlineStr">
+      <c r="I68" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B66" s="18" t="n"/>
-      <c r="C66" s="18" t="n"/>
-      <c r="D66" s="18" t="n"/>
-      <c r="E66" s="18" t="n"/>
-      <c r="F66" s="18" t="n"/>
-      <c r="G66" s="18" t="n"/>
-      <c r="H66" s="18" t="n"/>
-      <c r="I66" s="18" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="19" t="n"/>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B69" s="18" t="n"/>
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+      <c r="G69" s="18" t="n"/>
+      <c r="H69" s="18" t="n"/>
+      <c r="I69" s="18" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="n"/>
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C67" s="19" t="n"/>
-      <c r="D67" s="19" t="n"/>
-      <c r="E67" s="19" t="n"/>
-      <c r="F67" s="19" t="n"/>
-      <c r="G67" s="19" t="n"/>
-      <c r="H67" s="19" t="n"/>
-      <c r="I67" s="19" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr"/>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="C70" s="19" t="n"/>
+      <c r="D70" s="19" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="19" t="n"/>
+      <c r="G70" s="19" t="n"/>
+      <c r="H70" s="19" t="n"/>
+      <c r="I70" s="19" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr"/>
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C71" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D71" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E71" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F71" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H68" s="12" t="n">
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="I71" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B70" s="18" t="n"/>
-      <c r="C70" s="18" t="n"/>
-      <c r="D70" s="18" t="n"/>
-      <c r="E70" s="18" t="n"/>
-      <c r="F70" s="18" t="n"/>
-      <c r="G70" s="18" t="n"/>
-      <c r="H70" s="18" t="n"/>
-      <c r="I70" s="18" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="n"/>
-      <c r="B71" s="22" t="inlineStr">
+      <c r="B73" s="18" t="n"/>
+      <c r="C73" s="18" t="n"/>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="18" t="n"/>
+      <c r="H73" s="18" t="n"/>
+      <c r="I73" s="18" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="n"/>
+      <c r="B74" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C71" s="21" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="n"/>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="C74" s="21" t="n"/>
+      <c r="D74" s="21" t="n"/>
+      <c r="E74" s="21" t="n"/>
+      <c r="F74" s="21" t="n"/>
+      <c r="G74" s="21" t="n"/>
+      <c r="H74" s="21" t="n"/>
+      <c r="I74" s="21" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr"/>
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C75" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="n">
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G72" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H72" s="12" t="n">
+      <c r="H75" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I72" s="13" t="inlineStr">
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="16" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B74" s="18" t="n"/>
-      <c r="C74" s="18" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
-      <c r="G74" s="18" t="n"/>
-      <c r="H74" s="18" t="n"/>
-      <c r="I74" s="18" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="21" t="n"/>
-      <c r="B75" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C75" s="21" t="n"/>
-      <c r="D75" s="21" t="n"/>
-      <c r="E75" s="21" t="n"/>
-      <c r="F75" s="21" t="n"/>
-      <c r="G75" s="21" t="n"/>
-      <c r="H75" s="21" t="n"/>
-      <c r="I75" s="21" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr"/>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H76" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B77" s="18" t="n"/>
@@ -5502,11 +5579,11 @@
       <c r="A79" s="5" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C79" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
@@ -5514,18 +5591,18 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H79" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -5536,7 +5613,7 @@
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B80" s="18" t="n"/>
@@ -5567,171 +5644,171 @@
       <c r="A82" s="5" t="inlineStr"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="n"/>
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="n"/>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C84" s="21" t="n"/>
+      <c r="D84" s="21" t="n"/>
+      <c r="E84" s="21" t="n"/>
+      <c r="F84" s="21" t="n"/>
+      <c r="G84" s="21" t="n"/>
+      <c r="H84" s="21" t="n"/>
+      <c r="I84" s="21" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr"/>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C85" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="5" t="n">
+      <c r="E85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n">
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I82" s="13" t="inlineStr">
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="19" t="n"/>
-      <c r="B83" s="20" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="19" t="n"/>
+      <c r="B86" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C83" s="19" t="n"/>
-      <c r="D83" s="19" t="n"/>
-      <c r="E83" s="19" t="n"/>
-      <c r="F83" s="19" t="n"/>
-      <c r="G83" s="19" t="n"/>
-      <c r="H83" s="19" t="n"/>
-      <c r="I83" s="19" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr"/>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="C86" s="19" t="n"/>
+      <c r="D86" s="19" t="n"/>
+      <c r="E86" s="19" t="n"/>
+      <c r="F86" s="19" t="n"/>
+      <c r="G86" s="19" t="n"/>
+      <c r="H86" s="19" t="n"/>
+      <c r="I86" s="19" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr"/>
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C87" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D84" s="5" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="5" t="n">
+      <c r="E87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G84" s="5" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H84" s="12" t="n">
+      <c r="H87" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I84" s="13" t="inlineStr">
+      <c r="I87" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="16" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B85" s="2" t="n"/>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n"/>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B86" s="18" t="n"/>
-      <c r="C86" s="18" t="n"/>
-      <c r="D86" s="18" t="n"/>
-      <c r="E86" s="18" t="n"/>
-      <c r="F86" s="18" t="n"/>
-      <c r="G86" s="18" t="n"/>
-      <c r="H86" s="18" t="n"/>
-      <c r="I86" s="18" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="21" t="n"/>
-      <c r="B87" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C87" s="21" t="n"/>
-      <c r="D87" s="21" t="n"/>
-      <c r="E87" s="21" t="n"/>
-      <c r="F87" s="21" t="n"/>
-      <c r="G87" s="21" t="n"/>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="21" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr"/>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B89" s="18" t="n"/>
@@ -5744,40 +5821,40 @@
       <c r="I89" s="18" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="19" t="n"/>
-      <c r="B90" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C90" s="19" t="n"/>
-      <c r="D90" s="19" t="n"/>
-      <c r="E90" s="19" t="n"/>
-      <c r="F90" s="19" t="n"/>
-      <c r="G90" s="19" t="n"/>
-      <c r="H90" s="19" t="n"/>
-      <c r="I90" s="19" t="n"/>
+      <c r="A90" s="21" t="n"/>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C90" s="21" t="n"/>
+      <c r="D90" s="21" t="n"/>
+      <c r="E90" s="21" t="n"/>
+      <c r="F90" s="21" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="21" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C91" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
@@ -5785,7 +5862,7 @@
         </is>
       </c>
       <c r="H91" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -5796,7 +5873,7 @@
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B92" s="18" t="n"/>
@@ -5809,40 +5886,40 @@
       <c r="I92" s="18" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="21" t="n"/>
-      <c r="B93" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="21" t="n"/>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
+      <c r="A93" s="19" t="n"/>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="n"/>
+      <c r="D93" s="19" t="n"/>
+      <c r="E93" s="19" t="n"/>
+      <c r="F93" s="19" t="n"/>
+      <c r="G93" s="19" t="n"/>
+      <c r="H93" s="19" t="n"/>
+      <c r="I93" s="19" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -5850,7 +5927,7 @@
         </is>
       </c>
       <c r="H94" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -5861,7 +5938,7 @@
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B95" s="18" t="n"/>
@@ -5892,11 +5969,11 @@
       <c r="A97" s="5" t="inlineStr"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
@@ -5907,15 +5984,15 @@
         <v>2</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -5926,7 +6003,7 @@
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B98" s="18" t="n"/>
@@ -5957,121 +6034,121 @@
       <c r="A100" s="5" t="inlineStr"/>
       <c r="B100" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="18" t="n"/>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="n"/>
+      <c r="I101" s="18" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="21" t="n"/>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C102" s="21" t="n"/>
+      <c r="D102" s="21" t="n"/>
+      <c r="E102" s="21" t="n"/>
+      <c r="F102" s="21" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr"/>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C103" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E103" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F103" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H100" s="12" t="n">
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I100" s="13" t="inlineStr">
+      <c r="I103" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="16" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n"/>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="2" t="n"/>
-      <c r="G101" s="2" t="n"/>
-      <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B102" s="18" t="n"/>
-      <c r="C102" s="18" t="n"/>
-      <c r="D102" s="18" t="n"/>
-      <c r="E102" s="18" t="n"/>
-      <c r="F102" s="18" t="n"/>
-      <c r="G102" s="18" t="n"/>
-      <c r="H102" s="18" t="n"/>
-      <c r="I102" s="18" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="21" t="n"/>
-      <c r="B103" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C103" s="21" t="n"/>
-      <c r="D103" s="21" t="n"/>
-      <c r="E103" s="21" t="n"/>
-      <c r="F103" s="21" t="n"/>
-      <c r="G103" s="21" t="n"/>
-      <c r="H103" s="21" t="n"/>
-      <c r="I103" s="21" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr"/>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C104" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D104" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E104" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B105" s="18" t="n"/>
@@ -6087,7 +6164,7 @@
       <c r="A106" s="21" t="n"/>
       <c r="B106" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C106" s="21" t="n"/>
@@ -6102,294 +6179,361 @@
       <c r="A107" s="5" t="inlineStr"/>
       <c r="B107" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="n"/>
+      <c r="C108" s="18" t="n"/>
+      <c r="D108" s="18" t="n"/>
+      <c r="E108" s="18" t="n"/>
+      <c r="F108" s="18" t="n"/>
+      <c r="G108" s="18" t="n"/>
+      <c r="H108" s="18" t="n"/>
+      <c r="I108" s="18" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="n"/>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="n"/>
+      <c r="D109" s="21" t="n"/>
+      <c r="E109" s="21" t="n"/>
+      <c r="F109" s="21" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="21" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr"/>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C107" s="5" t="n">
+      <c r="C110" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D107" s="5" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E107" s="5" t="n">
+      <c r="E110" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F107" s="5" t="n">
+      <c r="F110" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G107" s="5" t="inlineStr">
+      <c r="G110" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H107" s="12" t="n">
+      <c r="H110" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I107" s="13" t="inlineStr">
+      <c r="I110" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="7" t="inlineStr"/>
-      <c r="B108" s="6" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr"/>
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C108" s="7" t="n">
+      <c r="C111" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D111" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E108" s="7" t="n">
+      <c r="E111" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F108" s="7" t="n">
+      <c r="F111" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H108" s="14" t="n">
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H111" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I108" s="15" t="inlineStr">
+      <c r="I111" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="17" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B109" s="18" t="n"/>
-      <c r="C109" s="18" t="n"/>
-      <c r="D109" s="18" t="n"/>
-      <c r="E109" s="18" t="n"/>
-      <c r="F109" s="18" t="n"/>
-      <c r="G109" s="18" t="n"/>
-      <c r="H109" s="18" t="n"/>
-      <c r="I109" s="18" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="21" t="n"/>
-      <c r="B110" s="22" t="inlineStr">
+      <c r="B112" s="18" t="n"/>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+      <c r="G112" s="18" t="n"/>
+      <c r="H112" s="18" t="n"/>
+      <c r="I112" s="18" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="21" t="n"/>
+      <c r="B113" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C110" s="21" t="n"/>
-      <c r="D110" s="21" t="n"/>
-      <c r="E110" s="21" t="n"/>
-      <c r="F110" s="21" t="n"/>
-      <c r="G110" s="21" t="n"/>
-      <c r="H110" s="21" t="n"/>
-      <c r="I110" s="21" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr"/>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="C113" s="21" t="n"/>
+      <c r="D113" s="21" t="n"/>
+      <c r="E113" s="21" t="n"/>
+      <c r="F113" s="21" t="n"/>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="21" t="n"/>
+      <c r="I113" s="21" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr"/>
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C114" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E111" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="5" t="n">
+      <c r="E114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H111" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I111" s="13" t="inlineStr">
+      <c r="I114" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="16" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n"/>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="17" t="inlineStr">
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B113" s="18" t="n"/>
-      <c r="C113" s="18" t="n"/>
-      <c r="D113" s="18" t="n"/>
-      <c r="E113" s="18" t="n"/>
-      <c r="F113" s="18" t="n"/>
-      <c r="G113" s="18" t="n"/>
-      <c r="H113" s="18" t="n"/>
-      <c r="I113" s="18" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="21" t="n"/>
-      <c r="B114" s="22" t="inlineStr">
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="n"/>
+      <c r="B117" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C114" s="21" t="n"/>
-      <c r="D114" s="21" t="n"/>
-      <c r="E114" s="21" t="n"/>
-      <c r="F114" s="21" t="n"/>
-      <c r="G114" s="21" t="n"/>
-      <c r="H114" s="21" t="n"/>
-      <c r="I114" s="21" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr"/>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="C117" s="21" t="n"/>
+      <c r="D117" s="21" t="n"/>
+      <c r="E117" s="21" t="n"/>
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr"/>
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C115" s="5" t="n">
+      <c r="C118" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E115" s="5" t="n">
+      <c r="E118" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F115" s="5" t="n">
+      <c r="F118" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H115" s="12" t="n">
+      <c r="H118" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I115" s="13" t="inlineStr">
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="77">
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B106:I106"/>
-    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A101:I101"/>
+    <mergeCell ref="B96:I96"/>
+    <mergeCell ref="B70:I70"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B113:I113"/>
+    <mergeCell ref="B109:I109"/>
+    <mergeCell ref="A89:I89"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="B102:I102"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A116:I116"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="A115:I115"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="B51:I51"/>
     <mergeCell ref="B63:I63"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="A66:I66"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="A89:I89"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A65:I65"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="B90:I90"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A74:I74"/>
-    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="B66:I66"/>
     <mergeCell ref="B27:I27"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B71:I71"/>
-    <mergeCell ref="A26:I26"/>
     <mergeCell ref="B93:I93"/>
-    <mergeCell ref="A101:I101"/>
-    <mergeCell ref="A86:I86"/>
-    <mergeCell ref="B96:I96"/>
-    <mergeCell ref="A95:I95"/>
-    <mergeCell ref="A113:I113"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="A104:I104"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
+    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="B106:I106"/>
+    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A95:I95"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A85:I85"/>
     <mergeCell ref="B42:I42"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="B14:I14"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="B67:I67"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A4:I4"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A109:I109"/>
-    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="A72:I72"/>
     <mergeCell ref="A29:I29"/>
     <mergeCell ref="A112:I112"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="B78:I78"/>
-    <mergeCell ref="B87:I87"/>
     <mergeCell ref="A13:I13"/>
-    <mergeCell ref="B103:I103"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A102:I102"/>
     <mergeCell ref="B99:I99"/>
-    <mergeCell ref="A77:I77"/>
-    <mergeCell ref="A92:I92"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="B84:I84"/>
     <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="B83:I83"/>
-    <mergeCell ref="B33:I33"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B51:I51"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="A70:I70"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B114:I114"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A69:I69"/>
-    <mergeCell ref="B110:I110"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A88:I88"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -6398,7 +6542,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId10"/>
@@ -6413,23 +6557,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6441,7 +6586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7205,18 +7350,67 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
+          <t>Range Sum Query 2D - Immutable</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>304</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>class NumMatrix {
+   private int[][] result;
+    public NumMatrix(int[][] matrix) {
+        result = new int[matrix.length][];  
+    for(int i=0;i&lt;matrix.length;i++){
+        result[i] = new int[matrix[i].length];
+        for(int j=0;j&lt;matrix[i].length;j++){
+            if(i==0 &amp;&amp; j==0) result[i][j] = matrix[i][j];
+            if(i==0 &amp;&amp; j&gt;0) result[i][j] = result[i][j-1] + matrix[i][j];
+            if(j == 0 &amp;&amp; i&gt;0) result[i][j] = result[i-1][j] + matrix[i][j];
+            if(i&gt;0 &amp;&amp; j&gt;0) result[i][j] = matrix[i][j] + result[i][j-1] + result[i-1][j] - result[i-1][j-1];
+        }
+    }    
+    }
+    public int sumRegion(int row1, int col1, int row2, int col2) {
+        int total = result[row2][col2];
+        int top = (row1&gt;0)?result[row1-1][col2]:0;
+        int left = (col1&gt;0)?result[row2][col1-1]:0;
+        int topleft = (row1&gt;0 &amp;&amp; col1&gt;0)?result[row1-1][col1-1]:0;
+        return total - top - left +topleft;
+    }
+}
+/**
+ * Your NumMatrix object will be instantiated and called as such:
+ * NumMatrix obj = new NumMatrix(matrix);
+ * int param_1 = obj.sumRegion(row1,col1,row2,col2);
+ */</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="420" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
@@ -7244,24 +7438,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="546" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="546" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -7305,24 +7499,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="196" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="196" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -7341,24 +7535,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="406" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="406" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -7391,24 +7585,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="378" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="378" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -7440,24 +7634,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="560" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="560" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -7493,24 +7687,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="294" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="294" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -7536,24 +7730,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="224" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="224" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -7574,24 +7768,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="420" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="420" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -7626,24 +7820,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="378" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="378" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -7675,24 +7869,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="350" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="350" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -7722,24 +7916,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="238" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="238" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -7761,24 +7955,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="308" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="308" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -7805,24 +7999,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="280" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="280" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -7845,24 +8039,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="448" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="448" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -7897,24 +8091,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="378" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="378" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -7946,24 +8140,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="490" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="490" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7991,24 +8185,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="308" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="308" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -8034,24 +8228,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="238" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="238" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -8071,24 +8265,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="560" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="560" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -8129,24 +8323,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="294" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="294" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -871,14 +871,14 @@
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table, Prefix Sum</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
@@ -887,17 +887,17 @@
         <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
@@ -913,24 +913,24 @@
         <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -939,24 +939,24 @@
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -965,17 +965,17 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -991,17 +991,17 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
@@ -1017,24 +1017,24 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -1043,24 +1043,24 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1069,24 +1069,24 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -1095,17 +1095,17 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
@@ -1121,24 +1121,24 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -1147,17 +1147,17 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
@@ -1173,17 +1173,17 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -1199,21 +1199,21 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>0</v>
@@ -1222,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H24" s="7" t="n">
         <v>47.2</v>
@@ -1235,274 +1235,274 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="5" t="n">
+      <c r="C26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H26" s="7" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="8" t="inlineStr"/>
-      <c r="C26" s="9" t="n">
+      <c r="B27" s="8" t="inlineStr"/>
+      <c r="C27" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="D27" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr"/>
+      <c r="H27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="n">
+      <c r="C28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr"/>
-      <c r="C28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H30" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
+      <c r="G32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr"/>
-      <c r="C32" s="9" t="n">
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="9" t="n">
+      <c r="D33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="9" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0</v>
@@ -1511,17 +1511,17 @@
         <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
@@ -1540,234 +1540,260 @@
         <v>2</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H38" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr"/>
-      <c r="C38" s="9" t="n">
+      <c r="B39" s="8" t="inlineStr"/>
+      <c r="C39" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="9" t="n">
+      <c r="D39" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr"/>
+      <c r="H39" s="9" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="5" t="n">
+      <c r="C40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr"/>
-      <c r="C42" s="9" t="n">
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9" t="n">
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="n">
+      <c r="C44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H44" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr"/>
-      <c r="C44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="9" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="10" t="inlineStr"/>
-      <c r="C45" s="11" t="n">
+      <c r="B46" s="10" t="inlineStr"/>
+      <c r="C46" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="D45" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="G45" s="11" t="inlineStr"/>
-      <c r="H45" s="11" t="inlineStr"/>
+      <c r="D46" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G46" s="11" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1783,7 +1809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3844,11 +3870,61 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>560</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Subarray Sum Equals K</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Hash Table, Prefix Sum</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>1544</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="14" t="n">
+        <v>46263.40873842593</v>
+      </c>
+      <c r="L44" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F43">
+  <conditionalFormatting sqref="F5:F44">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3899,6 +3975,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3910,7 +3987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3953,7 +4030,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   24 solved   (Low: 15 · Medium: 9 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   25 solved   (Low: 15 · Medium: 10 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4443,7 +4520,7 @@
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B26" s="18" t="n"/>
@@ -4456,40 +4533,40 @@
       <c r="I26" s="18" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="n"/>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="n"/>
-      <c r="D27" s="21" t="n"/>
-      <c r="E27" s="21" t="n"/>
-      <c r="F27" s="21" t="n"/>
-      <c r="G27" s="21" t="n"/>
-      <c r="H27" s="21" t="n"/>
-      <c r="I27" s="21" t="n"/>
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Contains Duplicate II</t>
+          <t>Subarray Sum Equals K</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>219</v>
+        <v>560</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
@@ -4497,7 +4574,7 @@
         </is>
       </c>
       <c r="H28" s="12" t="n">
-        <v>46258.98878472222</v>
+        <v>46263.40873842593</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -4508,7 +4585,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B29" s="18" t="n"/>
@@ -4539,11 +4616,11 @@
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1353</v>
+        <v>219</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
@@ -4551,10 +4628,10 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -4562,7 +4639,7 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -4573,7 +4650,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -4586,40 +4663,40 @@
       <c r="I32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="n"/>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
+      <c r="A33" s="21" t="n"/>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="21" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="21" t="n"/>
+      <c r="H33" s="21" t="n"/>
+      <c r="I33" s="21" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -4627,7 +4704,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -4638,7 +4715,7 @@
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B35" s="18" t="n"/>
@@ -4651,40 +4728,40 @@
       <c r="I35" s="18" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="n"/>
-      <c r="B36" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="21" t="n"/>
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
+      <c r="A36" s="19" t="n"/>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="19" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+      <c r="H36" s="19" t="n"/>
+      <c r="I36" s="19" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -4692,7 +4769,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4703,7 +4780,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
@@ -4734,11 +4811,11 @@
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
@@ -4746,10 +4823,10 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -4757,7 +4834,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -4768,7 +4845,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -4799,11 +4876,11 @@
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
@@ -4811,10 +4888,10 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4822,7 +4899,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -4833,7 +4910,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4846,40 +4923,40 @@
       <c r="I44" s="18" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="n"/>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-      <c r="G45" s="19" t="n"/>
-      <c r="H45" s="19" t="n"/>
-      <c r="I45" s="19" t="n"/>
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="n"/>
+      <c r="H45" s="21" t="n"/>
+      <c r="I45" s="21" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4887,7 +4964,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -4898,7 +4975,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -4911,40 +4988,40 @@
       <c r="I47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="21" t="n"/>
-      <c r="B48" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
+      <c r="A48" s="19" t="n"/>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="19" t="n"/>
+      <c r="H48" s="19" t="n"/>
+      <c r="I48" s="19" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -4952,7 +5029,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -4963,7 +5040,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -4976,40 +5053,40 @@
       <c r="I50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="n"/>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="19" t="n"/>
-      <c r="F51" s="19" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="19" t="n"/>
-      <c r="I51" s="19" t="n"/>
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -5017,7 +5094,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -5028,7 +5105,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -5059,11 +5136,11 @@
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Corporate Flight Bookings</t>
+          <t>Matrix Block Sum</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
@@ -5071,10 +5148,10 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -5082,7 +5159,7 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46262.6837962963</v>
+        <v>46262.8983912037</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -5093,7 +5170,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -5106,40 +5183,40 @@
       <c r="I56" s="18" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="n"/>
-      <c r="B57" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C57" s="21" t="n"/>
-      <c r="D57" s="21" t="n"/>
-      <c r="E57" s="21" t="n"/>
-      <c r="F57" s="21" t="n"/>
-      <c r="G57" s="21" t="n"/>
-      <c r="H57" s="21" t="n"/>
-      <c r="I57" s="21" t="n"/>
+      <c r="A57" s="19" t="n"/>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="n"/>
+      <c r="D57" s="19" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="19" t="n"/>
+      <c r="G57" s="19" t="n"/>
+      <c r="H57" s="19" t="n"/>
+      <c r="I57" s="19" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -5147,7 +5224,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -5158,7 +5235,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -5189,11 +5266,11 @@
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
@@ -5201,10 +5278,10 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
@@ -5212,7 +5289,7 @@
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -5223,7 +5300,7 @@
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -5254,11 +5331,11 @@
       <c r="A64" s="5" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
@@ -5266,10 +5343,10 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -5277,7 +5354,7 @@
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -5288,7 +5365,7 @@
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -5304,7 +5381,7 @@
       <c r="A66" s="21" t="n"/>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C66" s="21" t="n"/>
@@ -5319,301 +5396,301 @@
       <c r="A67" s="5" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="n"/>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="n"/>
+      <c r="B69" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="21" t="n"/>
+      <c r="E69" s="21" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="21" t="n"/>
+      <c r="I69" s="21" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr"/>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C70" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" s="5" t="n">
+      <c r="E70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="n">
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I67" s="13" t="inlineStr">
+      <c r="I70" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr"/>
-      <c r="B68" s="6" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C68" s="7" t="n">
+      <c r="C71" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D71" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E68" s="7" t="n">
+      <c r="E71" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F68" s="7" t="n">
+      <c r="F71" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="n">
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I68" s="15" t="inlineStr">
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="17" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B69" s="18" t="n"/>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-      <c r="G69" s="18" t="n"/>
-      <c r="H69" s="18" t="n"/>
-      <c r="I69" s="18" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="19" t="n"/>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B72" s="18" t="n"/>
+      <c r="C72" s="18" t="n"/>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="18" t="n"/>
+      <c r="H72" s="18" t="n"/>
+      <c r="I72" s="18" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="19" t="n"/>
+      <c r="B73" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C70" s="19" t="n"/>
-      <c r="D70" s="19" t="n"/>
-      <c r="E70" s="19" t="n"/>
-      <c r="F70" s="19" t="n"/>
-      <c r="G70" s="19" t="n"/>
-      <c r="H70" s="19" t="n"/>
-      <c r="I70" s="19" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="5" t="inlineStr"/>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="C73" s="19" t="n"/>
+      <c r="D73" s="19" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="19" t="n"/>
+      <c r="G73" s="19" t="n"/>
+      <c r="H73" s="19" t="n"/>
+      <c r="I73" s="19" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr"/>
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C74" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n">
+      <c r="E74" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F74" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H71" s="12" t="n">
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I71" s="13" t="inlineStr">
+      <c r="I74" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="16" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="18" t="n"/>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="18" t="n"/>
-      <c r="I73" s="18" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="21" t="n"/>
-      <c r="B74" s="22" t="inlineStr">
+      <c r="B76" s="18" t="n"/>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="18" t="n"/>
+      <c r="H76" s="18" t="n"/>
+      <c r="I76" s="18" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="n"/>
+      <c r="B77" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C74" s="21" t="n"/>
-      <c r="D74" s="21" t="n"/>
-      <c r="E74" s="21" t="n"/>
-      <c r="F74" s="21" t="n"/>
-      <c r="G74" s="21" t="n"/>
-      <c r="H74" s="21" t="n"/>
-      <c r="I74" s="21" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr"/>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="C77" s="21" t="n"/>
+      <c r="D77" s="21" t="n"/>
+      <c r="E77" s="21" t="n"/>
+      <c r="F77" s="21" t="n"/>
+      <c r="G77" s="21" t="n"/>
+      <c r="H77" s="21" t="n"/>
+      <c r="I77" s="21" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr"/>
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="5" t="n">
+      <c r="E78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G78" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H75" s="12" t="n">
+      <c r="H78" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I75" s="13" t="inlineStr">
+      <c r="I78" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="16" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B76" s="2" t="n"/>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="n"/>
-      <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B77" s="18" t="n"/>
-      <c r="C77" s="18" t="n"/>
-      <c r="D77" s="18" t="n"/>
-      <c r="E77" s="18" t="n"/>
-      <c r="F77" s="18" t="n"/>
-      <c r="G77" s="18" t="n"/>
-      <c r="H77" s="18" t="n"/>
-      <c r="I77" s="18" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="21" t="n"/>
-      <c r="B78" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C78" s="21" t="n"/>
-      <c r="D78" s="21" t="n"/>
-      <c r="E78" s="21" t="n"/>
-      <c r="F78" s="21" t="n"/>
-      <c r="G78" s="21" t="n"/>
-      <c r="H78" s="21" t="n"/>
-      <c r="I78" s="21" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr"/>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B80" s="18" t="n"/>
@@ -5644,11 +5721,11 @@
       <c r="A82" s="5" t="inlineStr"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C82" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
@@ -5656,18 +5733,18 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H82" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -5678,7 +5755,7 @@
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B83" s="18" t="n"/>
@@ -5709,171 +5786,171 @@
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="n"/>
+      <c r="C86" s="18" t="n"/>
+      <c r="D86" s="18" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="18" t="n"/>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="18" t="n"/>
+      <c r="I86" s="18" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="n"/>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="n"/>
+      <c r="D87" s="21" t="n"/>
+      <c r="E87" s="21" t="n"/>
+      <c r="F87" s="21" t="n"/>
+      <c r="G87" s="21" t="n"/>
+      <c r="H87" s="21" t="n"/>
+      <c r="I87" s="21" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr"/>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C88" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D88" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="5" t="n">
+      <c r="E88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="n">
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="I88" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="19" t="n"/>
-      <c r="B86" s="20" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="19" t="n"/>
+      <c r="B89" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C86" s="19" t="n"/>
-      <c r="D86" s="19" t="n"/>
-      <c r="E86" s="19" t="n"/>
-      <c r="F86" s="19" t="n"/>
-      <c r="G86" s="19" t="n"/>
-      <c r="H86" s="19" t="n"/>
-      <c r="I86" s="19" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr"/>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="C89" s="19" t="n"/>
+      <c r="D89" s="19" t="n"/>
+      <c r="E89" s="19" t="n"/>
+      <c r="F89" s="19" t="n"/>
+      <c r="G89" s="19" t="n"/>
+      <c r="H89" s="19" t="n"/>
+      <c r="I89" s="19" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr"/>
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C90" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="5" t="n">
+      <c r="E90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H87" s="12" t="n">
+      <c r="H90" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I87" s="13" t="inlineStr">
+      <c r="I90" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="16" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B88" s="2" t="n"/>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
-      <c r="G88" s="2" t="n"/>
-      <c r="H88" s="2" t="n"/>
-      <c r="I88" s="2" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="18" t="n"/>
-      <c r="D89" s="18" t="n"/>
-      <c r="E89" s="18" t="n"/>
-      <c r="F89" s="18" t="n"/>
-      <c r="G89" s="18" t="n"/>
-      <c r="H89" s="18" t="n"/>
-      <c r="I89" s="18" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="21" t="n"/>
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr"/>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B92" s="18" t="n"/>
@@ -5886,40 +5963,40 @@
       <c r="I92" s="18" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="19" t="n"/>
-      <c r="B93" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C93" s="19" t="n"/>
-      <c r="D93" s="19" t="n"/>
-      <c r="E93" s="19" t="n"/>
-      <c r="F93" s="19" t="n"/>
-      <c r="G93" s="19" t="n"/>
-      <c r="H93" s="19" t="n"/>
-      <c r="I93" s="19" t="n"/>
+      <c r="A93" s="21" t="n"/>
+      <c r="B93" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="n"/>
+      <c r="D93" s="21" t="n"/>
+      <c r="E93" s="21" t="n"/>
+      <c r="F93" s="21" t="n"/>
+      <c r="G93" s="21" t="n"/>
+      <c r="H93" s="21" t="n"/>
+      <c r="I93" s="21" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C94" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
@@ -5927,7 +6004,7 @@
         </is>
       </c>
       <c r="H94" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -5938,7 +6015,7 @@
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B95" s="18" t="n"/>
@@ -5951,40 +6028,40 @@
       <c r="I95" s="18" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="21" t="n"/>
-      <c r="B96" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C96" s="21" t="n"/>
-      <c r="D96" s="21" t="n"/>
-      <c r="E96" s="21" t="n"/>
-      <c r="F96" s="21" t="n"/>
-      <c r="G96" s="21" t="n"/>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
+      <c r="A96" s="19" t="n"/>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C96" s="19" t="n"/>
+      <c r="D96" s="19" t="n"/>
+      <c r="E96" s="19" t="n"/>
+      <c r="F96" s="19" t="n"/>
+      <c r="G96" s="19" t="n"/>
+      <c r="H96" s="19" t="n"/>
+      <c r="I96" s="19" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
@@ -5992,7 +6069,7 @@
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -6003,7 +6080,7 @@
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B98" s="18" t="n"/>
@@ -6034,11 +6111,11 @@
       <c r="A100" s="5" t="inlineStr"/>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
@@ -6049,15 +6126,15 @@
         <v>2</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H100" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -6068,7 +6145,7 @@
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B101" s="18" t="n"/>
@@ -6099,121 +6176,121 @@
       <c r="A103" s="5" t="inlineStr"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="n"/>
+      <c r="C104" s="18" t="n"/>
+      <c r="D104" s="18" t="n"/>
+      <c r="E104" s="18" t="n"/>
+      <c r="F104" s="18" t="n"/>
+      <c r="G104" s="18" t="n"/>
+      <c r="H104" s="18" t="n"/>
+      <c r="I104" s="18" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C105" s="21" t="n"/>
+      <c r="D105" s="21" t="n"/>
+      <c r="E105" s="21" t="n"/>
+      <c r="F105" s="21" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr"/>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C106" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E106" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F103" s="5" t="n">
+      <c r="F106" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H103" s="12" t="n">
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="16" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B105" s="18" t="n"/>
-      <c r="C105" s="18" t="n"/>
-      <c r="D105" s="18" t="n"/>
-      <c r="E105" s="18" t="n"/>
-      <c r="F105" s="18" t="n"/>
-      <c r="G105" s="18" t="n"/>
-      <c r="H105" s="18" t="n"/>
-      <c r="I105" s="18" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="21" t="n"/>
-      <c r="B106" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C106" s="21" t="n"/>
-      <c r="D106" s="21" t="n"/>
-      <c r="E106" s="21" t="n"/>
-      <c r="F106" s="21" t="n"/>
-      <c r="G106" s="21" t="n"/>
-      <c r="H106" s="21" t="n"/>
-      <c r="I106" s="21" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr"/>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B108" s="18" t="n"/>
@@ -6229,7 +6306,7 @@
       <c r="A109" s="21" t="n"/>
       <c r="B109" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C109" s="21" t="n"/>
@@ -6244,278 +6321,347 @@
       <c r="A110" s="5" t="inlineStr"/>
       <c r="B110" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B111" s="18" t="n"/>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="18" t="n"/>
+      <c r="E111" s="18" t="n"/>
+      <c r="F111" s="18" t="n"/>
+      <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="n"/>
+      <c r="I111" s="18" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="21" t="n"/>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C112" s="21" t="n"/>
+      <c r="D112" s="21" t="n"/>
+      <c r="E112" s="21" t="n"/>
+      <c r="F112" s="21" t="n"/>
+      <c r="G112" s="21" t="n"/>
+      <c r="H112" s="21" t="n"/>
+      <c r="I112" s="21" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr"/>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C110" s="5" t="n">
+      <c r="C113" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E110" s="5" t="n">
+      <c r="E113" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F110" s="5" t="n">
+      <c r="F113" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G110" s="5" t="inlineStr">
+      <c r="G113" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H110" s="12" t="n">
+      <c r="H113" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I110" s="13" t="inlineStr">
+      <c r="I113" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="7" t="inlineStr"/>
-      <c r="B111" s="6" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr"/>
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C111" s="7" t="n">
+      <c r="C114" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D111" s="7" t="inlineStr">
+      <c r="D114" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E111" s="7" t="n">
+      <c r="E114" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F111" s="7" t="n">
+      <c r="F114" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H111" s="14" t="n">
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I111" s="15" t="inlineStr">
+      <c r="I114" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="17" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="21" t="n"/>
-      <c r="B113" s="22" t="inlineStr">
+      <c r="B115" s="18" t="n"/>
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="n"/>
+      <c r="B116" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C113" s="21" t="n"/>
-      <c r="D113" s="21" t="n"/>
-      <c r="E113" s="21" t="n"/>
-      <c r="F113" s="21" t="n"/>
-      <c r="G113" s="21" t="n"/>
-      <c r="H113" s="21" t="n"/>
-      <c r="I113" s="21" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr"/>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="C116" s="21" t="n"/>
+      <c r="D116" s="21" t="n"/>
+      <c r="E116" s="21" t="n"/>
+      <c r="F116" s="21" t="n"/>
+      <c r="G116" s="21" t="n"/>
+      <c r="H116" s="21" t="n"/>
+      <c r="I116" s="21" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr"/>
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C117" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E114" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="5" t="n">
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H117" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I114" s="13" t="inlineStr">
+      <c r="I117" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n"/>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="17" t="inlineStr">
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B116" s="18" t="n"/>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="21" t="n"/>
-      <c r="B117" s="22" t="inlineStr">
+      <c r="B119" s="18" t="n"/>
+      <c r="C119" s="18" t="n"/>
+      <c r="D119" s="18" t="n"/>
+      <c r="E119" s="18" t="n"/>
+      <c r="F119" s="18" t="n"/>
+      <c r="G119" s="18" t="n"/>
+      <c r="H119" s="18" t="n"/>
+      <c r="I119" s="18" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="n"/>
+      <c r="B120" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C117" s="21" t="n"/>
-      <c r="D117" s="21" t="n"/>
-      <c r="E117" s="21" t="n"/>
-      <c r="F117" s="21" t="n"/>
-      <c r="G117" s="21" t="n"/>
-      <c r="H117" s="21" t="n"/>
-      <c r="I117" s="21" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr"/>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="C120" s="21" t="n"/>
+      <c r="D120" s="21" t="n"/>
+      <c r="E120" s="21" t="n"/>
+      <c r="F120" s="21" t="n"/>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="21" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr"/>
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C121" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E118" s="5" t="n">
+      <c r="E121" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F118" s="5" t="n">
+      <c r="F121" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H118" s="12" t="n">
+      <c r="H121" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I118" s="13" t="inlineStr">
+      <c r="I121" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="77">
+  <mergeCells count="79">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="A108:I108"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="A101:I101"/>
     <mergeCell ref="B96:I96"/>
-    <mergeCell ref="B70:I70"/>
+    <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
+    <mergeCell ref="B120:I120"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B73:I73"/>
     <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A111:I111"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="A59:I59"/>
-    <mergeCell ref="B74:I74"/>
     <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A79:I79"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B113:I113"/>
     <mergeCell ref="B109:I109"/>
-    <mergeCell ref="A89:I89"/>
-    <mergeCell ref="A105:I105"/>
     <mergeCell ref="B102:I102"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="B86:I86"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A116:I116"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
+    <mergeCell ref="A91:I91"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B78:I78"/>
     <mergeCell ref="A115:I115"/>
-    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="B87:I87"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="A92:I92"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="B63:I63"/>
-    <mergeCell ref="A69:I69"/>
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A75:I75"/>
     <mergeCell ref="A80:I80"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="B27:I27"/>
     <mergeCell ref="B93:I93"/>
     <mergeCell ref="A104:I104"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="B117:I117"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
+    <mergeCell ref="B116:I116"/>
+    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B112:I112"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="A119:I119"/>
     <mergeCell ref="A16:I16"/>
-    <mergeCell ref="B106:I106"/>
     <mergeCell ref="B81:I81"/>
-    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="A118:I118"/>
     <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A86:I86"/>
     <mergeCell ref="A95:I95"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
@@ -6523,17 +6669,15 @@
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A112:I112"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="B99:I99"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A107:I107"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="A88:I88"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -6558,23 +6702,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6586,7 +6731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7438,24 +7583,59 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="546" customHeight="1">
+    <row r="24" ht="182" customHeight="1">
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>Subarray Sum Equals K</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>560</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int subarraySum(int[] nums, int k) {
+            int count = 0;
+     for(int i=0;i&lt;nums.length;i++){
+        int sum =0;
+        for(int j = i;j&lt;nums.length;j++){
+              sum+=nums[j];
+              if(sum == k) count++;
+        }
+     }
+     return count;     
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="546" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -7499,24 +7679,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="196" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="196" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -7535,24 +7715,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="406" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="406" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -7585,24 +7765,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="378" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="378" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -7634,24 +7814,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="560" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="560" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -7687,24 +7867,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="294" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="294" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -7730,24 +7910,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="224" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="224" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -7768,24 +7948,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="420" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="420" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -7820,24 +8000,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="378" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="378" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -7869,24 +8049,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="350" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="350" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -7916,24 +8096,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="238" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="238" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -7955,24 +8135,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="308" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="308" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -7999,24 +8179,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="280" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="280" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -8039,24 +8219,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="448" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="448" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -8091,24 +8271,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="378" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="378" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -8140,24 +8320,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="490" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="490" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -8185,24 +8365,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="308" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="308" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -8228,24 +8408,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="238" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="238" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -8265,24 +8445,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="560" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="560" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -8323,24 +8503,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="294" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="294" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -819,7 +819,7 @@
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Divide and Conquer, Dynamic Programming</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -838,73 +838,73 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>98</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>26.5</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Prefix Sum</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1544</v>
+        <v>26.5</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>48.6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table, Prefix Sum</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -913,17 +913,17 @@
         <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -939,24 +939,24 @@
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -965,24 +965,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -991,17 +991,17 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
@@ -1017,17 +1017,17 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1043,24 +1043,24 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1069,24 +1069,24 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -1095,24 +1095,24 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1121,17 +1121,17 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
@@ -1147,24 +1147,24 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
@@ -1173,17 +1173,17 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -1199,17 +1199,17 @@
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
@@ -1225,21 +1225,21 @@
         <v>1</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
         <v>0</v>
@@ -1248,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>47.2</v>
@@ -1261,274 +1261,274 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7" t="n">
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="7" t="n">
+      <c r="H27" s="5" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="8" t="inlineStr"/>
-      <c r="C27" s="9" t="n">
+      <c r="B28" s="8" t="inlineStr"/>
+      <c r="C28" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D27" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="D28" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr"/>
+      <c r="H28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="7" t="n">
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H31" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="7" t="n">
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr"/>
-      <c r="C33" s="9" t="n">
+      <c r="B34" s="8" t="inlineStr"/>
+      <c r="C34" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9" t="n">
+      <c r="D34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="9" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr"/>
+      <c r="H34" s="9" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7" t="n">
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>0</v>
@@ -1537,17 +1537,17 @@
         <v>1</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -1566,234 +1566,260 @@
         <v>2</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="7" t="n">
+      <c r="H39" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr"/>
-      <c r="C39" s="9" t="n">
+      <c r="B40" s="8" t="inlineStr"/>
+      <c r="C40" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="9" t="n">
+      <c r="D40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G39" s="9" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="n">
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr"/>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="n">
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr"/>
-      <c r="C43" s="9" t="n">
+      <c r="B44" s="8" t="inlineStr"/>
+      <c r="C44" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="9" t="n">
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="G44" s="9" t="inlineStr"/>
+      <c r="H44" s="9" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7" t="n">
+      <c r="C45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H44" s="7" t="n">
+      <c r="H45" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr"/>
-      <c r="C45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="9" t="inlineStr"/>
-      <c r="H45" s="9" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+      <c r="B46" s="8" t="inlineStr"/>
+      <c r="C46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr"/>
-      <c r="C46" s="11" t="n">
+      <c r="B47" s="10" t="inlineStr"/>
+      <c r="C47" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="D46" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="G46" s="11" t="inlineStr"/>
-      <c r="H46" s="11" t="inlineStr"/>
+      <c r="D47" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1809,7 +1835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3920,11 +3946,61 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Maximum Subarray</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Divide and Conquer, Dynamic Programming</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>46263.45222222222</v>
+      </c>
+      <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F44">
+  <conditionalFormatting sqref="F5:F45">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -3976,6 +4052,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3987,7 +4064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4030,7 +4107,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   25 solved   (Low: 15 · Medium: 10 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   26 solved   (Low: 15 · Medium: 11 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4355,7 +4432,7 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Dynamic Programming   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B19" s="18" t="n"/>
@@ -4386,11 +4463,11 @@
       <c r="A21" s="5" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Maximum Subarray</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>4003</v>
+        <v>53</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
@@ -4401,15 +4478,15 @@
         <v>1</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>98</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H21" s="12" t="n">
-        <v>46247.80789351852</v>
+        <v>46263.45222222222</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -4420,7 +4497,7 @@
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B22" s="18" t="n"/>
@@ -4433,150 +4510,150 @@
       <c r="I22" s="18" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="21" t="n"/>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="21" t="n"/>
-      <c r="H23" s="21" t="n"/>
-      <c r="I23" s="21" t="n"/>
+      <c r="A23" s="19" t="n"/>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="19" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t>Longest Fibonacci Subarray</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4003</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>46247.80789351852</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="n"/>
+      <c r="I25" s="18" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="21" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>Two Sum</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E27" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F27" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n">
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>46251.8174537037</v>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr"/>
-      <c r="B25" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C28" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="7" t="n">
+      <c r="E28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="7" t="n">
         <v>45.1</v>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="n">
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="n">
         <v>46252.95966435185</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="18" t="n"/>
-      <c r="I26" s="18" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="19" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr"/>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Subarray Sum Equals K</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>560</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>1544</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>46263.40873842593</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I28" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4585,7 +4662,7 @@
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B29" s="18" t="n"/>
@@ -4598,40 +4675,40 @@
       <c r="I29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="n"/>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="21" t="n"/>
-      <c r="G30" s="21" t="n"/>
-      <c r="H30" s="21" t="n"/>
-      <c r="I30" s="21" t="n"/>
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Contains Duplicate II</t>
+          <t>Subarray Sum Equals K</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>219</v>
+        <v>560</v>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
@@ -4639,7 +4716,7 @@
         </is>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46258.98878472222</v>
+        <v>46263.40873842593</v>
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
@@ -4650,7 +4727,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -4681,11 +4758,11 @@
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>1353</v>
+        <v>219</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
@@ -4693,10 +4770,10 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -4704,7 +4781,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -4715,7 +4792,7 @@
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B35" s="18" t="n"/>
@@ -4728,40 +4805,40 @@
       <c r="I35" s="18" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="n"/>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="19" t="n"/>
-      <c r="G36" s="19" t="n"/>
-      <c r="H36" s="19" t="n"/>
-      <c r="I36" s="19" t="n"/>
+      <c r="A36" s="21" t="n"/>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="21" t="n"/>
+      <c r="H36" s="21" t="n"/>
+      <c r="I36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -4769,7 +4846,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4780,7 +4857,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
@@ -4793,40 +4870,40 @@
       <c r="I38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
+      <c r="A39" s="19" t="n"/>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="19" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="19" t="n"/>
+      <c r="I39" s="19" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -4834,7 +4911,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -4845,7 +4922,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -4876,11 +4953,11 @@
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
@@ -4888,10 +4965,10 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
@@ -4899,7 +4976,7 @@
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -4910,7 +4987,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -4941,11 +5018,11 @@
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
@@ -4953,10 +5030,10 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
@@ -4964,7 +5041,7 @@
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -4975,7 +5052,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -4988,40 +5065,40 @@
       <c r="I47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n"/>
-      <c r="B48" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-      <c r="G48" s="19" t="n"/>
-      <c r="H48" s="19" t="n"/>
-      <c r="I48" s="19" t="n"/>
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="n"/>
+      <c r="H48" s="21" t="n"/>
+      <c r="I48" s="21" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -5029,7 +5106,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -5040,7 +5117,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -5053,40 +5130,40 @@
       <c r="I50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="n"/>
-      <c r="B51" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
+      <c r="A51" s="19" t="n"/>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="n"/>
+      <c r="D51" s="19" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="19" t="n"/>
+      <c r="G51" s="19" t="n"/>
+      <c r="H51" s="19" t="n"/>
+      <c r="I51" s="19" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -5094,7 +5171,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -5105,7 +5182,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -5118,40 +5195,40 @@
       <c r="I53" s="18" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="n"/>
-      <c r="B54" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="19" t="n"/>
-      <c r="E54" s="19" t="n"/>
-      <c r="F54" s="19" t="n"/>
-      <c r="G54" s="19" t="n"/>
-      <c r="H54" s="19" t="n"/>
-      <c r="I54" s="19" t="n"/>
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="n"/>
+      <c r="H54" s="21" t="n"/>
+      <c r="I54" s="21" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -5159,7 +5236,7 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -5170,7 +5247,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -5201,11 +5278,11 @@
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Corporate Flight Bookings</t>
+          <t>Matrix Block Sum</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1206</v>
+        <v>1242</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
@@ -5213,10 +5290,10 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>85</v>
+        <v>46.8</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -5224,7 +5301,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46262.6837962963</v>
+        <v>46262.8983912037</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -5235,7 +5312,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -5248,40 +5325,40 @@
       <c r="I59" s="18" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="n"/>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n"/>
-      <c r="D60" s="21" t="n"/>
-      <c r="E60" s="21" t="n"/>
-      <c r="F60" s="21" t="n"/>
-      <c r="G60" s="21" t="n"/>
-      <c r="H60" s="21" t="n"/>
-      <c r="I60" s="21" t="n"/>
+      <c r="A60" s="19" t="n"/>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n"/>
+      <c r="G60" s="19" t="n"/>
+      <c r="H60" s="19" t="n"/>
+      <c r="I60" s="19" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
@@ -5289,7 +5366,7 @@
         </is>
       </c>
       <c r="H61" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -5300,7 +5377,7 @@
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -5331,11 +5408,11 @@
       <c r="A64" s="5" t="inlineStr"/>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C64" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
@@ -5343,10 +5420,10 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
@@ -5354,7 +5431,7 @@
         </is>
       </c>
       <c r="H64" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -5365,7 +5442,7 @@
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -5396,11 +5473,11 @@
       <c r="A67" s="5" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C67" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
@@ -5408,10 +5485,10 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
@@ -5419,7 +5496,7 @@
         </is>
       </c>
       <c r="H67" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -5430,7 +5507,7 @@
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B68" s="18" t="n"/>
@@ -5446,7 +5523,7 @@
       <c r="A69" s="21" t="n"/>
       <c r="B69" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C69" s="21" t="n"/>
@@ -5461,301 +5538,301 @@
       <c r="A70" s="5" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C73" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="5" t="n">
+      <c r="E73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H70" s="12" t="n">
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I70" s="13" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="7" t="inlineStr"/>
-      <c r="B71" s="6" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="7" t="inlineStr"/>
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C71" s="7" t="n">
+      <c r="C74" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E71" s="7" t="n">
+      <c r="E74" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F71" s="7" t="n">
+      <c r="F74" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H71" s="14" t="n">
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I71" s="15" t="inlineStr">
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B72" s="18" t="n"/>
-      <c r="C72" s="18" t="n"/>
-      <c r="D72" s="18" t="n"/>
-      <c r="E72" s="18" t="n"/>
-      <c r="F72" s="18" t="n"/>
-      <c r="G72" s="18" t="n"/>
-      <c r="H72" s="18" t="n"/>
-      <c r="I72" s="18" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="19" t="n"/>
-      <c r="B73" s="20" t="inlineStr">
+      <c r="B75" s="18" t="n"/>
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
+      <c r="G75" s="18" t="n"/>
+      <c r="H75" s="18" t="n"/>
+      <c r="I75" s="18" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="19" t="n"/>
+      <c r="B76" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C73" s="19" t="n"/>
-      <c r="D73" s="19" t="n"/>
-      <c r="E73" s="19" t="n"/>
-      <c r="F73" s="19" t="n"/>
-      <c r="G73" s="19" t="n"/>
-      <c r="H73" s="19" t="n"/>
-      <c r="I73" s="19" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr"/>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="C76" s="19" t="n"/>
+      <c r="D76" s="19" t="n"/>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="19" t="n"/>
+      <c r="G76" s="19" t="n"/>
+      <c r="H76" s="19" t="n"/>
+      <c r="I76" s="19" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr"/>
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C77" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E74" s="5" t="n">
+      <c r="E77" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F77" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H74" s="12" t="n">
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I74" s="13" t="inlineStr">
+      <c r="I77" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="16" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="n"/>
-      <c r="F75" s="2" t="n"/>
-      <c r="G75" s="2" t="n"/>
-      <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B76" s="18" t="n"/>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
-      <c r="H76" s="18" t="n"/>
-      <c r="I76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="n"/>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B79" s="18" t="n"/>
+      <c r="C79" s="18" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
+      <c r="G79" s="18" t="n"/>
+      <c r="H79" s="18" t="n"/>
+      <c r="I79" s="18" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="n"/>
+      <c r="B80" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C77" s="21" t="n"/>
-      <c r="D77" s="21" t="n"/>
-      <c r="E77" s="21" t="n"/>
-      <c r="F77" s="21" t="n"/>
-      <c r="G77" s="21" t="n"/>
-      <c r="H77" s="21" t="n"/>
-      <c r="I77" s="21" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="C80" s="21" t="n"/>
+      <c r="D80" s="21" t="n"/>
+      <c r="E80" s="21" t="n"/>
+      <c r="F80" s="21" t="n"/>
+      <c r="G80" s="21" t="n"/>
+      <c r="H80" s="21" t="n"/>
+      <c r="I80" s="21" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr"/>
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C81" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D81" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="5" t="n">
+      <c r="E81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G78" s="5" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I78" s="13" t="inlineStr">
+      <c r="I81" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="16" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
-      <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B80" s="18" t="n"/>
-      <c r="C80" s="18" t="n"/>
-      <c r="D80" s="18" t="n"/>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
-      <c r="G80" s="18" t="n"/>
-      <c r="H80" s="18" t="n"/>
-      <c r="I80" s="18" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="21" t="n"/>
-      <c r="B81" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C81" s="21" t="n"/>
-      <c r="D81" s="21" t="n"/>
-      <c r="E81" s="21" t="n"/>
-      <c r="F81" s="21" t="n"/>
-      <c r="G81" s="21" t="n"/>
-      <c r="H81" s="21" t="n"/>
-      <c r="I81" s="21" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr"/>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B83" s="18" t="n"/>
@@ -5786,11 +5863,11 @@
       <c r="A85" s="5" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C85" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
@@ -5798,18 +5875,18 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H85" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -5820,7 +5897,7 @@
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B86" s="18" t="n"/>
@@ -5851,171 +5928,171 @@
       <c r="A88" s="5" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="n"/>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+      <c r="G89" s="18" t="n"/>
+      <c r="H89" s="18" t="n"/>
+      <c r="I89" s="18" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="n"/>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C90" s="21" t="n"/>
+      <c r="D90" s="21" t="n"/>
+      <c r="E90" s="21" t="n"/>
+      <c r="F90" s="21" t="n"/>
+      <c r="G90" s="21" t="n"/>
+      <c r="H90" s="21" t="n"/>
+      <c r="I90" s="21" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr"/>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C91" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D91" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="5" t="n">
+      <c r="E91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="n">
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I88" s="13" t="inlineStr">
+      <c r="I91" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="19" t="n"/>
-      <c r="B89" s="20" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="19" t="n"/>
+      <c r="B92" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C89" s="19" t="n"/>
-      <c r="D89" s="19" t="n"/>
-      <c r="E89" s="19" t="n"/>
-      <c r="F89" s="19" t="n"/>
-      <c r="G89" s="19" t="n"/>
-      <c r="H89" s="19" t="n"/>
-      <c r="I89" s="19" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr"/>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="C92" s="19" t="n"/>
+      <c r="D92" s="19" t="n"/>
+      <c r="E92" s="19" t="n"/>
+      <c r="F92" s="19" t="n"/>
+      <c r="G92" s="19" t="n"/>
+      <c r="H92" s="19" t="n"/>
+      <c r="I92" s="19" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr"/>
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C93" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" s="5" t="n">
+      <c r="E93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H90" s="12" t="n">
+      <c r="H93" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I90" s="13" t="inlineStr">
+      <c r="I93" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="n"/>
-      <c r="G91" s="2" t="n"/>
-      <c r="H91" s="2" t="n"/>
-      <c r="I91" s="2" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B92" s="18" t="n"/>
-      <c r="C92" s="18" t="n"/>
-      <c r="D92" s="18" t="n"/>
-      <c r="E92" s="18" t="n"/>
-      <c r="F92" s="18" t="n"/>
-      <c r="G92" s="18" t="n"/>
-      <c r="H92" s="18" t="n"/>
-      <c r="I92" s="18" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="21" t="n"/>
-      <c r="B93" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="21" t="n"/>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr"/>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B95" s="18" t="n"/>
@@ -6028,40 +6105,40 @@
       <c r="I95" s="18" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="19" t="n"/>
-      <c r="B96" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C96" s="19" t="n"/>
-      <c r="D96" s="19" t="n"/>
-      <c r="E96" s="19" t="n"/>
-      <c r="F96" s="19" t="n"/>
-      <c r="G96" s="19" t="n"/>
-      <c r="H96" s="19" t="n"/>
-      <c r="I96" s="19" t="n"/>
+      <c r="A96" s="21" t="n"/>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="21" t="n"/>
+      <c r="E96" s="21" t="n"/>
+      <c r="F96" s="21" t="n"/>
+      <c r="G96" s="21" t="n"/>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="21" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
@@ -6069,7 +6146,7 @@
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -6080,7 +6157,7 @@
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B98" s="18" t="n"/>
@@ -6093,40 +6170,40 @@
       <c r="I98" s="18" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="21" t="n"/>
-      <c r="B99" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C99" s="21" t="n"/>
-      <c r="D99" s="21" t="n"/>
-      <c r="E99" s="21" t="n"/>
-      <c r="F99" s="21" t="n"/>
-      <c r="G99" s="21" t="n"/>
-      <c r="H99" s="21" t="n"/>
-      <c r="I99" s="21" t="n"/>
+      <c r="A99" s="19" t="n"/>
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C99" s="19" t="n"/>
+      <c r="D99" s="19" t="n"/>
+      <c r="E99" s="19" t="n"/>
+      <c r="F99" s="19" t="n"/>
+      <c r="G99" s="19" t="n"/>
+      <c r="H99" s="19" t="n"/>
+      <c r="I99" s="19" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr"/>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
@@ -6134,7 +6211,7 @@
         </is>
       </c>
       <c r="H100" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -6145,7 +6222,7 @@
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B101" s="18" t="n"/>
@@ -6176,11 +6253,11 @@
       <c r="A103" s="5" t="inlineStr"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C103" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
@@ -6191,15 +6268,15 @@
         <v>2</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H103" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -6210,7 +6287,7 @@
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B104" s="18" t="n"/>
@@ -6241,121 +6318,121 @@
       <c r="A106" s="5" t="inlineStr"/>
       <c r="B106" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="18" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="18" t="n"/>
+      <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="n"/>
+      <c r="I107" s="18" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="n"/>
+      <c r="B108" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C108" s="21" t="n"/>
+      <c r="D108" s="21" t="n"/>
+      <c r="E108" s="21" t="n"/>
+      <c r="F108" s="21" t="n"/>
+      <c r="G108" s="21" t="n"/>
+      <c r="H108" s="21" t="n"/>
+      <c r="I108" s="21" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr"/>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C109" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E106" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F106" s="5" t="n">
+      <c r="F109" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H106" s="12" t="n">
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I106" s="13" t="inlineStr">
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="16" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B107" s="2" t="n"/>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B108" s="18" t="n"/>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-      <c r="G108" s="18" t="n"/>
-      <c r="H108" s="18" t="n"/>
-      <c r="I108" s="18" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="21" t="n"/>
-      <c r="B109" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C109" s="21" t="n"/>
-      <c r="D109" s="21" t="n"/>
-      <c r="E109" s="21" t="n"/>
-      <c r="F109" s="21" t="n"/>
-      <c r="G109" s="21" t="n"/>
-      <c r="H109" s="21" t="n"/>
-      <c r="I109" s="21" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="inlineStr"/>
-      <c r="B110" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C110" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D110" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G110" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I110" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B111" s="18" t="n"/>
@@ -6371,7 +6448,7 @@
       <c r="A112" s="21" t="n"/>
       <c r="B112" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C112" s="21" t="n"/>
@@ -6386,298 +6463,365 @@
       <c r="A113" s="5" t="inlineStr"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="n"/>
+      <c r="C114" s="18" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="18" t="n"/>
+      <c r="F114" s="18" t="n"/>
+      <c r="G114" s="18" t="n"/>
+      <c r="H114" s="18" t="n"/>
+      <c r="I114" s="18" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="n"/>
+      <c r="B115" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C115" s="21" t="n"/>
+      <c r="D115" s="21" t="n"/>
+      <c r="E115" s="21" t="n"/>
+      <c r="F115" s="21" t="n"/>
+      <c r="G115" s="21" t="n"/>
+      <c r="H115" s="21" t="n"/>
+      <c r="I115" s="21" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr"/>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C116" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E113" s="5" t="n">
+      <c r="E116" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F113" s="5" t="n">
+      <c r="F116" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H113" s="12" t="n">
+      <c r="H116" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I113" s="13" t="inlineStr">
+      <c r="I116" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="7" t="inlineStr"/>
-      <c r="B114" s="6" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="7" t="inlineStr"/>
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C114" s="7" t="n">
+      <c r="C117" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D114" s="7" t="inlineStr">
+      <c r="D117" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E114" s="7" t="n">
+      <c r="E117" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F114" s="7" t="n">
+      <c r="F117" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H114" s="14" t="n">
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H117" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I114" s="15" t="inlineStr">
+      <c r="I117" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="17" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B115" s="18" t="n"/>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="18" t="n"/>
-      <c r="E115" s="18" t="n"/>
-      <c r="F115" s="18" t="n"/>
-      <c r="G115" s="18" t="n"/>
-      <c r="H115" s="18" t="n"/>
-      <c r="I115" s="18" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="21" t="n"/>
-      <c r="B116" s="22" t="inlineStr">
+      <c r="B118" s="18" t="n"/>
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="18" t="n"/>
+      <c r="E118" s="18" t="n"/>
+      <c r="F118" s="18" t="n"/>
+      <c r="G118" s="18" t="n"/>
+      <c r="H118" s="18" t="n"/>
+      <c r="I118" s="18" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="n"/>
+      <c r="B119" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C116" s="21" t="n"/>
-      <c r="D116" s="21" t="n"/>
-      <c r="E116" s="21" t="n"/>
-      <c r="F116" s="21" t="n"/>
-      <c r="G116" s="21" t="n"/>
-      <c r="H116" s="21" t="n"/>
-      <c r="I116" s="21" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr"/>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="C119" s="21" t="n"/>
+      <c r="D119" s="21" t="n"/>
+      <c r="E119" s="21" t="n"/>
+      <c r="F119" s="21" t="n"/>
+      <c r="G119" s="21" t="n"/>
+      <c r="H119" s="21" t="n"/>
+      <c r="I119" s="21" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr"/>
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C120" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E117" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" s="5" t="n">
+      <c r="E120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H117" s="12" t="n">
+      <c r="H120" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I117" s="13" t="inlineStr">
+      <c r="I120" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="17" t="inlineStr">
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="2" t="n"/>
+      <c r="H121" s="2" t="n"/>
+      <c r="I121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B119" s="18" t="n"/>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="18" t="n"/>
-      <c r="E119" s="18" t="n"/>
-      <c r="F119" s="18" t="n"/>
-      <c r="G119" s="18" t="n"/>
-      <c r="H119" s="18" t="n"/>
-      <c r="I119" s="18" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="21" t="n"/>
-      <c r="B120" s="22" t="inlineStr">
+      <c r="B122" s="18" t="n"/>
+      <c r="C122" s="18" t="n"/>
+      <c r="D122" s="18" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="18" t="n"/>
+      <c r="G122" s="18" t="n"/>
+      <c r="H122" s="18" t="n"/>
+      <c r="I122" s="18" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="n"/>
+      <c r="B123" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C120" s="21" t="n"/>
-      <c r="D120" s="21" t="n"/>
-      <c r="E120" s="21" t="n"/>
-      <c r="F120" s="21" t="n"/>
-      <c r="G120" s="21" t="n"/>
-      <c r="H120" s="21" t="n"/>
-      <c r="I120" s="21" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr"/>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="C123" s="21" t="n"/>
+      <c r="D123" s="21" t="n"/>
+      <c r="E123" s="21" t="n"/>
+      <c r="F123" s="21" t="n"/>
+      <c r="G123" s="21" t="n"/>
+      <c r="H123" s="21" t="n"/>
+      <c r="I123" s="21" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr"/>
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C124" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
+      <c r="E124" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F124" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H121" s="12" t="n">
+      <c r="H124" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I121" s="13" t="inlineStr">
+      <c r="I124" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="79">
+  <mergeCells count="81">
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="B54:I54"/>
-    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="B72:I72"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="A101:I101"/>
     <mergeCell ref="B96:I96"/>
     <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B120:I120"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B73:I73"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A111:I111"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="A59:I59"/>
+    <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="A79:I79"/>
+    <mergeCell ref="B76:I76"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B109:I109"/>
+    <mergeCell ref="A89:I89"/>
+    <mergeCell ref="B115:I115"/>
     <mergeCell ref="B102:I102"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A71:I71"/>
     <mergeCell ref="B39:I39"/>
-    <mergeCell ref="A76:I76"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
-    <mergeCell ref="A91:I91"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="A115:I115"/>
     <mergeCell ref="B87:I87"/>
     <mergeCell ref="A83:I83"/>
-    <mergeCell ref="A92:I92"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
+    <mergeCell ref="A94:I94"/>
     <mergeCell ref="B63:I63"/>
+    <mergeCell ref="A78:I78"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A75:I75"/>
-    <mergeCell ref="A80:I80"/>
     <mergeCell ref="B66:I66"/>
-    <mergeCell ref="B27:I27"/>
-    <mergeCell ref="B93:I93"/>
     <mergeCell ref="A104:I104"/>
-    <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B116:I116"/>
+    <mergeCell ref="B119:I119"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="B112:I112"/>
-    <mergeCell ref="B89:I89"/>
-    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A82:I82"/>
+    <mergeCell ref="A110:I110"/>
     <mergeCell ref="A16:I16"/>
-    <mergeCell ref="B81:I81"/>
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="A25:I25"/>
     <mergeCell ref="A118:I118"/>
+    <mergeCell ref="B90:I90"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="A86:I86"/>
     <mergeCell ref="A95:I95"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B60:I60"/>
+    <mergeCell ref="A122:I122"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A72:I72"/>
     <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A121:I121"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="B99:I99"/>
+    <mergeCell ref="B108:I108"/>
+    <mergeCell ref="A114:I114"/>
     <mergeCell ref="B84:I84"/>
+    <mergeCell ref="B92:I92"/>
     <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="A107:I107"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B80:I80"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -6687,7 +6831,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId11"/>
@@ -6703,23 +6847,24 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6731,7 +6876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6981,24 +7126,60 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="210" customHeight="1">
+    <row r="10" ht="196" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>Maximum Subarray</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>53</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int maxSubArray(int[] nums) {
+    int sum = 0;
+    int max = nums[0];
+    for(int i =0;i&lt;nums.length;i++){
+        sum+=nums[i];
+        if(sum&gt;max){
+            max = sum;
+        }
+        if(sum&lt;0) sum = 0;
+    }  
+    return max;  
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="210" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int lengthOfLastWord(String s) {
@@ -7018,24 +7199,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="560" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="560" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>94</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7074,24 +7255,24 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="406" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13" ht="406" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;111 - Minimum Depth of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/minimum-depth-of-binary-tree/"&gt;minimum-depth-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a binary tree, find its minimum depth.&lt;/p&gt;
 &lt;p&gt;The minimum depth is the number of nodes along the shortest path from the root node down to the nearest leaf node.&lt;/p&gt;
@@ -7118,24 +7299,24 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="532" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14" ht="532" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="7" t="n">
         <v>125</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -7169,24 +7350,24 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="126" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15" ht="126" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -7200,24 +7381,24 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="238" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="238" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -7239,24 +7420,24 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="294" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="17" ht="294" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -7282,24 +7463,24 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="238" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="238" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -7321,24 +7502,24 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="238" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="238" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -7360,24 +7541,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="392" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="392" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -7410,24 +7591,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="238" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="238" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -7448,24 +7629,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="308" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="308" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>303</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -7489,24 +7670,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="420" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="420" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -7538,24 +7719,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="420" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="420" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
@@ -7583,24 +7764,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="182" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="182" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -7618,24 +7799,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="546" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="546" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -7679,24 +7860,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="196" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="196" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -7715,24 +7896,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="406" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="406" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">class Solution {
     public static boolean isPalindrome(char[] ch, int left, int right) {
@@ -7765,24 +7946,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="378" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="378" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -7814,24 +7995,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="560" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="560" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -7867,24 +8048,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="294" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="294" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isBoomerang(int[][] points) {
@@ -7910,24 +8091,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="224" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="224" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -7948,24 +8129,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="420" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="420" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -8000,24 +8181,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="378" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="378" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -8049,24 +8230,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="350" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="350" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -8096,24 +8277,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="238" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="238" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -8135,24 +8316,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="308" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="308" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -8179,24 +8360,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="280" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="280" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -8219,24 +8400,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="448" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="448" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -8271,24 +8452,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="378" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="378" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -8320,24 +8501,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="490" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="490" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -8365,24 +8546,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="308" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="308" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int largestInteger(int[] nums, int k) {
@@ -8408,24 +8589,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="238" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="238" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -8445,24 +8626,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="560" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="560" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
@@ -8503,24 +8684,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="294" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="294" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1</v>
@@ -1170,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>85</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="23">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr"/>
       <c r="C28" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>11</v>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G28" s="9" t="inlineStr"/>
       <c r="H28" s="9" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B47" s="10" t="inlineStr"/>
       <c r="C47" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>13</v>
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G47" s="11" t="inlineStr"/>
       <c r="H47" s="11" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -3991,6 +3991,56 @@
         <v>46263.45222222222</v>
       </c>
       <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>4284</v>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Smallest Stable Index I</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Prefix Sum</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="14" t="n">
+        <v>46270.61052083333</v>
+      </c>
+      <c r="L46" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4000,7 +4050,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F45">
+  <conditionalFormatting sqref="F5:F46">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -4053,6 +4103,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4064,7 +4115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I124"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4107,7 +4158,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   26 solved   (Low: 15 · Medium: 11 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   27 solved   (Low: 16 · Medium: 11 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4237,7 +4288,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H10" s="12" t="n">
@@ -4547,7 +4598,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H24" s="12" t="n">
@@ -4612,7 +4663,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H27" s="12" t="n">
@@ -4647,7 +4698,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H28" s="14" t="n">
@@ -4972,7 +5023,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H43" s="12" t="n">
@@ -5312,7 +5363,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -5325,1503 +5376,1554 @@
       <c r="I59" s="18" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="19" t="n"/>
-      <c r="B60" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-      <c r="G60" s="19" t="n"/>
-      <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="n"/>
+      <c r="H60" s="21" t="n"/>
+      <c r="I60" s="21" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>Smallest Stable Index I</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>4284</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>46270.61052083333</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="19" t="n"/>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="n"/>
+      <c r="D62" s="19" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="19" t="n"/>
+      <c r="G62" s="19" t="n"/>
+      <c r="H62" s="19" t="n"/>
+      <c r="I62" s="19" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C63" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E63" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F63" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
+      <c r="G63" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H61" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>46262.6837962963</v>
       </c>
-      <c r="I61" s="13" t="inlineStr">
+      <c r="I63" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="18" t="n"/>
-      <c r="D62" s="18" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="18" t="n"/>
-      <c r="G62" s="18" t="n"/>
-      <c r="H62" s="18" t="n"/>
-      <c r="I62" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="21" t="n"/>
-      <c r="B63" s="22" t="inlineStr">
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="18" t="n"/>
+      <c r="I64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="n"/>
+      <c r="B65" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C63" s="21" t="n"/>
-      <c r="D63" s="21" t="n"/>
-      <c r="E63" s="21" t="n"/>
-      <c r="F63" s="21" t="n"/>
-      <c r="G63" s="21" t="n"/>
-      <c r="H63" s="21" t="n"/>
-      <c r="I63" s="21" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr"/>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="21" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr"/>
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C66" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="n">
+      <c r="E66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="H66" s="12" t="n">
         <v>46255.01133101852</v>
       </c>
-      <c r="I64" s="13" t="inlineStr">
+      <c r="I66" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-      <c r="G65" s="18" t="n"/>
-      <c r="H65" s="18" t="n"/>
-      <c r="I65" s="18" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="21" t="n"/>
-      <c r="B66" s="22" t="inlineStr">
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="18" t="n"/>
+      <c r="I67" s="18" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="n"/>
+      <c r="B68" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C66" s="21" t="n"/>
-      <c r="D66" s="21" t="n"/>
-      <c r="E66" s="21" t="n"/>
-      <c r="F66" s="21" t="n"/>
-      <c r="G66" s="21" t="n"/>
-      <c r="H66" s="21" t="n"/>
-      <c r="I66" s="21" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr"/>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="21" t="n"/>
+      <c r="E68" s="21" t="n"/>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="21" t="n"/>
+      <c r="H68" s="21" t="n"/>
+      <c r="I68" s="21" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr"/>
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C69" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
+      <c r="E69" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F69" s="5" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H67" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>46256.65385416667</v>
       </c>
-      <c r="I67" s="13" t="inlineStr">
+      <c r="I69" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B68" s="18" t="n"/>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="18" t="n"/>
-      <c r="I68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="21" t="n"/>
-      <c r="B69" s="22" t="inlineStr">
+      <c r="B70" s="18" t="n"/>
+      <c r="C70" s="18" t="n"/>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="18" t="n"/>
+      <c r="G70" s="18" t="n"/>
+      <c r="H70" s="18" t="n"/>
+      <c r="I70" s="18" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="n"/>
+      <c r="B71" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr"/>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="21" t="n"/>
+      <c r="E71" s="21" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="21" t="n"/>
+      <c r="H71" s="21" t="n"/>
+      <c r="I71" s="21" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr"/>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C72" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D72" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E70" s="5" t="n">
+      <c r="E72" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F72" s="5" t="n">
         <v>47.2</v>
       </c>
-      <c r="G70" s="5" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H70" s="12" t="n">
+      <c r="H72" s="12" t="n">
         <v>46247.02123842593</v>
       </c>
-      <c r="I70" s="13" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="17" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="18" t="n"/>
-      <c r="I71" s="18" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="21" t="n"/>
-      <c r="B72" s="22" t="inlineStr">
+      <c r="B73" s="18" t="n"/>
+      <c r="C73" s="18" t="n"/>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="18" t="n"/>
+      <c r="H73" s="18" t="n"/>
+      <c r="I73" s="18" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="n"/>
+      <c r="B74" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C72" s="21" t="n"/>
-      <c r="D72" s="21" t="n"/>
-      <c r="E72" s="21" t="n"/>
-      <c r="F72" s="21" t="n"/>
-      <c r="G72" s="21" t="n"/>
-      <c r="H72" s="21" t="n"/>
-      <c r="I72" s="21" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr"/>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="C74" s="21" t="n"/>
+      <c r="D74" s="21" t="n"/>
+      <c r="E74" s="21" t="n"/>
+      <c r="F74" s="21" t="n"/>
+      <c r="G74" s="21" t="n"/>
+      <c r="H74" s="21" t="n"/>
+      <c r="I74" s="21" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr"/>
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C75" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="5" t="n">
+      <c r="E75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H73" s="12" t="n">
+      <c r="H75" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I73" s="13" t="inlineStr">
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="7" t="inlineStr"/>
-      <c r="B74" s="6" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="7" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C74" s="7" t="n">
+      <c r="C76" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E74" s="7" t="n">
+      <c r="E76" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="7" t="n">
+      <c r="F76" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G74" s="7" t="inlineStr">
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H74" s="14" t="n">
+      <c r="H76" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I74" s="15" t="inlineStr">
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="17" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B75" s="18" t="n"/>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="18" t="n"/>
-      <c r="E75" s="18" t="n"/>
-      <c r="F75" s="18" t="n"/>
-      <c r="G75" s="18" t="n"/>
-      <c r="H75" s="18" t="n"/>
-      <c r="I75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="19" t="n"/>
-      <c r="B76" s="20" t="inlineStr">
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="19" t="n"/>
+      <c r="B78" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C76" s="19" t="n"/>
-      <c r="D76" s="19" t="n"/>
-      <c r="E76" s="19" t="n"/>
-      <c r="F76" s="19" t="n"/>
-      <c r="G76" s="19" t="n"/>
-      <c r="H76" s="19" t="n"/>
-      <c r="I76" s="19" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="5" t="inlineStr"/>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="C78" s="19" t="n"/>
+      <c r="D78" s="19" t="n"/>
+      <c r="E78" s="19" t="n"/>
+      <c r="F78" s="19" t="n"/>
+      <c r="G78" s="19" t="n"/>
+      <c r="H78" s="19" t="n"/>
+      <c r="I78" s="19" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr"/>
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C79" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E79" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F79" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H77" s="12" t="n">
+      <c r="H79" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I77" s="13" t="inlineStr">
+      <c r="I79" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B78" s="2" t="n"/>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
-      <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B79" s="18" t="n"/>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="18" t="n"/>
-      <c r="E79" s="18" t="n"/>
-      <c r="F79" s="18" t="n"/>
-      <c r="G79" s="18" t="n"/>
-      <c r="H79" s="18" t="n"/>
-      <c r="I79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="21" t="n"/>
-      <c r="B80" s="22" t="inlineStr">
+      <c r="B81" s="18" t="n"/>
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="21" t="n"/>
+      <c r="B82" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C80" s="21" t="n"/>
-      <c r="D80" s="21" t="n"/>
-      <c r="E80" s="21" t="n"/>
-      <c r="F80" s="21" t="n"/>
-      <c r="G80" s="21" t="n"/>
-      <c r="H80" s="21" t="n"/>
-      <c r="I80" s="21" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr"/>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="C82" s="21" t="n"/>
+      <c r="D82" s="21" t="n"/>
+      <c r="E82" s="21" t="n"/>
+      <c r="F82" s="21" t="n"/>
+      <c r="G82" s="21" t="n"/>
+      <c r="H82" s="21" t="n"/>
+      <c r="I82" s="21" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr"/>
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C83" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D81" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" s="5" t="n">
+      <c r="E83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G83" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H81" s="12" t="n">
+      <c r="H83" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I81" s="13" t="inlineStr">
+      <c r="I83" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="16" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="n"/>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B83" s="18" t="n"/>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="18" t="n"/>
-      <c r="I83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="21" t="n"/>
-      <c r="B84" s="22" t="inlineStr">
+      <c r="B85" s="18" t="n"/>
+      <c r="C85" s="18" t="n"/>
+      <c r="D85" s="18" t="n"/>
+      <c r="E85" s="18" t="n"/>
+      <c r="F85" s="18" t="n"/>
+      <c r="G85" s="18" t="n"/>
+      <c r="H85" s="18" t="n"/>
+      <c r="I85" s="18" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="n"/>
+      <c r="B86" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C84" s="21" t="n"/>
-      <c r="D84" s="21" t="n"/>
-      <c r="E84" s="21" t="n"/>
-      <c r="F84" s="21" t="n"/>
-      <c r="G84" s="21" t="n"/>
-      <c r="H84" s="21" t="n"/>
-      <c r="I84" s="21" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr"/>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="C86" s="21" t="n"/>
+      <c r="D86" s="21" t="n"/>
+      <c r="E86" s="21" t="n"/>
+      <c r="F86" s="21" t="n"/>
+      <c r="G86" s="21" t="n"/>
+      <c r="H86" s="21" t="n"/>
+      <c r="I86" s="21" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr"/>
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C87" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D87" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E87" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F87" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G87" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H85" s="12" t="n">
+      <c r="H87" s="12" t="n">
         <v>46255.88138888889</v>
       </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="I87" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="17" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B86" s="18" t="n"/>
-      <c r="C86" s="18" t="n"/>
-      <c r="D86" s="18" t="n"/>
-      <c r="E86" s="18" t="n"/>
-      <c r="F86" s="18" t="n"/>
-      <c r="G86" s="18" t="n"/>
-      <c r="H86" s="18" t="n"/>
-      <c r="I86" s="18" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="21" t="n"/>
-      <c r="B87" s="22" t="inlineStr">
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="18" t="n"/>
+      <c r="E88" s="18" t="n"/>
+      <c r="F88" s="18" t="n"/>
+      <c r="G88" s="18" t="n"/>
+      <c r="H88" s="18" t="n"/>
+      <c r="I88" s="18" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C87" s="21" t="n"/>
-      <c r="D87" s="21" t="n"/>
-      <c r="E87" s="21" t="n"/>
-      <c r="F87" s="21" t="n"/>
-      <c r="G87" s="21" t="n"/>
-      <c r="H87" s="21" t="n"/>
-      <c r="I87" s="21" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr"/>
-      <c r="B88" s="4" t="inlineStr">
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="21" t="n"/>
+      <c r="E89" s="21" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="21" t="n"/>
+      <c r="I89" s="21" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr"/>
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C90" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E88" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="5" t="n">
+      <c r="E90" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H88" s="12" t="n">
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="n">
         <v>46240.74578703703</v>
       </c>
-      <c r="I88" s="13" t="inlineStr">
+      <c r="I90" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="17" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="18" t="n"/>
-      <c r="D89" s="18" t="n"/>
-      <c r="E89" s="18" t="n"/>
-      <c r="F89" s="18" t="n"/>
-      <c r="G89" s="18" t="n"/>
-      <c r="H89" s="18" t="n"/>
-      <c r="I89" s="18" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="21" t="n"/>
-      <c r="B90" s="22" t="inlineStr">
+      <c r="B91" s="18" t="n"/>
+      <c r="C91" s="18" t="n"/>
+      <c r="D91" s="18" t="n"/>
+      <c r="E91" s="18" t="n"/>
+      <c r="F91" s="18" t="n"/>
+      <c r="G91" s="18" t="n"/>
+      <c r="H91" s="18" t="n"/>
+      <c r="I91" s="18" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="n"/>
+      <c r="B92" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C90" s="21" t="n"/>
-      <c r="D90" s="21" t="n"/>
-      <c r="E90" s="21" t="n"/>
-      <c r="F90" s="21" t="n"/>
-      <c r="G90" s="21" t="n"/>
-      <c r="H90" s="21" t="n"/>
-      <c r="I90" s="21" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="inlineStr"/>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="n">
-        <v>3918</v>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>46256.95832175926</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="19" t="n"/>
-      <c r="B92" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C92" s="19" t="n"/>
-      <c r="D92" s="19" t="n"/>
-      <c r="E92" s="19" t="n"/>
-      <c r="F92" s="19" t="n"/>
-      <c r="G92" s="19" t="n"/>
-      <c r="H92" s="19" t="n"/>
-      <c r="I92" s="19" t="n"/>
+      <c r="C92" s="21" t="n"/>
+      <c r="D92" s="21" t="n"/>
+      <c r="E92" s="21" t="n"/>
+      <c r="F92" s="21" t="n"/>
+      <c r="G92" s="21" t="n"/>
+      <c r="H92" s="21" t="n"/>
+      <c r="I92" s="21" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="n"/>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="n"/>
+      <c r="D94" s="19" t="n"/>
+      <c r="E94" s="19" t="n"/>
+      <c r="F94" s="19" t="n"/>
+      <c r="G94" s="19" t="n"/>
+      <c r="H94" s="19" t="n"/>
+      <c r="I94" s="19" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C95" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D95" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="5" t="n">
+      <c r="E95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H93" s="12" t="n">
+      <c r="H95" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I95" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="16" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B94" s="2" t="n"/>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="17" t="inlineStr">
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
+      <c r="I96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B95" s="18" t="n"/>
-      <c r="C95" s="18" t="n"/>
-      <c r="D95" s="18" t="n"/>
-      <c r="E95" s="18" t="n"/>
-      <c r="F95" s="18" t="n"/>
-      <c r="G95" s="18" t="n"/>
-      <c r="H95" s="18" t="n"/>
-      <c r="I95" s="18" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="21" t="n"/>
-      <c r="B96" s="22" t="inlineStr">
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="18" t="n"/>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="n"/>
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C96" s="21" t="n"/>
-      <c r="D96" s="21" t="n"/>
-      <c r="E96" s="21" t="n"/>
-      <c r="F96" s="21" t="n"/>
-      <c r="G96" s="21" t="n"/>
-      <c r="H96" s="21" t="n"/>
-      <c r="I96" s="21" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr"/>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="21" t="n"/>
+      <c r="E98" s="21" t="n"/>
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C99" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D97" s="5" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="5" t="n">
+      <c r="E99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G97" s="5" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>46241.78204861111</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="18" t="n"/>
+      <c r="D100" s="18" t="n"/>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+      <c r="G100" s="18" t="n"/>
+      <c r="H100" s="18" t="n"/>
+      <c r="I100" s="18" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="n"/>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C101" s="19" t="n"/>
+      <c r="D101" s="19" t="n"/>
+      <c r="E101" s="19" t="n"/>
+      <c r="F101" s="19" t="n"/>
+      <c r="G101" s="19" t="n"/>
+      <c r="H101" s="19" t="n"/>
+      <c r="I101" s="19" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr"/>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Longest Substring Without Repeating Characters</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>69</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H97" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
+      <c r="H102" s="12" t="n">
+        <v>46253.82314814815</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B98" s="18" t="n"/>
-      <c r="C98" s="18" t="n"/>
-      <c r="D98" s="18" t="n"/>
-      <c r="E98" s="18" t="n"/>
-      <c r="F98" s="18" t="n"/>
-      <c r="G98" s="18" t="n"/>
-      <c r="H98" s="18" t="n"/>
-      <c r="I98" s="18" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="19" t="n"/>
-      <c r="B99" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C99" s="19" t="n"/>
-      <c r="D99" s="19" t="n"/>
-      <c r="E99" s="19" t="n"/>
-      <c r="F99" s="19" t="n"/>
-      <c r="G99" s="19" t="n"/>
-      <c r="H99" s="19" t="n"/>
-      <c r="I99" s="19" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="5" t="inlineStr"/>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>Longest Substring Without Repeating Characters</t>
-        </is>
-      </c>
-      <c r="C100" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="F100" s="5" t="n">
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="n"/>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="n"/>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C104" s="21" t="n"/>
+      <c r="D104" s="21" t="n"/>
+      <c r="E104" s="21" t="n"/>
+      <c r="F104" s="21" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="21" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr"/>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Valid Anagram</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>46243.94849537037</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="n"/>
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="n"/>
+      <c r="B107" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C107" s="21" t="n"/>
+      <c r="D107" s="21" t="n"/>
+      <c r="E107" s="21" t="n"/>
+      <c r="F107" s="21" t="n"/>
+      <c r="G107" s="21" t="n"/>
+      <c r="H107" s="21" t="n"/>
+      <c r="I107" s="21" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr"/>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="n"/>
+      <c r="C109" s="18" t="n"/>
+      <c r="D109" s="18" t="n"/>
+      <c r="E109" s="18" t="n"/>
+      <c r="F109" s="18" t="n"/>
+      <c r="G109" s="18" t="n"/>
+      <c r="H109" s="18" t="n"/>
+      <c r="I109" s="18" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="n"/>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C110" s="21" t="n"/>
+      <c r="D110" s="21" t="n"/>
+      <c r="E110" s="21" t="n"/>
+      <c r="F110" s="21" t="n"/>
+      <c r="G110" s="21" t="n"/>
+      <c r="H110" s="21" t="n"/>
+      <c r="I110" s="21" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr"/>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Valid Palindrome II</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>680</v>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F111" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>46245.98399305555</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B113" s="18" t="n"/>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="n"/>
+      <c r="B114" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C114" s="21" t="n"/>
+      <c r="D114" s="21" t="n"/>
+      <c r="E114" s="21" t="n"/>
+      <c r="F114" s="21" t="n"/>
+      <c r="G114" s="21" t="n"/>
+      <c r="H114" s="21" t="n"/>
+      <c r="I114" s="21" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr"/>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>Java</t>
         </is>
       </c>
-      <c r="H100" s="12" t="n">
-        <v>46253.82314814815</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
+      <c r="H115" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-      <c r="G101" s="18" t="n"/>
-      <c r="H101" s="18" t="n"/>
-      <c r="I101" s="18" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="21" t="n"/>
-      <c r="B102" s="22" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="n"/>
+      <c r="B117" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C117" s="21" t="n"/>
+      <c r="D117" s="21" t="n"/>
+      <c r="E117" s="21" t="n"/>
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr"/>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Minimum Depth of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>46246.95925925926</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="7" t="inlineStr"/>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Average of Levels in Binary Tree</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>637</v>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H119" s="14" t="n">
+        <v>46246.98880787037</v>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="n"/>
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="18" t="n"/>
+      <c r="E120" s="18" t="n"/>
+      <c r="F120" s="18" t="n"/>
+      <c r="G120" s="18" t="n"/>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="n"/>
+      <c r="B121" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C102" s="21" t="n"/>
-      <c r="D102" s="21" t="n"/>
-      <c r="E102" s="21" t="n"/>
-      <c r="F102" s="21" t="n"/>
-      <c r="G102" s="21" t="n"/>
-      <c r="H102" s="21" t="n"/>
-      <c r="I102" s="21" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr"/>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Valid Anagram</t>
-        </is>
-      </c>
-      <c r="C103" s="5" t="n">
-        <v>242</v>
-      </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="C121" s="21" t="n"/>
+      <c r="D121" s="21" t="n"/>
+      <c r="E121" s="21" t="n"/>
+      <c r="F121" s="21" t="n"/>
+      <c r="G121" s="21" t="n"/>
+      <c r="H121" s="21" t="n"/>
+      <c r="I121" s="21" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr"/>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Binary Tree Inorder Traversal</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E103" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>46243.94849537037</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="E122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>46246.86910879629</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B104" s="18" t="n"/>
-      <c r="C104" s="18" t="n"/>
-      <c r="D104" s="18" t="n"/>
-      <c r="E104" s="18" t="n"/>
-      <c r="F104" s="18" t="n"/>
-      <c r="G104" s="18" t="n"/>
-      <c r="H104" s="18" t="n"/>
-      <c r="I104" s="18" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="n"/>
-      <c r="B105" s="22" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="n"/>
+      <c r="C124" s="18" t="n"/>
+      <c r="D124" s="18" t="n"/>
+      <c r="E124" s="18" t="n"/>
+      <c r="F124" s="18" t="n"/>
+      <c r="G124" s="18" t="n"/>
+      <c r="H124" s="18" t="n"/>
+      <c r="I124" s="18" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="n"/>
+      <c r="B125" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C105" s="21" t="n"/>
-      <c r="D105" s="21" t="n"/>
-      <c r="E105" s="21" t="n"/>
-      <c r="F105" s="21" t="n"/>
-      <c r="G105" s="21" t="n"/>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
-      <c r="B106" s="4" t="inlineStr">
-        <is>
-          <t>Valid Palindrome</t>
-        </is>
-      </c>
-      <c r="C106" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="C125" s="21" t="n"/>
+      <c r="D125" s="21" t="n"/>
+      <c r="E125" s="21" t="n"/>
+      <c r="F125" s="21" t="n"/>
+      <c r="G125" s="21" t="n"/>
+      <c r="H125" s="21" t="n"/>
+      <c r="I125" s="21" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr"/>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Generate Fibonacci Sequence</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>2775</v>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E106" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="G106" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>46243.9169675926</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
+      <c r="E126" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>46247.79274305556</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B107" s="18" t="n"/>
-      <c r="C107" s="18" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="21" t="n"/>
-      <c r="B108" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C108" s="21" t="n"/>
-      <c r="D108" s="21" t="n"/>
-      <c r="E108" s="21" t="n"/>
-      <c r="F108" s="21" t="n"/>
-      <c r="G108" s="21" t="n"/>
-      <c r="H108" s="21" t="n"/>
-      <c r="I108" s="21" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr"/>
-      <c r="B109" s="4" t="inlineStr">
-        <is>
-          <t>Valid Palindrome II</t>
-        </is>
-      </c>
-      <c r="C109" s="5" t="n">
-        <v>680</v>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>46245.98399305555</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="n"/>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B111" s="18" t="n"/>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="18" t="n"/>
-      <c r="E111" s="18" t="n"/>
-      <c r="F111" s="18" t="n"/>
-      <c r="G111" s="18" t="n"/>
-      <c r="H111" s="18" t="n"/>
-      <c r="I111" s="18" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="21" t="n"/>
-      <c r="B112" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C112" s="21" t="n"/>
-      <c r="D112" s="21" t="n"/>
-      <c r="E112" s="21" t="n"/>
-      <c r="F112" s="21" t="n"/>
-      <c r="G112" s="21" t="n"/>
-      <c r="H112" s="21" t="n"/>
-      <c r="I112" s="21" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr"/>
-      <c r="B113" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C113" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H113" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B114" s="18" t="n"/>
-      <c r="C114" s="18" t="n"/>
-      <c r="D114" s="18" t="n"/>
-      <c r="E114" s="18" t="n"/>
-      <c r="F114" s="18" t="n"/>
-      <c r="G114" s="18" t="n"/>
-      <c r="H114" s="18" t="n"/>
-      <c r="I114" s="18" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="21" t="n"/>
-      <c r="B115" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C115" s="21" t="n"/>
-      <c r="D115" s="21" t="n"/>
-      <c r="E115" s="21" t="n"/>
-      <c r="F115" s="21" t="n"/>
-      <c r="G115" s="21" t="n"/>
-      <c r="H115" s="21" t="n"/>
-      <c r="I115" s="21" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="inlineStr"/>
-      <c r="B116" s="4" t="inlineStr">
-        <is>
-          <t>Minimum Depth of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E116" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G116" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>46246.95925925926</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="7" t="inlineStr"/>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>Average of Levels in Binary Tree</t>
-        </is>
-      </c>
-      <c r="C117" s="7" t="n">
-        <v>637</v>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F117" s="7" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H117" s="14" t="n">
-        <v>46246.98880787037</v>
-      </c>
-      <c r="I117" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B118" s="18" t="n"/>
-      <c r="C118" s="18" t="n"/>
-      <c r="D118" s="18" t="n"/>
-      <c r="E118" s="18" t="n"/>
-      <c r="F118" s="18" t="n"/>
-      <c r="G118" s="18" t="n"/>
-      <c r="H118" s="18" t="n"/>
-      <c r="I118" s="18" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="21" t="n"/>
-      <c r="B119" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C119" s="21" t="n"/>
-      <c r="D119" s="21" t="n"/>
-      <c r="E119" s="21" t="n"/>
-      <c r="F119" s="21" t="n"/>
-      <c r="G119" s="21" t="n"/>
-      <c r="H119" s="21" t="n"/>
-      <c r="I119" s="21" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="inlineStr"/>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>Binary Tree Inorder Traversal</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G120" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="n">
-        <v>46246.86910879629</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="n"/>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="2" t="n"/>
-      <c r="F121" s="2" t="n"/>
-      <c r="G121" s="2" t="n"/>
-      <c r="H121" s="2" t="n"/>
-      <c r="I121" s="2" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="18" t="n"/>
-      <c r="D122" s="18" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
-      <c r="G122" s="18" t="n"/>
-      <c r="H122" s="18" t="n"/>
-      <c r="I122" s="18" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="21" t="n"/>
-      <c r="B123" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C123" s="21" t="n"/>
-      <c r="D123" s="21" t="n"/>
-      <c r="E123" s="21" t="n"/>
-      <c r="F123" s="21" t="n"/>
-      <c r="G123" s="21" t="n"/>
-      <c r="H123" s="21" t="n"/>
-      <c r="I123" s="21" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr"/>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>Generate Fibonacci Sequence</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="n">
-        <v>2775</v>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="G124" s="5" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="H124" s="12" t="n">
-        <v>46247.79274305556</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="81">
+  <mergeCells count="82">
     <mergeCell ref="A41:I41"/>
+    <mergeCell ref="B62:I62"/>
     <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B125:I125"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A101:I101"/>
-    <mergeCell ref="B96:I96"/>
-    <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
+    <mergeCell ref="A85:I85"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A109:I109"/>
     <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B82:I82"/>
     <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A111:I111"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="A59:I59"/>
-    <mergeCell ref="B123:I123"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="A103:I103"/>
     <mergeCell ref="B36:I36"/>
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="B76:I76"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="A89:I89"/>
-    <mergeCell ref="B115:I115"/>
-    <mergeCell ref="B102:I102"/>
-    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="B110:I110"/>
+    <mergeCell ref="B86:I86"/>
     <mergeCell ref="B39:I39"/>
+    <mergeCell ref="A116:I116"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
+    <mergeCell ref="A91:I91"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="B87:I87"/>
-    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A100:I100"/>
+    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="A77:I77"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
-    <mergeCell ref="A94:I94"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="A78:I78"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A75:I75"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="B114:I114"/>
+    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A120:I120"/>
+    <mergeCell ref="A113:I113"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
+    <mergeCell ref="B117:I117"/>
     <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A106:I106"/>
+    <mergeCell ref="B101:I101"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B119:I119"/>
-    <mergeCell ref="B69:I69"/>
-    <mergeCell ref="B112:I112"/>
-    <mergeCell ref="A82:I82"/>
-    <mergeCell ref="A110:I110"/>
+    <mergeCell ref="A96:I96"/>
+    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="B104:I104"/>
+    <mergeCell ref="A124:I124"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="B26:I26"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A118:I118"/>
-    <mergeCell ref="B90:I90"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="B121:I121"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A86:I86"/>
-    <mergeCell ref="A95:I95"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B107:I107"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A122:I122"/>
+    <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A121:I121"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="A112:I112"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="B99:I99"/>
-    <mergeCell ref="B108:I108"/>
-    <mergeCell ref="A114:I114"/>
-    <mergeCell ref="B84:I84"/>
+    <mergeCell ref="A64:I64"/>
     <mergeCell ref="B92:I92"/>
-    <mergeCell ref="A98:I98"/>
     <mergeCell ref="B30:I30"/>
-    <mergeCell ref="A107:I107"/>
+    <mergeCell ref="A73:I73"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B80:I80"/>
+    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="B94:I94"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
@@ -6844,27 +6946,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6876,7 +6979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6931,7 +7034,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="196" customHeight="1">
+    <row r="5" ht="560" customHeight="1">
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
@@ -6945,25 +7048,41 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int[] twoSum(int[] nums, int target) {
-        int[] arr=new int[2];
-       	 for(int i=0;i&lt;nums.length;i++) { 
-		 for(int j=i+1;j&lt;nums.length;j++) { 
-			 if(nums[i]+nums[j]==target) { 
-				arr[0]=i;
-                arr[1]=j;
-			 }
-		 }
-	 }
-     return arr;
-}
-}</t>
+          <t>&lt;h1&gt;1 - Two Sum&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/two-sum/"&gt;two-sum&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of integers &lt;code&gt;nums&lt;/code&gt;&amp;nbsp;and an integer &lt;code&gt;target&lt;/code&gt;, return &lt;em&gt;indices of the two numbers such that they add up to &lt;code&gt;target&lt;/code&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;You may assume that each input would have &lt;strong&gt;&lt;em&gt;exactly&lt;/em&gt; one solution&lt;/strong&gt;, and you may not use the &lt;em&gt;same&lt;/em&gt; element twice.&lt;/p&gt;
+&lt;p&gt;You can return the answer in any order.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [2,7,11,15], target = 9
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;strong&gt;Explanation:&lt;/strong&gt; Because nums[0] + nums[1] == 9, we return [0, 1].
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,2,4], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [1,2]
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; nums = [3,3], target = 6
+&lt;strong&gt;Output:&lt;/strong&gt; [0,1]
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;2 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-10&lt;sup&gt;9&lt;/sup&gt; &amp;lt;= target &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Only one valid answer exists.&lt;/strong&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;strong&gt;Follow-up:&amp;nbsp;&lt;/strong&gt;Can you come up with an algorithm that is less than &lt;code&gt;O(n&lt;sup&gt;2&lt;/sup&gt;)&lt;/code&gt;&lt;font face="monospace"&gt;&amp;nbsp;&lt;/font&gt;time complexity?</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7281,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="210" customHeight="1">
+    <row r="11" ht="532" customHeight="1">
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
@@ -7176,26 +7295,40 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int lengthOfLastWord(String s) {
-    char[] ch =s.toCharArray();
-    int count=0;
-    int i = s.length()-1;
-    while(s.charAt(i) == ' '){
-        i--;
-    }
-    while(i&gt;=0 &amp;&amp; s.charAt(i) !=' '){
-        count++;
-        i--;
-    }
-    return count;
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;Hello World&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 5
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;World&amp;quot; with length 5.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;   fly me   to   the moon  &amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 4
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;moon&amp;quot; with length 4.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;luffy is still joyboy&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; 6
+&lt;strong&gt;Explanation:&lt;/strong&gt; The last word is &amp;quot;joyboy&amp;quot; with length 6.
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of only English letters and spaces &lt;code&gt;&amp;#39; &amp;#39;&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;There will be at least one word in &lt;code&gt;s&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -7350,7 +7483,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="126" customHeight="1">
+    <row r="15" ht="532" customHeight="1">
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
@@ -7364,20 +7497,37 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
-          <t>class Solution {
-    public int singleNumber(int[] nums) {
-    int result = 0;
-    for (int n : nums) {
-    result ^= n;
-}
-return result;
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;136 - Single Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/single-number/"&gt;single-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a &lt;strong&gt;non-empty&lt;/strong&gt;&amp;nbsp;array of integers &lt;code&gt;nums&lt;/code&gt;, every element appears &lt;em&gt;twice&lt;/em&gt; except for one. Find that single one.&lt;/p&gt;
+&lt;p&gt;You must&amp;nbsp;implement a solution with a linear runtime complexity and use&amp;nbsp;only constant&amp;nbsp;extra space.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [2,2,1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;1&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [4,1,2,1,2]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;4&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [1]&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;1&lt;/span&gt;&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 3 * 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;-3 * 10&lt;sup&gt;4&lt;/sup&gt; &amp;lt;= nums[i] &amp;lt;= 3 * 10&lt;sup&gt;4&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;Each element in the array appears twice except for one element which appears only once.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7741,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="238" customHeight="1">
+    <row r="21" ht="182" customHeight="1">
       <c r="A21" s="5" t="n">
         <v>17</v>
       </c>
@@ -7612,18 +7762,15 @@
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
-        if(nums.length&lt;1){ 
-            return;
+    int numbers = 0;
+    for(int traverse = 0;traverse&lt;nums.length;traverse++){
+        if(nums[traverse] != 0){
+            int temp = nums[traverse];
+            nums[traverse] = nums[numbers];
+            nums[numbers] = temp;
+            numbers++;
         }
-        int n=0;
-      for(int i=0;i&lt;nums.length;i++){ 
-        if(nums[i]!=0){ 
-            int temp=nums[i];
-           nums[i]=nums[n];
-           nums[n]=temp;
-           n++;
-         }
-      } 
+    }  
     }
 }</t>
         </is>
@@ -7719,7 +7866,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="420" customHeight="1">
+    <row r="24" ht="546" customHeight="1">
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
@@ -7733,34 +7880,44 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;543 - Diameter of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/diameter-of-binary-tree/"&gt;diameter-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the length of the &lt;strong&gt;diameter&lt;/strong&gt; of the tree&lt;/em&gt;.&lt;/p&gt;
-&lt;p&gt;The &lt;strong&gt;diameter&lt;/strong&gt; of a binary tree is the &lt;strong&gt;length&lt;/strong&gt; of the longest path between any two nodes in a tree. This path may or may not pass through the &lt;code&gt;root&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;The &lt;strong&gt;length&lt;/strong&gt; of a path between two nodes is represented by the number of edges between them.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;img alt="" src="https://assets.leetcode.com/uploads/2021/03/06/diamtree.jpg" style="width: 292px; height: 302px;" /&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; root = [1,2,3,4,5]
-&lt;strong&gt;Output:&lt;/strong&gt; 3
-&lt;strong&gt;Explanation:&lt;/strong&gt; 3 is the length of the path [4,2,1,3] or [5,2,1,3].
-&lt;/pre&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;pre&gt;
-&lt;strong&gt;Input:&lt;/strong&gt; root = [1,2]
-&lt;strong&gt;Output:&lt;/strong&gt; 1
-&lt;/pre&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;The number of nodes in the tree is in the range &lt;code&gt;[1, 10&lt;sup&gt;4&lt;/sup&gt;]&lt;/code&gt;.&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;-100 &amp;lt;= Node.val &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>/**
+ * Definition for a binary tree node.
+ * public class TreeNode {
+ *     int val;
+ *     TreeNode left;
+ *     TreeNode right;
+ *     TreeNode() {}
+ *     TreeNode(int val) { this.val = val; }
+ *     TreeNode(int val, TreeNode left, TreeNode right) {
+ *         this.val = val;
+ *         this.left = left;
+ *         this.right = right;
+ *     }
+ * }
+ */
+class Solution {
+    int max = 0;
+    public int height(TreeNode root) {
+        if (root == null) {
+            return 0;
+        }
+        int left = height(root.left);
+        int right = height(root.right);
+        // Diameter passing through this node
+        max = Math.max(max, left + right);
+        // Return height of this node
+        return 1 + Math.max(left, right);
+    }
+    public int diameterOfBinaryTree(TreeNode root) {
+        height(root);
+        return max;
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -7896,7 +8053,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="406" customHeight="1">
+    <row r="28" ht="462" customHeight="1">
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
@@ -7910,38 +8067,35 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">class Solution {
-    public static boolean isPalindrome(char[] ch, int left, int right) {
-    while(left &lt; right) {
-        if(ch[left] != ch[right]) {
-            return false;
-        }
-        left++;
-        right--;
-    }
-    return true;
-}
-    public boolean validPalindrome(String s) {
-      char[] ch = s.toCharArray();
-      int left =0;
-      int right = ch.length-1;
-      while(left&lt;=right){
-        if(ch[left] == ch[right]){
-           left++;
-           right--;
-        }else {
-            return isPalindrome(ch, left + 1, right) ||
-            isPalindrome(ch, left, right - 1);
-      }
-      }
-      return true;
-    }
-    }
+          <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;aba&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abca&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;strong&gt;Explanation:&lt;/strong&gt; You could delete the character &amp;#39;c&amp;#39;.
+&lt;/pre&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;
+&lt;strong&gt;Input:&lt;/strong&gt; s = &amp;quot;abc&amp;quot;
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= s.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;s&lt;/code&gt; consists of lowercase English letters.&lt;/li&gt;
+&lt;/ul&gt;
 </t>
         </is>
       </c>
@@ -8062,32 +8216,29 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>class Solution {
-    public boolean isBoomerang(int[][] points) {
-    int x1=0,x2=0,x3=0;
-    int y1=0,y2=0,y3=0;
-    for(int i =0;i&lt;points.length;i++){
-        for(int j=0;j&lt;points[i].length-1;j++){
-           if(i==0){
-            x1 = points[i][j];
-            y1 = points[i][j+1];
-           }else if(i == 1){
-             x2 = points[i][j];
-             y2 = points[i][j+1];
-           }else{
-            x3 = points[i][j];
-            y3 = points[i][j+1];
-           }
-        }
-    } 
-    return !((y2-y1)*(x3-x1) == (y3 - y1)*(x2-x1));   
-    }
-}</t>
+          <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
+&lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,3],[3,2]]
+&lt;strong&gt;Output:&lt;/strong&gt; true
+&lt;/pre&gt;&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
+&lt;pre&gt;&lt;strong&gt;Input:&lt;/strong&gt; points = [[1,1],[2,2],[3,3]]
+&lt;strong&gt;Output:&lt;/strong&gt; false
+&lt;/pre&gt;
+&lt;p&gt;&amp;nbsp;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;&lt;code&gt;points.length == 3&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;points[i].length == 2&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt; &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
         </is>
       </c>
     </row>
@@ -8501,7 +8652,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="490" customHeight="1">
+    <row r="41" ht="266" customHeight="1">
       <c r="A41" s="5" t="n">
         <v>37</v>
       </c>
@@ -8515,77 +8666,100 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public static int digits(int num){
+        int multiply =1;
+        while(num!=0){
+            int rem = num%10;
+            multiply *= rem;
+            num /= 10;
+        }
+        return multiply;
+    }
+    public int smallestNumber(int n, int t) {
+    while(true){
+        if(digits(n)%t == 0){
+          return n;
+        } 
+        n++;
+    }
+}
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="560" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Find the Largest Almost Missing Integer</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>3705</v>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;h1&gt;3626 - Smallest Divisible Digit Product I&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/smallest-divisible-digit-product-i/"&gt;smallest-divisible-digit-product-i&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given two integers &lt;code&gt;n&lt;/code&gt; and &lt;code&gt;t&lt;/code&gt;. Return the &lt;strong&gt;smallest&lt;/strong&gt; number greater than or equal to &lt;code&gt;n&lt;/code&gt; such that the &lt;strong&gt;product of its digits&lt;/strong&gt; is divisible by &lt;code&gt;t&lt;/code&gt;.&lt;/p&gt;
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
+&lt;p&gt;Return the &lt;b&gt;largest&lt;/b&gt; &lt;strong&gt;almost missing&lt;/strong&gt; integer from &lt;code&gt;nums&lt;/code&gt;. If no such integer exists, return &lt;code&gt;-1&lt;/code&gt;.&lt;/p&gt;
+A &lt;strong&gt;subarray&lt;/strong&gt; is a contiguous sequence of elements within an array.
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 10, t = 2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;10&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,2,1,7], k = 3&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;7&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 10 is 0, which is divisible by 2, making it the smallest number greater than or equal to 10 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 3: &lt;code&gt;[9, 2, 1]&lt;/code&gt; and &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, &lt;code&gt;[9, 2, 1]&lt;/code&gt;, &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="2"&gt;3 appears in 1 subarray of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="3"&gt;7 appears in 1 subarray of size 3: &lt;code&gt;[2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li index="4"&gt;9 appears in 2 subarrays of size 3: &lt;code&gt;[3, 9, 2]&lt;/code&gt;, and &lt;code&gt;[9, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 7 since it is the largest integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
 &lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;n = 15, t = 3&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;16&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [3,9,7,2,1,7], k = 4&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;3&lt;/span&gt;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The digit product of 16 is 6, which is divisible by 3, making it the smallest number greater than or equal to 15 that satisfies the condition.&lt;/p&gt;
+&lt;ul&gt;
+	&lt;li&gt;1 appears in 2 subarrays of size 4: &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;2 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;3 appears in 1 subarray of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;7 appears in 3 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;, &lt;code&gt;[7, 2, 1, 7]&lt;/code&gt;.&lt;/li&gt;
+	&lt;li&gt;9 appears in 2 subarrays of size 4: &lt;code&gt;[3, 9, 7, 2]&lt;/code&gt;, &lt;code&gt;[9, 7, 2, 1]&lt;/code&gt;.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;p&gt;We return 3 since it is the largest and only integer that appears in exactly one subarray of size &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
+&lt;/div&gt;
+&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
+&lt;div class="example-block"&gt;
+&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [0,0], k = 1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;-1&lt;/span&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;There is no integer that appears in only one subarray of size 1.&lt;/p&gt;
 &lt;/div&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= n &amp;lt;= 100&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= t &amp;lt;= 10&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums.length &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;0 &amp;lt;= nums[i] &amp;lt;= 50&lt;/code&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;code&gt;1 &amp;lt;= k &amp;lt;= nums.length&lt;/code&gt;&lt;/li&gt;
 &lt;/ul&gt;
 </t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="308" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Find the Largest Almost Missing Integer</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>3705</v>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>class Solution {
-    public int largestInteger(int[] nums, int k) {
-    int[] arr = new int[51];
-    for(int i = 0;i&lt;nums.length-k+1;i++){
-        boolean[] seen = new boolean[51];
-        for(int j = i;j&lt;i+k &amp;&amp; j&lt;nums.length;j++){
-            if (!seen[nums[j]]){
-               arr[nums[j]]++;
-               seen[nums[j]] = true;
-            } 
-        }
-    } 
-    int high =-1;
-    for(int i=0;i&lt;arr.length;i++){
-        if(arr[i] == 1){
-           if(high&lt;i) high = i;
-        }
-    } 
-    return high;
-    }
-}</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8800,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="560" customHeight="1">
+    <row r="44" ht="252" customHeight="1">
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
@@ -8640,47 +8814,29 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;h1&gt;4003 - Longest Fibonacci Subarray&lt;/h1&gt;&lt;h2&gt;Difficulty: Medium - &lt;a href="https://leetcode.com/problems/longest-fibonacci-subarray/"&gt;longest-fibonacci-subarray&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an array of &lt;strong&gt;positive&lt;/strong&gt; integers &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;A &lt;strong&gt;Fibonacci&lt;/strong&gt; array is a contiguous sequence whose third and subsequent terms each equal the sum of the two preceding terms.&lt;/p&gt;
-&lt;p&gt;Return the length of the longest &lt;strong&gt;Fibonacci&lt;/strong&gt; &lt;strong&gt;&lt;span data-keyword="subarray-nonempty"&gt;subarray&lt;/span&gt;&lt;/strong&gt; in &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Note:&lt;/strong&gt; Subarrays of length 1 or 2 are always &lt;strong&gt;Fibonacci&lt;/strong&gt;.&lt;/p&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 1:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [1,1,1,1,2,3,5,1]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;5&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The longest Fibonacci subarray is &lt;code&gt;nums[2..6] = [1, 1, 2, 3, 5]&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;code&gt;[1, 1, 2, 3, 5]&lt;/code&gt; is Fibonacci because &lt;code&gt;1 + 1 = 2&lt;/code&gt;, &lt;code&gt;1 + 2 = 3&lt;/code&gt;, and &lt;code&gt;2 + 3 = 5&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 2:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [5,2,7,9,16]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;5&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The longest Fibonacci subarray is &lt;code&gt;nums[0..4] = [5, 2, 7, 9, 16]&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;code&gt;[5, 2, 7, 9, 16]&lt;/code&gt; is Fibonacci because &lt;code&gt;5 + 2 = 7&lt;/code&gt;, &lt;code&gt;2 + 7 = 9&lt;/code&gt;, and &lt;code&gt;7 + 9 = 16&lt;/code&gt;.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&lt;strong class="example"&gt;Example 3:&lt;/strong&gt;&lt;/p&gt;
-&lt;div class="example-block"&gt;
-&lt;p&gt;&lt;strong&gt;Input:&lt;/strong&gt; &lt;span class="example-io"&gt;nums = [1000000000,1000000000,1000000000]&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Output:&lt;/strong&gt; &lt;span class="example-io"&gt;2&lt;/span&gt;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Explanation:&lt;/strong&gt;&lt;/p&gt;
-&lt;p&gt;The longest Fibonacci subarray is &lt;code&gt;nums[1..2] = [1000000000, 1000000000]&lt;/code&gt;.&lt;/p&gt;
-&lt;p&gt;&lt;code&gt;[1000000000, 1000000000]&lt;/code&gt; is Fibonacci because its length is 2.&lt;/p&gt;
-&lt;/div&gt;
-&lt;p&gt;&amp;nbsp;&lt;/p&gt;
-&lt;p&gt;&lt;strong&gt;Constraints:&lt;/strong&gt;&lt;/p&gt;
-&lt;ul&gt;
-	&lt;li&gt;&lt;code&gt;3 &amp;lt;= nums.length &amp;lt;= 10&lt;sup&gt;5&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;code&gt;1 &amp;lt;= nums[i] &amp;lt;= 10&lt;sup&gt;9&lt;/sup&gt;&lt;/code&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>class Solution {
+    public int longestSubarray(int[] nums) {
+    int high = 2;
+    int count = 2;
+    for(int i = 2 ; i&lt;nums.length;i++ ){
+     if(nums[i] == nums[i-1] +  nums[i-2]){
+        count++;
+     }else if(count&gt;high){
+        high = count;
+        count = 2;
+     }else{
+        count =2;
+     }
+    } 
+    if(count &gt; high) return count;
+    return high;   
+    }
+}</t>
         </is>
       </c>
     </row>
@@ -8727,6 +8883,45 @@
         </is>
       </c>
     </row>
+    <row r="46" ht="252" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Smallest Stable Index I</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>4284</v>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int firstStableIndex(int[] nums, int k) {
+        int max = Integer.MIN_VALUE;
+        int j =0;
+    for(int i =0;i&lt;nums.length;i++){
+        max = Math.max(max,nums[i]);
+        int min = Integer.MAX_VALUE;
+        for(j=i;j&lt;nums.length;j++){
+            min = Math.min(min,nums[j]);
+        }
+         if(max - min &lt;=k){
+            return i;
+        }
+    }   
+    return -1;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E2"/>

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Binary Search, Sliding Window, Prefix Sum</t>
+          <t>Binary Search</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -731,21 +731,21 @@
         <v>1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>69.2</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Bit Manipulation</t>
+          <t>Binary Search, Sliding Window, Prefix Sum</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>1</v>
@@ -754,24 +754,24 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>46.1</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Design, Matrix, Prefix Sum</t>
+          <t>Bit Manipulation</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>1</v>
@@ -780,27 +780,27 @@
         <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>112</v>
+        <v>2.5</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>142</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Design, Prefix Sum</t>
+          <t>Design, Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -809,24 +809,24 @@
         <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>47.7</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Divide and Conquer, Dynamic Programming</t>
+          <t>Design, Prefix Sum</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>0</v>
@@ -835,17 +835,17 @@
         <v>1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>80.90000000000001</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Divide and Conquer, Dynamic Programming</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -864,73 +864,73 @@
         <v>1</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>98</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Hash Table</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>26.5</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>46</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Prefix Sum</t>
+          <t>Hash Table</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1544</v>
+        <v>26.5</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>48.6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sliding Window</t>
+          <t>Hash Table, Prefix Sum</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -939,17 +939,17 @@
         <v>1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
@@ -965,24 +965,24 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -991,24 +991,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1017,17 +1017,17 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1043,17 +1043,17 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -1069,24 +1069,24 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
@@ -1095,24 +1095,24 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1121,24 +1121,24 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -1147,21 +1147,21 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>1</v>
@@ -1170,46 +1170,46 @@
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>65.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>46.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
@@ -1225,17 +1225,17 @@
         <v>1</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -1251,21 +1251,21 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
@@ -1274,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H26" s="7" t="n">
         <v>47.2</v>
@@ -1287,274 +1287,274 @@
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>47.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="5" t="n">
+      <c r="C28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H28" s="7" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="8" t="inlineStr"/>
-      <c r="C28" s="9" t="n">
+      <c r="B29" s="8" t="inlineStr"/>
+      <c r="C29" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>27</v>
-      </c>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="D29" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr"/>
+      <c r="H29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="5" t="n">
+      <c r="C30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H32" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="G34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="7" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr"/>
-      <c r="C34" s="9" t="n">
+      <c r="B35" s="8" t="inlineStr"/>
+      <c r="C35" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="9" t="n">
+      <c r="D35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr"/>
+      <c r="H35" s="9" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="5" t="n">
+      <c r="C36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H36" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0</v>
@@ -1563,17 +1563,17 @@
         <v>1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
@@ -1592,234 +1592,260 @@
         <v>2</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
+      <c r="C40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H40" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr"/>
-      <c r="C40" s="9" t="n">
+      <c r="B41" s="8" t="inlineStr"/>
+      <c r="C41" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="D41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="5" t="n">
+      <c r="C44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr"/>
-      <c r="C44" s="9" t="n">
+      <c r="B45" s="8" t="inlineStr"/>
+      <c r="C45" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9" t="n">
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr"/>
+      <c r="H45" s="9" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="n">
+      <c r="C46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H46" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
-      <c r="C46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="9" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr"/>
+      <c r="C47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="9" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B47" s="10" t="inlineStr"/>
-      <c r="C47" s="11" t="n">
+      <c r="B48" s="10" t="inlineStr"/>
+      <c r="C48" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="D47" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="G47" s="11" t="inlineStr"/>
-      <c r="H47" s="11" t="inlineStr"/>
+      <c r="D48" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="G48" s="11" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1835,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4046,11 +4072,61 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Search in Rotated Sorted Array</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="12" t="n">
+        <v>46272.91475694445</v>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F46">
+  <conditionalFormatting sqref="F5:F47">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -4104,6 +4180,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4115,7 +4192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4158,7 +4235,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   27 solved   (Low: 16 · Medium: 11 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   28 solved   (Low: 16 · Medium: 12 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4173,7 +4250,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Binary Search, Sliding Window, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B5" s="18" t="n"/>
@@ -4204,11 +4281,11 @@
       <c r="A7" s="5" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Minimum Size Subarray Sum</t>
+          <t>Search in Rotated Sorted Array</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>209</v>
+        <v>33</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -4216,10 +4293,10 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>69.2</v>
+        <v>43.8</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
@@ -4227,7 +4304,7 @@
         </is>
       </c>
       <c r="H7" s="12" t="n">
-        <v>46256.69032407407</v>
+        <v>46272.91475694445</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -4238,7 +4315,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Binary Search, Sliding Window, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B8" s="18" t="n"/>
@@ -4251,119 +4328,119 @@
       <c r="I8" s="18" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="F9" s="21" t="n"/>
-      <c r="G9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>Minimum Size Subarray Sum</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>46256.69032407407</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="21" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C13" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>46242.88846064815</v>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n"/>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="n"/>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="19" t="n"/>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Single Number II</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>137</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>46256.48149305556</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Design, Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="n"/>
-      <c r="C13" s="18" t="n"/>
-      <c r="D13" s="18" t="n"/>
-      <c r="E13" s="18" t="n"/>
-      <c r="F13" s="18" t="n"/>
-      <c r="G13" s="18" t="n"/>
-      <c r="H13" s="18" t="n"/>
-      <c r="I13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="n"/>
@@ -4384,11 +4461,11 @@
       <c r="A15" s="5" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Range Sum Query 2D - Immutable</t>
+          <t>Single Number II</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>304</v>
+        <v>137</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -4396,10 +4473,10 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>142</v>
+        <v>45.1</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -4407,7 +4484,7 @@
         </is>
       </c>
       <c r="H15" s="12" t="n">
-        <v>46263.00756944445</v>
+        <v>46256.48149305556</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -4418,7 +4495,7 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Design, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Design, Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
@@ -4431,40 +4508,40 @@
       <c r="I16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n"/>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="n"/>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="n"/>
-      <c r="F17" s="21" t="n"/>
-      <c r="G17" s="21" t="n"/>
-      <c r="H17" s="21" t="n"/>
-      <c r="I17" s="21" t="n"/>
+      <c r="A17" s="19" t="n"/>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Range Sum Query - Immutable</t>
+          <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>47.7</v>
+        <v>142</v>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
@@ -4472,7 +4549,7 @@
         </is>
       </c>
       <c r="H18" s="12" t="n">
-        <v>46262.9494212963</v>
+        <v>46263.00756944445</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -4483,7 +4560,7 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Divide and Conquer, Dynamic Programming   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Design, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B19" s="18" t="n"/>
@@ -4496,40 +4573,40 @@
       <c r="I19" s="18" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="n"/>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="19" t="n"/>
-      <c r="F20" s="19" t="n"/>
-      <c r="G20" s="19" t="n"/>
-      <c r="H20" s="19" t="n"/>
-      <c r="I20" s="19" t="n"/>
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="21" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Maximum Subarray</t>
+          <t>Range Sum Query - Immutable</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>53</v>
+        <v>303</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>80.90000000000001</v>
+        <v>47.7</v>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
@@ -4537,7 +4614,7 @@
         </is>
       </c>
       <c r="H21" s="12" t="n">
-        <v>46263.45222222222</v>
+        <v>46262.9494212963</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -4548,7 +4625,7 @@
     <row r="22">
       <c r="A22" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Divide and Conquer, Dynamic Programming   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B22" s="18" t="n"/>
@@ -4579,11 +4656,11 @@
       <c r="A24" s="5" t="inlineStr"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Longest Fibonacci Subarray</t>
+          <t>Maximum Subarray</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>4003</v>
+        <v>53</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
@@ -4594,7 +4671,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>98</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
@@ -4602,7 +4679,7 @@
         </is>
       </c>
       <c r="H24" s="12" t="n">
-        <v>46247.80789351852</v>
+        <v>46263.45222222222</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -4613,7 +4690,7 @@
     <row r="25">
       <c r="A25" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B25" s="18" t="n"/>
@@ -4626,150 +4703,150 @@
       <c r="I25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="n"/>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 2 problem(s)</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-      <c r="G26" s="21" t="n"/>
-      <c r="H26" s="21" t="n"/>
-      <c r="I26" s="21" t="n"/>
+      <c r="A26" s="19" t="n"/>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="19" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="19" t="n"/>
+      <c r="I26" s="19" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>Longest Fibonacci Subarray</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>4003</v>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>46247.80789351852</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="18" t="n"/>
+      <c r="I28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="n"/>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="21" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="21" t="n"/>
+      <c r="H29" s="21" t="n"/>
+      <c r="I29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
           <t>Two Sum</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="C30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E30" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F30" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>46251.8174537037</v>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C31" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="7" t="n">
+      <c r="E31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="7" t="n">
         <v>45.1</v>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H31" s="14" t="n">
         <v>46252.95966435185</v>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="18" t="n"/>
-      <c r="I29" s="18" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="n"/>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Subarray Sum Equals K</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>560</v>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>1544</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>46263.40873842593</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
+      <c r="I31" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -4778,7 +4855,7 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B32" s="18" t="n"/>
@@ -4791,40 +4868,40 @@
       <c r="I32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="n"/>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="n"/>
-      <c r="D33" s="21" t="n"/>
-      <c r="E33" s="21" t="n"/>
-      <c r="F33" s="21" t="n"/>
-      <c r="G33" s="21" t="n"/>
-      <c r="H33" s="21" t="n"/>
-      <c r="I33" s="21" t="n"/>
+      <c r="A33" s="19" t="n"/>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="19" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="19" t="n"/>
+      <c r="I33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Contains Duplicate II</t>
+          <t>Subarray Sum Equals K</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>219</v>
+        <v>560</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>36</v>
+        <v>1544</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>104.8</v>
+        <v>48.6</v>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
@@ -4832,7 +4909,7 @@
         </is>
       </c>
       <c r="H34" s="12" t="n">
-        <v>46258.98878472222</v>
+        <v>46263.40873842593</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -4843,7 +4920,7 @@
     <row r="35">
       <c r="A35" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B35" s="18" t="n"/>
@@ -4874,11 +4951,11 @@
       <c r="A37" s="5" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Contains Duplicate II</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1353</v>
+        <v>219</v>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
@@ -4886,10 +4963,10 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>46.3</v>
+        <v>104.8</v>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
@@ -4897,7 +4974,7 @@
         </is>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46258.98878472222</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -4908,7 +4985,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B38" s="18" t="n"/>
@@ -4921,40 +4998,40 @@
       <c r="I38" s="18" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="n"/>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="21" t="n"/>
+      <c r="H39" s="21" t="n"/>
+      <c r="I39" s="21" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
@@ -4962,7 +5039,7 @@
         </is>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -4973,7 +5050,7 @@
     <row r="41">
       <c r="A41" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B41" s="18" t="n"/>
@@ -4986,48 +5063,48 @@
       <c r="I41" s="18" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="21" t="n"/>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="21" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="19" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="19" t="n"/>
+      <c r="I42" s="19" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H43" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -5038,7 +5115,7 @@
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B44" s="18" t="n"/>
@@ -5069,11 +5146,11 @@
       <c r="A46" s="5" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
@@ -5081,18 +5158,18 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H46" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -5103,7 +5180,7 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -5134,11 +5211,11 @@
       <c r="A49" s="5" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
@@ -5146,10 +5223,10 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
@@ -5157,7 +5234,7 @@
         </is>
       </c>
       <c r="H49" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -5168,7 +5245,7 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -5181,40 +5258,40 @@
       <c r="I50" s="18" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="n"/>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="19" t="n"/>
-      <c r="F51" s="19" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="19" t="n"/>
-      <c r="I51" s="19" t="n"/>
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
@@ -5222,7 +5299,7 @@
         </is>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -5233,7 +5310,7 @@
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -5246,40 +5323,40 @@
       <c r="I53" s="18" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="n"/>
-      <c r="B54" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-      <c r="G54" s="21" t="n"/>
-      <c r="H54" s="21" t="n"/>
-      <c r="I54" s="21" t="n"/>
+      <c r="A54" s="19" t="n"/>
+      <c r="B54" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="19" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
@@ -5287,7 +5364,7 @@
         </is>
       </c>
       <c r="H55" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -5298,7 +5375,7 @@
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -5311,40 +5388,40 @@
       <c r="I56" s="18" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="19" t="n"/>
-      <c r="B57" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="19" t="n"/>
-      <c r="F57" s="19" t="n"/>
-      <c r="G57" s="19" t="n"/>
-      <c r="H57" s="19" t="n"/>
-      <c r="I57" s="19" t="n"/>
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="n"/>
+      <c r="H57" s="21" t="n"/>
+      <c r="I57" s="21" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
@@ -5352,7 +5429,7 @@
         </is>
       </c>
       <c r="H58" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -5363,7 +5440,7 @@
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -5376,155 +5453,155 @@
       <c r="I59" s="18" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="21" t="n"/>
-      <c r="B60" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C60" s="21" t="n"/>
-      <c r="D60" s="21" t="n"/>
-      <c r="E60" s="21" t="n"/>
-      <c r="F60" s="21" t="n"/>
-      <c r="G60" s="21" t="n"/>
-      <c r="H60" s="21" t="n"/>
-      <c r="I60" s="21" t="n"/>
+      <c r="A60" s="19" t="n"/>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n"/>
+      <c r="G60" s="19" t="n"/>
+      <c r="H60" s="19" t="n"/>
+      <c r="I60" s="19" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>Matrix Block Sum</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>46262.8983912037</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="18" t="n"/>
+      <c r="H62" s="18" t="n"/>
+      <c r="I62" s="18" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="n"/>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="21" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="n"/>
+      <c r="H63" s="21" t="n"/>
+      <c r="I63" s="21" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr"/>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C64" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" s="5" t="n">
+      <c r="E64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="n">
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="n">
         <v>46270.61052083333</v>
       </c>
-      <c r="I61" s="13" t="inlineStr">
+      <c r="I64" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="19" t="n"/>
-      <c r="B62" s="20" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="19" t="n"/>
+      <c r="B65" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="19" t="n"/>
-      <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Flight Bookings</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H63" s="12" t="n">
-        <v>46262.6837962963</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="18" t="n"/>
-      <c r="I64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C65" s="21" t="n"/>
-      <c r="D65" s="21" t="n"/>
-      <c r="E65" s="21" t="n"/>
-      <c r="F65" s="21" t="n"/>
-      <c r="G65" s="21" t="n"/>
-      <c r="H65" s="21" t="n"/>
-      <c r="I65" s="21" t="n"/>
+      <c r="C65" s="19" t="n"/>
+      <c r="D65" s="19" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="19" t="n"/>
+      <c r="G65" s="19" t="n"/>
+      <c r="H65" s="19" t="n"/>
+      <c r="I65" s="19" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr"/>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C66" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
@@ -5532,7 +5609,7 @@
         </is>
       </c>
       <c r="H66" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -5543,7 +5620,7 @@
     <row r="67">
       <c r="A67" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B67" s="18" t="n"/>
@@ -5574,11 +5651,11 @@
       <c r="A69" s="5" t="inlineStr"/>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C69" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
@@ -5586,10 +5663,10 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
@@ -5597,7 +5674,7 @@
         </is>
       </c>
       <c r="H69" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -5608,7 +5685,7 @@
     <row r="70">
       <c r="A70" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B70" s="18" t="n"/>
@@ -5639,11 +5716,11 @@
       <c r="A72" s="5" t="inlineStr"/>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C72" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
@@ -5651,10 +5728,10 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
@@ -5662,7 +5739,7 @@
         </is>
       </c>
       <c r="H72" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -5673,7 +5750,7 @@
     <row r="73">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B73" s="18" t="n"/>
@@ -5689,7 +5766,7 @@
       <c r="A74" s="21" t="n"/>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C74" s="21" t="n"/>
@@ -5704,301 +5781,301 @@
       <c r="A75" s="5" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G75" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="n"/>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="18" t="n"/>
+      <c r="H76" s="18" t="n"/>
+      <c r="I76" s="18" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="n"/>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C77" s="21" t="n"/>
+      <c r="D77" s="21" t="n"/>
+      <c r="E77" s="21" t="n"/>
+      <c r="F77" s="21" t="n"/>
+      <c r="G77" s="21" t="n"/>
+      <c r="H77" s="21" t="n"/>
+      <c r="I77" s="21" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr"/>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C78" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D78" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="5" t="n">
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="n">
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I75" s="13" t="inlineStr">
+      <c r="I78" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="7" t="inlineStr"/>
-      <c r="B76" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C76" s="7" t="n">
+      <c r="C79" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D79" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E76" s="7" t="n">
+      <c r="E79" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F76" s="7" t="n">
+      <c r="F79" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="n">
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I76" s="15" t="inlineStr">
+      <c r="I79" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="17" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B77" s="18" t="n"/>
-      <c r="C77" s="18" t="n"/>
-      <c r="D77" s="18" t="n"/>
-      <c r="E77" s="18" t="n"/>
-      <c r="F77" s="18" t="n"/>
-      <c r="G77" s="18" t="n"/>
-      <c r="H77" s="18" t="n"/>
-      <c r="I77" s="18" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="19" t="n"/>
-      <c r="B78" s="20" t="inlineStr">
+      <c r="B80" s="18" t="n"/>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="19" t="n"/>
+      <c r="B81" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C78" s="19" t="n"/>
-      <c r="D78" s="19" t="n"/>
-      <c r="E78" s="19" t="n"/>
-      <c r="F78" s="19" t="n"/>
-      <c r="G78" s="19" t="n"/>
-      <c r="H78" s="19" t="n"/>
-      <c r="I78" s="19" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr"/>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="C81" s="19" t="n"/>
+      <c r="D81" s="19" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="19" t="n"/>
+      <c r="G81" s="19" t="n"/>
+      <c r="H81" s="19" t="n"/>
+      <c r="I81" s="19" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr"/>
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E82" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F82" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="n">
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I79" s="13" t="inlineStr">
+      <c r="I82" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="16" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B80" s="2" t="n"/>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
-      <c r="G80" s="2" t="n"/>
-      <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B81" s="18" t="n"/>
-      <c r="C81" s="18" t="n"/>
-      <c r="D81" s="18" t="n"/>
-      <c r="E81" s="18" t="n"/>
-      <c r="F81" s="18" t="n"/>
-      <c r="G81" s="18" t="n"/>
-      <c r="H81" s="18" t="n"/>
-      <c r="I81" s="18" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="21" t="n"/>
-      <c r="B82" s="22" t="inlineStr">
+      <c r="B84" s="18" t="n"/>
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="n"/>
+      <c r="B85" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C82" s="21" t="n"/>
-      <c r="D82" s="21" t="n"/>
-      <c r="E82" s="21" t="n"/>
-      <c r="F82" s="21" t="n"/>
-      <c r="G82" s="21" t="n"/>
-      <c r="H82" s="21" t="n"/>
-      <c r="I82" s="21" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr"/>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="C85" s="21" t="n"/>
+      <c r="D85" s="21" t="n"/>
+      <c r="E85" s="21" t="n"/>
+      <c r="F85" s="21" t="n"/>
+      <c r="G85" s="21" t="n"/>
+      <c r="H85" s="21" t="n"/>
+      <c r="I85" s="21" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr"/>
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C86" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D83" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" s="5" t="n">
+      <c r="E86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G86" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H83" s="12" t="n">
+      <c r="H86" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I83" s="13" t="inlineStr">
+      <c r="I86" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="16" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n"/>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B85" s="18" t="n"/>
-      <c r="C85" s="18" t="n"/>
-      <c r="D85" s="18" t="n"/>
-      <c r="E85" s="18" t="n"/>
-      <c r="F85" s="18" t="n"/>
-      <c r="G85" s="18" t="n"/>
-      <c r="H85" s="18" t="n"/>
-      <c r="I85" s="18" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="21" t="n"/>
-      <c r="B86" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C86" s="21" t="n"/>
-      <c r="D86" s="21" t="n"/>
-      <c r="E86" s="21" t="n"/>
-      <c r="F86" s="21" t="n"/>
-      <c r="G86" s="21" t="n"/>
-      <c r="H86" s="21" t="n"/>
-      <c r="I86" s="21" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr"/>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B88" s="18" t="n"/>
@@ -6029,11 +6106,11 @@
       <c r="A90" s="5" t="inlineStr"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C90" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
@@ -6041,10 +6118,10 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
@@ -6052,7 +6129,7 @@
         </is>
       </c>
       <c r="H90" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -6063,7 +6140,7 @@
     <row r="91">
       <c r="A91" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B91" s="18" t="n"/>
@@ -6094,171 +6171,171 @@
       <c r="A93" s="5" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="n"/>
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+      <c r="G94" s="18" t="n"/>
+      <c r="H94" s="18" t="n"/>
+      <c r="I94" s="18" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="n"/>
+      <c r="B95" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="n"/>
+      <c r="D95" s="21" t="n"/>
+      <c r="E95" s="21" t="n"/>
+      <c r="F95" s="21" t="n"/>
+      <c r="G95" s="21" t="n"/>
+      <c r="H95" s="21" t="n"/>
+      <c r="I95" s="21" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr"/>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C96" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D96" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="5" t="n">
+      <c r="E96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="n">
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I96" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="19" t="n"/>
-      <c r="B94" s="20" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="19" t="n"/>
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C94" s="19" t="n"/>
-      <c r="D94" s="19" t="n"/>
-      <c r="E94" s="19" t="n"/>
-      <c r="F94" s="19" t="n"/>
-      <c r="G94" s="19" t="n"/>
-      <c r="H94" s="19" t="n"/>
-      <c r="I94" s="19" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="5" t="inlineStr"/>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="C97" s="19" t="n"/>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="19" t="n"/>
+      <c r="G97" s="19" t="n"/>
+      <c r="H97" s="19" t="n"/>
+      <c r="I97" s="19" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr"/>
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C98" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" s="5" t="n">
+      <c r="E98" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G98" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H95" s="12" t="n">
+      <c r="H98" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I95" s="13" t="inlineStr">
+      <c r="I98" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="16" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B96" s="2" t="n"/>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="n"/>
-      <c r="I96" s="2" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="n"/>
-      <c r="B98" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C98" s="21" t="n"/>
-      <c r="D98" s="21" t="n"/>
-      <c r="E98" s="21" t="n"/>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr"/>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="n"/>
+      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="2" t="n"/>
+      <c r="I99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B100" s="18" t="n"/>
@@ -6271,48 +6348,48 @@
       <c r="I100" s="18" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="19" t="n"/>
-      <c r="B101" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C101" s="19" t="n"/>
-      <c r="D101" s="19" t="n"/>
-      <c r="E101" s="19" t="n"/>
-      <c r="F101" s="19" t="n"/>
-      <c r="G101" s="19" t="n"/>
-      <c r="H101" s="19" t="n"/>
-      <c r="I101" s="19" t="n"/>
+      <c r="A101" s="21" t="n"/>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="n"/>
+      <c r="D101" s="21" t="n"/>
+      <c r="E101" s="21" t="n"/>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr"/>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C102" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H102" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -6323,7 +6400,7 @@
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B103" s="18" t="n"/>
@@ -6336,40 +6413,40 @@
       <c r="I103" s="18" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="21" t="n"/>
-      <c r="B104" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C104" s="21" t="n"/>
-      <c r="D104" s="21" t="n"/>
-      <c r="E104" s="21" t="n"/>
-      <c r="F104" s="21" t="n"/>
-      <c r="G104" s="21" t="n"/>
-      <c r="H104" s="21" t="n"/>
-      <c r="I104" s="21" t="n"/>
+      <c r="A104" s="19" t="n"/>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C104" s="19" t="n"/>
+      <c r="D104" s="19" t="n"/>
+      <c r="E104" s="19" t="n"/>
+      <c r="F104" s="19" t="n"/>
+      <c r="G104" s="19" t="n"/>
+      <c r="H104" s="19" t="n"/>
+      <c r="I104" s="19" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr"/>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
@@ -6377,7 +6454,7 @@
         </is>
       </c>
       <c r="H105" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -6388,7 +6465,7 @@
     <row r="106">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B106" s="18" t="n"/>
@@ -6419,11 +6496,11 @@
       <c r="A108" s="5" t="inlineStr"/>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
@@ -6434,15 +6511,15 @@
         <v>2</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H108" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -6453,7 +6530,7 @@
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B109" s="18" t="n"/>
@@ -6484,121 +6561,121 @@
       <c r="A111" s="5" t="inlineStr"/>
       <c r="B111" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="n"/>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+      <c r="G112" s="18" t="n"/>
+      <c r="H112" s="18" t="n"/>
+      <c r="I112" s="18" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="21" t="n"/>
+      <c r="B113" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="n"/>
+      <c r="D113" s="21" t="n"/>
+      <c r="E113" s="21" t="n"/>
+      <c r="F113" s="21" t="n"/>
+      <c r="G113" s="21" t="n"/>
+      <c r="H113" s="21" t="n"/>
+      <c r="I113" s="21" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr"/>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C114" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D114" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E111" s="5" t="n">
+      <c r="E114" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F111" s="5" t="n">
+      <c r="F114" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G111" s="5" t="inlineStr">
+      <c r="G114" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H111" s="12" t="n">
+      <c r="H114" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I111" s="13" t="inlineStr">
+      <c r="I114" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="16" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n"/>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B113" s="18" t="n"/>
-      <c r="C113" s="18" t="n"/>
-      <c r="D113" s="18" t="n"/>
-      <c r="E113" s="18" t="n"/>
-      <c r="F113" s="18" t="n"/>
-      <c r="G113" s="18" t="n"/>
-      <c r="H113" s="18" t="n"/>
-      <c r="I113" s="18" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="21" t="n"/>
-      <c r="B114" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C114" s="21" t="n"/>
-      <c r="D114" s="21" t="n"/>
-      <c r="E114" s="21" t="n"/>
-      <c r="F114" s="21" t="n"/>
-      <c r="G114" s="21" t="n"/>
-      <c r="H114" s="21" t="n"/>
-      <c r="I114" s="21" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr"/>
-      <c r="B115" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H115" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="n"/>
+      <c r="I115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B116" s="18" t="n"/>
@@ -6614,7 +6691,7 @@
       <c r="A117" s="21" t="n"/>
       <c r="B117" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C117" s="21" t="n"/>
@@ -6629,312 +6706,379 @@
       <c r="A118" s="5" t="inlineStr"/>
       <c r="B118" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B119" s="18" t="n"/>
+      <c r="C119" s="18" t="n"/>
+      <c r="D119" s="18" t="n"/>
+      <c r="E119" s="18" t="n"/>
+      <c r="F119" s="18" t="n"/>
+      <c r="G119" s="18" t="n"/>
+      <c r="H119" s="18" t="n"/>
+      <c r="I119" s="18" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="n"/>
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C120" s="21" t="n"/>
+      <c r="D120" s="21" t="n"/>
+      <c r="E120" s="21" t="n"/>
+      <c r="F120" s="21" t="n"/>
+      <c r="G120" s="21" t="n"/>
+      <c r="H120" s="21" t="n"/>
+      <c r="I120" s="21" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr"/>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C121" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D121" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E118" s="5" t="n">
+      <c r="E121" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F118" s="5" t="n">
+      <c r="F121" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G121" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H118" s="12" t="n">
+      <c r="H121" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I118" s="13" t="inlineStr">
+      <c r="I121" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="7" t="inlineStr"/>
-      <c r="B119" s="6" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr"/>
+      <c r="B122" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C119" s="7" t="n">
+      <c r="C122" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D119" s="7" t="inlineStr">
+      <c r="D122" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E119" s="7" t="n">
+      <c r="E122" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F119" s="7" t="n">
+      <c r="F122" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G119" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H119" s="14" t="n">
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I119" s="15" t="inlineStr">
+      <c r="I122" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="17" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B120" s="18" t="n"/>
-      <c r="C120" s="18" t="n"/>
-      <c r="D120" s="18" t="n"/>
-      <c r="E120" s="18" t="n"/>
-      <c r="F120" s="18" t="n"/>
-      <c r="G120" s="18" t="n"/>
-      <c r="H120" s="18" t="n"/>
-      <c r="I120" s="18" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="21" t="n"/>
-      <c r="B121" s="22" t="inlineStr">
+      <c r="B123" s="18" t="n"/>
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
+      <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="21" t="n"/>
+      <c r="B124" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C121" s="21" t="n"/>
-      <c r="D121" s="21" t="n"/>
-      <c r="E121" s="21" t="n"/>
-      <c r="F121" s="21" t="n"/>
-      <c r="G121" s="21" t="n"/>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="21" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr"/>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="C124" s="21" t="n"/>
+      <c r="D124" s="21" t="n"/>
+      <c r="E124" s="21" t="n"/>
+      <c r="F124" s="21" t="n"/>
+      <c r="G124" s="21" t="n"/>
+      <c r="H124" s="21" t="n"/>
+      <c r="I124" s="21" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr"/>
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C122" s="5" t="n">
+      <c r="C125" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="5" t="n">
+      <c r="E125" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G122" s="5" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="H125" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I122" s="13" t="inlineStr">
+      <c r="I125" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="16" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B123" s="2" t="n"/>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n"/>
-      <c r="E123" s="2" t="n"/>
-      <c r="F123" s="2" t="n"/>
-      <c r="G123" s="2" t="n"/>
-      <c r="H123" s="2" t="n"/>
-      <c r="I123" s="2" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="17" t="inlineStr">
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B124" s="18" t="n"/>
-      <c r="C124" s="18" t="n"/>
-      <c r="D124" s="18" t="n"/>
-      <c r="E124" s="18" t="n"/>
-      <c r="F124" s="18" t="n"/>
-      <c r="G124" s="18" t="n"/>
-      <c r="H124" s="18" t="n"/>
-      <c r="I124" s="18" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="21" t="n"/>
-      <c r="B125" s="22" t="inlineStr">
+      <c r="B127" s="18" t="n"/>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+      <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="n"/>
+      <c r="B128" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C125" s="21" t="n"/>
-      <c r="D125" s="21" t="n"/>
-      <c r="E125" s="21" t="n"/>
-      <c r="F125" s="21" t="n"/>
-      <c r="G125" s="21" t="n"/>
-      <c r="H125" s="21" t="n"/>
-      <c r="I125" s="21" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr"/>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="C128" s="21" t="n"/>
+      <c r="D128" s="21" t="n"/>
+      <c r="E128" s="21" t="n"/>
+      <c r="F128" s="21" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="21" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr"/>
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C126" s="5" t="n">
+      <c r="C129" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E126" s="5" t="n">
+      <c r="E129" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F126" s="5" t="n">
+      <c r="F129" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H126" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I126" s="13" t="inlineStr">
+      <c r="I129" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="82">
+  <mergeCells count="84">
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="A99:I99"/>
     <mergeCell ref="B54:I54"/>
-    <mergeCell ref="B125:I125"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="B48:I48"/>
-    <mergeCell ref="A85:I85"/>
-    <mergeCell ref="B98:I98"/>
+    <mergeCell ref="B120:I120"/>
+    <mergeCell ref="A126:I126"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A109:I109"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B82:I82"/>
     <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="A59:I59"/>
     <mergeCell ref="B74:I74"/>
     <mergeCell ref="B68:I68"/>
+    <mergeCell ref="A11:I11"/>
     <mergeCell ref="A103:I103"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="B110:I110"/>
-    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="B85:I85"/>
+    <mergeCell ref="B113:I113"/>
+    <mergeCell ref="B12:I12"/>
     <mergeCell ref="B39:I39"/>
+    <mergeCell ref="A76:I76"/>
     <mergeCell ref="A116:I116"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="B23:I23"/>
     <mergeCell ref="A100:I100"/>
-    <mergeCell ref="B78:I78"/>
-    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="A115:I115"/>
+    <mergeCell ref="B128:I128"/>
+    <mergeCell ref="A83:I83"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
-    <mergeCell ref="B114:I114"/>
+    <mergeCell ref="A94:I94"/>
+    <mergeCell ref="B63:I63"/>
     <mergeCell ref="A80:I80"/>
-    <mergeCell ref="A120:I120"/>
-    <mergeCell ref="A113:I113"/>
+    <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="B11:I11"/>
     <mergeCell ref="A32:I32"/>
     <mergeCell ref="B117:I117"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A106:I106"/>
+    <mergeCell ref="A4:I4"/>
     <mergeCell ref="B101:I101"/>
-    <mergeCell ref="A4:I4"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A96:I96"/>
+    <mergeCell ref="B29:I29"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A123:I123"/>
+    <mergeCell ref="B95:I95"/>
     <mergeCell ref="B89:I89"/>
     <mergeCell ref="B104:I104"/>
-    <mergeCell ref="A124:I124"/>
+    <mergeCell ref="A119:I119"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B97:I97"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A84:I84"/>
-    <mergeCell ref="B121:I121"/>
+    <mergeCell ref="B81:I81"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B107:I107"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A81:I81"/>
     <mergeCell ref="A112:I112"/>
-    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A127:I127"/>
     <mergeCell ref="B92:I92"/>
-    <mergeCell ref="B30:I30"/>
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="A88:I88"/>
     <mergeCell ref="A70:I70"/>
-    <mergeCell ref="B94:I94"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId12"/>
@@ -6946,28 +7090,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6979,7 +7124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7245,24 +7390,72 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="196" customHeight="1">
+    <row r="10" ht="364" customHeight="1">
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>Search in Rotated Sorted Array</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int search(int[] nums, int target) {
+     int low = 0;
+     int high = nums.length-1;
+     while(low&lt;=high){
+        int mid = low +(high - low)/2;
+        if(nums[mid] == target){
+            return mid;
+        }
+        if(nums[low]&lt;=nums[mid]){
+            if(nums[low]&lt;=target &amp;&amp; nums[mid]&gt;target){
+                high = mid -1;
+            }else{
+               low = mid + 1;
+            }
+        }else{
+            if(nums[mid]&lt;target &amp;&amp; nums[high]&gt;=target){
+                low = mid +1;
+            }else{
+                high = mid -1;
+            }
+        }
+     }
+     return -1;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="196" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Maximum Subarray</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C11" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int maxSubArray(int[] nums) {
@@ -7281,24 +7474,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="532" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="532" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C12" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;58 - Length of Last Word&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/length-of-last-word/"&gt;length-of-last-word&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt; consisting of words and spaces, return &lt;em&gt;the length of the &lt;strong&gt;last&lt;/strong&gt; word in the string.&lt;/em&gt;&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;word&lt;/strong&gt; is a maximal &lt;span data-keyword="substring-nonempty"&gt;substring&lt;/span&gt; consisting of non-space characters only.&lt;/p&gt;
@@ -7332,24 +7525,24 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="560" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="13" ht="560" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C13" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>&lt;h1&gt;94 - Binary Tree Inorder Traversal&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/binary-tree-inorder-traversal/"&gt;binary-tree-inorder-traversal&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given the &lt;code&gt;root&lt;/code&gt; of a binary tree, return &lt;em&gt;the inorder traversal of its nodes&amp;#39; values&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -7388,24 +7581,24 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="406" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+    <row r="14" ht="406" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;111 - Minimum Depth of Binary Tree&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/minimum-depth-of-binary-tree/"&gt;minimum-depth-of-binary-tree&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a binary tree, find its minimum depth.&lt;/p&gt;
 &lt;p&gt;The minimum depth is the number of nodes along the shortest path from the root node down to the nearest leaf node.&lt;/p&gt;
@@ -7432,24 +7625,24 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="532" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="15" ht="532" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C15" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;125 - Valid Palindrome&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome/"&gt;valid-palindrome&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;A phrase is a &lt;strong&gt;palindrome&lt;/strong&gt; if, after converting all uppercase letters into lowercase letters and removing all non-alphanumeric characters, it reads the same forward and backward. Alphanumeric characters include letters and numbers.&lt;/p&gt;
 &lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt;&lt;em&gt; if it is a &lt;strong&gt;palindrome&lt;/strong&gt;, or &lt;/em&gt;&lt;code&gt;false&lt;/code&gt;&lt;em&gt; otherwise&lt;/em&gt;.&lt;/p&gt;
@@ -7483,24 +7676,24 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="532" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="532" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="7" t="n">
         <v>136</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;136 - Single Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/single-number/"&gt;single-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a &lt;strong&gt;non-empty&lt;/strong&gt;&amp;nbsp;array of integers &lt;code&gt;nums&lt;/code&gt;, every element appears &lt;em&gt;twice&lt;/em&gt; except for one. Find that single one.&lt;/p&gt;
 &lt;p&gt;You must&amp;nbsp;implement a solution with a linear runtime complexity and use&amp;nbsp;only constant&amp;nbsp;extra space.&lt;/p&gt;
@@ -7531,24 +7724,24 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="238" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="17" ht="238" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C17" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int singleNumber(int[] nums) {
@@ -7570,24 +7763,24 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="294" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="294" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -7613,24 +7806,24 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="238" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19" ht="238" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -7652,24 +7845,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="238" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="238" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>219</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -7691,24 +7884,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="392" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="392" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -7741,24 +7934,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="182" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="182" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -7776,24 +7969,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="308" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="308" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -7817,24 +8010,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="420" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="420" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>304</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -7866,24 +8059,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="546" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="546" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -7921,24 +8114,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="182" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="182" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -7956,24 +8149,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="546" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="546" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -8017,24 +8210,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="196" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="196" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -8053,24 +8246,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="462" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="462" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -8100,24 +8293,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="378" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="378" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -8149,24 +8342,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="560" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="560" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -8202,24 +8395,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="294" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="294" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -8242,24 +8435,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="224" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="224" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -8280,24 +8473,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="420" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="420" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -8332,24 +8525,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="378" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="378" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -8381,24 +8574,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="350" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="350" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -8428,24 +8621,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="238" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="238" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -8467,24 +8660,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="308" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="308" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -8511,24 +8704,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="280" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="280" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -8551,24 +8744,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="448" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="448" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -8603,24 +8796,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="378" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="378" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -8652,24 +8845,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="266" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="266" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -8693,24 +8886,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="560" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="560" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -8763,24 +8956,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="238" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="238" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -8800,24 +8993,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="252" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="252" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -8840,24 +9033,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="294" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="294" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -8883,24 +9076,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="252" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="252" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1313,274 +1313,274 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers, Binary Search</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H29" s="5" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="8" t="inlineStr"/>
-      <c r="C29" s="9" t="n">
+      <c r="B30" s="8" t="inlineStr"/>
+      <c r="C30" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="D30" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr"/>
+      <c r="H30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="7" t="n">
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr"/>
-      <c r="C31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr"/>
+      <c r="C32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="9" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="7" t="n">
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H33" s="5" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="7" t="n">
+      <c r="G35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="n">
         <v>42.3</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr"/>
-      <c r="C35" s="9" t="n">
+      <c r="B36" s="8" t="inlineStr"/>
+      <c r="C36" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="9" t="n">
+      <c r="D36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="9" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="7" t="n">
+      <c r="C37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>0</v>
@@ -1589,17 +1589,17 @@
         <v>1</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -1618,234 +1618,260 @@
         <v>2</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H41" s="5" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr"/>
-      <c r="C41" s="9" t="n">
+      <c r="B42" s="8" t="inlineStr"/>
+      <c r="C42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9" t="n">
+      <c r="D42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr"/>
+      <c r="H42" s="9" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="n">
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="5" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr"/>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="5" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="7" t="n">
+      <c r="C45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="5" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr"/>
-      <c r="C45" s="9" t="n">
+      <c r="B46" s="8" t="inlineStr"/>
+      <c r="C46" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="9" t="n">
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G45" s="9" t="inlineStr"/>
-      <c r="H45" s="9" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr"/>
+      <c r="H46" s="9" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="7" t="n">
+      <c r="C47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="H46" s="7" t="n">
+      <c r="H47" s="5" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr"/>
-      <c r="C47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="9" t="inlineStr"/>
-      <c r="H47" s="9" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr"/>
+      <c r="C48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="9" t="inlineStr"/>
+      <c r="H48" s="9" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr"/>
-      <c r="C48" s="11" t="n">
+      <c r="B49" s="10" t="inlineStr"/>
+      <c r="C49" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="D48" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="G48" s="11" t="inlineStr"/>
-      <c r="H48" s="11" t="inlineStr"/>
+      <c r="D49" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="G49" s="11" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1861,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4122,11 +4148,61 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>167</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Two Sum II - Input Array Is Sorted</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Two Pointers, Binary Search</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="14" t="n">
+        <v>46272.93130787037</v>
+      </c>
+      <c r="L48" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F47">
+  <conditionalFormatting sqref="F5:F48">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -4181,6 +4257,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4192,7 +4269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4235,7 +4312,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   28 solved   (Low: 16 · Medium: 12 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   29 solved   (Low: 16 · Medium: 13 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -5915,7 +5992,7 @@
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B80" s="18" t="n"/>
@@ -5946,201 +6023,201 @@
       <c r="A82" s="5" t="inlineStr"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
+          <t>Two Sum II - Input Array Is Sorted</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>46272.93130787037</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="n"/>
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="19" t="n"/>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C84" s="19" t="n"/>
+      <c r="D84" s="19" t="n"/>
+      <c r="E84" s="19" t="n"/>
+      <c r="F84" s="19" t="n"/>
+      <c r="G84" s="19" t="n"/>
+      <c r="H84" s="19" t="n"/>
+      <c r="I84" s="19" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr"/>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C85" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E85" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F85" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n">
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I82" s="13" t="inlineStr">
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="16" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="n"/>
-      <c r="F83" s="2" t="n"/>
-      <c r="G83" s="2" t="n"/>
-      <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="17" t="inlineStr">
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B84" s="18" t="n"/>
-      <c r="C84" s="18" t="n"/>
-      <c r="D84" s="18" t="n"/>
-      <c r="E84" s="18" t="n"/>
-      <c r="F84" s="18" t="n"/>
-      <c r="G84" s="18" t="n"/>
-      <c r="H84" s="18" t="n"/>
-      <c r="I84" s="18" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="21" t="n"/>
-      <c r="B85" s="22" t="inlineStr">
+      <c r="B87" s="18" t="n"/>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="18" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+      <c r="G87" s="18" t="n"/>
+      <c r="H87" s="18" t="n"/>
+      <c r="I87" s="18" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="n"/>
+      <c r="B88" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C85" s="21" t="n"/>
-      <c r="D85" s="21" t="n"/>
-      <c r="E85" s="21" t="n"/>
-      <c r="F85" s="21" t="n"/>
-      <c r="G85" s="21" t="n"/>
-      <c r="H85" s="21" t="n"/>
-      <c r="I85" s="21" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr"/>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="C88" s="21" t="n"/>
+      <c r="D88" s="21" t="n"/>
+      <c r="E88" s="21" t="n"/>
+      <c r="F88" s="21" t="n"/>
+      <c r="G88" s="21" t="n"/>
+      <c r="H88" s="21" t="n"/>
+      <c r="I88" s="21" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr"/>
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C89" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="5" t="n">
+      <c r="E89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H86" s="12" t="n">
+      <c r="H89" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I86" s="13" t="inlineStr">
+      <c r="I89" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n"/>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B88" s="18" t="n"/>
-      <c r="C88" s="18" t="n"/>
-      <c r="D88" s="18" t="n"/>
-      <c r="E88" s="18" t="n"/>
-      <c r="F88" s="18" t="n"/>
-      <c r="G88" s="18" t="n"/>
-      <c r="H88" s="18" t="n"/>
-      <c r="I88" s="18" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="21" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr"/>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H90" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B91" s="18" t="n"/>
@@ -6171,11 +6248,11 @@
       <c r="A93" s="5" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C93" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
@@ -6183,10 +6260,10 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
@@ -6194,7 +6271,7 @@
         </is>
       </c>
       <c r="H93" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -6205,7 +6282,7 @@
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B94" s="18" t="n"/>
@@ -6236,171 +6313,171 @@
       <c r="A96" s="5" t="inlineStr"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
+          <t>Smallest Divisible Digit Product I</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>3626</v>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>46240.74578703703</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="18" t="n"/>
+      <c r="D97" s="18" t="n"/>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="n"/>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="21" t="n"/>
+      <c r="E98" s="21" t="n"/>
+      <c r="F98" s="21" t="n"/>
+      <c r="G98" s="21" t="n"/>
+      <c r="H98" s="21" t="n"/>
+      <c r="I98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr"/>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C99" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="5" t="n">
+      <c r="E99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="n">
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H99" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I96" s="13" t="inlineStr">
+      <c r="I99" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="19" t="n"/>
-      <c r="B97" s="20" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="19" t="n"/>
+      <c r="B100" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C97" s="19" t="n"/>
-      <c r="D97" s="19" t="n"/>
-      <c r="E97" s="19" t="n"/>
-      <c r="F97" s="19" t="n"/>
-      <c r="G97" s="19" t="n"/>
-      <c r="H97" s="19" t="n"/>
-      <c r="I97" s="19" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr"/>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="C100" s="19" t="n"/>
+      <c r="D100" s="19" t="n"/>
+      <c r="E100" s="19" t="n"/>
+      <c r="F100" s="19" t="n"/>
+      <c r="G100" s="19" t="n"/>
+      <c r="H100" s="19" t="n"/>
+      <c r="I100" s="19" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr"/>
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C101" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D98" s="5" t="inlineStr">
+      <c r="D101" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="5" t="n">
+      <c r="E101" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G98" s="5" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H98" s="12" t="n">
+      <c r="H101" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I98" s="13" t="inlineStr">
+      <c r="I101" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="16" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B99" s="2" t="n"/>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n"/>
-      <c r="E99" s="2" t="n"/>
-      <c r="F99" s="2" t="n"/>
-      <c r="G99" s="2" t="n"/>
-      <c r="H99" s="2" t="n"/>
-      <c r="I99" s="2" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B100" s="18" t="n"/>
-      <c r="C100" s="18" t="n"/>
-      <c r="D100" s="18" t="n"/>
-      <c r="E100" s="18" t="n"/>
-      <c r="F100" s="18" t="n"/>
-      <c r="G100" s="18" t="n"/>
-      <c r="H100" s="18" t="n"/>
-      <c r="I100" s="18" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="21" t="n"/>
-      <c r="B101" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C101" s="21" t="n"/>
-      <c r="D101" s="21" t="n"/>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr"/>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="n"/>
+      <c r="I102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B103" s="18" t="n"/>
@@ -6413,48 +6490,48 @@
       <c r="I103" s="18" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="19" t="n"/>
-      <c r="B104" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C104" s="19" t="n"/>
-      <c r="D104" s="19" t="n"/>
-      <c r="E104" s="19" t="n"/>
-      <c r="F104" s="19" t="n"/>
-      <c r="G104" s="19" t="n"/>
-      <c r="H104" s="19" t="n"/>
-      <c r="I104" s="19" t="n"/>
+      <c r="A104" s="21" t="n"/>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C104" s="21" t="n"/>
+      <c r="D104" s="21" t="n"/>
+      <c r="E104" s="21" t="n"/>
+      <c r="F104" s="21" t="n"/>
+      <c r="G104" s="21" t="n"/>
+      <c r="H104" s="21" t="n"/>
+      <c r="I104" s="21" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr"/>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C105" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H105" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -6465,7 +6542,7 @@
     <row r="106">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B106" s="18" t="n"/>
@@ -6478,40 +6555,40 @@
       <c r="I106" s="18" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="21" t="n"/>
-      <c r="B107" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C107" s="21" t="n"/>
-      <c r="D107" s="21" t="n"/>
-      <c r="E107" s="21" t="n"/>
-      <c r="F107" s="21" t="n"/>
-      <c r="G107" s="21" t="n"/>
-      <c r="H107" s="21" t="n"/>
-      <c r="I107" s="21" t="n"/>
+      <c r="A107" s="19" t="n"/>
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C107" s="19" t="n"/>
+      <c r="D107" s="19" t="n"/>
+      <c r="E107" s="19" t="n"/>
+      <c r="F107" s="19" t="n"/>
+      <c r="G107" s="19" t="n"/>
+      <c r="H107" s="19" t="n"/>
+      <c r="I107" s="19" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr"/>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C108" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
@@ -6519,7 +6596,7 @@
         </is>
       </c>
       <c r="H108" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -6530,7 +6607,7 @@
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B109" s="18" t="n"/>
@@ -6561,11 +6638,11 @@
       <c r="A111" s="5" t="inlineStr"/>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C111" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
@@ -6576,15 +6653,15 @@
         <v>2</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H111" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -6595,7 +6672,7 @@
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B112" s="18" t="n"/>
@@ -6626,121 +6703,121 @@
       <c r="A114" s="5" t="inlineStr"/>
       <c r="B114" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B115" s="18" t="n"/>
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="n"/>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C116" s="21" t="n"/>
+      <c r="D116" s="21" t="n"/>
+      <c r="E116" s="21" t="n"/>
+      <c r="F116" s="21" t="n"/>
+      <c r="G116" s="21" t="n"/>
+      <c r="H116" s="21" t="n"/>
+      <c r="I116" s="21" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr"/>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C117" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D117" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E114" s="5" t="n">
+      <c r="E117" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F114" s="5" t="n">
+      <c r="F117" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G117" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H117" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I114" s="13" t="inlineStr">
+      <c r="I117" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="16" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n"/>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="2" t="n"/>
-      <c r="G115" s="2" t="n"/>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B116" s="18" t="n"/>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="21" t="n"/>
-      <c r="B117" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C117" s="21" t="n"/>
-      <c r="D117" s="21" t="n"/>
-      <c r="E117" s="21" t="n"/>
-      <c r="F117" s="21" t="n"/>
-      <c r="G117" s="21" t="n"/>
-      <c r="H117" s="21" t="n"/>
-      <c r="I117" s="21" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr"/>
-      <c r="B118" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E118" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G118" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H118" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+      <c r="I118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B119" s="18" t="n"/>
@@ -6756,7 +6833,7 @@
       <c r="A120" s="21" t="n"/>
       <c r="B120" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C120" s="21" t="n"/>
@@ -6771,232 +6848,299 @@
       <c r="A121" s="5" t="inlineStr"/>
       <c r="B121" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B122" s="18" t="n"/>
+      <c r="C122" s="18" t="n"/>
+      <c r="D122" s="18" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="18" t="n"/>
+      <c r="G122" s="18" t="n"/>
+      <c r="H122" s="18" t="n"/>
+      <c r="I122" s="18" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="n"/>
+      <c r="B123" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="n"/>
+      <c r="D123" s="21" t="n"/>
+      <c r="E123" s="21" t="n"/>
+      <c r="F123" s="21" t="n"/>
+      <c r="G123" s="21" t="n"/>
+      <c r="H123" s="21" t="n"/>
+      <c r="I123" s="21" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr"/>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C124" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
+      <c r="E124" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F124" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H121" s="12" t="n">
+      <c r="H124" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I121" s="13" t="inlineStr">
+      <c r="I124" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="7" t="inlineStr"/>
-      <c r="B122" s="6" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="7" t="inlineStr"/>
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C122" s="7" t="n">
+      <c r="C125" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D122" s="7" t="inlineStr">
+      <c r="D125" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E122" s="7" t="n">
+      <c r="E125" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F122" s="7" t="n">
+      <c r="F125" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H122" s="14" t="n">
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H125" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I122" s="15" t="inlineStr">
+      <c r="I125" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="17" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B123" s="18" t="n"/>
-      <c r="C123" s="18" t="n"/>
-      <c r="D123" s="18" t="n"/>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
-      <c r="G123" s="18" t="n"/>
-      <c r="H123" s="18" t="n"/>
-      <c r="I123" s="18" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="21" t="n"/>
-      <c r="B124" s="22" t="inlineStr">
+      <c r="B126" s="18" t="n"/>
+      <c r="C126" s="18" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="18" t="n"/>
+      <c r="G126" s="18" t="n"/>
+      <c r="H126" s="18" t="n"/>
+      <c r="I126" s="18" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="n"/>
+      <c r="B127" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C124" s="21" t="n"/>
-      <c r="D124" s="21" t="n"/>
-      <c r="E124" s="21" t="n"/>
-      <c r="F124" s="21" t="n"/>
-      <c r="G124" s="21" t="n"/>
-      <c r="H124" s="21" t="n"/>
-      <c r="I124" s="21" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr"/>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="C127" s="21" t="n"/>
+      <c r="D127" s="21" t="n"/>
+      <c r="E127" s="21" t="n"/>
+      <c r="F127" s="21" t="n"/>
+      <c r="G127" s="21" t="n"/>
+      <c r="H127" s="21" t="n"/>
+      <c r="I127" s="21" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr"/>
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C128" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E125" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" s="5" t="n">
+      <c r="E128" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H125" s="12" t="n">
+      <c r="H128" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I125" s="13" t="inlineStr">
+      <c r="I128" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="16" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B126" s="2" t="n"/>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="17" t="inlineStr">
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="2" t="n"/>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="2" t="n"/>
+      <c r="I129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B127" s="18" t="n"/>
-      <c r="C127" s="18" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-      <c r="G127" s="18" t="n"/>
-      <c r="H127" s="18" t="n"/>
-      <c r="I127" s="18" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="21" t="n"/>
-      <c r="B128" s="22" t="inlineStr">
+      <c r="B130" s="18" t="n"/>
+      <c r="C130" s="18" t="n"/>
+      <c r="D130" s="18" t="n"/>
+      <c r="E130" s="18" t="n"/>
+      <c r="F130" s="18" t="n"/>
+      <c r="G130" s="18" t="n"/>
+      <c r="H130" s="18" t="n"/>
+      <c r="I130" s="18" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="21" t="n"/>
+      <c r="B131" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C128" s="21" t="n"/>
-      <c r="D128" s="21" t="n"/>
-      <c r="E128" s="21" t="n"/>
-      <c r="F128" s="21" t="n"/>
-      <c r="G128" s="21" t="n"/>
-      <c r="H128" s="21" t="n"/>
-      <c r="I128" s="21" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr"/>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="C131" s="21" t="n"/>
+      <c r="D131" s="21" t="n"/>
+      <c r="E131" s="21" t="n"/>
+      <c r="F131" s="21" t="n"/>
+      <c r="G131" s="21" t="n"/>
+      <c r="H131" s="21" t="n"/>
+      <c r="I131" s="21" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr"/>
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C129" s="5" t="n">
+      <c r="C132" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D132" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E129" s="5" t="n">
+      <c r="E132" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F129" s="5" t="n">
+      <c r="F132" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G129" s="5" t="inlineStr">
+      <c r="G132" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H129" s="12" t="n">
+      <c r="H132" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I129" s="13" t="inlineStr">
+      <c r="I132" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="86">
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A90:I90"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="A56:I56"/>
     <mergeCell ref="B48:I48"/>
     <mergeCell ref="B120:I120"/>
     <mergeCell ref="A126:I126"/>
+    <mergeCell ref="B98:I98"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
     <mergeCell ref="A109:I109"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B88:I88"/>
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="B65:I65"/>
@@ -7006,23 +7150,23 @@
     <mergeCell ref="B68:I68"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="A103:I103"/>
+    <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="B110:I110"/>
     <mergeCell ref="A87:I87"/>
-    <mergeCell ref="B85:I85"/>
     <mergeCell ref="B113:I113"/>
+    <mergeCell ref="B100:I100"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A116:I116"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="A100:I100"/>
     <mergeCell ref="A115:I115"/>
-    <mergeCell ref="B128:I128"/>
+    <mergeCell ref="A102:I102"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
@@ -7032,41 +7176,41 @@
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A32:I32"/>
-    <mergeCell ref="B117:I117"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A106:I106"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="B101:I101"/>
     <mergeCell ref="A38:I38"/>
+    <mergeCell ref="B116:I116"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A130:I130"/>
+    <mergeCell ref="B127:I127"/>
     <mergeCell ref="B95:I95"/>
-    <mergeCell ref="B89:I89"/>
     <mergeCell ref="B104:I104"/>
     <mergeCell ref="A119:I119"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="B26:I26"/>
-    <mergeCell ref="B97:I97"/>
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A84:I84"/>
     <mergeCell ref="B81:I81"/>
+    <mergeCell ref="A118:I118"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
+    <mergeCell ref="B131:I131"/>
+    <mergeCell ref="A86:I86"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="B107:I107"/>
     <mergeCell ref="B60:I60"/>
+    <mergeCell ref="A122:I122"/>
+    <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
     <mergeCell ref="A112:I112"/>
     <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A127:I127"/>
+    <mergeCell ref="B84:I84"/>
     <mergeCell ref="B92:I92"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B20:I20"/>
-    <mergeCell ref="A88:I88"/>
     <mergeCell ref="A70:I70"/>
   </mergeCells>
   <hyperlinks>
@@ -7098,21 +7242,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7124,7 +7269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7763,24 +7908,65 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="294" customHeight="1">
+    <row r="18" ht="266" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>Two Sum II - Input Array Is Sorted</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>167</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int[] twoSum(int[] numbers, int target) {
+     int left = 0;
+     int right = numbers.length - 1;
+     while(left&lt;=right){
+        int total = numbers[left]+ numbers[right];
+        if(total == target){
+            return new int[]{left+1,right+1};
+        }
+         if(total&gt;target){
+            right--;
+         }
+          if(total&lt;target){
+            left++;
+         }
+     }   
+     return new int[]{-1,-1};
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="294" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -7806,24 +7992,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="238" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="238" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -7845,24 +8031,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="238" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="238" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -7884,24 +8070,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="392" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="392" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>242</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -7934,24 +8120,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="182" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="182" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -7969,24 +8155,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="308" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="308" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>303</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -8010,24 +8196,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="420" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="420" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -8059,24 +8245,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="546" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="546" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>543</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -8114,24 +8300,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="182" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="182" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -8149,24 +8335,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="546" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="546" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -8210,24 +8396,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="196" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="196" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -8246,24 +8432,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="462" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="462" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>680</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -8293,24 +8479,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="378" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="378" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -8342,24 +8528,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="560" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="560" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>1013</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -8395,24 +8581,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="294" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="294" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -8435,24 +8621,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="224" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="224" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>1206</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -8473,24 +8659,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="420" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="420" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -8525,24 +8711,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="378" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="378" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>1353</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -8574,24 +8760,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="350" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="350" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -8621,24 +8807,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="238" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="238" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>2106</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -8660,24 +8846,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="308" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="308" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -8704,24 +8890,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="280" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="280" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>2775</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -8744,24 +8930,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="448" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="448" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -8796,24 +8982,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="378" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="378" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>3373</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -8845,24 +9031,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="266" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="266" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -8886,24 +9072,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="560" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="560" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -8956,24 +9142,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="238" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="238" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -8993,24 +9179,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="252" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="252" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>4003</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -9033,24 +9219,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="294" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="294" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -9076,24 +9262,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="252" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="252" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="5" t="n">
         <v>1</v>
@@ -1508,13 +1508,13 @@
         <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="36">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr"/>
       <c r="C36" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>1</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
       <c r="H36" s="9" t="inlineStr"/>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="B49" s="10" t="inlineStr"/>
       <c r="C49" s="11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>15</v>
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
       <c r="H49" s="11" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4198,11 +4198,61 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4245</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Math</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="12" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="L49" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F48">
+  <conditionalFormatting sqref="F5:F49">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -4258,6 +4308,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4269,7 +4320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I132"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6202,7 +6253,7 @@
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: MATH   —   4 solved   (Low: 3 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B90" s="2" t="n"/>
@@ -6347,7 +6398,7 @@
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B97" s="18" t="n"/>
@@ -6363,7 +6414,7 @@
       <c r="A98" s="21" t="n"/>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 1 problem(s)</t>
+          <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
       <c r="C98" s="21" t="n"/>
@@ -6410,715 +6461,750 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="19" t="n"/>
-      <c r="B100" s="20" t="inlineStr">
+      <c r="A100" s="7" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="19" t="n"/>
+      <c r="B101" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C100" s="19" t="n"/>
-      <c r="D100" s="19" t="n"/>
-      <c r="E100" s="19" t="n"/>
-      <c r="F100" s="19" t="n"/>
-      <c r="G100" s="19" t="n"/>
-      <c r="H100" s="19" t="n"/>
-      <c r="I100" s="19" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr"/>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="C101" s="19" t="n"/>
+      <c r="D101" s="19" t="n"/>
+      <c r="E101" s="19" t="n"/>
+      <c r="F101" s="19" t="n"/>
+      <c r="G101" s="19" t="n"/>
+      <c r="H101" s="19" t="n"/>
+      <c r="I101" s="19" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr"/>
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C102" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D102" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" s="5" t="n">
+      <c r="E102" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H101" s="12" t="n">
+      <c r="H102" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I101" s="13" t="inlineStr">
+      <c r="I102" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="16" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2" t="n"/>
-      <c r="I102" s="2" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="17" t="inlineStr">
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="n"/>
+      <c r="I103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B103" s="18" t="n"/>
-      <c r="C103" s="18" t="n"/>
-      <c r="D103" s="18" t="n"/>
-      <c r="E103" s="18" t="n"/>
-      <c r="F103" s="18" t="n"/>
-      <c r="G103" s="18" t="n"/>
-      <c r="H103" s="18" t="n"/>
-      <c r="I103" s="18" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="21" t="n"/>
-      <c r="B104" s="22" t="inlineStr">
+      <c r="B104" s="18" t="n"/>
+      <c r="C104" s="18" t="n"/>
+      <c r="D104" s="18" t="n"/>
+      <c r="E104" s="18" t="n"/>
+      <c r="F104" s="18" t="n"/>
+      <c r="G104" s="18" t="n"/>
+      <c r="H104" s="18" t="n"/>
+      <c r="I104" s="18" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C104" s="21" t="n"/>
-      <c r="D104" s="21" t="n"/>
-      <c r="E104" s="21" t="n"/>
-      <c r="F104" s="21" t="n"/>
-      <c r="G104" s="21" t="n"/>
-      <c r="H104" s="21" t="n"/>
-      <c r="I104" s="21" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr"/>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="C105" s="21" t="n"/>
+      <c r="D105" s="21" t="n"/>
+      <c r="E105" s="21" t="n"/>
+      <c r="F105" s="21" t="n"/>
+      <c r="G105" s="21" t="n"/>
+      <c r="H105" s="21" t="n"/>
+      <c r="I105" s="21" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr"/>
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C106" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E105" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="5" t="n">
+      <c r="E106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G105" s="5" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H105" s="12" t="n">
+      <c r="H106" s="12" t="n">
         <v>46241.78204861111</v>
       </c>
-      <c r="I105" s="13" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="17" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B106" s="18" t="n"/>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="18" t="n"/>
-      <c r="G106" s="18" t="n"/>
-      <c r="H106" s="18" t="n"/>
-      <c r="I106" s="18" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="19" t="n"/>
-      <c r="B107" s="20" t="inlineStr">
+      <c r="B107" s="18" t="n"/>
+      <c r="C107" s="18" t="n"/>
+      <c r="D107" s="18" t="n"/>
+      <c r="E107" s="18" t="n"/>
+      <c r="F107" s="18" t="n"/>
+      <c r="G107" s="18" t="n"/>
+      <c r="H107" s="18" t="n"/>
+      <c r="I107" s="18" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="19" t="n"/>
+      <c r="B108" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C107" s="19" t="n"/>
-      <c r="D107" s="19" t="n"/>
-      <c r="E107" s="19" t="n"/>
-      <c r="F107" s="19" t="n"/>
-      <c r="G107" s="19" t="n"/>
-      <c r="H107" s="19" t="n"/>
-      <c r="I107" s="19" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr"/>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="C108" s="19" t="n"/>
+      <c r="D108" s="19" t="n"/>
+      <c r="E108" s="19" t="n"/>
+      <c r="F108" s="19" t="n"/>
+      <c r="G108" s="19" t="n"/>
+      <c r="H108" s="19" t="n"/>
+      <c r="I108" s="19" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr"/>
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
-      <c r="C108" s="5" t="n">
+      <c r="C109" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="F108" s="5" t="n">
+      <c r="F109" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H108" s="12" t="n">
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H109" s="12" t="n">
         <v>46253.82314814815</v>
       </c>
-      <c r="I108" s="13" t="inlineStr">
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="17" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B109" s="18" t="n"/>
-      <c r="C109" s="18" t="n"/>
-      <c r="D109" s="18" t="n"/>
-      <c r="E109" s="18" t="n"/>
-      <c r="F109" s="18" t="n"/>
-      <c r="G109" s="18" t="n"/>
-      <c r="H109" s="18" t="n"/>
-      <c r="I109" s="18" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="21" t="n"/>
-      <c r="B110" s="22" t="inlineStr">
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="18" t="n"/>
+      <c r="E110" s="18" t="n"/>
+      <c r="F110" s="18" t="n"/>
+      <c r="G110" s="18" t="n"/>
+      <c r="H110" s="18" t="n"/>
+      <c r="I110" s="18" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="n"/>
+      <c r="B111" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C110" s="21" t="n"/>
-      <c r="D110" s="21" t="n"/>
-      <c r="E110" s="21" t="n"/>
-      <c r="F110" s="21" t="n"/>
-      <c r="G110" s="21" t="n"/>
-      <c r="H110" s="21" t="n"/>
-      <c r="I110" s="21" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr"/>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="C111" s="21" t="n"/>
+      <c r="D111" s="21" t="n"/>
+      <c r="E111" s="21" t="n"/>
+      <c r="F111" s="21" t="n"/>
+      <c r="G111" s="21" t="n"/>
+      <c r="H111" s="21" t="n"/>
+      <c r="I111" s="21" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr"/>
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C112" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D112" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E111" s="5" t="n">
+      <c r="E112" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F111" s="5" t="n">
+      <c r="F112" s="5" t="n">
         <v>44.6</v>
       </c>
-      <c r="G111" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H111" s="12" t="n">
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H112" s="12" t="n">
         <v>46243.94849537037</v>
       </c>
-      <c r="I111" s="13" t="inlineStr">
+      <c r="I112" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="17" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="21" t="n"/>
-      <c r="B113" s="22" t="inlineStr">
+      <c r="B113" s="18" t="n"/>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+      <c r="G113" s="18" t="n"/>
+      <c r="H113" s="18" t="n"/>
+      <c r="I113" s="18" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="n"/>
+      <c r="B114" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C113" s="21" t="n"/>
-      <c r="D113" s="21" t="n"/>
-      <c r="E113" s="21" t="n"/>
-      <c r="F113" s="21" t="n"/>
-      <c r="G113" s="21" t="n"/>
-      <c r="H113" s="21" t="n"/>
-      <c r="I113" s="21" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr"/>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="C114" s="21" t="n"/>
+      <c r="D114" s="21" t="n"/>
+      <c r="E114" s="21" t="n"/>
+      <c r="F114" s="21" t="n"/>
+      <c r="G114" s="21" t="n"/>
+      <c r="H114" s="21" t="n"/>
+      <c r="I114" s="21" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr"/>
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C115" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D114" s="5" t="inlineStr">
+      <c r="D115" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E114" s="5" t="n">
+      <c r="E115" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F114" s="5" t="n">
+      <c r="F115" s="5" t="n">
         <v>45.3</v>
       </c>
-      <c r="G114" s="5" t="inlineStr">
+      <c r="G115" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H114" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>46243.9169675926</v>
       </c>
-      <c r="I114" s="13" t="inlineStr">
+      <c r="I115" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="17" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B115" s="18" t="n"/>
-      <c r="C115" s="18" t="n"/>
-      <c r="D115" s="18" t="n"/>
-      <c r="E115" s="18" t="n"/>
-      <c r="F115" s="18" t="n"/>
-      <c r="G115" s="18" t="n"/>
-      <c r="H115" s="18" t="n"/>
-      <c r="I115" s="18" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="21" t="n"/>
-      <c r="B116" s="22" t="inlineStr">
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="18" t="n"/>
+      <c r="I116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="n"/>
+      <c r="B117" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C116" s="21" t="n"/>
-      <c r="D116" s="21" t="n"/>
-      <c r="E116" s="21" t="n"/>
-      <c r="F116" s="21" t="n"/>
-      <c r="G116" s="21" t="n"/>
-      <c r="H116" s="21" t="n"/>
-      <c r="I116" s="21" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr"/>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="C117" s="21" t="n"/>
+      <c r="D117" s="21" t="n"/>
+      <c r="E117" s="21" t="n"/>
+      <c r="F117" s="21" t="n"/>
+      <c r="G117" s="21" t="n"/>
+      <c r="H117" s="21" t="n"/>
+      <c r="I117" s="21" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr"/>
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C118" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E117" s="5" t="n">
+      <c r="E118" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F117" s="5" t="n">
+      <c r="F118" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H117" s="12" t="n">
+      <c r="H118" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I117" s="13" t="inlineStr">
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="16" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="n"/>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="17" t="inlineStr">
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="n"/>
+      <c r="I119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B119" s="18" t="n"/>
-      <c r="C119" s="18" t="n"/>
-      <c r="D119" s="18" t="n"/>
-      <c r="E119" s="18" t="n"/>
-      <c r="F119" s="18" t="n"/>
-      <c r="G119" s="18" t="n"/>
-      <c r="H119" s="18" t="n"/>
-      <c r="I119" s="18" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="21" t="n"/>
-      <c r="B120" s="22" t="inlineStr">
+      <c r="B120" s="18" t="n"/>
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="18" t="n"/>
+      <c r="E120" s="18" t="n"/>
+      <c r="F120" s="18" t="n"/>
+      <c r="G120" s="18" t="n"/>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="n"/>
+      <c r="B121" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C120" s="21" t="n"/>
-      <c r="D120" s="21" t="n"/>
-      <c r="E120" s="21" t="n"/>
-      <c r="F120" s="21" t="n"/>
-      <c r="G120" s="21" t="n"/>
-      <c r="H120" s="21" t="n"/>
-      <c r="I120" s="21" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr"/>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="C121" s="21" t="n"/>
+      <c r="D121" s="21" t="n"/>
+      <c r="E121" s="21" t="n"/>
+      <c r="F121" s="21" t="n"/>
+      <c r="G121" s="21" t="n"/>
+      <c r="H121" s="21" t="n"/>
+      <c r="I121" s="21" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr"/>
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C122" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E121" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="5" t="n">
+      <c r="E122" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G121" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="n">
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="n">
         <v>46248.99621527778</v>
       </c>
-      <c r="I121" s="13" t="inlineStr">
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="17" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="18" t="n"/>
-      <c r="D122" s="18" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
-      <c r="G122" s="18" t="n"/>
-      <c r="H122" s="18" t="n"/>
-      <c r="I122" s="18" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="21" t="n"/>
-      <c r="B123" s="22" t="inlineStr">
+      <c r="B123" s="18" t="n"/>
+      <c r="C123" s="18" t="n"/>
+      <c r="D123" s="18" t="n"/>
+      <c r="E123" s="18" t="n"/>
+      <c r="F123" s="18" t="n"/>
+      <c r="G123" s="18" t="n"/>
+      <c r="H123" s="18" t="n"/>
+      <c r="I123" s="18" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="21" t="n"/>
+      <c r="B124" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C123" s="21" t="n"/>
-      <c r="D123" s="21" t="n"/>
-      <c r="E123" s="21" t="n"/>
-      <c r="F123" s="21" t="n"/>
-      <c r="G123" s="21" t="n"/>
-      <c r="H123" s="21" t="n"/>
-      <c r="I123" s="21" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr"/>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="C124" s="21" t="n"/>
+      <c r="D124" s="21" t="n"/>
+      <c r="E124" s="21" t="n"/>
+      <c r="F124" s="21" t="n"/>
+      <c r="G124" s="21" t="n"/>
+      <c r="H124" s="21" t="n"/>
+      <c r="I124" s="21" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr"/>
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C124" s="5" t="n">
+      <c r="C125" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D125" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E124" s="5" t="n">
+      <c r="E125" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F124" s="5" t="n">
+      <c r="F125" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G125" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H124" s="12" t="n">
+      <c r="H125" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I124" s="13" t="inlineStr">
+      <c r="I125" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="7" t="inlineStr"/>
-      <c r="B125" s="6" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="7" t="inlineStr"/>
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C125" s="7" t="n">
+      <c r="C126" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D125" s="7" t="inlineStr">
+      <c r="D126" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E125" s="7" t="n">
+      <c r="E126" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F125" s="7" t="n">
+      <c r="F126" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G125" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H125" s="14" t="n">
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I125" s="15" t="inlineStr">
+      <c r="I126" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="17" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B126" s="18" t="n"/>
-      <c r="C126" s="18" t="n"/>
-      <c r="D126" s="18" t="n"/>
-      <c r="E126" s="18" t="n"/>
-      <c r="F126" s="18" t="n"/>
-      <c r="G126" s="18" t="n"/>
-      <c r="H126" s="18" t="n"/>
-      <c r="I126" s="18" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="21" t="n"/>
-      <c r="B127" s="22" t="inlineStr">
+      <c r="B127" s="18" t="n"/>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+      <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="n"/>
+      <c r="B128" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C127" s="21" t="n"/>
-      <c r="D127" s="21" t="n"/>
-      <c r="E127" s="21" t="n"/>
-      <c r="F127" s="21" t="n"/>
-      <c r="G127" s="21" t="n"/>
-      <c r="H127" s="21" t="n"/>
-      <c r="I127" s="21" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr"/>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="C128" s="21" t="n"/>
+      <c r="D128" s="21" t="n"/>
+      <c r="E128" s="21" t="n"/>
+      <c r="F128" s="21" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="21" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr"/>
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C128" s="5" t="n">
+      <c r="C129" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E128" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="5" t="n">
+      <c r="E129" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H128" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I128" s="13" t="inlineStr">
+      <c r="I129" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B129" s="2" t="n"/>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="n"/>
-      <c r="F129" s="2" t="n"/>
-      <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="17" t="inlineStr">
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B130" s="18" t="n"/>
-      <c r="C130" s="18" t="n"/>
-      <c r="D130" s="18" t="n"/>
-      <c r="E130" s="18" t="n"/>
-      <c r="F130" s="18" t="n"/>
-      <c r="G130" s="18" t="n"/>
-      <c r="H130" s="18" t="n"/>
-      <c r="I130" s="18" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="21" t="n"/>
-      <c r="B131" s="22" t="inlineStr">
+      <c r="B131" s="18" t="n"/>
+      <c r="C131" s="18" t="n"/>
+      <c r="D131" s="18" t="n"/>
+      <c r="E131" s="18" t="n"/>
+      <c r="F131" s="18" t="n"/>
+      <c r="G131" s="18" t="n"/>
+      <c r="H131" s="18" t="n"/>
+      <c r="I131" s="18" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="21" t="n"/>
+      <c r="B132" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C131" s="21" t="n"/>
-      <c r="D131" s="21" t="n"/>
-      <c r="E131" s="21" t="n"/>
-      <c r="F131" s="21" t="n"/>
-      <c r="G131" s="21" t="n"/>
-      <c r="H131" s="21" t="n"/>
-      <c r="I131" s="21" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr"/>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="C132" s="21" t="n"/>
+      <c r="D132" s="21" t="n"/>
+      <c r="E132" s="21" t="n"/>
+      <c r="F132" s="21" t="n"/>
+      <c r="G132" s="21" t="n"/>
+      <c r="H132" s="21" t="n"/>
+      <c r="I132" s="21" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr"/>
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C132" s="5" t="n">
+      <c r="C133" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E132" s="5" t="n">
+      <c r="E133" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F132" s="5" t="n">
+      <c r="F133" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G132" s="5" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H132" s="12" t="n">
+      <c r="H133" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I132" s="13" t="inlineStr">
+      <c r="I133" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7130,14 +7216,13 @@
     <mergeCell ref="A90:I90"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="A56:I56"/>
+    <mergeCell ref="B105:I105"/>
     <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B120:I120"/>
-    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="B111:I111"/>
     <mergeCell ref="B98:I98"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A53:I53"/>
     <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A109:I109"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="B17:I17"/>
     <mergeCell ref="B88:I88"/>
@@ -7150,65 +7235,66 @@
     <mergeCell ref="B68:I68"/>
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="A103:I103"/>
-    <mergeCell ref="B123:I123"/>
     <mergeCell ref="B36:I36"/>
     <mergeCell ref="B45:I45"/>
-    <mergeCell ref="B110:I110"/>
     <mergeCell ref="A87:I87"/>
-    <mergeCell ref="B113:I113"/>
-    <mergeCell ref="B100:I100"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="A129:I129"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A116:I116"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="B14:I14"/>
     <mergeCell ref="A91:I91"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="A115:I115"/>
-    <mergeCell ref="A102:I102"/>
+    <mergeCell ref="A131:I131"/>
+    <mergeCell ref="B128:I128"/>
     <mergeCell ref="A83:I83"/>
     <mergeCell ref="B33:I33"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="A94:I94"/>
+    <mergeCell ref="B114:I114"/>
     <mergeCell ref="B63:I63"/>
     <mergeCell ref="A80:I80"/>
+    <mergeCell ref="A120:I120"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A113:I113"/>
     <mergeCell ref="B77:I77"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A32:I32"/>
+    <mergeCell ref="B117:I117"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A106:I106"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="B101:I101"/>
+    <mergeCell ref="B132:I132"/>
     <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B116:I116"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="A67:I67"/>
     <mergeCell ref="A130:I130"/>
-    <mergeCell ref="B127:I127"/>
+    <mergeCell ref="A123:I123"/>
     <mergeCell ref="B95:I95"/>
-    <mergeCell ref="B104:I104"/>
+    <mergeCell ref="A110:I110"/>
     <mergeCell ref="A119:I119"/>
     <mergeCell ref="A16:I16"/>
     <mergeCell ref="B26:I26"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="B81:I81"/>
-    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="B121:I121"/>
     <mergeCell ref="A50:I50"/>
     <mergeCell ref="B71:I71"/>
-    <mergeCell ref="B131:I131"/>
     <mergeCell ref="A86:I86"/>
     <mergeCell ref="A47:I47"/>
     <mergeCell ref="B42:I42"/>
-    <mergeCell ref="B107:I107"/>
     <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A122:I122"/>
     <mergeCell ref="A97:I97"/>
     <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A112:I112"/>
     <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A127:I127"/>
+    <mergeCell ref="B108:I108"/>
     <mergeCell ref="B84:I84"/>
     <mergeCell ref="B92:I92"/>
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A107:I107"/>
+    <mergeCell ref="B124:I124"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="A70:I70"/>
@@ -7247,17 +7333,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7269,7 +7356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9219,24 +9306,55 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="294" customHeight="1">
+    <row r="47" ht="140" customHeight="1">
       <c r="A47" s="5" t="n">
         <v>43</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int countCommas(int n) {
+        int count = 0;
+    if(n&gt;999 &amp;&amp; n&lt;=100000){
+        count = n - 999;
+    } 
+    return count ;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="294" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>4281</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -9262,24 +9380,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="252" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="252" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -722,19 +722,19 @@
         <v>0</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>43.8</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="6">
@@ -1372,13 +1372,13 @@
         <v>16</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G30" s="9" t="inlineStr"/>
       <c r="H30" s="9" t="inlineStr"/>
@@ -1862,13 +1862,13 @@
         <v>30</v>
       </c>
       <c r="D49" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G49" s="11" t="inlineStr"/>
       <c r="H49" s="11" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4248,11 +4248,61 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Find Peak Element</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Binary Search</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" s="14" t="n">
+        <v>46273.41739583333</v>
+      </c>
+      <c r="L50" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F49">
+  <conditionalFormatting sqref="F5:F50">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -4309,6 +4359,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4320,7 +4371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4363,7 +4414,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   29 solved   (Low: 16 · Medium: 13 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   30 solved   (Low: 16 · Medium: 14 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -4378,7 +4429,7 @@
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Binary Search   —   2 solved   (Low: 0 · Medium: 2 · High: 0)</t>
         </is>
       </c>
       <c r="B5" s="18" t="n"/>
@@ -4394,7 +4445,7 @@
       <c r="A6" s="19" t="n"/>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
+          <t>Medium (Medium) — 2 problem(s)</t>
         </is>
       </c>
       <c r="C6" s="19" t="n"/>
@@ -4441,2770 +4492,2805 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Find Peak Element</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>46273.41739583333</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Binary Search, Sliding Window, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="18" t="n"/>
-      <c r="I8" s="18" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n"/>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n"/>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="19" t="n"/>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="19" t="n"/>
-      <c r="I9" s="19" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C11" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>69.2</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="n">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>46256.69032407407</v>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Bit Manipulation   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n"/>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="18" t="n"/>
-      <c r="I11" s="18" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="n"/>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="n"/>
+      <c r="I12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
-      <c r="G12" s="21" t="n"/>
-      <c r="H12" s="21" t="n"/>
-      <c r="I12" s="21" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Single Number</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C14" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>47.1</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>46242.88846064815</v>
       </c>
-      <c r="I13" s="13" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="19" t="n"/>
-      <c r="B14" s="20" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="19" t="n"/>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Single Number II</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E16" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>45.1</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="n">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="n">
         <v>46256.48149305556</v>
       </c>
-      <c r="I15" s="13" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Design, Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="18" t="n"/>
-      <c r="I16" s="18" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="n"/>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="18" t="n"/>
+      <c r="I17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="n"/>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="19" t="n"/>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="19" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C19" s="5" t="n">
         <v>304</v>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E19" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="n">
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>46263.00756944445</v>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Design, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="n"/>
-      <c r="I19" s="18" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n"/>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="18" t="n"/>
+      <c r="I20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="21" t="n"/>
-      <c r="I20" s="21" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr"/>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
+      <c r="I21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E22" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F22" s="5" t="n">
         <v>47.7</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="n">
         <v>46262.9494212963</v>
       </c>
-      <c r="I21" s="13" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Divide and Conquer, Dynamic Programming   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="18" t="n"/>
-      <c r="I22" s="18" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="n"/>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="18" t="n"/>
+      <c r="I23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="n"/>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="19" t="n"/>
-      <c r="F23" s="19" t="n"/>
-      <c r="G23" s="19" t="n"/>
-      <c r="H23" s="19" t="n"/>
-      <c r="I23" s="19" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr"/>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="19" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="19" t="n"/>
+      <c r="I24" s="19" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Maximum Subarray</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C25" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5" t="n">
+      <c r="E25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="n">
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n">
         <v>46263.45222222222</v>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I25" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="18" t="n"/>
-      <c r="I25" s="18" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="19" t="n"/>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="18" t="n"/>
+      <c r="I26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="n"/>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C26" s="19" t="n"/>
-      <c r="D26" s="19" t="n"/>
-      <c r="E26" s="19" t="n"/>
-      <c r="F26" s="19" t="n"/>
-      <c r="G26" s="19" t="n"/>
-      <c r="H26" s="19" t="n"/>
-      <c r="I26" s="19" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr"/>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5" t="n">
+      <c r="E28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="n">
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>46247.80789351852</v>
       </c>
-      <c r="I27" s="13" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="18" t="n"/>
-      <c r="I28" s="18" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="n"/>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="18" t="n"/>
+      <c r="I29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n"/>
-      <c r="D29" s="21" t="n"/>
-      <c r="E29" s="21" t="n"/>
-      <c r="F29" s="21" t="n"/>
-      <c r="G29" s="21" t="n"/>
-      <c r="H29" s="21" t="n"/>
-      <c r="I29" s="21" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="21" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="21" t="n"/>
+      <c r="H30" s="21" t="n"/>
+      <c r="I30" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Two Sum</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E31" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F31" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>46251.8174537037</v>
       </c>
-      <c r="I30" s="13" t="inlineStr">
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr"/>
-      <c r="B31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C32" s="7" t="n">
         <v>3705</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="7" t="n">
+      <c r="E32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="7" t="n">
         <v>45.1</v>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="H32" s="14" t="n">
         <v>46252.95966435185</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
+      <c r="I32" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="18" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="19" t="n"/>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="19" t="n"/>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C33" s="19" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="19" t="n"/>
-      <c r="F33" s="19" t="n"/>
-      <c r="G33" s="19" t="n"/>
-      <c r="H33" s="19" t="n"/>
-      <c r="I33" s="19" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr"/>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="19" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="19" t="n"/>
+      <c r="H34" s="19" t="n"/>
+      <c r="I34" s="19" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C35" s="5" t="n">
         <v>560</v>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E35" s="5" t="n">
         <v>1544</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F35" s="5" t="n">
         <v>48.6</v>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="n">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>46263.40873842593</v>
       </c>
-      <c r="I34" s="13" t="inlineStr">
+      <c r="I35" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="18" t="n"/>
-      <c r="I35" s="18" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="n"/>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="18" t="n"/>
+      <c r="I36" s="18" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="n"/>
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="21" t="n"/>
-      <c r="G36" s="21" t="n"/>
-      <c r="H36" s="21" t="n"/>
-      <c r="I36" s="21" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr"/>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="21" t="n"/>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="21" t="n"/>
+      <c r="H37" s="21" t="n"/>
+      <c r="I37" s="21" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr"/>
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E38" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F38" s="5" t="n">
         <v>104.8</v>
       </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="n">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>46258.98878472222</v>
       </c>
-      <c r="I37" s="13" t="inlineStr">
+      <c r="I38" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="18" t="n"/>
-      <c r="I38" s="18" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="n"/>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
-      <c r="H39" s="21" t="n"/>
-      <c r="I39" s="21" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr"/>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="21" t="n"/>
+      <c r="I40" s="21" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C41" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="5" t="n">
+      <c r="E41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="n">
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="n">
         <v>46243.98008101852</v>
       </c>
-      <c r="I40" s="13" t="inlineStr">
+      <c r="I41" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="18" t="n"/>
-      <c r="I41" s="18" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="19" t="n"/>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="18" t="n"/>
+      <c r="I42" s="18" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="n"/>
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="19" t="n"/>
-      <c r="I42" s="19" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr"/>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="19" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="19" t="n"/>
+      <c r="H43" s="19" t="n"/>
+      <c r="I43" s="19" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E44" s="5" t="n">
         <v>709</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F44" s="5" t="n">
         <v>79.8</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="n">
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="n">
         <v>46255.64438657407</v>
       </c>
-      <c r="I43" s="13" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="18" t="n"/>
-      <c r="I44" s="18" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="21" t="n"/>
-      <c r="B45" s="22" t="inlineStr">
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="18" t="n"/>
+      <c r="H45" s="18" t="n"/>
+      <c r="I45" s="18" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="21" t="n"/>
-      <c r="F45" s="21" t="n"/>
-      <c r="G45" s="21" t="n"/>
-      <c r="H45" s="21" t="n"/>
-      <c r="I45" s="21" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr"/>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="n"/>
+      <c r="H46" s="21" t="n"/>
+      <c r="I46" s="21" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C47" s="5" t="n">
         <v>1115</v>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="5" t="n">
+      <c r="E47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="5" t="n">
         <v>42.9</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>46244.79871527778</v>
       </c>
-      <c r="I46" s="13" t="inlineStr">
+      <c r="I47" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B47" s="18" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="18" t="n"/>
-      <c r="E47" s="18" t="n"/>
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="18" t="n"/>
-      <c r="H47" s="18" t="n"/>
-      <c r="I47" s="18" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="21" t="n"/>
-      <c r="B48" s="22" t="inlineStr">
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="18" t="n"/>
+      <c r="I48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="n"/>
+      <c r="B49" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C48" s="21" t="n"/>
-      <c r="D48" s="21" t="n"/>
-      <c r="E48" s="21" t="n"/>
-      <c r="F48" s="21" t="n"/>
-      <c r="G48" s="21" t="n"/>
-      <c r="H48" s="21" t="n"/>
-      <c r="I48" s="21" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr"/>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="n"/>
+      <c r="H49" s="21" t="n"/>
+      <c r="I49" s="21" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="5" t="n">
         <v>2722</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E50" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F50" s="5" t="n">
         <v>82.5</v>
       </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H49" s="12" t="n">
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="n">
         <v>46255.61045138889</v>
       </c>
-      <c r="I49" s="13" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="18" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-      <c r="G50" s="18" t="n"/>
-      <c r="H50" s="18" t="n"/>
-      <c r="I50" s="18" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="21" t="n"/>
-      <c r="B51" s="22" t="inlineStr">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="18" t="n"/>
+      <c r="I51" s="18" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="n"/>
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="21" t="n"/>
-      <c r="F51" s="21" t="n"/>
-      <c r="G51" s="21" t="n"/>
-      <c r="H51" s="21" t="n"/>
-      <c r="I51" s="21" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr"/>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="n"/>
+      <c r="H52" s="21" t="n"/>
+      <c r="I52" s="21" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr"/>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C53" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="n">
+      <c r="E53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="5" t="n">
         <v>45.2</v>
       </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H52" s="12" t="n">
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="n">
         <v>46255.57113425926</v>
       </c>
-      <c r="I52" s="13" t="inlineStr">
+      <c r="I53" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B53" s="18" t="n"/>
-      <c r="C53" s="18" t="n"/>
-      <c r="D53" s="18" t="n"/>
-      <c r="E53" s="18" t="n"/>
-      <c r="F53" s="18" t="n"/>
-      <c r="G53" s="18" t="n"/>
-      <c r="H53" s="18" t="n"/>
-      <c r="I53" s="18" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="19" t="n"/>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="18" t="n"/>
+      <c r="H54" s="18" t="n"/>
+      <c r="I54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="19" t="n"/>
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="19" t="n"/>
-      <c r="E54" s="19" t="n"/>
-      <c r="F54" s="19" t="n"/>
-      <c r="G54" s="19" t="n"/>
-      <c r="H54" s="19" t="n"/>
-      <c r="I54" s="19" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr"/>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
+      <c r="G55" s="19" t="n"/>
+      <c r="H55" s="19" t="n"/>
+      <c r="I55" s="19" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr"/>
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C56" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="5" t="n">
+      <c r="E56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="5" t="n">
         <v>117.3</v>
       </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H55" s="12" t="n">
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="n">
         <v>46255.5928587963</v>
       </c>
-      <c r="I55" s="13" t="inlineStr">
+      <c r="I56" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B56" s="18" t="n"/>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="18" t="n"/>
-      <c r="F56" s="18" t="n"/>
-      <c r="G56" s="18" t="n"/>
-      <c r="H56" s="18" t="n"/>
-      <c r="I56" s="18" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="21" t="n"/>
-      <c r="B57" s="22" t="inlineStr">
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="18" t="n"/>
+      <c r="I57" s="18" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="n"/>
+      <c r="B58" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C57" s="21" t="n"/>
-      <c r="D57" s="21" t="n"/>
-      <c r="E57" s="21" t="n"/>
-      <c r="F57" s="21" t="n"/>
-      <c r="G57" s="21" t="n"/>
-      <c r="H57" s="21" t="n"/>
-      <c r="I57" s="21" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr"/>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="21" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="n"/>
+      <c r="H58" s="21" t="n"/>
+      <c r="I58" s="21" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C59" s="5" t="n">
         <v>1693</v>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D59" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E59" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F59" s="5" t="n">
         <v>42.8</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H58" s="12" t="n">
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="n">
         <v>46261.883125</v>
       </c>
-      <c r="I58" s="13" t="inlineStr">
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B59" s="18" t="n"/>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="18" t="n"/>
-      <c r="I59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="19" t="n"/>
-      <c r="B60" s="20" t="inlineStr">
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="18" t="n"/>
+      <c r="I60" s="18" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="n"/>
+      <c r="B61" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-      <c r="G60" s="19" t="n"/>
-      <c r="H60" s="19" t="n"/>
-      <c r="I60" s="19" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr"/>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+      <c r="G61" s="19" t="n"/>
+      <c r="H61" s="19" t="n"/>
+      <c r="I61" s="19" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr"/>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C62" s="5" t="n">
         <v>1242</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E61" s="5" t="n">
+      <c r="E62" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F62" s="5" t="n">
         <v>46.8</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H61" s="12" t="n">
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="n">
         <v>46262.8983912037</v>
       </c>
-      <c r="I61" s="13" t="inlineStr">
+      <c r="I62" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="18" t="n"/>
-      <c r="D62" s="18" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="18" t="n"/>
-      <c r="G62" s="18" t="n"/>
-      <c r="H62" s="18" t="n"/>
-      <c r="I62" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="21" t="n"/>
-      <c r="B63" s="22" t="inlineStr">
+      <c r="B63" s="18" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="18" t="n"/>
+      <c r="I63" s="18" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="n"/>
+      <c r="B64" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C63" s="21" t="n"/>
-      <c r="D63" s="21" t="n"/>
-      <c r="E63" s="21" t="n"/>
-      <c r="F63" s="21" t="n"/>
-      <c r="G63" s="21" t="n"/>
-      <c r="H63" s="21" t="n"/>
-      <c r="I63" s="21" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr"/>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="21" t="n"/>
+      <c r="E64" s="21" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="n"/>
+      <c r="H64" s="21" t="n"/>
+      <c r="I64" s="21" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C65" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="5" t="n">
+      <c r="E65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H64" s="12" t="n">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="n">
         <v>46270.61052083333</v>
       </c>
-      <c r="I64" s="13" t="inlineStr">
+      <c r="I65" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="19" t="n"/>
-      <c r="B65" s="20" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="19" t="n"/>
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C65" s="19" t="n"/>
-      <c r="D65" s="19" t="n"/>
-      <c r="E65" s="19" t="n"/>
-      <c r="F65" s="19" t="n"/>
-      <c r="G65" s="19" t="n"/>
-      <c r="H65" s="19" t="n"/>
-      <c r="I65" s="19" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr"/>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="C66" s="19" t="n"/>
+      <c r="D66" s="19" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="19" t="n"/>
+      <c r="G66" s="19" t="n"/>
+      <c r="H66" s="19" t="n"/>
+      <c r="I66" s="19" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr"/>
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C67" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
+      <c r="E67" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F67" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H66" s="12" t="n">
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H67" s="12" t="n">
         <v>46262.6837962963</v>
       </c>
-      <c r="I66" s="13" t="inlineStr">
+      <c r="I67" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B67" s="18" t="n"/>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-      <c r="G67" s="18" t="n"/>
-      <c r="H67" s="18" t="n"/>
-      <c r="I67" s="18" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="21" t="n"/>
-      <c r="B68" s="22" t="inlineStr">
+      <c r="B68" s="18" t="n"/>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="n"/>
+      <c r="B69" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C68" s="21" t="n"/>
-      <c r="D68" s="21" t="n"/>
-      <c r="E68" s="21" t="n"/>
-      <c r="F68" s="21" t="n"/>
-      <c r="G68" s="21" t="n"/>
-      <c r="H68" s="21" t="n"/>
-      <c r="I68" s="21" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr"/>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="21" t="n"/>
+      <c r="E69" s="21" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="21" t="n"/>
+      <c r="I69" s="21" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr"/>
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C70" s="5" t="n">
         <v>3347</v>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D70" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" s="5" t="n">
+      <c r="E70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H69" s="12" t="n">
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="n">
         <v>46255.01133101852</v>
       </c>
-      <c r="I69" s="13" t="inlineStr">
+      <c r="I70" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B70" s="18" t="n"/>
-      <c r="C70" s="18" t="n"/>
-      <c r="D70" s="18" t="n"/>
-      <c r="E70" s="18" t="n"/>
-      <c r="F70" s="18" t="n"/>
-      <c r="G70" s="18" t="n"/>
-      <c r="H70" s="18" t="n"/>
-      <c r="I70" s="18" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="21" t="n"/>
-      <c r="B71" s="22" t="inlineStr">
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="18" t="n"/>
+      <c r="I71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C71" s="21" t="n"/>
-      <c r="D71" s="21" t="n"/>
-      <c r="E71" s="21" t="n"/>
-      <c r="F71" s="21" t="n"/>
-      <c r="G71" s="21" t="n"/>
-      <c r="H71" s="21" t="n"/>
-      <c r="I71" s="21" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr"/>
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C73" s="5" t="n">
         <v>643</v>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
+      <c r="E73" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F73" s="5" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="n">
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="n">
         <v>46256.65385416667</v>
       </c>
-      <c r="I72" s="13" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B73" s="18" t="n"/>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="18" t="n"/>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="18" t="n"/>
-      <c r="I73" s="18" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="21" t="n"/>
-      <c r="B74" s="22" t="inlineStr">
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="18" t="n"/>
+      <c r="I74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="n"/>
+      <c r="B75" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C74" s="21" t="n"/>
-      <c r="D74" s="21" t="n"/>
-      <c r="E74" s="21" t="n"/>
-      <c r="F74" s="21" t="n"/>
-      <c r="G74" s="21" t="n"/>
-      <c r="H74" s="21" t="n"/>
-      <c r="I74" s="21" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr"/>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="C75" s="21" t="n"/>
+      <c r="D75" s="21" t="n"/>
+      <c r="E75" s="21" t="n"/>
+      <c r="F75" s="21" t="n"/>
+      <c r="G75" s="21" t="n"/>
+      <c r="H75" s="21" t="n"/>
+      <c r="I75" s="21" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr"/>
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C76" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E76" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F76" s="5" t="n">
         <v>47.2</v>
       </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H75" s="12" t="n">
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>46247.02123842593</v>
       </c>
-      <c r="I75" s="13" t="inlineStr">
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B76" s="18" t="n"/>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
-      <c r="H76" s="18" t="n"/>
-      <c r="I76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="21" t="n"/>
-      <c r="B77" s="22" t="inlineStr">
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C77" s="21" t="n"/>
-      <c r="D77" s="21" t="n"/>
-      <c r="E77" s="21" t="n"/>
-      <c r="F77" s="21" t="n"/>
-      <c r="G77" s="21" t="n"/>
-      <c r="H77" s="21" t="n"/>
-      <c r="I77" s="21" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr"/>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="21" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="21" t="n"/>
+      <c r="H78" s="21" t="n"/>
+      <c r="I78" s="21" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr"/>
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C79" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D78" s="5" t="inlineStr">
+      <c r="D79" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="5" t="n">
+      <c r="E79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H78" s="12" t="n">
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I78" s="13" t="inlineStr">
+      <c r="I79" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr"/>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C79" s="7" t="n">
+      <c r="C80" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E79" s="7" t="n">
+      <c r="E80" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F79" s="7" t="n">
+      <c r="F80" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H79" s="14" t="n">
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I79" s="15" t="inlineStr">
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="17" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B80" s="18" t="n"/>
-      <c r="C80" s="18" t="n"/>
-      <c r="D80" s="18" t="n"/>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
-      <c r="G80" s="18" t="n"/>
-      <c r="H80" s="18" t="n"/>
-      <c r="I80" s="18" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="19" t="n"/>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="18" t="n"/>
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="18" t="n"/>
+      <c r="I81" s="18" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="19" t="n"/>
+      <c r="B82" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C81" s="19" t="n"/>
-      <c r="D81" s="19" t="n"/>
-      <c r="E81" s="19" t="n"/>
-      <c r="F81" s="19" t="n"/>
-      <c r="G81" s="19" t="n"/>
-      <c r="H81" s="19" t="n"/>
-      <c r="I81" s="19" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr"/>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="C82" s="19" t="n"/>
+      <c r="D82" s="19" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="19" t="n"/>
+      <c r="G82" s="19" t="n"/>
+      <c r="H82" s="19" t="n"/>
+      <c r="I82" s="19" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr"/>
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C83" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="D82" s="5" t="inlineStr">
+      <c r="D83" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E83" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F83" s="5" t="n">
         <v>48.4</v>
       </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H82" s="12" t="n">
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="n">
         <v>46272.93130787037</v>
       </c>
-      <c r="I82" s="13" t="inlineStr">
+      <c r="I83" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B83" s="18" t="n"/>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="18" t="n"/>
-      <c r="I83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="19" t="n"/>
-      <c r="B84" s="20" t="inlineStr">
+      <c r="B84" s="18" t="n"/>
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="19" t="n"/>
+      <c r="B85" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C84" s="19" t="n"/>
-      <c r="D84" s="19" t="n"/>
-      <c r="E84" s="19" t="n"/>
-      <c r="F84" s="19" t="n"/>
-      <c r="G84" s="19" t="n"/>
-      <c r="H84" s="19" t="n"/>
-      <c r="I84" s="19" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr"/>
-      <c r="B85" s="4" t="inlineStr">
+      <c r="C85" s="19" t="n"/>
+      <c r="D85" s="19" t="n"/>
+      <c r="E85" s="19" t="n"/>
+      <c r="F85" s="19" t="n"/>
+      <c r="G85" s="19" t="n"/>
+      <c r="H85" s="19" t="n"/>
+      <c r="I85" s="19" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr"/>
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C86" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D86" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="5" t="n">
+      <c r="E86" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F86" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H85" s="12" t="n">
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I85" s="13" t="inlineStr">
+      <c r="I86" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="16" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B86" s="2" t="n"/>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="17" t="inlineStr">
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B87" s="18" t="n"/>
-      <c r="C87" s="18" t="n"/>
-      <c r="D87" s="18" t="n"/>
-      <c r="E87" s="18" t="n"/>
-      <c r="F87" s="18" t="n"/>
-      <c r="G87" s="18" t="n"/>
-      <c r="H87" s="18" t="n"/>
-      <c r="I87" s="18" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="21" t="n"/>
-      <c r="B88" s="22" t="inlineStr">
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="18" t="n"/>
+      <c r="E88" s="18" t="n"/>
+      <c r="F88" s="18" t="n"/>
+      <c r="G88" s="18" t="n"/>
+      <c r="H88" s="18" t="n"/>
+      <c r="I88" s="18" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C88" s="21" t="n"/>
-      <c r="D88" s="21" t="n"/>
-      <c r="E88" s="21" t="n"/>
-      <c r="F88" s="21" t="n"/>
-      <c r="G88" s="21" t="n"/>
-      <c r="H88" s="21" t="n"/>
-      <c r="I88" s="21" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr"/>
-      <c r="B89" s="4" t="inlineStr">
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="21" t="n"/>
+      <c r="E89" s="21" t="n"/>
+      <c r="F89" s="21" t="n"/>
+      <c r="G89" s="21" t="n"/>
+      <c r="H89" s="21" t="n"/>
+      <c r="I89" s="21" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr"/>
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C90" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E89" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="5" t="n">
+      <c r="E90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G89" s="5" t="inlineStr">
+      <c r="G90" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H89" s="12" t="n">
+      <c r="H90" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I89" s="13" t="inlineStr">
+      <c r="I90" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="16" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n"/>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
-      <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="17" t="inlineStr">
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="n"/>
+      <c r="I91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B91" s="18" t="n"/>
-      <c r="C91" s="18" t="n"/>
-      <c r="D91" s="18" t="n"/>
-      <c r="E91" s="18" t="n"/>
-      <c r="F91" s="18" t="n"/>
-      <c r="G91" s="18" t="n"/>
-      <c r="H91" s="18" t="n"/>
-      <c r="I91" s="18" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="21" t="n"/>
-      <c r="B92" s="22" t="inlineStr">
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="n"/>
+      <c r="D92" s="18" t="n"/>
+      <c r="E92" s="18" t="n"/>
+      <c r="F92" s="18" t="n"/>
+      <c r="G92" s="18" t="n"/>
+      <c r="H92" s="18" t="n"/>
+      <c r="I92" s="18" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="n"/>
+      <c r="B93" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C92" s="21" t="n"/>
-      <c r="D92" s="21" t="n"/>
-      <c r="E92" s="21" t="n"/>
-      <c r="F92" s="21" t="n"/>
-      <c r="G92" s="21" t="n"/>
-      <c r="H92" s="21" t="n"/>
-      <c r="I92" s="21" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="inlineStr"/>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="C93" s="21" t="n"/>
+      <c r="D93" s="21" t="n"/>
+      <c r="E93" s="21" t="n"/>
+      <c r="F93" s="21" t="n"/>
+      <c r="G93" s="21" t="n"/>
+      <c r="H93" s="21" t="n"/>
+      <c r="I93" s="21" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr"/>
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C94" s="5" t="n">
         <v>767</v>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E94" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F94" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H93" s="12" t="n">
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="n">
         <v>46255.88138888889</v>
       </c>
-      <c r="I93" s="13" t="inlineStr">
+      <c r="I94" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B94" s="18" t="n"/>
-      <c r="C94" s="18" t="n"/>
-      <c r="D94" s="18" t="n"/>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="18" t="n"/>
-      <c r="G94" s="18" t="n"/>
-      <c r="H94" s="18" t="n"/>
-      <c r="I94" s="18" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="21" t="n"/>
-      <c r="B95" s="22" t="inlineStr">
+      <c r="B95" s="18" t="n"/>
+      <c r="C95" s="18" t="n"/>
+      <c r="D95" s="18" t="n"/>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="18" t="n"/>
+      <c r="G95" s="18" t="n"/>
+      <c r="H95" s="18" t="n"/>
+      <c r="I95" s="18" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="n"/>
+      <c r="B96" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C95" s="21" t="n"/>
-      <c r="D95" s="21" t="n"/>
-      <c r="E95" s="21" t="n"/>
-      <c r="F95" s="21" t="n"/>
-      <c r="G95" s="21" t="n"/>
-      <c r="H95" s="21" t="n"/>
-      <c r="I95" s="21" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr"/>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="21" t="n"/>
+      <c r="E96" s="21" t="n"/>
+      <c r="F96" s="21" t="n"/>
+      <c r="G96" s="21" t="n"/>
+      <c r="H96" s="21" t="n"/>
+      <c r="I96" s="21" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr"/>
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C97" s="5" t="n">
         <v>3626</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D97" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" s="5" t="n">
+      <c r="E97" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="5" t="n">
         <v>42.5</v>
       </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H96" s="12" t="n">
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="n">
         <v>46240.74578703703</v>
       </c>
-      <c r="I96" s="13" t="inlineStr">
+      <c r="I97" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="17" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="21" t="n"/>
-      <c r="B98" s="22" t="inlineStr">
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="18" t="n"/>
+      <c r="D98" s="18" t="n"/>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="n"/>
+      <c r="B99" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C98" s="21" t="n"/>
-      <c r="D98" s="21" t="n"/>
-      <c r="E98" s="21" t="n"/>
-      <c r="F98" s="21" t="n"/>
-      <c r="G98" s="21" t="n"/>
-      <c r="H98" s="21" t="n"/>
-      <c r="I98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="5" t="inlineStr"/>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="C99" s="21" t="n"/>
+      <c r="D99" s="21" t="n"/>
+      <c r="E99" s="21" t="n"/>
+      <c r="F99" s="21" t="n"/>
+      <c r="G99" s="21" t="n"/>
+      <c r="H99" s="21" t="n"/>
+      <c r="I99" s="21" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr"/>
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C100" s="5" t="n">
         <v>3918</v>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="5" t="n">
+      <c r="E100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="5" t="n">
         <v>42.3</v>
       </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H99" s="12" t="n">
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="n">
         <v>46256.95832175926</v>
       </c>
-      <c r="I99" s="13" t="inlineStr">
+      <c r="I100" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="7" t="inlineStr"/>
-      <c r="B100" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr"/>
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C100" s="7" t="n">
+      <c r="C101" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E100" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="7" t="n">
+      <c r="E101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="7" t="n">
         <v>42.6</v>
       </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H100" s="14" t="n">
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H101" s="14" t="n">
         <v>46273.3956712963</v>
       </c>
-      <c r="I100" s="15" t="inlineStr">
+      <c r="I101" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="19" t="n"/>
-      <c r="B101" s="20" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="19" t="n"/>
+      <c r="B102" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C101" s="19" t="n"/>
-      <c r="D101" s="19" t="n"/>
-      <c r="E101" s="19" t="n"/>
-      <c r="F101" s="19" t="n"/>
-      <c r="G101" s="19" t="n"/>
-      <c r="H101" s="19" t="n"/>
-      <c r="I101" s="19" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr"/>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="C102" s="19" t="n"/>
+      <c r="D102" s="19" t="n"/>
+      <c r="E102" s="19" t="n"/>
+      <c r="F102" s="19" t="n"/>
+      <c r="G102" s="19" t="n"/>
+      <c r="H102" s="19" t="n"/>
+      <c r="I102" s="19" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr"/>
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C103" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D103" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E102" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" s="5" t="n">
+      <c r="E103" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G103" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H102" s="12" t="n">
+      <c r="H103" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I102" s="13" t="inlineStr">
+      <c r="I103" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="16" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="2" t="n"/>
-      <c r="G103" s="2" t="n"/>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="17" t="inlineStr">
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+      <c r="I104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B104" s="18" t="n"/>
-      <c r="C104" s="18" t="n"/>
-      <c r="D104" s="18" t="n"/>
-      <c r="E104" s="18" t="n"/>
-      <c r="F104" s="18" t="n"/>
-      <c r="G104" s="18" t="n"/>
-      <c r="H104" s="18" t="n"/>
-      <c r="I104" s="18" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="21" t="n"/>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="B105" s="18" t="n"/>
+      <c r="C105" s="18" t="n"/>
+      <c r="D105" s="18" t="n"/>
+      <c r="E105" s="18" t="n"/>
+      <c r="F105" s="18" t="n"/>
+      <c r="G105" s="18" t="n"/>
+      <c r="H105" s="18" t="n"/>
+      <c r="I105" s="18" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="n"/>
+      <c r="B106" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C105" s="21" t="n"/>
-      <c r="D105" s="21" t="n"/>
-      <c r="E105" s="21" t="n"/>
-      <c r="F105" s="21" t="n"/>
-      <c r="G105" s="21" t="n"/>
-      <c r="H105" s="21" t="n"/>
-      <c r="I105" s="21" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr"/>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="C106" s="21" t="n"/>
+      <c r="D106" s="21" t="n"/>
+      <c r="E106" s="21" t="n"/>
+      <c r="F106" s="21" t="n"/>
+      <c r="G106" s="21" t="n"/>
+      <c r="H106" s="21" t="n"/>
+      <c r="I106" s="21" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr"/>
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>Length of Last Word</t>
         </is>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C107" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D106" s="5" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E106" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="5" t="n">
+      <c r="E107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G106" s="5" t="inlineStr">
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H106" s="12" t="n">
+      <c r="H107" s="12" t="n">
         <v>46241.78204861111</v>
       </c>
-      <c r="I106" s="13" t="inlineStr">
+      <c r="I107" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="17" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B107" s="18" t="n"/>
-      <c r="C107" s="18" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="19" t="n"/>
-      <c r="B108" s="20" t="inlineStr">
+      <c r="B108" s="18" t="n"/>
+      <c r="C108" s="18" t="n"/>
+      <c r="D108" s="18" t="n"/>
+      <c r="E108" s="18" t="n"/>
+      <c r="F108" s="18" t="n"/>
+      <c r="G108" s="18" t="n"/>
+      <c r="H108" s="18" t="n"/>
+      <c r="I108" s="18" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="19" t="n"/>
+      <c r="B109" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C108" s="19" t="n"/>
-      <c r="D108" s="19" t="n"/>
-      <c r="E108" s="19" t="n"/>
-      <c r="F108" s="19" t="n"/>
-      <c r="G108" s="19" t="n"/>
-      <c r="H108" s="19" t="n"/>
-      <c r="I108" s="19" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr"/>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="C109" s="19" t="n"/>
+      <c r="D109" s="19" t="n"/>
+      <c r="E109" s="19" t="n"/>
+      <c r="F109" s="19" t="n"/>
+      <c r="G109" s="19" t="n"/>
+      <c r="H109" s="19" t="n"/>
+      <c r="I109" s="19" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr"/>
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C110" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D110" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E110" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F110" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G109" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H109" s="12" t="n">
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H110" s="12" t="n">
         <v>46253.82314814815</v>
       </c>
-      <c r="I109" s="13" t="inlineStr">
+      <c r="I110" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="17" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B110" s="18" t="n"/>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="18" t="n"/>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="18" t="n"/>
-      <c r="G110" s="18" t="n"/>
-      <c r="H110" s="18" t="n"/>
-      <c r="I110" s="18" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="21" t="n"/>
-      <c r="B111" s="22" t="inlineStr">
+      <c r="B111" s="18" t="n"/>
+      <c r="C111" s="18" t="n"/>
+      <c r="D111" s="18" t="n"/>
+      <c r="E111" s="18" t="n"/>
+      <c r="F111" s="18" t="n"/>
+      <c r="G111" s="18" t="n"/>
+      <c r="H111" s="18" t="n"/>
+      <c r="I111" s="18" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="21" t="n"/>
+      <c r="B112" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C111" s="21" t="n"/>
-      <c r="D111" s="21" t="n"/>
-      <c r="E111" s="21" t="n"/>
-      <c r="F111" s="21" t="n"/>
-      <c r="G111" s="21" t="n"/>
-      <c r="H111" s="21" t="n"/>
-      <c r="I111" s="21" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr"/>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="C112" s="21" t="n"/>
+      <c r="D112" s="21" t="n"/>
+      <c r="E112" s="21" t="n"/>
+      <c r="F112" s="21" t="n"/>
+      <c r="G112" s="21" t="n"/>
+      <c r="H112" s="21" t="n"/>
+      <c r="I112" s="21" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr"/>
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C113" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D112" s="5" t="inlineStr">
+      <c r="D113" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E112" s="5" t="n">
+      <c r="E113" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F112" s="5" t="n">
+      <c r="F113" s="5" t="n">
         <v>44.6</v>
       </c>
-      <c r="G112" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H112" s="12" t="n">
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="n">
         <v>46243.94849537037</v>
       </c>
-      <c r="I112" s="13" t="inlineStr">
+      <c r="I113" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="17" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B113" s="18" t="n"/>
-      <c r="C113" s="18" t="n"/>
-      <c r="D113" s="18" t="n"/>
-      <c r="E113" s="18" t="n"/>
-      <c r="F113" s="18" t="n"/>
-      <c r="G113" s="18" t="n"/>
-      <c r="H113" s="18" t="n"/>
-      <c r="I113" s="18" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="21" t="n"/>
-      <c r="B114" s="22" t="inlineStr">
+      <c r="B114" s="18" t="n"/>
+      <c r="C114" s="18" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="18" t="n"/>
+      <c r="F114" s="18" t="n"/>
+      <c r="G114" s="18" t="n"/>
+      <c r="H114" s="18" t="n"/>
+      <c r="I114" s="18" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="n"/>
+      <c r="B115" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C114" s="21" t="n"/>
-      <c r="D114" s="21" t="n"/>
-      <c r="E114" s="21" t="n"/>
-      <c r="F114" s="21" t="n"/>
-      <c r="G114" s="21" t="n"/>
-      <c r="H114" s="21" t="n"/>
-      <c r="I114" s="21" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr"/>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="C115" s="21" t="n"/>
+      <c r="D115" s="21" t="n"/>
+      <c r="E115" s="21" t="n"/>
+      <c r="F115" s="21" t="n"/>
+      <c r="G115" s="21" t="n"/>
+      <c r="H115" s="21" t="n"/>
+      <c r="I115" s="21" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr"/>
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome</t>
         </is>
       </c>
-      <c r="C115" s="5" t="n">
+      <c r="C116" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="D115" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E115" s="5" t="n">
+      <c r="E116" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F115" s="5" t="n">
+      <c r="F116" s="5" t="n">
         <v>45.3</v>
       </c>
-      <c r="G115" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H115" s="12" t="n">
+      <c r="H116" s="12" t="n">
         <v>46243.9169675926</v>
       </c>
-      <c r="I115" s="13" t="inlineStr">
+      <c r="I116" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="17" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B116" s="18" t="n"/>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="18" t="n"/>
-      <c r="F116" s="18" t="n"/>
-      <c r="G116" s="18" t="n"/>
-      <c r="H116" s="18" t="n"/>
-      <c r="I116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="21" t="n"/>
-      <c r="B117" s="22" t="inlineStr">
+      <c r="B117" s="18" t="n"/>
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="18" t="n"/>
+      <c r="E117" s="18" t="n"/>
+      <c r="F117" s="18" t="n"/>
+      <c r="G117" s="18" t="n"/>
+      <c r="H117" s="18" t="n"/>
+      <c r="I117" s="18" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="21" t="n"/>
+      <c r="B118" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C117" s="21" t="n"/>
-      <c r="D117" s="21" t="n"/>
-      <c r="E117" s="21" t="n"/>
-      <c r="F117" s="21" t="n"/>
-      <c r="G117" s="21" t="n"/>
-      <c r="H117" s="21" t="n"/>
-      <c r="I117" s="21" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr"/>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="C118" s="21" t="n"/>
+      <c r="D118" s="21" t="n"/>
+      <c r="E118" s="21" t="n"/>
+      <c r="F118" s="21" t="n"/>
+      <c r="G118" s="21" t="n"/>
+      <c r="H118" s="21" t="n"/>
+      <c r="I118" s="21" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr"/>
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C119" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E118" s="5" t="n">
+      <c r="E119" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F118" s="5" t="n">
+      <c r="F119" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H118" s="12" t="n">
+      <c r="H119" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I118" s="13" t="inlineStr">
+      <c r="I119" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="16" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B119" s="2" t="n"/>
-      <c r="C119" s="2" t="n"/>
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="2" t="n"/>
-      <c r="G119" s="2" t="n"/>
-      <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="17" t="inlineStr">
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="n"/>
+      <c r="I120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B120" s="18" t="n"/>
-      <c r="C120" s="18" t="n"/>
-      <c r="D120" s="18" t="n"/>
-      <c r="E120" s="18" t="n"/>
-      <c r="F120" s="18" t="n"/>
-      <c r="G120" s="18" t="n"/>
-      <c r="H120" s="18" t="n"/>
-      <c r="I120" s="18" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="21" t="n"/>
-      <c r="B121" s="22" t="inlineStr">
+      <c r="B121" s="18" t="n"/>
+      <c r="C121" s="18" t="n"/>
+      <c r="D121" s="18" t="n"/>
+      <c r="E121" s="18" t="n"/>
+      <c r="F121" s="18" t="n"/>
+      <c r="G121" s="18" t="n"/>
+      <c r="H121" s="18" t="n"/>
+      <c r="I121" s="18" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="21" t="n"/>
+      <c r="B122" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C121" s="21" t="n"/>
-      <c r="D121" s="21" t="n"/>
-      <c r="E121" s="21" t="n"/>
-      <c r="F121" s="21" t="n"/>
-      <c r="G121" s="21" t="n"/>
-      <c r="H121" s="21" t="n"/>
-      <c r="I121" s="21" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr"/>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="C122" s="21" t="n"/>
+      <c r="D122" s="21" t="n"/>
+      <c r="E122" s="21" t="n"/>
+      <c r="F122" s="21" t="n"/>
+      <c r="G122" s="21" t="n"/>
+      <c r="H122" s="21" t="n"/>
+      <c r="I122" s="21" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr"/>
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C122" s="5" t="n">
+      <c r="C123" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D122" s="5" t="inlineStr">
+      <c r="D123" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E122" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="5" t="n">
+      <c r="E123" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="G122" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="n">
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="n">
         <v>46248.99621527778</v>
       </c>
-      <c r="I122" s="13" t="inlineStr">
+      <c r="I123" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="17" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B123" s="18" t="n"/>
-      <c r="C123" s="18" t="n"/>
-      <c r="D123" s="18" t="n"/>
-      <c r="E123" s="18" t="n"/>
-      <c r="F123" s="18" t="n"/>
-      <c r="G123" s="18" t="n"/>
-      <c r="H123" s="18" t="n"/>
-      <c r="I123" s="18" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="21" t="n"/>
-      <c r="B124" s="22" t="inlineStr">
+      <c r="B124" s="18" t="n"/>
+      <c r="C124" s="18" t="n"/>
+      <c r="D124" s="18" t="n"/>
+      <c r="E124" s="18" t="n"/>
+      <c r="F124" s="18" t="n"/>
+      <c r="G124" s="18" t="n"/>
+      <c r="H124" s="18" t="n"/>
+      <c r="I124" s="18" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="n"/>
+      <c r="B125" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 2 problem(s)</t>
         </is>
       </c>
-      <c r="C124" s="21" t="n"/>
-      <c r="D124" s="21" t="n"/>
-      <c r="E124" s="21" t="n"/>
-      <c r="F124" s="21" t="n"/>
-      <c r="G124" s="21" t="n"/>
-      <c r="H124" s="21" t="n"/>
-      <c r="I124" s="21" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr"/>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="C125" s="21" t="n"/>
+      <c r="D125" s="21" t="n"/>
+      <c r="E125" s="21" t="n"/>
+      <c r="F125" s="21" t="n"/>
+      <c r="G125" s="21" t="n"/>
+      <c r="H125" s="21" t="n"/>
+      <c r="I125" s="21" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr"/>
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C126" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E125" s="5" t="n">
+      <c r="E126" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F125" s="5" t="n">
+      <c r="F126" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G125" s="5" t="inlineStr">
+      <c r="G126" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H125" s="12" t="n">
+      <c r="H126" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I125" s="13" t="inlineStr">
+      <c r="I126" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="7" t="inlineStr"/>
-      <c r="B126" s="6" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="7" t="inlineStr"/>
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C126" s="7" t="n">
+      <c r="C127" s="7" t="n">
         <v>637</v>
       </c>
-      <c r="D126" s="7" t="inlineStr">
+      <c r="D127" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E126" s="7" t="n">
+      <c r="E127" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F126" s="7" t="n">
+      <c r="F127" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="G126" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="n">
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H127" s="14" t="n">
         <v>46246.98880787037</v>
       </c>
-      <c r="I126" s="15" t="inlineStr">
+      <c r="I127" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="17" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Stack, Depth-First Search, Binary Tree   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B127" s="18" t="n"/>
-      <c r="C127" s="18" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-      <c r="G127" s="18" t="n"/>
-      <c r="H127" s="18" t="n"/>
-      <c r="I127" s="18" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="21" t="n"/>
-      <c r="B128" s="22" t="inlineStr">
+      <c r="B128" s="18" t="n"/>
+      <c r="C128" s="18" t="n"/>
+      <c r="D128" s="18" t="n"/>
+      <c r="E128" s="18" t="n"/>
+      <c r="F128" s="18" t="n"/>
+      <c r="G128" s="18" t="n"/>
+      <c r="H128" s="18" t="n"/>
+      <c r="I128" s="18" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="n"/>
+      <c r="B129" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C128" s="21" t="n"/>
-      <c r="D128" s="21" t="n"/>
-      <c r="E128" s="21" t="n"/>
-      <c r="F128" s="21" t="n"/>
-      <c r="G128" s="21" t="n"/>
-      <c r="H128" s="21" t="n"/>
-      <c r="I128" s="21" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr"/>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="C129" s="21" t="n"/>
+      <c r="D129" s="21" t="n"/>
+      <c r="E129" s="21" t="n"/>
+      <c r="F129" s="21" t="n"/>
+      <c r="G129" s="21" t="n"/>
+      <c r="H129" s="21" t="n"/>
+      <c r="I129" s="21" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr"/>
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>Binary Tree Inorder Traversal</t>
         </is>
       </c>
-      <c r="C129" s="5" t="n">
+      <c r="C130" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D130" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E129" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="5" t="n">
+      <c r="E130" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="5" t="n">
         <v>43.2</v>
       </c>
-      <c r="G129" s="5" t="inlineStr">
+      <c r="G130" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H129" s="12" t="n">
+      <c r="H130" s="12" t="n">
         <v>46246.86910879629</v>
       </c>
-      <c r="I129" s="13" t="inlineStr">
+      <c r="I130" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="16" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: UNCATEGORIZED   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B130" s="2" t="n"/>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="n"/>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="n"/>
-      <c r="I130" s="2" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="17" t="inlineStr">
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B131" s="18" t="n"/>
-      <c r="C131" s="18" t="n"/>
-      <c r="D131" s="18" t="n"/>
-      <c r="E131" s="18" t="n"/>
-      <c r="F131" s="18" t="n"/>
-      <c r="G131" s="18" t="n"/>
-      <c r="H131" s="18" t="n"/>
-      <c r="I131" s="18" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="21" t="n"/>
-      <c r="B132" s="22" t="inlineStr">
+      <c r="B132" s="18" t="n"/>
+      <c r="C132" s="18" t="n"/>
+      <c r="D132" s="18" t="n"/>
+      <c r="E132" s="18" t="n"/>
+      <c r="F132" s="18" t="n"/>
+      <c r="G132" s="18" t="n"/>
+      <c r="H132" s="18" t="n"/>
+      <c r="I132" s="18" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="n"/>
+      <c r="B133" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C132" s="21" t="n"/>
-      <c r="D132" s="21" t="n"/>
-      <c r="E132" s="21" t="n"/>
-      <c r="F132" s="21" t="n"/>
-      <c r="G132" s="21" t="n"/>
-      <c r="H132" s="21" t="n"/>
-      <c r="I132" s="21" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="5" t="inlineStr"/>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="C133" s="21" t="n"/>
+      <c r="D133" s="21" t="n"/>
+      <c r="E133" s="21" t="n"/>
+      <c r="F133" s="21" t="n"/>
+      <c r="G133" s="21" t="n"/>
+      <c r="H133" s="21" t="n"/>
+      <c r="I133" s="21" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr"/>
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C133" s="5" t="n">
+      <c r="C134" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D134" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E133" s="5" t="n">
+      <c r="E134" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="F133" s="5" t="n">
+      <c r="F134" s="5" t="n">
         <v>53.9</v>
       </c>
-      <c r="G133" s="5" t="inlineStr">
+      <c r="G134" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="H133" s="12" t="n">
+      <c r="H134" s="12" t="n">
         <v>46247.79274305556</v>
       </c>
-      <c r="I133" s="13" t="inlineStr">
+      <c r="I134" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7212,139 +7298,140 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="A90:I90"/>
-    <mergeCell ref="B54:I54"/>
-    <mergeCell ref="A56:I56"/>
-    <mergeCell ref="B105:I105"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="B111:I111"/>
-    <mergeCell ref="B98:I98"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B88:I88"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="A59:I59"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A103:I103"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="A108:I108"/>
+    <mergeCell ref="B125:I125"/>
+    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B96:I96"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="B82:I82"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A117:I117"/>
+    <mergeCell ref="A111:I111"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A48:I48"/>
     <mergeCell ref="A87:I87"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B39:I39"/>
-    <mergeCell ref="A76:I76"/>
-    <mergeCell ref="A116:I116"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B85:I85"/>
+    <mergeCell ref="A128:I128"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="B109:I109"/>
+    <mergeCell ref="B115:I115"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="B102:I102"/>
+    <mergeCell ref="A105:I105"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="A71:I71"/>
     <mergeCell ref="A91:I91"/>
-    <mergeCell ref="B23:I23"/>
     <mergeCell ref="A131:I131"/>
-    <mergeCell ref="B128:I128"/>
-    <mergeCell ref="A83:I83"/>
-    <mergeCell ref="B33:I33"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="A94:I94"/>
-    <mergeCell ref="B114:I114"/>
-    <mergeCell ref="B63:I63"/>
-    <mergeCell ref="A80:I80"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="B78:I78"/>
+    <mergeCell ref="A77:I77"/>
+    <mergeCell ref="B49:I49"/>
+    <mergeCell ref="A92:I92"/>
+    <mergeCell ref="B64:I64"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="B66:I66"/>
     <mergeCell ref="A120:I120"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="B93:I93"/>
     <mergeCell ref="A104:I104"/>
-    <mergeCell ref="A113:I113"/>
-    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="A57:I57"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A32:I32"/>
-    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="A23:I23"/>
     <mergeCell ref="A1:I2"/>
+    <mergeCell ref="B61:I61"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="B101:I101"/>
-    <mergeCell ref="B132:I132"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="B29:I29"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A130:I130"/>
-    <mergeCell ref="A123:I123"/>
-    <mergeCell ref="B95:I95"/>
-    <mergeCell ref="A110:I110"/>
-    <mergeCell ref="A119:I119"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="B81:I81"/>
-    <mergeCell ref="B121:I121"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B71:I71"/>
-    <mergeCell ref="A86:I86"/>
-    <mergeCell ref="A47:I47"/>
-    <mergeCell ref="B42:I42"/>
-    <mergeCell ref="B60:I60"/>
-    <mergeCell ref="A97:I97"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="A127:I127"/>
-    <mergeCell ref="B108:I108"/>
-    <mergeCell ref="B84:I84"/>
-    <mergeCell ref="B92:I92"/>
-    <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A107:I107"/>
-    <mergeCell ref="B124:I124"/>
+    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B112:I112"/>
+    <mergeCell ref="B118:I118"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B55:I55"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B89:I89"/>
+    <mergeCell ref="A132:I132"/>
+    <mergeCell ref="A124:I124"/>
+    <mergeCell ref="B106:I106"/>
+    <mergeCell ref="B129:I129"/>
+    <mergeCell ref="A84:I84"/>
+    <mergeCell ref="B122:I122"/>
+    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B58:I58"/>
+    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="A95:I95"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A81:I81"/>
+    <mergeCell ref="A121:I121"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B99:I99"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="A114:I114"/>
+    <mergeCell ref="A98:I98"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="A51:I51"/>
     <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="A70:I70"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="B133:I133"/>
+    <mergeCell ref="A88:I88"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7356,7 +7443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7995,24 +8082,61 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="266" customHeight="1">
+    <row r="18" ht="210" customHeight="1">
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
+          <t>Find Peak Element</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>162</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>class Solution {
+    public int findPeakElement(int[] nums) {
+       int left = 0;
+       int right = nums.length -1;
+       while(left&lt;right){
+        int mid = left+(right - left)/2;
+       if(nums[mid] &lt; nums[mid+1]){
+          left= mid +1;
+       }else{
+          right = mid;
+       }
+       }
+       return left;
+    }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="266" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>Two Sum II - Input Array Is Sorted</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] twoSum(int[] numbers, int target) {
@@ -8036,24 +8160,24 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="294" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="294" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Count Primes</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C20" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int countPrimes(int n) {
@@ -8079,24 +8203,24 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="238" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
+    <row r="21" ht="238" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Minimum Size Subarray Sum</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C21" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int minSubArrayLen(int target, int[] nums) {
@@ -8118,24 +8242,24 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="238" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22" ht="238" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Contains Duplicate II</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C22" s="7" t="n">
         <v>219</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean containsNearbyDuplicate(int[] nums, int k) {
@@ -8157,24 +8281,24 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="392" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+    <row r="23" ht="392" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Valid Anagram</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C23" s="5" t="n">
         <v>242</v>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E22" s="24" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean isAnagram(String s, String t) {
@@ -8207,24 +8331,24 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="182" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24" ht="182" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C24" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public void moveZeroes(int[] nums) {
@@ -8242,24 +8366,24 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="308" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
+    <row r="25" ht="308" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Range Sum Query - Immutable</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C25" s="5" t="n">
         <v>303</v>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E24" s="24" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>class NumArray {
     int[] prefix;
@@ -8283,24 +8407,24 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="420" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
+    <row r="26" ht="420" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Range Sum Query 2D - Immutable</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="7" t="n">
         <v>304</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>class NumMatrix {
    private int[][] result;
@@ -8332,24 +8456,24 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="546" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
+    <row r="27" ht="546" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Diameter of Binary Tree</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C27" s="5" t="n">
         <v>543</v>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E26" s="24" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -8387,24 +8511,24 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="182" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="28" ht="182" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Subarray Sum Equals K</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="7" t="n">
         <v>560</v>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int subarraySum(int[] nums, int k) {
@@ -8422,24 +8546,24 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="546" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
+    <row r="29" ht="546" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Average of Levels in Binary Tree</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C29" s="5" t="n">
         <v>637</v>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>/**
  * Definition for a binary tree node.
@@ -8483,24 +8607,24 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="196" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="196" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Maximum Average Subarray I</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C30" s="7" t="n">
         <v>643</v>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public double findMaxAverage(int[] nums, int k) {
@@ -8519,24 +8643,24 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="462" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+    <row r="31" ht="462" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C31" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E30" s="24" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;680 - Valid Palindrome II&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-palindrome-ii/"&gt;valid-palindrome-ii&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given a string &lt;code&gt;s&lt;/code&gt;, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if the &lt;/em&gt;&lt;code&gt;s&lt;/code&gt;&lt;em&gt; can be palindrome after deleting &lt;strong&gt;at most one&lt;/strong&gt; character from it&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;&amp;nbsp;&lt;/p&gt;
@@ -8566,24 +8690,24 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="378" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="378" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C32" s="7" t="n">
         <v>767</v>
       </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int setbit(int n){
@@ -8615,24 +8739,24 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="560" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
+    <row r="33" ht="560" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C33" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E32" s="24" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1013 - Fibonacci Number&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/fibonacci-number/"&gt;fibonacci-number&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;The &lt;b&gt;Fibonacci numbers&lt;/b&gt;, commonly denoted &lt;code&gt;F(n)&lt;/code&gt; form a sequence, called the &lt;b&gt;Fibonacci sequence&lt;/b&gt;, such that each number is the sum of the two preceding ones, starting from &lt;code&gt;0&lt;/code&gt; and &lt;code&gt;1&lt;/code&gt;. That is,&lt;/p&gt;
 &lt;pre&gt;
@@ -8668,24 +8792,24 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="294" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34" ht="294" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Valid Boomerang</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C34" s="7" t="n">
         <v>1115</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;1115 - Valid Boomerang&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/valid-boomerang/"&gt;valid-boomerang&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;Given an array &lt;code&gt;points&lt;/code&gt; where &lt;code&gt;points[i] = [x&lt;sub&gt;i&lt;/sub&gt;, y&lt;sub&gt;i&lt;/sub&gt;]&lt;/code&gt; represents a point on the &lt;strong&gt;X-Y&lt;/strong&gt; plane, return &lt;code&gt;true&lt;/code&gt; &lt;em&gt;if these points are a &lt;strong&gt;boomerang&lt;/strong&gt;&lt;/em&gt;.&lt;/p&gt;
 &lt;p&gt;A &lt;strong&gt;boomerang&lt;/strong&gt; is a set of three points that are &lt;strong&gt;all distinct&lt;/strong&gt; and &lt;strong&gt;not in a straight line&lt;/strong&gt;.&lt;/p&gt;
@@ -8708,24 +8832,24 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="224" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
+    <row r="35" ht="224" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Corporate Flight Bookings</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C35" s="5" t="n">
         <v>1206</v>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E34" s="24" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] corpFlightBookings(int[][] bookings, int n) {
@@ -8746,24 +8870,24 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="420" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="36" ht="420" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Matrix Block Sum</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>1242</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[][] matrixBlockSum(int[][] mat, int k) {
@@ -8798,24 +8922,24 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="378" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+    <row r="37" ht="378" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C37" s="5" t="n">
         <v>1353</v>
       </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isAnagram(String str1,String str2){
@@ -8847,24 +8971,24 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="350" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="38" ht="350" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C38" s="7" t="n">
         <v>1693</v>
       </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isOdd(int num){
@@ -8894,24 +9018,24 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="238" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
+    <row r="39" ht="238" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C39" s="5" t="n">
         <v>2106</v>
       </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int GCD(int a,int b){
@@ -8933,24 +9057,24 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="308" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40" ht="308" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Prime In Diagonal</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C40" s="7" t="n">
         <v>2722</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     		public static boolean isPrime(int n) {
@@ -8977,24 +9101,24 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="280" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
+    <row r="41" ht="280" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Generate Fibonacci Sequence</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C41" s="5" t="n">
         <v>2775</v>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
+      <c r="E41" s="23" t="inlineStr">
         <is>
           <t>/**
  * @return {Generator&lt;number&gt;}
@@ -9017,24 +9141,24 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="448" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="448" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="7" t="n">
         <v>3347</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] resultArray(int[] nums) {
@@ -9069,24 +9193,24 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="378" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
+    <row r="43" ht="378" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Maximum Prime Difference</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C43" s="5" t="n">
         <v>3373</v>
       </c>
-      <c r="D42" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public static boolean isPrime(int n){
@@ -9118,24 +9242,24 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="266" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44" ht="266" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C44" s="7" t="n">
         <v>3626</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public static int digits(int num){
@@ -9159,24 +9283,24 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="560" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
+    <row r="45" ht="560" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Find the Largest Almost Missing Integer</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C45" s="5" t="n">
         <v>3705</v>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="E44" s="24" t="inlineStr">
+      <c r="E45" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;h1&gt;3705 - Find the Largest Almost Missing Integer&lt;/h1&gt;&lt;h2&gt;Difficulty: Easy - &lt;a href="https://leetcode.com/problems/find-the-largest-almost-missing-integer/"&gt;find-the-largest-almost-missing-integer&lt;/a&gt;&lt;/h2&gt;&lt;p&gt;You are given an integer array &lt;code&gt;nums&lt;/code&gt; and an integer &lt;code&gt;k&lt;/code&gt;.&lt;/p&gt;
 &lt;p&gt;An integer &lt;code&gt;x&lt;/code&gt; is &lt;strong&gt;almost missing&lt;/strong&gt; from &lt;code&gt;nums&lt;/code&gt; if &lt;code&gt;x&lt;/code&gt; appears in &lt;em&gt;exactly&lt;/em&gt; one subarray of size &lt;code&gt;k&lt;/code&gt; within &lt;code&gt;nums&lt;/code&gt;.&lt;/p&gt;
@@ -9229,24 +9353,24 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="238" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="238" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Check Divisibility by Digit Sum and Product</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C46" s="7" t="n">
         <v>3918</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public boolean checkDivisibility(int n) {
@@ -9266,24 +9390,24 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="252" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
+    <row r="47" ht="252" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Longest Fibonacci Subarray</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C47" s="5" t="n">
         <v>4003</v>
       </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int longestSubarray(int[] nums) {
@@ -9306,24 +9430,24 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="140" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
+    <row r="48" ht="140" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>Count Commas in Range</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C48" s="7" t="n">
         <v>4245</v>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int countCommas(int n) {
@@ -9337,24 +9461,24 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="294" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
+    <row r="49" ht="294" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Score Validator</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C49" s="5" t="n">
         <v>4281</v>
       </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
         <is>
           <t>class Solution {
     public int[] scoreValidator(String[] events) {
@@ -9380,24 +9504,24 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="252" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="252" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C50" s="7" t="n">
         <v>4284</v>
       </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
         <is>
           <t>class Solution {
     public int firstStableIndex(int[] nums, int k) {

--- a/reports/LeetCode_Analytics.xlsx
+++ b/reports/LeetCode_Analytics.xlsx
@@ -628,7 +628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -975,14 +975,14 @@
       <c r="A15" s="4" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, String, Sorting</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>0</v>
@@ -991,24 +991,24 @@
         <v>1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>46.3</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
+          <t>Hash Table, String, Sorting</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1017,24 +1017,24 @@
         <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Math, Geometry</t>
+          <t>Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -1043,17 +1043,17 @@
         <v>1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Math, Matrix, Number Theory</t>
+          <t>Math, Geometry</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -1069,17 +1069,17 @@
         <v>1</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
+          <t>Math, Matrix, Number Theory</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -1095,24 +1095,24 @@
         <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Math, Number Theory, Primality Test</t>
+          <t>Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1121,24 +1121,24 @@
         <v>1</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Math, Prefix Sum</t>
+          <t>Math, Number Theory, Primality Test</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -1147,24 +1147,24 @@
         <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Matrix, Prefix Sum</t>
+          <t>Math, Prefix Sum</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
@@ -1173,21 +1173,21 @@
         <v>1</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Prefix Sum</t>
+          <t>Matrix, Prefix Sum</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>1</v>
@@ -1196,46 +1196,46 @@
         <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>65.7</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Simulation</t>
+          <t>Prefix Sum</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>46.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Sliding Window</t>
+          <t>Simulation</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
@@ -1251,17 +1251,17 @@
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>String, Simulation</t>
+          <t>Sliding Window</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
@@ -1277,21 +1277,21 @@
         <v>1</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>String, Simulation</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
         <v>0</v>
@@ -1300,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>47.2</v>
@@ -1313,300 +1313,300 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers, Binary Search</t>
+          <t>Two Pointers</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>48.4</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers, Binary Search</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="5" t="n">
+      <c r="C30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H30" s="7" t="n">
         <v>77.2</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Array — TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr"/>
-      <c r="C30" s="9" t="n">
+      <c r="B31" s="8" t="inlineStr"/>
+      <c r="C31" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="D31" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G31" s="9" t="inlineStr"/>
+      <c r="H31" s="9" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Dynamic Programming</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Math, Recursion, Memoization</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5" t="n">
+      <c r="C32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="n">
         <v>42.1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Dynamic Programming — TOTAL</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr"/>
-      <c r="C32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="9" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr"/>
+      <c r="C33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr"/>
+      <c r="H33" s="9" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Math</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Bit Manipulation, Primality Test</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="5" t="n">
+      <c r="C34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H34" s="7" t="n">
         <v>42.3</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Enumeration</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="7" t="n">
-        <v>42.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>Enumeration</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C36" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="5" t="n">
+      <c r="D36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G36" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H36" s="7" t="n">
         <v>42.4</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Math — TOTAL</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr"/>
-      <c r="C36" s="9" t="n">
+      <c r="B37" s="8" t="inlineStr"/>
+      <c r="C37" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="9" t="n">
+      <c r="D37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="9" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="5" t="n">
+      <c r="C38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="n">
         <v>43.2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Hash Table, Sliding Window</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>47.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Hash Table, Sorting</t>
+          <t>Hash Table, Sliding Window</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>0</v>
@@ -1615,17 +1615,17 @@
         <v>1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Two Pointers</t>
+          <t>Hash Table, Sorting</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
@@ -1644,234 +1644,260 @@
         <v>2</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>Two Pointers</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>Two Pointers, Greedy</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="5" t="n">
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H42" s="7" t="n">
         <v>47.9</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>String — TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr"/>
-      <c r="C42" s="9" t="n">
+      <c r="B43" s="8" t="inlineStr"/>
+      <c r="C43" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9" t="n">
+      <c r="D43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr"/>
+      <c r="H43" s="9" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>Tree</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>Depth-First Search, Binary Tree, DP on Trees</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="5" t="n">
+      <c r="C44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="n">
         <v>47</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr"/>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
+          <t>Depth-First Search, Breadth-First Search, Binary Tree</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
           <t>Stack, Depth-First Search, Binary Tree</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="5" t="n">
+      <c r="C46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="7" t="n">
         <v>43.2</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Tree — TOTAL</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr"/>
-      <c r="C46" s="9" t="n">
+      <c r="B47" s="8" t="inlineStr"/>
+      <c r="C47" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="9" t="n">
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="9" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr"/>
+      <c r="H47" s="9" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>Uncategorized</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="n">
+      <c r="C48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="H47" s="5" t="n">
+      <c r="H48" s="7" t="n">
         <v>53.9</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Uncategorized — TOTAL</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr"/>
-      <c r="C48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="9" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr"/>
+      <c r="C49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr"/>
+      <c r="H49" s="9" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr"/>
-      <c r="C49" s="11" t="n">
+      <c r="B50" s="10" t="inlineStr"/>
+      <c r="C50" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="D49" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="G49" s="11" t="inlineStr"/>
-      <c r="H49" s="11" t="inlineStr"/>
+      <c r="D50" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1887,7 +1913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4298,11 +4324,61 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>442</v>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Find All Duplicates in an Array</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Hash Table, Sorting</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>46273.57508101852</v>
+      </c>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F50">
+  <conditionalFormatting sqref="F5:F51">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>F5="Easy"</formula>
     </cfRule>
@@ -4360,6 +4436,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4371,7 +4448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I134"/>
+  <dimension ref="A1:I137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4414,7 +4491,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  TOPIC: ARRAY   —   30 solved   (Low: 16 · Medium: 14 · High: 0)</t>
+          <t xml:space="preserve">  TOPIC: ARRAY   —   31 solved   (Low: 16 · Medium: 15 · High: 0)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -5199,7 +5276,7 @@
     <row r="39">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B39" s="18" t="n"/>
@@ -5212,40 +5289,40 @@
       <c r="I39" s="18" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="n"/>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="21" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
+      <c r="A40" s="19" t="n"/>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="19" t="n"/>
+      <c r="H40" s="19" t="n"/>
+      <c r="I40" s="19" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Find Resultant Array After Removing Anagrams</t>
+          <t>Find All Duplicates in an Array</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1353</v>
+        <v>442</v>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>46.3</v>
+        <v>57.9</v>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
@@ -5253,7 +5330,7 @@
         </is>
       </c>
       <c r="H41" s="12" t="n">
-        <v>46243.98008101852</v>
+        <v>46273.57508101852</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -5264,7 +5341,7 @@
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, String, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B42" s="18" t="n"/>
@@ -5277,40 +5354,40 @@
       <c r="I42" s="18" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="n"/>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C43" s="19" t="n"/>
-      <c r="D43" s="19" t="n"/>
-      <c r="E43" s="19" t="n"/>
-      <c r="F43" s="19" t="n"/>
-      <c r="G43" s="19" t="n"/>
-      <c r="H43" s="19" t="n"/>
-      <c r="I43" s="19" t="n"/>
+      <c r="A43" s="21" t="n"/>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="n"/>
+      <c r="H43" s="21" t="n"/>
+      <c r="I43" s="21" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr"/>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Count Primes</t>
+          <t>Find Resultant Array After Removing Anagrams</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>204</v>
+        <v>1353</v>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>709</v>
+        <v>1</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>79.8</v>
+        <v>46.3</v>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
@@ -5318,7 +5395,7 @@
         </is>
       </c>
       <c r="H44" s="12" t="n">
-        <v>46255.64438657407</v>
+        <v>46243.98008101852</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -5329,7 +5406,7 @@
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Enumeration, Number Theory, Primality Test, Sieve Theory, Prime Number Sieve   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B45" s="18" t="n"/>
@@ -5342,48 +5419,48 @@
       <c r="I45" s="18" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="n"/>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="21" t="n"/>
-      <c r="G46" s="21" t="n"/>
-      <c r="H46" s="21" t="n"/>
-      <c r="I46" s="21" t="n"/>
+      <c r="A46" s="19" t="n"/>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="19" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Valid Boomerang</t>
+          <t>Count Primes</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1115</v>
+        <v>204</v>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>42.9</v>
+        <v>79.8</v>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H47" s="12" t="n">
-        <v>46244.79871527778</v>
+        <v>46255.64438657407</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -5394,7 +5471,7 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Geometry   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B48" s="18" t="n"/>
@@ -5425,11 +5502,11 @@
       <c r="A50" s="5" t="inlineStr"/>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Prime In Diagonal</t>
+          <t>Valid Boomerang</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>2722</v>
+        <v>1115</v>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
@@ -5437,18 +5514,18 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>82.5</v>
+        <v>42.9</v>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H50" s="12" t="n">
-        <v>46255.61045138889</v>
+        <v>46244.79871527778</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -5459,7 +5536,7 @@
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Matrix, Number Theory   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B51" s="18" t="n"/>
@@ -5490,11 +5567,11 @@
       <c r="A53" s="5" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Find Greatest Common Divisor of Array</t>
+          <t>Prime In Diagonal</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2106</v>
+        <v>2722</v>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
@@ -5502,10 +5579,10 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>45.2</v>
+        <v>82.5</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
@@ -5513,7 +5590,7 @@
         </is>
       </c>
       <c r="H53" s="12" t="n">
-        <v>46255.57113425926</v>
+        <v>46255.61045138889</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -5524,7 +5601,7 @@
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Euclidean Algorithm, Greatest Common Divisor   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B54" s="18" t="n"/>
@@ -5537,40 +5614,40 @@
       <c r="I54" s="18" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="19" t="n"/>
-      <c r="B55" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="19" t="n"/>
-      <c r="G55" s="19" t="n"/>
-      <c r="H55" s="19" t="n"/>
-      <c r="I55" s="19" t="n"/>
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="n"/>
+      <c r="H55" s="21" t="n"/>
+      <c r="I55" s="21" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr"/>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Maximum Prime Difference</t>
+          <t>Find Greatest Common Divisor of Array</t>
         </is>
       </c>
       <c r="C56" s="5" t="n">
-        <v>3373</v>
+        <v>2106</v>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>117.3</v>
+        <v>45.2</v>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
@@ -5578,7 +5655,7 @@
         </is>
       </c>
       <c r="H56" s="12" t="n">
-        <v>46255.5928587963</v>
+        <v>46255.57113425926</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -5589,7 +5666,7 @@
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Number Theory, Primality Test   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B57" s="18" t="n"/>
@@ -5602,40 +5679,40 @@
       <c r="I57" s="18" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="n"/>
-      <c r="B58" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="n"/>
-      <c r="D58" s="21" t="n"/>
-      <c r="E58" s="21" t="n"/>
-      <c r="F58" s="21" t="n"/>
-      <c r="G58" s="21" t="n"/>
-      <c r="H58" s="21" t="n"/>
-      <c r="I58" s="21" t="n"/>
+      <c r="A58" s="19" t="n"/>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="19" t="n"/>
+      <c r="G58" s="19" t="n"/>
+      <c r="H58" s="19" t="n"/>
+      <c r="I58" s="19" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr"/>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Sum of All Odd Length Subarrays</t>
+          <t>Maximum Prime Difference</t>
         </is>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1693</v>
+        <v>3373</v>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>42.8</v>
+        <v>117.3</v>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
@@ -5643,7 +5720,7 @@
         </is>
       </c>
       <c r="H59" s="12" t="n">
-        <v>46261.883125</v>
+        <v>46255.5928587963</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -5654,7 +5731,7 @@
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Math, Prefix Sum   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B60" s="18" t="n"/>
@@ -5667,40 +5744,40 @@
       <c r="I60" s="18" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="19" t="n"/>
-      <c r="B61" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-      <c r="G61" s="19" t="n"/>
-      <c r="H61" s="19" t="n"/>
-      <c r="I61" s="19" t="n"/>
+      <c r="A61" s="21" t="n"/>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="21" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="n"/>
+      <c r="H61" s="21" t="n"/>
+      <c r="I61" s="21" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr"/>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Matrix Block Sum</t>
+          <t>Sum of All Odd Length Subarrays</t>
         </is>
       </c>
       <c r="C62" s="5" t="n">
-        <v>1242</v>
+        <v>1693</v>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>46.8</v>
+        <v>42.8</v>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
@@ -5708,7 +5785,7 @@
         </is>
       </c>
       <c r="H62" s="12" t="n">
-        <v>46262.8983912037</v>
+        <v>46261.883125</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -5719,7 +5796,7 @@
     <row r="63">
       <c r="A63" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Matrix, Prefix Sum   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B63" s="18" t="n"/>
@@ -5732,155 +5809,155 @@
       <c r="I63" s="18" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="21" t="n"/>
-      <c r="B64" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C64" s="21" t="n"/>
-      <c r="D64" s="21" t="n"/>
-      <c r="E64" s="21" t="n"/>
-      <c r="F64" s="21" t="n"/>
-      <c r="G64" s="21" t="n"/>
-      <c r="H64" s="21" t="n"/>
-      <c r="I64" s="21" t="n"/>
+      <c r="A64" s="19" t="n"/>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="n"/>
+      <c r="D64" s="19" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="19" t="n"/>
+      <c r="G64" s="19" t="n"/>
+      <c r="H64" s="19" t="n"/>
+      <c r="I64" s="19" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr"/>
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>Matrix Block Sum</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>1242</v>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>46262.8983912037</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Prefix Sum   —   2 solved   (Low: 1 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="18" t="n"/>
+      <c r="I66" s="18" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="21" t="n"/>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="21" t="n"/>
+      <c r="E67" s="21" t="n"/>
+      <c r="F67" s="21" t="n"/>
+      <c r="G67" s="21" t="n"/>
+      <c r="H67" s="21" t="n"/>
+      <c r="I67" s="21" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr"/>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
           <t>Smallest Stable Index I</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C68" s="5" t="n">
         <v>4284</v>
       </c>
-      <c r="D65" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="5" t="n">
+      <c r="E68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="5" t="n">
         <v>46.3</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H65" s="12" t="n">
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="n">
         <v>46270.61052083333</v>
       </c>
-      <c r="I65" s="13" t="inlineStr">
+      <c r="I68" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="19" t="n"/>
-      <c r="B66" s="20" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="19" t="n"/>
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>Medium (Medium) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C66" s="19" t="n"/>
-      <c r="D66" s="19" t="n"/>
-      <c r="E66" s="19" t="n"/>
-      <c r="F66" s="19" t="n"/>
-      <c r="G66" s="19" t="n"/>
-      <c r="H66" s="19" t="n"/>
-      <c r="I66" s="19" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr"/>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Corporate Flight Bookings</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="n">
-        <v>1206</v>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>46262.6837962963</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B68" s="18" t="n"/>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="18" t="n"/>
-      <c r="I68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="21" t="n"/>
-      <c r="B69" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C69" s="21" t="n"/>
-      <c r="D69" s="21" t="n"/>
-      <c r="E69" s="21" t="n"/>
-      <c r="F69" s="21" t="n"/>
-      <c r="G69" s="21" t="n"/>
-      <c r="H69" s="21" t="n"/>
-      <c r="I69" s="21" t="n"/>
+      <c r="C69" s="19" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="19" t="n"/>
+      <c r="H69" s="19" t="n"/>
+      <c r="I69" s="19" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Distribute Elements Into Two Arrays I</t>
+          <t>Corporate Flight Bookings</t>
         </is>
       </c>
       <c r="C70" s="5" t="n">
-        <v>3347</v>
+        <v>1206</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>46.7</v>
+        <v>85</v>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
@@ -5888,7 +5965,7 @@
         </is>
       </c>
       <c r="H70" s="12" t="n">
-        <v>46255.01133101852</v>
+        <v>46262.6837962963</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -5899,7 +5976,7 @@
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B71" s="18" t="n"/>
@@ -5930,11 +6007,11 @@
       <c r="A73" s="5" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Maximum Average Subarray I</t>
+          <t>Distribute Elements Into Two Arrays I</t>
         </is>
       </c>
       <c r="C73" s="5" t="n">
-        <v>643</v>
+        <v>3347</v>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
@@ -5942,10 +6019,10 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
@@ -5953,7 +6030,7 @@
         </is>
       </c>
       <c r="H73" s="12" t="n">
-        <v>46256.65385416667</v>
+        <v>46255.01133101852</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -5964,7 +6041,7 @@
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Sliding Window   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B74" s="18" t="n"/>
@@ -5995,11 +6072,11 @@
       <c r="A76" s="5" t="inlineStr"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Score Validator</t>
+          <t>Maximum Average Subarray I</t>
         </is>
       </c>
       <c r="C76" s="5" t="n">
-        <v>4281</v>
+        <v>643</v>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
@@ -6007,10 +6084,10 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>47.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
@@ -6018,7 +6095,7 @@
         </is>
       </c>
       <c r="H76" s="12" t="n">
-        <v>46247.02123842593</v>
+        <v>46256.65385416667</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -6029,7 +6106,7 @@
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: String, Simulation   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B77" s="18" t="n"/>
@@ -6045,7 +6122,7 @@
       <c r="A78" s="21" t="n"/>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C78" s="21" t="n"/>
@@ -6060,132 +6137,132 @@
       <c r="A79" s="5" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
+          <t>Score Validator</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>4281</v>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>46247.02123842593</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="n"/>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="21" t="n"/>
+      <c r="B81" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="21" t="n"/>
+      <c r="E81" s="21" t="n"/>
+      <c r="F81" s="21" t="n"/>
+      <c r="G81" s="21" t="n"/>
+      <c r="H81" s="21" t="n"/>
+      <c r="I81" s="21" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr"/>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
           <t>Remove Duplicates from Sorted Array</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C82" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D79" s="5" t="inlineStr">
+      <c r="D82" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E79" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="5" t="n">
+      <c r="E82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H79" s="12" t="n">
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="n">
         <v>46259.58225694444</v>
       </c>
-      <c r="I79" s="13" t="inlineStr">
+      <c r="I82" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr"/>
-      <c r="B80" s="6" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr"/>
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Move Zeroes</t>
         </is>
       </c>
-      <c r="C80" s="7" t="n">
+      <c r="C83" s="7" t="n">
         <v>283</v>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D83" s="7" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E80" s="7" t="n">
+      <c r="E83" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F80" s="7" t="n">
+      <c r="F83" s="7" t="n">
         <v>47.8</v>
       </c>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H80" s="14" t="n">
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="n">
         <v>46259.51340277777</v>
       </c>
-      <c r="I80" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B81" s="18" t="n"/>
-      <c r="C81" s="18" t="n"/>
-      <c r="D81" s="18" t="n"/>
-      <c r="E81" s="18" t="n"/>
-      <c r="F81" s="18" t="n"/>
-      <c r="G81" s="18" t="n"/>
-      <c r="H81" s="18" t="n"/>
-      <c r="I81" s="18" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="19" t="n"/>
-      <c r="B82" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C82" s="19" t="n"/>
-      <c r="D82" s="19" t="n"/>
-      <c r="E82" s="19" t="n"/>
-      <c r="F82" s="19" t="n"/>
-      <c r="G82" s="19" t="n"/>
-      <c r="H82" s="19" t="n"/>
-      <c r="I82" s="19" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr"/>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Two Sum II - Input Array Is Sorted</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="n">
-        <v>167</v>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H83" s="12" t="n">
-        <v>46272.93130787037</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
+      <c r="I83" s="15" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -6194,7 +6271,7 @@
     <row r="84">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Binary Search   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B84" s="18" t="n"/>
@@ -6225,201 +6302,201 @@
       <c r="A86" s="5" t="inlineStr"/>
       <c r="B86" s="4" t="inlineStr">
         <is>
+          <t>Two Sum II - Input Array Is Sorted</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>46272.93130787037</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="n"/>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="18" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+      <c r="G87" s="18" t="n"/>
+      <c r="H87" s="18" t="n"/>
+      <c r="I87" s="18" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="19" t="n"/>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C88" s="19" t="n"/>
+      <c r="D88" s="19" t="n"/>
+      <c r="E88" s="19" t="n"/>
+      <c r="F88" s="19" t="n"/>
+      <c r="G88" s="19" t="n"/>
+      <c r="H88" s="19" t="n"/>
+      <c r="I88" s="19" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr"/>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
           <t>Container With Most Water</t>
         </is>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C89" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D89" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="5" t="n">
+      <c r="E89" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F86" s="5" t="n">
+      <c r="F89" s="5" t="n">
         <v>77.2</v>
       </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H86" s="12" t="n">
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="n">
         <v>46259.68393518519</v>
       </c>
-      <c r="I86" s="13" t="inlineStr">
+      <c r="I89" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="16" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: DYNAMIC PROGRAMMING   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n"/>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="2" t="n"/>
-      <c r="G87" s="2" t="n"/>
-      <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="17" t="inlineStr">
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="n"/>
+      <c r="I90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">      Subtopic: Math, Recursion, Memoization   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B88" s="18" t="n"/>
-      <c r="C88" s="18" t="n"/>
-      <c r="D88" s="18" t="n"/>
-      <c r="E88" s="18" t="n"/>
-      <c r="F88" s="18" t="n"/>
-      <c r="G88" s="18" t="n"/>
-      <c r="H88" s="18" t="n"/>
-      <c r="I88" s="18" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="21" t="n"/>
-      <c r="B89" s="22" t="inlineStr">
+      <c r="B91" s="18" t="n"/>
+      <c r="C91" s="18" t="n"/>
+      <c r="D91" s="18" t="n"/>
+      <c r="E91" s="18" t="n"/>
+      <c r="F91" s="18" t="n"/>
+      <c r="G91" s="18" t="n"/>
+      <c r="H91" s="18" t="n"/>
+      <c r="I91" s="18" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="n"/>
+      <c r="B92" s="22" t="inlineStr">
         <is>
           <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
-      <c r="C89" s="21" t="n"/>
-      <c r="D89" s="21" t="n"/>
-      <c r="E89" s="21" t="n"/>
-      <c r="F89" s="21" t="n"/>
-      <c r="G89" s="21" t="n"/>
-      <c r="H89" s="21" t="n"/>
-      <c r="I89" s="21" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr"/>
-      <c r="B90" s="4" t="inlineStr">
+      <c r="C92" s="21" t="n"/>
+      <c r="D92" s="21" t="n"/>
+      <c r="E92" s="21" t="n"/>
+      <c r="F92" s="21" t="n"/>
+      <c r="G92" s="21" t="n"/>
+      <c r="H92" s="21" t="n"/>
+      <c r="I92" s="21" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr"/>
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Fibonacci Number</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C93" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="D90" s="5" t="inlineStr">
+      <c r="D93" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" s="5" t="n">
+      <c r="E93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="5" t="n">
         <v>42.1</v>
       </c>
-      <c r="G90" s="5" t="inlineStr">
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H90" s="12" t="n">
+      <c r="H93" s="12" t="n">
         <v>46247.78516203703</v>
       </c>
-      <c r="I90" s="13" t="inlineStr">
+      <c r="I93" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: MATH   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="2" t="n"/>
-      <c r="G91" s="2" t="n"/>
-      <c r="H91" s="2" t="n"/>
-      <c r="I91" s="2" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B92" s="18" t="n"/>
-      <c r="C92" s="18" t="n"/>
-      <c r="D92" s="18" t="n"/>
-      <c r="E92" s="18" t="n"/>
-      <c r="F92" s="18" t="n"/>
-      <c r="G92" s="18" t="n"/>
-      <c r="H92" s="18" t="n"/>
-      <c r="I92" s="18" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="21" t="n"/>
-      <c r="B93" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C93" s="21" t="n"/>
-      <c r="D93" s="21" t="n"/>
-      <c r="E93" s="21" t="n"/>
-      <c r="F93" s="21" t="n"/>
-      <c r="G93" s="21" t="n"/>
-      <c r="H93" s="21" t="n"/>
-      <c r="I93" s="21" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr"/>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>Prime Number of Set Bits in Binary Representation</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="n">
-        <v>767</v>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>46255.88138888889</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+      <c r="I94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Bit Manipulation, Primality Test   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B95" s="18" t="n"/>
@@ -6450,11 +6527,11 @@
       <c r="A97" s="5" t="inlineStr"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Smallest Divisible Digit Product I</t>
+          <t>Prime Number of Set Bits in Binary Representation</t>
         </is>
       </c>
       <c r="C97" s="5" t="n">
-        <v>3626</v>
+        <v>767</v>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
@@ -6462,10 +6539,10 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
@@ -6473,7 +6550,7 @@
         </is>
       </c>
       <c r="H97" s="12" t="n">
-        <v>46240.74578703703</v>
+        <v>46255.88138888889</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -6484,7 +6561,7 @@
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Enumeration   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B98" s="18" t="n"/>
@@ -6500,7 +6577,7 @@
       <c r="A99" s="21" t="n"/>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C99" s="21" t="n"/>
@@ -6515,11 +6592,11 @@
       <c r="A100" s="5" t="inlineStr"/>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Check Divisibility by Digit Sum and Product</t>
+          <t>Smallest Divisible Digit Product I</t>
         </is>
       </c>
       <c r="C100" s="5" t="n">
-        <v>3918</v>
+        <v>3626</v>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
@@ -6530,7 +6607,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
@@ -6538,7 +6615,7 @@
         </is>
       </c>
       <c r="H100" s="12" t="n">
-        <v>46256.95832175926</v>
+        <v>46240.74578703703</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -6547,174 +6624,174 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="inlineStr"/>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Count Commas in Range</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="n">
-        <v>4245</v>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H101" s="14" t="n">
-        <v>46273.3956712963</v>
-      </c>
-      <c r="I101" s="15" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: General   —   3 solved   (Low: 2 · Medium: 1 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="18" t="n"/>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+      <c r="G101" s="18" t="n"/>
+      <c r="H101" s="18" t="n"/>
+      <c r="I101" s="18" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="19" t="n"/>
-      <c r="B102" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C102" s="19" t="n"/>
-      <c r="D102" s="19" t="n"/>
-      <c r="E102" s="19" t="n"/>
-      <c r="F102" s="19" t="n"/>
-      <c r="G102" s="19" t="n"/>
-      <c r="H102" s="19" t="n"/>
-      <c r="I102" s="19" t="n"/>
+      <c r="A102" s="21" t="n"/>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C102" s="21" t="n"/>
+      <c r="D102" s="21" t="n"/>
+      <c r="E102" s="21" t="n"/>
+      <c r="F102" s="21" t="n"/>
+      <c r="G102" s="21" t="n"/>
+      <c r="H102" s="21" t="n"/>
+      <c r="I102" s="21" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
+          <t>Check Divisibility by Digit Sum and Product</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>3918</v>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>46256.95832175926</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr"/>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Count Commas in Range</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>4245</v>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="7" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H104" s="14" t="n">
+        <v>46273.3956712963</v>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="19" t="n"/>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C105" s="19" t="n"/>
+      <c r="D105" s="19" t="n"/>
+      <c r="E105" s="19" t="n"/>
+      <c r="F105" s="19" t="n"/>
+      <c r="G105" s="19" t="n"/>
+      <c r="H105" s="19" t="n"/>
+      <c r="I105" s="19" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr"/>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
           <t>Reverse Integer</t>
         </is>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C106" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D103" s="5" t="inlineStr">
+      <c r="D106" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E103" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F103" s="5" t="n">
+      <c r="E106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="5" t="n">
         <v>42.4</v>
       </c>
-      <c r="G103" s="5" t="inlineStr">
+      <c r="G106" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H103" s="12" t="n">
+      <c r="H106" s="12" t="n">
         <v>46241.79645833333</v>
       </c>
-      <c r="I103" s="13" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="16" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: STRING   —   5 solved   (Low: 4 · Medium: 1 · High: 0)</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B105" s="18" t="n"/>
-      <c r="C105" s="18" t="n"/>
-      <c r="D105" s="18" t="n"/>
-      <c r="E105" s="18" t="n"/>
-      <c r="F105" s="18" t="n"/>
-      <c r="G105" s="18" t="n"/>
-      <c r="H105" s="18" t="n"/>
-      <c r="I105" s="18" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="21" t="n"/>
-      <c r="B106" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C106" s="21" t="n"/>
-      <c r="D106" s="21" t="n"/>
-      <c r="E106" s="21" t="n"/>
-      <c r="F106" s="21" t="n"/>
-      <c r="G106" s="21" t="n"/>
-      <c r="H106" s="21" t="n"/>
-      <c r="I106" s="21" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr"/>
-      <c r="B107" s="4" t="inlineStr">
-        <is>
-          <t>Length of Last Word</t>
-        </is>
-      </c>
-      <c r="C107" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="G107" s="5" t="inlineStr">
-        <is>
-          <t>md</t>
-        </is>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>46241.78204861111</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: General   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B108" s="18" t="n"/>
@@ -6727,48 +6804,48 @@
       <c r="I108" s="18" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="19" t="n"/>
-      <c r="B109" s="20" t="inlineStr">
-        <is>
-          <t>Medium (Medium) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C109" s="19" t="n"/>
-      <c r="D109" s="19" t="n"/>
-      <c r="E109" s="19" t="n"/>
-      <c r="F109" s="19" t="n"/>
-      <c r="G109" s="19" t="n"/>
-      <c r="H109" s="19" t="n"/>
-      <c r="I109" s="19" t="n"/>
+      <c r="A109" s="21" t="n"/>
+      <c r="B109" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="n"/>
+      <c r="D109" s="21" t="n"/>
+      <c r="E109" s="21" t="n"/>
+      <c r="F109" s="21" t="n"/>
+      <c r="G109" s="21" t="n"/>
+      <c r="H109" s="21" t="n"/>
+      <c r="I109" s="21" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr"/>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Longest Substring Without Repeating Characters</t>
+          <t>Length of Last Word</t>
         </is>
       </c>
       <c r="C110" s="5" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Easy</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>47.9</v>
+        <v>43.2</v>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>md</t>
         </is>
       </c>
       <c r="H110" s="12" t="n">
-        <v>46253.82314814815</v>
+        <v>46241.78204861111</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -6779,7 +6856,7 @@
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sliding Window   —   1 solved   (Low: 0 · Medium: 1 · High: 0)</t>
         </is>
       </c>
       <c r="B111" s="18" t="n"/>
@@ -6792,40 +6869,40 @@
       <c r="I111" s="18" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="21" t="n"/>
-      <c r="B112" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C112" s="21" t="n"/>
-      <c r="D112" s="21" t="n"/>
-      <c r="E112" s="21" t="n"/>
-      <c r="F112" s="21" t="n"/>
-      <c r="G112" s="21" t="n"/>
-      <c r="H112" s="21" t="n"/>
-      <c r="I112" s="21" t="n"/>
+      <c r="A112" s="19" t="n"/>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>Medium (Medium) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="n"/>
+      <c r="D112" s="19" t="n"/>
+      <c r="E112" s="19" t="n"/>
+      <c r="F112" s="19" t="n"/>
+      <c r="G112" s="19" t="n"/>
+      <c r="H112" s="19" t="n"/>
+      <c r="I112" s="19" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr"/>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Valid Anagram</t>
+          <t>Longest Substring Without Repeating Characters</t>
         </is>
       </c>
       <c r="C113" s="5" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>44.6</v>
+        <v>47.9</v>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
@@ -6833,7 +6910,7 @@
         </is>
       </c>
       <c r="H113" s="12" t="n">
-        <v>46243.94849537037</v>
+        <v>46253.82314814815</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -6844,7 +6921,7 @@
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Hash Table, Sorting   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B114" s="18" t="n"/>
@@ -6875,11 +6952,11 @@
       <c r="A116" s="5" t="inlineStr"/>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Valid Palindrome</t>
+          <t>Valid Anagram</t>
         </is>
       </c>
       <c r="C116" s="5" t="n">
-        <v>125</v>
+        <v>242</v>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
@@ -6890,15 +6967,15 @@
         <v>2</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>45.3</v>
+        <v>44.6</v>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>md</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="H116" s="12" t="n">
-        <v>46243.9169675926</v>
+        <v>46243.94849537037</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -6909,7 +6986,7 @@
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Two Pointers   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B117" s="18" t="n"/>
@@ -6940,121 +7017,121 @@
       <c r="A119" s="5" t="inlineStr"/>
       <c r="B119" s="4" t="inlineStr">
         <is>
+          <t>Valid Palindrome</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>md</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>46243.9169675926</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Two Pointers, Greedy   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="n"/>
+      <c r="C120" s="18" t="n"/>
+      <c r="D120" s="18" t="n"/>
+      <c r="E120" s="18" t="n"/>
+      <c r="F120" s="18" t="n"/>
+      <c r="G120" s="18" t="n"/>
+      <c r="H120" s="18" t="n"/>
+      <c r="I120" s="18" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="n"/>
+      <c r="B121" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 1 problem(s)</t>
+        </is>
+      </c>
+      <c r="C121" s="21" t="n"/>
+      <c r="D121" s="21" t="n"/>
+      <c r="E121" s="21" t="n"/>
+      <c r="F121" s="21" t="n"/>
+      <c r="G121" s="21" t="n"/>
+      <c r="H121" s="21" t="n"/>
+      <c r="I121" s="21" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr"/>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
           <t>Valid Palindrome II</t>
         </is>
       </c>
-      <c r="C119" s="5" t="n">
+      <c r="C122" s="5" t="n">
         <v>680</v>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E119" s="5" t="n">
+      <c r="E122" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F119" s="5" t="n">
+      <c r="F122" s="5" t="n">
         <v>47.9</v>
       </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H119" s="12" t="n">
+      <c r="H122" s="12" t="n">
         <v>46245.98399305555</v>
       </c>
-      <c r="I119" s="13" t="inlineStr">
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="16" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  TOPIC: TREE   —   4 solved   (Low: 4 · Medium: 0 · High: 0)</t>
         </is>
       </c>
-      <c r="B120" s="2" t="n"/>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
-        </is>
-      </c>
-      <c r="B121" s="18" t="n"/>
-      <c r="C121" s="18" t="n"/>
-      <c r="D121" s="18" t="n"/>
-      <c r="E121" s="18" t="n"/>
-      <c r="F121" s="18" t="n"/>
-      <c r="G121" s="18" t="n"/>
-      <c r="H121" s="18" t="n"/>
-      <c r="I121" s="18" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="21" t="n"/>
-      <c r="B122" s="22" t="inlineStr">
-        <is>
-          <t>Low (Easy) — 1 problem(s)</t>
-        </is>
-      </c>
-      <c r="C122" s="21" t="n"/>
-      <c r="D122" s="21" t="n"/>
-      <c r="E122" s="21" t="n"/>
-      <c r="F122" s="21" t="n"/>
-      <c r="G122" s="21" t="n"/>
-      <c r="H122" s="21" t="n"/>
-      <c r="I122" s="21" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr"/>
-      <c r="B123" s="4" t="inlineStr">
-        <is>
-          <t>Diameter of Binary Tree</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="n">
-        <v>543</v>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="G123" s="5" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
-      <c r="H123" s="12" t="n">
-        <v>46248.99621527778</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Binary Tree, DP on Trees   —   1 solved   (Low: 1 · Medium: 0 · High: 0)</t>
         </is>
       </c>
       <c r="B124" s="18" t="n"/>
@@ -7070,7 +7147,7 @@
       <c r="A125" s="21" t="n"/>
       <c r="B125" s="22" t="inlineStr">
         <is>
-          <t>Low (Easy) — 2 problem(s)</t>
+          <t>Low (Easy) — 1 problem(s)</t>
         </is>
       </c>
       <c r="C125" s="21" t="n"/>
@@ -7085,228 +7162,296 @@
       <c r="A126" s="5" t="inlineStr"/>
       <c r="B126" s="4" t="inlineStr">
         <is>
+          <t>Diameter of Binary Tree</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>543</v>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>46248.99621527778</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Subtopic: Depth-First Search, Breadth-First Search, Binary Tree   —   2 solved   (Low: 2 · Medium: 0 · High: 0)</t>
+        </is>
+      </c>
+      <c r="B127" s="18" t="n"/>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+      <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="n"/>
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t>Low (Easy) — 2 problem(s)</t>
+        </is>
+      </c>
+      <c r="C128" s="21" t="n"/>
+      <c r="D128" s="21" t="n"/>
+      <c r="E128" s="21" t="n"/>
+      <c r="F128" s="21" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="21" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr"/>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
           <t>Minimum Depth of Binary Tree</t>
         </is>
       </c>
-      <c r="C126" s="5" t="n">
+      <c r="C129" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="E126" s="5" t="n">
+      <c r="E129" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F126" s="5" t="n">
+      <c r="F129" s="5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="G126" s="5" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>md</t>
         </is>
       </c>
-      <c r="H126" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>46246.95925925926</v>
       </c>
-      <c r="I126" s="13" t="inlineStr">
+      <c r="I129" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="7" t="inlin